--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -520,57 +520,57 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
@@ -757,37 +757,37 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>5.137752525252495</v>
+        <v>26730865.8008658</v>
       </c>
       <c r="T2" t="n">
         <v>-0.1189213564213567</v>
       </c>
       <c r="U2" t="n">
+        <v>0.5399331691276772</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6.596242594044668</v>
+      </c>
+      <c r="W2" t="n">
+        <v>13809076.69498694</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.7450757575757576</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.085918603347665</v>
+      </c>
+      <c r="Z2" t="n">
         <v>9.273250360750339</v>
       </c>
-      <c r="V2" t="n">
-        <v>26730865.8008658</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.5399331691276772</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
         <v>10.47252886002885</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>0.5549742282465218</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.7450757575757576</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9.085918603347665</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13809076.69498694</v>
-      </c>
       <c r="AC2" t="n">
-        <v>6.596242594044668</v>
+        <v>5.137752525252495</v>
       </c>
       <c r="AD2" t="n">
         <v>-1.345127149272454</v>
@@ -881,37 +881,37 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.752479338842988</v>
+        <v>-13718440.08264463</v>
       </c>
       <c r="T3" t="n">
         <v>-1.766735537190087</v>
       </c>
       <c r="U3" t="n">
+        <v>-0.2947911750085661</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-6.790306286086903</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-10822359.77262197</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.5239669421487605</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-4.0347488015571</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-6.257851239669421</v>
       </c>
-      <c r="V3" t="n">
-        <v>-13718440.08264463</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.2947911750085661</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
         <v>-3.877479338842974</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
         <v>-3.394648479174151</v>
       </c>
-      <c r="Z3" t="n">
-        <v>-0.5239669421487605</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-4.0347488015571</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-10822359.77262197</v>
-      </c>
       <c r="AC3" t="n">
-        <v>-6.790306286086903</v>
+        <v>-2.752479338842988</v>
       </c>
       <c r="AD3" t="n">
         <v>-2.161241373543746</v>
@@ -1005,37 +1005,37 @@
         <v>-2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.697727272727207</v>
+        <v>-18103636.36363636</v>
       </c>
       <c r="T4" t="n">
         <v>-1.168181818181818</v>
       </c>
       <c r="U4" t="n">
+        <v>-0.8100739617980994</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-6.128442881352356</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-14254208.26930094</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.9477272727272728</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-6.339558641390525</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-6.572727272727278</v>
       </c>
-      <c r="V4" t="n">
-        <v>-18103636.36363636</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.8100739617980994</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>-4.57386363636364</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>-0.02284171368222587</v>
       </c>
-      <c r="Z4" t="n">
-        <v>-0.9477272727272728</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-6.339558641390525</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-14254208.26930094</v>
-      </c>
       <c r="AC4" t="n">
-        <v>-6.128442881352356</v>
+        <v>1.697727272727207</v>
       </c>
       <c r="AD4" t="n">
         <v>0.6009995193184814</v>
@@ -1129,37 +1129,37 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8743801652892955</v>
+        <v>15189251.60697888</v>
       </c>
       <c r="T5" t="n">
         <v>1.855463728191001</v>
       </c>
       <c r="U5" t="n">
+        <v>0.7337142148854234</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8.971793864550278</v>
+      </c>
+      <c r="W5" t="n">
+        <v>14304179.26118215</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.7323232323232323</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.218498831758652</v>
+      </c>
+      <c r="Z5" t="n">
         <v>7.525068870523413</v>
       </c>
-      <c r="V5" t="n">
-        <v>15189251.60697888</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.7337142148854234</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="AA5" t="n">
         <v>5.239210284664836</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>0.3014113012552855</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0.7323232323232323</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>7.218498831758652</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14304179.26118215</v>
-      </c>
       <c r="AC5" t="n">
-        <v>8.971793864550278</v>
+        <v>-0.8743801652892955</v>
       </c>
       <c r="AD5" t="n">
         <v>0.6626653311092667</v>
@@ -1201,7 +1201,7 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" t="n">
         <v>34</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N6" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1296,9 +1296,11 @@
         <v>126</v>
       </c>
       <c r="D7" t="n">
-        <v>88</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14650</v>
+      </c>
       <c r="F7" t="n">
         <v>42</v>
       </c>
@@ -1335,37 +1337,37 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-5.279090909090911</v>
+        <v>-4028488.636363637</v>
       </c>
       <c r="T7" t="n">
         <v>1.117954545454548</v>
       </c>
       <c r="U7" t="n">
+        <v>-0.1314215290096099</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-4.777819365243843</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-2776084.917026446</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.2147727272727273</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-6.471429843360312</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-5.819090909090903</v>
       </c>
-      <c r="V7" t="n">
-        <v>-4028488.636363637</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.1314215290096099</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>-6.969090909090909</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>-5.569708202578141</v>
       </c>
-      <c r="Z7" t="n">
-        <v>-0.2147727272727273</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-6.471429843360312</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-2776084.917026446</v>
-      </c>
       <c r="AC7" t="n">
-        <v>-4.777819365243843</v>
+        <v>-5.279090909090911</v>
       </c>
       <c r="AD7" t="n">
         <v>1.443403829976734</v>
@@ -1407,7 +1409,7 @@
         <v>45522.64583333334</v>
       </c>
       <c r="C8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -1444,7 +1446,7 @@
         <v>54</v>
       </c>
       <c r="N8" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1547,37 +1549,37 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>0.5363636363636886</v>
+        <v>2042386.363636364</v>
       </c>
       <c r="T9" t="n">
         <v>0.4420454545454575</v>
       </c>
       <c r="U9" t="n">
+        <v>-0.1631535326241038</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.031120537886963</v>
+      </c>
+      <c r="W9" t="n">
+        <v>153377.3845989867</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.1522727272727273</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.3112512524114948</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.85227272727272</v>
       </c>
-      <c r="V9" t="n">
-        <v>2042386.363636364</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.1631535326241038</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>1.18295454545455</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>0.887576817189796</v>
       </c>
-      <c r="Z9" t="n">
-        <v>-0.1522727272727273</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.3112512524114948</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>153377.3845989867</v>
-      </c>
       <c r="AC9" t="n">
-        <v>-1.031120537886963</v>
+        <v>0.5363636363636886</v>
       </c>
       <c r="AD9" t="n">
         <v>-1.457437235416108</v>
@@ -1671,37 +1673,37 @@
         <v>-2</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.335196117014306</v>
+        <v>-573281.5164633342</v>
       </c>
       <c r="T10" t="n">
         <v>-0.4609996064541484</v>
       </c>
       <c r="U10" t="n">
+        <v>-0.1231447735400304</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-3.178571065883318</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-634151.1288265241</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.08512396694214885</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.1611064532013131</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-1.218273645546375</v>
       </c>
-      <c r="V10" t="n">
-        <v>-573281.5164633342</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.1231447735400304</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>-1.500721500721482</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>-3.154538892523107</v>
       </c>
-      <c r="Z10" t="n">
-        <v>-0.08512396694214885</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.1611064532013131</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-634151.1288265241</v>
-      </c>
       <c r="AC10" t="n">
-        <v>-3.178571065883318</v>
+        <v>-3.335196117014306</v>
       </c>
       <c r="AD10" t="n">
         <v>-3.308291113073718</v>
@@ -1795,37 +1797,37 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.670454545454561</v>
+        <v>6197727.272727272</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2272727272727302</v>
       </c>
       <c r="U11" t="n">
+        <v>0.1214716872602266</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4948934508227154</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3729395.905956695</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.2272727272727275</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.347507658088276</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.818181818181827</v>
       </c>
-      <c r="V11" t="n">
-        <v>6197727.272727272</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.1214716872602266</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>2.39772727272728</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>1.863865511132303</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0.2272727272727275</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.347507658088276</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>3729395.905956695</v>
-      </c>
       <c r="AC11" t="n">
-        <v>0.4948934508227154</v>
+        <v>-1.670454545454561</v>
       </c>
       <c r="AD11" t="n">
         <v>-2.273305940781857</v>
@@ -1919,37 +1921,37 @@
         <v>-3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.436363636363609</v>
+        <v>-31189602.27272727</v>
       </c>
       <c r="T12" t="n">
         <v>-1.209090909090911</v>
       </c>
       <c r="U12" t="n">
+        <v>-0.480748113971798</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-5.189861179412262</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-12658761.62263304</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.5874999999999997</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-3.799755194782279</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-7.836363636363657</v>
       </c>
-      <c r="V12" t="n">
-        <v>-31189602.27272727</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.480748113971798</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>-6.047727272727272</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>2.07267263860723</v>
       </c>
-      <c r="Z12" t="n">
-        <v>-0.5874999999999997</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-3.799755194782279</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-12658761.62263304</v>
-      </c>
       <c r="AC12" t="n">
-        <v>-5.189861179412262</v>
+        <v>1.436363636363609</v>
       </c>
       <c r="AD12" t="n">
         <v>-0.7889116065393154</v>
@@ -2043,37 +2045,37 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.834217171717171</v>
+        <v>19151470.95959596</v>
       </c>
       <c r="T13" t="n">
         <v>-0.5242424242424235</v>
       </c>
       <c r="U13" t="n">
+        <v>0.3207038962069921</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.203836320162765</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16330589.09981917</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.5503787878787878</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.236519588011447</v>
+      </c>
+      <c r="Z13" t="n">
         <v>4.020707070707076</v>
       </c>
-      <c r="V13" t="n">
-        <v>19151470.95959596</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.3207038962069921</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>4.528914141414148</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>0.1954370250277293</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0.5503787878787878</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>6.236519588011447</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>16330589.09981917</v>
-      </c>
       <c r="AC13" t="n">
-        <v>4.203836320162765</v>
+        <v>-1.834217171717171</v>
       </c>
       <c r="AD13" t="n">
         <v>-0.6596914672659615</v>
@@ -2167,37 +2169,37 @@
         <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3852272727272918</v>
+        <v>-2847727.272727272</v>
       </c>
       <c r="T14" t="n">
         <v>0.005681818181816567</v>
       </c>
       <c r="U14" t="n">
+        <v>-0.1575027649484173</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.441979802604806</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1084997.819838173</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.3193181818181818</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.972126842561607</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-1.019318181818178</v>
       </c>
-      <c r="V14" t="n">
-        <v>-2847727.272727272</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-0.1575027649484173</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>-1.532954545454572</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>-0.09437078621863293</v>
       </c>
-      <c r="Z14" t="n">
-        <v>-0.3193181818181818</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-1.972126842561607</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-1084997.819838173</v>
-      </c>
       <c r="AC14" t="n">
-        <v>-1.441979802604806</v>
+        <v>0.3852272727272918</v>
       </c>
       <c r="AD14" t="n">
         <v>-0.631120334979034</v>
@@ -2291,37 +2293,37 @@
         <v>-1</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.425108225108175</v>
+        <v>-144906.2049062047</v>
       </c>
       <c r="T15" t="n">
         <v>-0.07748917748918061</v>
       </c>
       <c r="U15" t="n">
+        <v>0.1146631146631145</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.470945654874228</v>
+      </c>
+      <c r="W15" t="n">
+        <v>209588.2817579245</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1047619047619048</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.4465687883544973</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-0.9748917748917592</v>
       </c>
-      <c r="V15" t="n">
-        <v>-144906.2049062047</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1146631146631145</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AA15" t="n">
         <v>-0.4891774891774929</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>-2.460494782994829</v>
       </c>
-      <c r="Z15" t="n">
-        <v>-0.1047619047619048</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-0.4465687883544973</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>209588.2817579245</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.470945654874228</v>
+        <v>-1.425108225108175</v>
       </c>
       <c r="AD15" t="n">
         <v>2.645089407946553</v>
@@ -2363,7 +2365,7 @@
         <v>45521.64583333334</v>
       </c>
       <c r="C16" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D16" t="n">
         <v>76</v>
@@ -2400,7 +2402,7 @@
         <v>196</v>
       </c>
       <c r="N16" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2511,37 +2513,37 @@
         <v>-1</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9753246753246572</v>
+        <v>-281123.3766233767</v>
       </c>
       <c r="T17" t="n">
         <v>2.455844155844161</v>
       </c>
       <c r="U17" t="n">
+        <v>0.03588935908811708</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.105598955909514</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-30343.84931263793</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1571428571428573</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.9711973648619505</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.5909090909090935</v>
       </c>
-      <c r="V17" t="n">
-        <v>-281123.3766233767</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.03588935908811708</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>-0.5727272727272776</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>1.659728467989339</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0.1571428571428573</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.9711973648619505</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-30343.84931263793</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.105598955909514</v>
+        <v>-0.9753246753246572</v>
       </c>
       <c r="AD17" t="n">
         <v>0.8013587757997769</v>
@@ -2631,37 +2633,37 @@
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>1.591684704184729</v>
+        <v>1929656.385281385</v>
       </c>
       <c r="T18" t="n">
         <v>0.2825216450216459</v>
       </c>
       <c r="U18" t="n">
+        <v>0.2106879614193855</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.379412618071399</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2130819.998786534</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.3265151515151514</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.561950199905752</v>
+      </c>
+      <c r="Z18" t="n">
         <v>4.575054112554099</v>
       </c>
-      <c r="V18" t="n">
-        <v>1929656.385281385</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.2106879614193855</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
         <v>6.17613636363636</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>0.4400401392921083</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0.3265151515151514</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>6.561950199905752</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2130819.998786534</v>
-      </c>
       <c r="AC18" t="n">
-        <v>5.379412618071399</v>
+        <v>1.591684704184729</v>
       </c>
       <c r="AD18" t="n">
         <v>-0.06794419829028442</v>
@@ -2753,37 +2755,37 @@
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1.200389610389635</v>
+        <v>-9618805.194805196</v>
       </c>
       <c r="T19" t="n">
         <v>-1.565324675324678</v>
       </c>
       <c r="U19" t="n">
+        <v>-0.4653025480544217</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-6.244488243973251</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-9149322.650899824</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.5484415584415583</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-5.676065365058619</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-6.719480519480527</v>
       </c>
-      <c r="V19" t="n">
-        <v>-9618805.194805196</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-0.4653025480544217</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>-4.187532467532463</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>2.665251358752812</v>
       </c>
-      <c r="Z19" t="n">
-        <v>-0.5484415584415583</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-5.676065365058619</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-9149322.650899824</v>
-      </c>
       <c r="AC19" t="n">
-        <v>-6.244488243973251</v>
+        <v>1.200389610389635</v>
       </c>
       <c r="AD19" t="n">
         <v>-0.04407209978649007</v>
@@ -2877,37 +2879,37 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.220454545454572</v>
+        <v>-32638892.04545454</v>
       </c>
       <c r="T20" t="n">
         <v>-1.927272727272729</v>
       </c>
       <c r="U20" t="n">
+        <v>-0.5871377026284312</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-8.970682125786013</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-19940126.21675621</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.181818181818182</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-7.428792979008762</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-9.746590909090912</v>
       </c>
-      <c r="V20" t="n">
-        <v>-32638892.04545454</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-0.5871377026284312</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="AA20" t="n">
         <v>-7.047727272727286</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>2.478937175948062</v>
       </c>
-      <c r="Z20" t="n">
-        <v>-1.181818181818182</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>-7.428792979008762</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-19940126.21675621</v>
-      </c>
       <c r="AC20" t="n">
-        <v>-8.970682125786013</v>
+        <v>1.220454545454572</v>
       </c>
       <c r="AD20" t="n">
         <v>-1.064166324463638</v>
@@ -3001,37 +3003,37 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3840909090909861</v>
+        <v>-1077357.954545455</v>
       </c>
       <c r="T21" t="n">
         <v>-0.7386363636363598</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-4.581173248464282</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-869664.7429776408</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-2.204454930654336</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-3.072727272727263</v>
       </c>
-      <c r="V21" t="n">
-        <v>-1077357.954545455</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="AA21" t="n">
         <v>-3.125</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>0.2055993214473233</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-2.204454930654336</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-869664.7429776408</v>
-      </c>
       <c r="AC21" t="n">
-        <v>-4.581173248464282</v>
+        <v>-0.3840909090909861</v>
       </c>
       <c r="AD21" t="n">
         <v>-2.065331805632592</v>
@@ -3125,37 +3127,37 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>1.931367243867271</v>
+        <v>1462473.845598846</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1650974025974037</v>
       </c>
       <c r="U22" t="n">
+        <v>0.2106879614193855</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.639715133016765</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2022559.271616879</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.2217532467532466</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>4.896107590134577</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.70203823953824</v>
       </c>
-      <c r="V22" t="n">
-        <v>1462473.845598846</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.2106879614193855</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
         <v>4.187247474747466</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>-0.6564889268798311</v>
       </c>
-      <c r="Z22" t="n">
-        <v>0.2217532467532466</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.896107590134577</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2022559.271616879</v>
-      </c>
       <c r="AC22" t="n">
-        <v>5.639715133016765</v>
+        <v>1.931367243867271</v>
       </c>
       <c r="AD22" t="n">
         <v>0.8801902069869776</v>
@@ -3249,37 +3251,37 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.928571428571416</v>
+        <v>2787727.272727272</v>
       </c>
       <c r="T23" t="n">
         <v>-1.710714285714285</v>
       </c>
       <c r="U23" t="n">
+        <v>-0.1146631146631145</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.7487109312962019</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1207378.704094783</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>4.230070082930837</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.52402597402596</v>
       </c>
-      <c r="V23" t="n">
-        <v>2787727.272727272</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-0.1146631146631145</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>4.510389610389609</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>2.686402286563492</v>
       </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.230070082930837</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1207378.704094783</v>
-      </c>
       <c r="AC23" t="n">
-        <v>0.7487109312962019</v>
+        <v>2.928571428571416</v>
       </c>
       <c r="AD23" t="n">
         <v>-3.395083739765152</v>
@@ -3369,37 +3371,37 @@
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>3.912824675324714</v>
+        <v>12203165.58441558</v>
       </c>
       <c r="T24" t="n">
         <v>-0.4803571428571445</v>
       </c>
       <c r="U24" t="n">
+        <v>0.2191846874315915</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.160803484477043</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4143985.203192633</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.2352272727272728</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.821433199941325</v>
+      </c>
+      <c r="Z24" t="n">
         <v>8.069318181818176</v>
       </c>
-      <c r="V24" t="n">
-        <v>12203165.58441558</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.2191846874315915</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
         <v>8.230519480519462</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>2.615569283478578</v>
       </c>
-      <c r="Z24" t="n">
-        <v>0.2352272727272728</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.821433199941325</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>4143985.203192633</v>
-      </c>
       <c r="AC24" t="n">
-        <v>5.160803484477043</v>
+        <v>3.912824675324714</v>
       </c>
       <c r="AD24" t="n">
         <v>1.023828117652613</v>
@@ -3493,37 +3495,37 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.913131313131288</v>
+        <v>-1099803.391053391</v>
       </c>
       <c r="T25" t="n">
         <v>-2.158820346320351</v>
       </c>
       <c r="U25" t="n">
+        <v>-0.08479111532054406</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.33220168284997</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-243800.5675060903</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.1078282828282828</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.403595357616354</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-2.825360750360758</v>
       </c>
-      <c r="V25" t="n">
-        <v>-1099803.391053391</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-0.08479111532054406</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>1.825559163059154</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>0.3672755378237014</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0.1078282828282828</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.403595357616354</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-243800.5675060903</v>
-      </c>
       <c r="AC25" t="n">
-        <v>-1.33220168284997</v>
+        <v>2.913131313131288</v>
       </c>
       <c r="AD25" t="n">
         <v>-1.64982321652575</v>
@@ -3617,37 +3619,37 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>1.537662337662312</v>
+        <v>419285.7142857141</v>
       </c>
       <c r="T26" t="n">
         <v>-1.6025974025974</v>
       </c>
       <c r="U26" t="n">
+        <v>0.1064991771513513</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.05710520960519716</v>
+      </c>
+      <c r="W26" t="n">
+        <v>338386.3462423247</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.06883116883116891</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.1382925448142913</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.7558441558441586</v>
       </c>
-      <c r="V26" t="n">
-        <v>419285.7142857141</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.1064991771513513</v>
-      </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
         <v>0.9961038961038895</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>2.707428597972068</v>
       </c>
-      <c r="Z26" t="n">
-        <v>0.06883116883116891</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.1382925448142913</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>338386.3462423247</v>
-      </c>
       <c r="AC26" t="n">
-        <v>-0.05710520960519716</v>
+        <v>1.537662337662312</v>
       </c>
       <c r="AD26" t="n">
         <v>-0.4041245067332007</v>
@@ -3741,37 +3743,37 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.949380165289284</v>
+        <v>-1349672.004132232</v>
       </c>
       <c r="T27" t="n">
         <v>0.6663223140495873</v>
       </c>
       <c r="U27" t="n">
+        <v>-0.0360203432930708</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-3.484680887436355</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-474531.2390035735</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-1.178873265211024</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-2.617355371900814</v>
       </c>
-      <c r="V27" t="n">
-        <v>-1349672.004132232</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-0.0360203432930708</v>
-      </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
         <v>-3.351446280991738</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>0.2937520635229589</v>
       </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>-1.178873265211024</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-474531.2390035735</v>
-      </c>
       <c r="AC27" t="n">
-        <v>-3.484680887436355</v>
+        <v>-1.949380165289284</v>
       </c>
       <c r="AD27" t="n">
         <v>-2.147897146893587</v>
@@ -3861,37 +3863,37 @@
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>-1.848701298701286</v>
+        <v>34549058.44155844</v>
       </c>
       <c r="T28" t="n">
         <v>-0.2292207792207748</v>
       </c>
       <c r="U28" t="n">
+        <v>0.5265483785220626</v>
+      </c>
+      <c r="V28" t="n">
+        <v>11.61543115866236</v>
+      </c>
+      <c r="W28" t="n">
+        <v>15048306.9673806</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.457919826762918</v>
+      </c>
+      <c r="Z28" t="n">
         <v>13.52792207792209</v>
       </c>
-      <c r="V28" t="n">
-        <v>34549058.44155844</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.5265483785220626</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="AA28" t="n">
         <v>12.0461038961039</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
         <v>-2.702244859864209</v>
       </c>
-      <c r="Z28" t="n">
-        <v>0.7124999999999999</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>9.457919826762918</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>15048306.9673806</v>
-      </c>
       <c r="AC28" t="n">
-        <v>11.61543115866236</v>
+        <v>-1.848701298701286</v>
       </c>
       <c r="AD28" t="n">
         <v>0.4528896527339796</v>
@@ -3981,37 +3983,37 @@
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>2.320000000000022</v>
+        <v>3226954.545454546</v>
       </c>
       <c r="T29" t="n">
         <v>-1.325909090909093</v>
       </c>
       <c r="U29" t="n">
+        <v>0.1336487586487585</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.963576368076374</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1860737.445424945</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.03409090909090917</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4.221840446590448</v>
+      </c>
+      <c r="Z29" t="n">
         <v>4.955454545454543</v>
       </c>
-      <c r="V29" t="n">
-        <v>3226954.545454546</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.1336487586487585</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="AA29" t="n">
         <v>5.725909090909084</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
         <v>2.631591769341782</v>
       </c>
-      <c r="Z29" t="n">
-        <v>0.03409090909090917</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.221840446590448</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1860737.445424945</v>
-      </c>
       <c r="AC29" t="n">
-        <v>3.963576368076374</v>
+        <v>2.320000000000022</v>
       </c>
       <c r="AD29" t="n">
         <v>-0.6765201095201121</v>
@@ -4105,37 +4107,37 @@
         <v>-1</v>
       </c>
       <c r="S30" t="n">
-        <v>4.714304662789488</v>
+        <v>699320.4775022955</v>
       </c>
       <c r="T30" t="n">
         <v>-1.108825630037753</v>
       </c>
       <c r="U30" t="n">
+        <v>0.1231447735400304</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.002679919992175</v>
+      </c>
+      <c r="W30" t="n">
+        <v>865610.5606185647</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.08512396694214885</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>3.53772168981655</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.700204060810123</v>
       </c>
-      <c r="V30" t="n">
-        <v>699320.4775022955</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.1231447735400304</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
         <v>2.847025813692468</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
         <v>6.904574959515656</v>
       </c>
-      <c r="Z30" t="n">
-        <v>0.08512396694214885</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.53772168981655</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>865610.5606185647</v>
-      </c>
       <c r="AC30" t="n">
-        <v>5.002679919992175</v>
+        <v>4.714304662789488</v>
       </c>
       <c r="AD30" t="n">
         <v>2.165032021118975</v>
@@ -4221,37 +4223,37 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>0.1777597402597166</v>
+        <v>6306772.727272728</v>
       </c>
       <c r="T31" t="n">
         <v>-3.34301948051948</v>
       </c>
       <c r="U31" t="n">
+        <v>0.2552621645090587</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.175921114915681</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3135098.336140941</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.1962662337662338</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.155626252916619</v>
+      </c>
+      <c r="Z31" t="n">
         <v>5.619967532467527</v>
       </c>
-      <c r="V31" t="n">
-        <v>6306772.727272728</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.2552621645090587</v>
-      </c>
-      <c r="X31" t="n">
+      <c r="AA31" t="n">
         <v>7.558603896103918</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AB31" t="n">
         <v>-2.887619158216978</v>
       </c>
-      <c r="Z31" t="n">
-        <v>0.1962662337662338</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>8.155626252916619</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>3135098.336140941</v>
-      </c>
       <c r="AC31" t="n">
-        <v>6.175921114915681</v>
+        <v>0.1777597402597166</v>
       </c>
       <c r="AD31" t="n">
         <v>0.3646378043971197</v>
@@ -4345,37 +4347,37 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.08376623376625503</v>
+        <v>4940179.383116883</v>
       </c>
       <c r="T32" t="n">
         <v>-0.1112012987012996</v>
       </c>
       <c r="U32" t="n">
+        <v>0.3309646358543419</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.719531615786423</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2309020.077770517</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.1988636363636365</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5.897947168927047</v>
+      </c>
+      <c r="Z32" t="n">
         <v>7.290584415584419</v>
       </c>
-      <c r="V32" t="n">
-        <v>4940179.383116883</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.3309646358543419</v>
-      </c>
-      <c r="X32" t="n">
+      <c r="AA32" t="n">
         <v>8.510227272727278</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
         <v>2.553664596273279</v>
       </c>
-      <c r="Z32" t="n">
-        <v>0.1988636363636365</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>5.897947168927047</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2309020.077770517</v>
-      </c>
       <c r="AC32" t="n">
-        <v>5.719531615786423</v>
+        <v>0.08376623376625503</v>
       </c>
       <c r="AD32" t="n">
         <v>0.2736907299151525</v>
@@ -4465,37 +4467,37 @@
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>3.372871572871588</v>
+        <v>4094492.243867244</v>
       </c>
       <c r="T33" t="n">
         <v>0.2991883116883116</v>
       </c>
       <c r="U33" t="n">
+        <v>0.1314215290096099</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.231971181681374</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2933482.377502478</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.2147727272727273</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7.897352830426158</v>
+      </c>
+      <c r="Z33" t="n">
         <v>6.603968253968247</v>
       </c>
-      <c r="V33" t="n">
-        <v>4094492.243867244</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.1314215290096099</v>
-      </c>
-      <c r="X33" t="n">
+      <c r="AA33" t="n">
         <v>6.810101010101008</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AB33" t="n">
         <v>1.694985853498622</v>
       </c>
-      <c r="Z33" t="n">
-        <v>0.2147727272727273</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>7.897352830426158</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2933482.377502478</v>
-      </c>
       <c r="AC33" t="n">
-        <v>6.231971181681374</v>
+        <v>3.372871572871588</v>
       </c>
       <c r="AD33" t="n">
         <v>-0.7053242481828654</v>
@@ -4537,7 +4539,7 @@
         <v>45508.65625</v>
       </c>
       <c r="C34" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D34" t="n">
         <v>60</v>
@@ -4571,10 +4573,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N34" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -4633,7 +4635,7 @@
         <v>45508.64583333334</v>
       </c>
       <c r="C35" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D35" t="n">
         <v>34</v>
@@ -4667,10 +4669,10 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N35" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O35" t="n">
         <v>-1</v>
@@ -4729,7 +4731,7 @@
         <v>45507.64583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D36" t="n">
         <v>86</v>
@@ -4763,10 +4765,10 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N36" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -4821,7 +4823,7 @@
         <v>45507.54166666666</v>
       </c>
       <c r="C37" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D37" t="n">
         <v>86</v>
@@ -4855,10 +4857,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N37" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD38"/>
+  <dimension ref="A1:BD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,182 +520,182 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
-        </is>
-      </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -712,29 +712,29 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45527.64583333334</v>
+        <v>45529.5625</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>193</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
       </c>
       <c r="H2" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -746,23 +746,23 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="M2" t="n">
-        <v>91</v>
+        <v>239</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -776,8 +776,12 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -787,51 +791,53 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>69.25010101010102</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+        <v>67.94949494949496</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>72.15454545454546</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-2.817205447414679</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.9651048951049006</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-0.4313131313131322</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3.754419191919197</v>
-      </c>
+        <v>-0.2916783216783219</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>0.8051767676767696</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-0.1895018158240251</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-2.931196967849502</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>-237051.9441508574</v>
+        <v>-1.558063040344678</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0.05839160839160584</v>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>5.092140960890987</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-1.547979797979803</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>-2.253986013986008</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-7686396.441251528</v>
+      </c>
       <c r="AX2" t="n">
-        <v>66515.15151515161</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-0.1441137284615763</v>
-      </c>
+        <v>-5574601.398601398</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>-0.7146300539235284</v>
-      </c>
+      <c r="BA2" t="n">
+        <v>-2.228811188811193</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>-0.4326694320172635</v>
+        <v>-0.5409925563644009</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -840,23 +846,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -878,19 +884,23 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>243</v>
+        <v>63</v>
       </c>
       <c r="M3" t="n">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -910,52 +920,52 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="n">
-        <v>68.29870129870129</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>72.2583164983165</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>6.962481244144342</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-1.206585081585075</v>
+      </c>
       <c r="AM3" t="n">
-        <v>9.109960718294033</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5.26108305274974</v>
-      </c>
+        <v>0.6348484848484848</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>10.54963524130191</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>0.5202832329242575</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.130471246356834</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>13998548.57304884</v>
+        <v>0.1167385776855951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7266273849607183</v>
+        <v>1.384790209790207</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>0.7489669781584212</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.5441757321696299</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-0.3257856341189687</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>4.949417249417237</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>9957761.567015752</v>
+      </c>
       <c r="AX3" t="n">
-        <v>26209072.671156</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.012608876418952</v>
-      </c>
+        <v>9822243.589743592</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>6.525920071255698</v>
-      </c>
+      <c r="BA3" t="n">
+        <v>6.43292540792541</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-1.357039029422705</v>
+        <v>-0.7737368355341303</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -964,23 +974,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45523.5625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1002,22 +1012,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="M4" t="n">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
-        <v>-7</v>
+        <v>21</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1040,48 +1050,48 @@
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>6.65528255319559</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-1.723636363636388</v>
+      </c>
       <c r="AM4" t="n">
-        <v>-6.159610389610393</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-2.706493506493501</v>
-      </c>
+        <v>1.413636363636364</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-3.921558441558432</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>0.8034183256357164</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10.73580513045731</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>-11139252.02872007</v>
+        <v>-0.1614972772799206</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.4863636363636366</v>
+        <v>3.944545454545459</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-3.248647318864727</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-0.3045656396743355</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-1.572857142857146</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>6.882727272727266</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>21456964.51109277</v>
+      </c>
       <c r="AX4" t="n">
-        <v>-13577857.14285714</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-4.167799965734758</v>
-      </c>
+        <v>34633181.81818182</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>-6.951507118485381</v>
-      </c>
+      <c r="BA4" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>-2.238816205533595</v>
+        <v>3.738508599291208</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1090,23 +1100,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C5" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1128,19 +1138,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -1165,51 +1175,51 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>67.27142857142857</v>
+        <v>68</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>2.652878273568803</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.3595041322314216</v>
+      </c>
       <c r="AM5" t="n">
-        <v>7.580681818181816</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1.175000000000011</v>
-      </c>
+        <v>0.1826446280991736</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>5.179545454545462</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>-0.1362484380259315</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.253094596035766</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>14226236.15865828</v>
+        <v>-2.656239420804638</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.7238636363636364</v>
+        <v>-0.6157024793388466</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>0.2272154952217988</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.7342835457829735</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.952272727272728</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>0.1685950413223054</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>665603.2398855281</v>
+      </c>
       <c r="AX5" t="n">
-        <v>15314772.72727273</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>7.244130639002492</v>
-      </c>
+        <v>1170785.123966942</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>8.908835802641292</v>
-      </c>
+      <c r="BA5" t="n">
+        <v>0.3297520661156881</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>0.5073936023930266</v>
+        <v>-0.9744789585710301</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1218,29 +1228,29 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>202</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
       </c>
       <c r="H6" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1252,26 +1262,26 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="M6" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="N6" t="n">
-        <v>-13</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1282,8 +1292,12 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-2</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1292,50 +1306,54 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>70.95432098765433</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>7.001744382569882</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.2447727272727604</v>
+      </c>
       <c r="AM6" t="n">
-        <v>-6.446753246753232</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.732467532467467</v>
-      </c>
+        <v>0.1490909090909092</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>-4.65584415584415</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>0.1671894927659499</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.721666220919303</v>
+      </c>
       <c r="AQ6" t="n">
-        <v>-14448254.88450612</v>
+        <v>1.166737703002326</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.9012987012987013</v>
+        <v>-2.370909090909091</v>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>0.1758656277128807</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-0.7867309847605415</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.9714285714285751</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+        <v>6.274318181818174</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>1493340.43294634</v>
+      </c>
       <c r="AX6" t="n">
-        <v>-17645714.28571429</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-6.294660425325432</v>
-      </c>
+        <v>1122479.545454546</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>-6.185442868570959</v>
-      </c>
+      <c r="BA6" t="n">
+        <v>2.803409090909099</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>0.6341851270422687</v>
+        <v>-1.132070792965429</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -1344,23 +1362,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C7" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F7" t="n">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1382,10 +1400,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>48</v>
+        <v>267</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -1412,48 +1430,36 @@
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>2.291231304926953</v>
+      </c>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
-        <v>-5.733333333333334</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-5.475468975468971</v>
-      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>-6.982395382395367</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>0.1303978630065585</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8.277944953597135</v>
+      </c>
       <c r="AQ7" t="n">
-        <v>-2829199.275302224</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-0.2064935064935065</v>
-      </c>
+        <v>5.551512545425624</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>-5.38282499980474</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-0.1315624927811692</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.149350649350648</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>-3930764.790764791</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-6.799307512758759</v>
-      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>1323139.105459758</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>-4.712575952336437</v>
-      </c>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>1.687464474639579</v>
+        <v>5.859432234432237</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -1462,23 +1468,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C8" t="n">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -1500,15 +1506,23 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="M8" t="n">
-        <v>265</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1518,8 +1532,12 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Y8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1</v>
+      </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
@@ -1528,38 +1546,54 @@
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>70.22027972027972</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>71.35525252525252</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.580513003488264</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.9542312008979081</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.6704514426103572</v>
+      </c>
       <c r="AQ8" t="n">
-        <v>-816356.6827697261</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+        <v>-1.212662816027915</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.6116161616161584</v>
+      </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>0.8396135265700764</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
+        <v>1.187250280583626</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="n">
-        <v>-2.1892646269458</v>
-      </c>
+      <c r="AW8" t="n">
+        <v>92685.09134085965</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>210329.0684624016</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
-        <v>-5.883038110574347</v>
-      </c>
+      <c r="BA8" t="n">
+        <v>0.3175308641975505</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>-2.818035426731075</v>
+        <v>-1.195239684436832</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -1568,23 +1602,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
@@ -1606,23 +1640,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="M9" t="n">
-        <v>151</v>
+        <v>267</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1646,47 +1676,23 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>-1.174343434343442</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-2.587979797979813</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-1.148888888888905</v>
-      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>-614954.2216304897</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-0.08363636363636373</v>
-      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
-        <v>-3.414807053922999</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-0.1271259175607002</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-0.7572727272727278</v>
-      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="n">
-        <v>-524494.9494949493</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-0.1472118075161575</v>
-      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
-        <v>-3.164204797081609</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-3.329381315142179</v>
-      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
@@ -1694,23 +1700,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C10" t="n">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F10" t="n">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
@@ -1732,14 +1738,18 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>253</v>
+        <v>105</v>
       </c>
       <c r="M10" t="n">
-        <v>265</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
@@ -1758,33 +1768,53 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
+      <c r="AK10" t="n">
+        <v>-4.006217479006082</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-1.69084175084177</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.1049382716049383</v>
+      </c>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-3.527149144884021</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.2558478563100834</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.006722783389453</v>
+      </c>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>-4.333692480359161</v>
+      </c>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-1446289.031374394</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-2743978.114478115</v>
+      </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>-2.543052749719422</v>
+      </c>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>0.7338007518792153</v>
+      </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
@@ -1792,23 +1822,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F11" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
@@ -1830,19 +1860,23 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>240</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
       <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -1852,8 +1886,12 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1862,52 +1900,54 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>68.59876543209877</v>
+      </c>
       <c r="AJ11" t="n">
-        <v>67.48333333333333</v>
-      </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
+        <v>68.4549494949495</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-2.564590493376741</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.7020202020202646</v>
+      </c>
       <c r="AM11" t="n">
-        <v>2.675324675324688</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0.5740259740260285</v>
-      </c>
+        <v>0.02020202020202011</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>1.027272727272745</v>
-      </c>
-      <c r="AP11" t="inlineStr"/>
+        <v>0.1237123370456703</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.559575786979153</v>
+      </c>
       <c r="AQ11" t="n">
-        <v>155071.8960277415</v>
+        <v>-0.9355128815092542</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.1480519480519482</v>
+        <v>-0.4055555555555515</v>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>0.8813685792513866</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-0.1626516563323093</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.4142857142857146</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
+        <v>-2.39444444444446</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>-596430.810332984</v>
+      </c>
       <c r="AX11" t="n">
-        <v>1933831.168831169</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-0.31774363165583</v>
-      </c>
+        <v>-1025555.555555556</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>-1.085032667273111</v>
-      </c>
+      <c r="BA11" t="n">
+        <v>-3.031313131313127</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="n">
-        <v>-1.501233687766192</v>
+        <v>1.158789198813356</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -1916,29 +1956,29 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>CjGqFjre</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45528.60416666666</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="G12" t="n">
         <v>77</v>
       </c>
       <c r="H12" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1950,27 +1990,21 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>224</v>
       </c>
       <c r="N12" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -1990,75 +2024,77 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>67.01010101010101</v>
+      </c>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
+      <c r="AK12" t="n">
+        <v>-6.924043655446681</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-1.444141414141427</v>
+      </c>
       <c r="AM12" t="n">
-        <v>-7.725974025974025</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.606493506493479</v>
-      </c>
+        <v>-0.1612121212121211</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>-5.880519480519496</v>
-      </c>
-      <c r="AP12" t="inlineStr"/>
+        <v>-0.2075812569272655</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-4.904440942390195</v>
+      </c>
       <c r="AQ12" t="n">
-        <v>-12584070.82269173</v>
+        <v>0.9966628418519576</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.5831168831168825</v>
+        <v>3.209696969696967</v>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>1.832393068461215</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-0.4707227122640656</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-1.262337662337664</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
+        <v>-6.506464646464664</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>-2157500.636523966</v>
+      </c>
       <c r="AX12" t="n">
-        <v>-30375129.87012987</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-3.728159376047486</v>
-      </c>
+        <v>-2142594.94949495</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="n">
-        <v>-5.053624416682794</v>
-      </c>
+      <c r="BA12" t="n">
+        <v>-3.446868686868669</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="n">
-        <v>-0.6469836349867322</v>
+        <v>0.1388302979955292</v>
       </c>
       <c r="BD12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
         <v>77</v>
@@ -2080,23 +2116,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>223</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>34</v>
+        <v>224</v>
       </c>
       <c r="N13" t="n">
-        <v>-8</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
+        <v>-17</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2116,50 +2148,52 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>73.43674242424242</v>
+      </c>
       <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
+      <c r="AK13" t="n">
+        <v>-8.555568695573498</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.3419191919192031</v>
+      </c>
       <c r="AM13" t="n">
-        <v>1.584415584415581</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-1.870129870129858</v>
-      </c>
+        <v>-0.743838383838384</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>2.246753246753244</v>
-      </c>
-      <c r="AP13" t="inlineStr"/>
+        <v>-0.4287476892404425</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-7.878065401229648</v>
+      </c>
       <c r="AQ13" t="n">
-        <v>3925235.823448154</v>
+        <v>-0.1530747406109754</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.2207792207792212</v>
+        <v>-0.665252525252523</v>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>1.735312546474518</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.1290131684857849</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-0.1688311688311686</v>
-      </c>
-      <c r="AW13" t="inlineStr"/>
+        <v>-8.633333333333326</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="n">
+        <v>-18824955.94225509</v>
+      </c>
       <c r="AX13" t="n">
-        <v>5690909.090909092</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.448956946763374</v>
-      </c>
+        <v>-32115520.20202021</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="n">
-        <v>0.6770524838287884</v>
-      </c>
+      <c r="BA13" t="n">
+        <v>-10.72484848484848</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="n">
-        <v>-2.242883398570157</v>
+        <v>0.6018855109821253</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -2168,23 +2202,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="G14" t="n">
         <v>77</v>
@@ -2206,22 +2240,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>99</v>
+        <v>254</v>
       </c>
       <c r="M14" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>-23</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2243,51 +2277,49 @@
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="n">
-        <v>67.35757575757576</v>
-      </c>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="n">
+        <v>-4.647603690858261</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.65136975818794</v>
+      </c>
       <c r="AM14" t="n">
-        <v>-0.8441558441558357</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0.3376623376623797</v>
-      </c>
+        <v>-0.688544536271809</v>
+      </c>
+      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
-        <v>-1.61298701298702</v>
-      </c>
-      <c r="AP14" t="inlineStr"/>
+        <v>-0.7226153653968179</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-5.645385867424679</v>
+      </c>
       <c r="AQ14" t="n">
-        <v>-1069497.915386891</v>
+        <v>1.09954191581329</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.3077922077922075</v>
+        <v>-1.748974594429139</v>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
-        <v>-0.1463138655685725</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>-0.1901781701160583</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.2428571428571438</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
+        <v>-2.707698194061834</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>-12931898.87869197</v>
+      </c>
       <c r="AX14" t="n">
-        <v>-2894285.714285715</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>-1.955324450107042</v>
-      </c>
+        <v>-13061801.34680135</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="n">
-        <v>-1.572274841560557</v>
-      </c>
+      <c r="BA14" t="n">
+        <v>-4.157790021426379</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
-        <v>-0.7752079367607365</v>
+        <v>-1.110334613348563</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -2296,29 +2328,29 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45527.64583333334</v>
       </c>
       <c r="C15" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="G15" t="n">
         <v>77</v>
       </c>
       <c r="H15" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2330,26 +2362,26 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="M15" t="n">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="N15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P15" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2372,48 +2404,48 @@
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
+      <c r="AK15" t="n">
+        <v>0.1792291262471082</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>3.314233241505974</v>
+      </c>
       <c r="AM15" t="n">
-        <v>3.918470418470434</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-1.92611832611837</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
-        <v>4.348629148629144</v>
-      </c>
-      <c r="AP15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.431862519464616</v>
+      </c>
       <c r="AQ15" t="n">
-        <v>16715402.86942896</v>
+        <v>4.732712034139325</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.5290043290043291</v>
+        <v>-1.708631772268138</v>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
-        <v>0.4902738932647992</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0.3086818385801138</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>-0.4783549783549752</v>
-      </c>
-      <c r="AW15" t="inlineStr"/>
+        <v>0.7447199265380959</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>-195391.3025693221</v>
+      </c>
       <c r="AX15" t="n">
-        <v>18106356.42135642</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>6.257873167096946</v>
-      </c>
+        <v>56919.19191919174</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="n">
-        <v>4.23584763946883</v>
-      </c>
+      <c r="BA15" t="n">
+        <v>-0.5790633608815483</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
-        <v>-0.6590805895416629</v>
+        <v>-0.4125488396019783</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -2422,29 +2454,29 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45523.65625</v>
       </c>
       <c r="C16" t="n">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="G16" t="n">
         <v>77</v>
       </c>
       <c r="H16" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2456,21 +2488,21 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="M16" t="n">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
@@ -2493,26 +2525,52 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>68.15454545454546</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>8.91534620783159</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.950882759216114</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.7411313994647331</v>
+      </c>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
+      <c r="AO16" t="n">
+        <v>0.5431710215183396</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6.535526614950712</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.6247532497825148</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.05622248122247342</v>
+      </c>
       <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>10.44818052318054</v>
+      </c>
       <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>13065393.51073116</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>26936113.7011137</v>
+      </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
+      <c r="BA16" t="n">
+        <v>9.424369766036421</v>
+      </c>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
+      <c r="BC16" t="n">
+        <v>-1.225805823739964</v>
+      </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
@@ -2520,29 +2578,29 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45523.5625</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
         <v>77</v>
       </c>
       <c r="H17" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2554,26 +2612,26 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="M17" t="n">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="N17" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="O17" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2594,52 +2652,50 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="n">
-        <v>80.58311688311689</v>
-      </c>
+      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
+      <c r="AK17" t="n">
+        <v>-4.006907119017484</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-2.540559440559434</v>
+      </c>
       <c r="AM17" t="n">
-        <v>0.5939393939393938</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>-0.925757575757558</v>
-      </c>
+        <v>-0.5398601398601401</v>
+      </c>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="n">
-        <v>-0.6863636363636374</v>
-      </c>
-      <c r="AP17" t="inlineStr"/>
+        <v>-0.3007820680496265</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-6.720152785774857</v>
+      </c>
       <c r="AQ17" t="n">
-        <v>-8767.824198077549</v>
+        <v>-3.919959208634737</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.1500000000000001</v>
+        <v>-1.790209790209794</v>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1.52968321265422</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.02853758560280317</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.507575757575761</v>
-      </c>
-      <c r="AW17" t="inlineStr"/>
+        <v>-3.841258741258741</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="n">
+        <v>-10821912.99744477</v>
+      </c>
       <c r="AX17" t="n">
-        <v>-285265.1515151516</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>-0.7263969256722902</v>
-      </c>
+        <v>-13582692.30769231</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="n">
-        <v>1.089865448561113</v>
-      </c>
+      <c r="BA17" t="n">
+        <v>-6.152447552447555</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="n">
-        <v>0.6215852384330702</v>
+        <v>-2.124285181064444</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -2648,29 +2704,29 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>YH892O2B</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45522.65625</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="G18" t="n">
         <v>77</v>
       </c>
       <c r="H18" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2682,23 +2738,27 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>241</v>
       </c>
       <c r="M18" t="n">
-        <v>31</v>
+        <v>250</v>
       </c>
       <c r="N18" t="n">
+        <v>-13</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-2</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -2716,60 +2776,52 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>73.09090909090909</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>68.40555555555555</v>
-      </c>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="n">
+        <v>-6.053703107237581</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.793636363636324</v>
+      </c>
       <c r="AM18" t="n">
-        <v>4.651346801346804</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.674699374699372</v>
-      </c>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
-        <v>6.014526214526214</v>
-      </c>
-      <c r="AP18" t="inlineStr"/>
+        <v>-0.8262053527570767</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-5.902823074116185</v>
+      </c>
       <c r="AQ18" t="n">
-        <v>2181277.634631736</v>
+        <v>0.2795260199570748</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.3303030303030303</v>
+        <v>-0.9372727272727275</v>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
-        <v>0.1257951846341427</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.1913356921716054</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.614718614718619</v>
-      </c>
-      <c r="AW18" t="inlineStr"/>
+        <v>-4.859999999999999</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>-13687718.22168891</v>
+      </c>
       <c r="AX18" t="n">
-        <v>1915938.552188553</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>6.733875877304669</v>
-      </c>
+        <v>-17727272.72727273</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="n">
-        <v>5.595407893619964</v>
-      </c>
+      <c r="BA18" t="n">
+        <v>-6.484545454545454</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="n">
-        <v>-0.1300433198265978</v>
+        <v>0.5211965110240939</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -2778,29 +2830,29 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>8jyraADG</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45522.65625</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
         <v>77</v>
       </c>
       <c r="H19" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2812,26 +2864,26 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="M19" t="n">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2852,52 +2904,52 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="n">
-        <v>71.23838383838384</v>
-      </c>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="n">
+        <v>67.02000000000001</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>7.357223343262774</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.7963157213157217</v>
+      </c>
       <c r="AM19" t="n">
-        <v>-0.9222222222222172</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>-1.894444444444474</v>
-      </c>
+        <v>0.7381313131313132</v>
+      </c>
+      <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="n">
-        <v>-0.5722222222222229</v>
-      </c>
-      <c r="AP19" t="inlineStr"/>
+        <v>0.7523791514378557</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8.97950453202256</v>
+      </c>
       <c r="AQ19" t="n">
-        <v>176327.3543586042</v>
+        <v>0.4738651437846215</v>
       </c>
       <c r="AR19" t="n">
-        <v>-0.1055555555555554</v>
+        <v>1.876120176120175</v>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
-        <v>-2.482115708365768</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.1209531209531209</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.02777777777777857</v>
-      </c>
-      <c r="AW19" t="inlineStr"/>
+        <v>5.194030044030029</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="n">
+        <v>14583889.23023524</v>
+      </c>
       <c r="AX19" t="n">
-        <v>-149814.8148148146</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>-0.476125124875125</v>
-      </c>
+        <v>15428060.08806009</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="n">
-        <v>2.12700069991736</v>
-      </c>
+      <c r="BA19" t="n">
+        <v>7.51061901061901</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="n">
-        <v>2.437860719527389</v>
+        <v>0.5301586758896164</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
@@ -2906,29 +2958,29 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C20" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="G20" t="n">
         <v>77</v>
       </c>
       <c r="H20" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2940,23 +2992,21 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="M20" t="n">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="N20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
@@ -2978,52 +3028,52 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="n">
-        <v>70.31313131313131</v>
-      </c>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>67.42323232323233</v>
+      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="n">
+        <v>-0.1280161534443494</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.58727272727279</v>
+      </c>
       <c r="AM20" t="n">
-        <v>-6.446464646464648</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.634848484848476</v>
-      </c>
+        <v>-0.1490909090909092</v>
+      </c>
+      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="n">
-        <v>-3.953030303030303</v>
-      </c>
-      <c r="AP20" t="inlineStr"/>
+        <v>-0.1671894927659499</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1.195485655898793</v>
+      </c>
       <c r="AQ20" t="n">
-        <v>-9233159.995276239</v>
+        <v>1.250187716378093</v>
       </c>
       <c r="AR20" t="n">
-        <v>-0.5515151515151513</v>
+        <v>0.3909090909090907</v>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>2.396423695966433</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>-0.4758297999623169</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>-1.42878787878788</v>
-      </c>
-      <c r="AW20" t="inlineStr"/>
+        <v>1.475454545454568</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="n">
+        <v>49983.43124821316</v>
+      </c>
       <c r="AX20" t="n">
-        <v>-9485176.767676769</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>-5.817136360764138</v>
-      </c>
+        <v>2195000</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="inlineStr"/>
-      <c r="BB20" t="n">
-        <v>-6.357474776890484</v>
-      </c>
+      <c r="BA20" t="n">
+        <v>2.987272727272739</v>
+      </c>
+      <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="n">
-        <v>-0.09784493148893958</v>
+        <v>-1.686118138501239</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -3032,29 +3082,29 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C21" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="G21" t="n">
         <v>77</v>
       </c>
       <c r="H21" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3066,27 +3116,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>223</v>
       </c>
       <c r="M21" t="n">
-        <v>189</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-19</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3107,51 +3149,37 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="n">
-        <v>65.63939393939394</v>
-      </c>
-      <c r="AK21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="n">
+        <v>-2.31823826334697</v>
+      </c>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="n">
-        <v>-9.632467532467544</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.277922077922113</v>
-      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="n">
-        <v>-6.859740259740249</v>
-      </c>
-      <c r="AP21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-6.170239533011269</v>
+      </c>
       <c r="AQ21" t="n">
-        <v>-20508971.88747294</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>-1.129870129870129</v>
-      </c>
+        <v>0.5929347826087223</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="n">
-        <v>2.423754288040016</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>-0.6020704179107534</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>-2.085714285714285</v>
-      </c>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="n">
-        <v>-32123668.83116883</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>-7.431974584705657</v>
-      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="n">
+        <v>-817326.8301746562</v>
+      </c>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="n">
-        <v>-8.979537336302045</v>
-      </c>
+      <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="n">
-        <v>-0.9239540602565874</v>
+        <v>-3.009571256038647</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -3160,23 +3188,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45520.64583333334</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C22" t="n">
+        <v>102</v>
+      </c>
+      <c r="D22" t="n">
+        <v>54</v>
+      </c>
+      <c r="E22" t="n">
+        <v>42</v>
+      </c>
+      <c r="F22" t="n">
         <v>87</v>
-      </c>
-      <c r="D22" t="n">
-        <v>51</v>
-      </c>
-      <c r="E22" t="n">
-        <v>94</v>
-      </c>
-      <c r="F22" t="n">
-        <v>153</v>
       </c>
       <c r="G22" t="n">
         <v>77</v>
@@ -3198,23 +3226,15 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="M22" t="n">
-        <v>240</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -3232,60 +3252,52 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>69.83636363636363</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>69.95454545454545</v>
-      </c>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="n">
+        <v>-6.384684417096963</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-5.110399449035839</v>
+      </c>
       <c r="AM22" t="n">
-        <v>-3.041702741702736</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>-0.5888888888889596</v>
-      </c>
+        <v>-0.2272727272727273</v>
+      </c>
+      <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="n">
-        <v>-3.259595959595956</v>
-      </c>
-      <c r="AP22" t="inlineStr"/>
+        <v>-0.1262877158379407</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-4.661759441208474</v>
+      </c>
       <c r="AQ22" t="n">
-        <v>-926190.3871600449</v>
+        <v>-5.453919881759077</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.088016528925614</v>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
-        <v>0.3035735504537058</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>-0.6007215007215017</v>
-      </c>
-      <c r="AW22" t="inlineStr"/>
+        <v>-6.625068870523407</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="n">
+        <v>-2772414.687150819</v>
+      </c>
       <c r="AX22" t="n">
-        <v>-1092741.702741703</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>-2.388123217254488</v>
-      </c>
+        <v>-4028078.512396694</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="n">
-        <v>-4.87466349267175</v>
-      </c>
+      <c r="BA22" t="n">
+        <v>-5.686088154269981</v>
+      </c>
+      <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="n">
-        <v>-2.220045505427219</v>
+        <v>1.42665827851236</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -3294,20 +3306,20 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45516.67708333334</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C23" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="F23" t="n">
         <v>135</v>
@@ -3316,10 +3328,10 @@
         <v>77</v>
       </c>
       <c r="H23" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -3328,14 +3340,14 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="M23" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -3350,8 +3362,12 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-1</v>
+      </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -3368,31 +3384,19 @@
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="n">
-        <v>1884948.519460835</v>
-      </c>
+      <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
       <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="n">
-        <v>3.460255508038728</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0.1651951496779083</v>
-      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="inlineStr"/>
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="n">
-        <v>3.304306284848167</v>
-      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="inlineStr"/>
-      <c r="BB23" t="n">
-        <v>8.51228188888286</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.632094588498532</v>
-      </c>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
@@ -3400,60 +3404,60 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C24" t="n">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="G24" t="n">
         <v>77</v>
       </c>
       <c r="H24" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>67</v>
+      </c>
+      <c r="M24" t="n">
+        <v>151</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>36</v>
-      </c>
-      <c r="M24" t="n">
-        <v>38</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3476,48 +3480,48 @@
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
+      <c r="AK24" t="n">
+        <v>-0.2796706844774519</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>-3.599145299145277</v>
+      </c>
       <c r="AM24" t="n">
-        <v>2.832828282828288</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.037662337662312</v>
-      </c>
+        <v>-0.08671328671328693</v>
+      </c>
+      <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="n">
-        <v>4.044155844155839</v>
-      </c>
-      <c r="AP24" t="inlineStr"/>
+        <v>-0.1303978630065585</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-2.919958248943772</v>
+      </c>
       <c r="AQ24" t="n">
-        <v>2006506.786267138</v>
+        <v>-3.177685384931834</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.2247474747474749</v>
+        <v>-0.7808857808857823</v>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
-        <v>-0.8534887258997799</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0.1913356921716054</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0.07582972582972758</v>
-      </c>
-      <c r="AW24" t="inlineStr"/>
+        <v>-1.544366744366741</v>
+      </c>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="n">
+        <v>-619920.9984638728</v>
+      </c>
       <c r="AX24" t="n">
-        <v>1460475.58922559</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.837059499238293</v>
-      </c>
+        <v>-596305.3613053614</v>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
-      <c r="BB24" t="n">
-        <v>5.344094161056233</v>
-      </c>
+      <c r="BA24" t="n">
+        <v>-1.568065268065254</v>
+      </c>
+      <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="n">
-        <v>0.6677801529968725</v>
+        <v>-2.92950504228282</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -3526,32 +3530,32 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>6RvR2hEi</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45516.5625</v>
+        <v>45522.5625</v>
       </c>
       <c r="C25" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="D25" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="F25" t="n">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
         <v>77</v>
       </c>
       <c r="H25" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -3560,23 +3564,27 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="M25" t="n">
-        <v>265</v>
+        <v>100</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+        <v>-16</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-4</v>
+      </c>
       <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3</v>
+      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -3598,98 +3606,110 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
+      <c r="AK25" t="n">
+        <v>-3.793878229899889</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.971818181818179</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-0.5736363636363637</v>
+      </c>
       <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
+      <c r="AO25" t="n">
+        <v>-0.5118471684261157</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-5.24970640384727</v>
+      </c>
       <c r="AQ25" t="n">
-        <v>691074.7296182076</v>
-      </c>
-      <c r="AR25" t="inlineStr"/>
+        <v>1.910730703478436</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>-1.259090909090911</v>
+      </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
-        <v>1.703784910741433</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0.07389045736871824</v>
-      </c>
+        <v>-6.010909090909095</v>
+      </c>
+      <c r="AU25" t="inlineStr"/>
       <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="n">
-        <v>4.362201276983882</v>
-      </c>
+      <c r="AW25" t="n">
+        <v>-12428700.10498474</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>-30504409.09090909</v>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="inlineStr"/>
-      <c r="BB25" t="n">
-        <v>-2.205070581592324</v>
-      </c>
+      <c r="BA25" t="n">
+        <v>-7.815454545454557</v>
+      </c>
+      <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="n">
-        <v>-5.690916909177776</v>
+        <v>-0.835851507453679</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>4xHh663n</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45522.5625</v>
       </c>
       <c r="C26" t="n">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E26" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G26" t="n">
         <v>77</v>
       </c>
       <c r="H26" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M26" t="n">
+        <v>266</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>194</v>
-      </c>
-      <c r="M26" t="n">
-        <v>73</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2</v>
-      </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3712,48 +3732,48 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
+      <c r="AK26" t="n">
+        <v>3.279644234116674</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-1.303305785123939</v>
+      </c>
       <c r="AM26" t="n">
-        <v>3.490692640692643</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>3.271645021645043</v>
-      </c>
+        <v>0.2140495867768599</v>
+      </c>
+      <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="n">
-        <v>4.374675324675323</v>
-      </c>
-      <c r="AP26" t="inlineStr"/>
+        <v>0.130071290563269</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.3268449268749833</v>
+      </c>
       <c r="AQ26" t="n">
-        <v>1188514.470231861</v>
+        <v>1.444302914581556</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>-0.4537190082644642</v>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
-        <v>2.83923995489215</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>-0.1209531209531209</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>-1.662770562770568</v>
-      </c>
-      <c r="AW26" t="inlineStr"/>
+        <v>2.566115702479351</v>
+      </c>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="n">
+        <v>3760315.510724925</v>
+      </c>
       <c r="AX26" t="n">
-        <v>2731920.995670996</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>4.167060869886953</v>
-      </c>
+        <v>6059318.181818182</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
-      <c r="BB26" t="n">
-        <v>0.6788605784982593</v>
-      </c>
+      <c r="BA26" t="n">
+        <v>1.724793388429745</v>
+      </c>
+      <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="n">
-        <v>-3.395937546082475</v>
+        <v>-2.367817123022178</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -3762,32 +3782,32 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45521.65625</v>
       </c>
       <c r="C27" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>165</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
         <v>77</v>
       </c>
       <c r="H27" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -3796,23 +3816,27 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="M27" t="n">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
       <c r="P27" t="n">
         <v>5</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -3832,50 +3856,52 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
+      <c r="AI27" t="n">
+        <v>67.51060606060607</v>
+      </c>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
+      <c r="AK27" t="n">
+        <v>-2.060821593865057</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.114049586776872</v>
+      </c>
       <c r="AM27" t="n">
-        <v>7.97878787878787</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>3.612121212121281</v>
-      </c>
+        <v>-0.3165289256198347</v>
+      </c>
+      <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="n">
-        <v>8.065367965367969</v>
-      </c>
-      <c r="AP27" t="inlineStr"/>
+        <v>-0.1353895862591517</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-1.635386095386096</v>
+      </c>
       <c r="AQ27" t="n">
-        <v>4308948.512434322</v>
+        <v>0.1535870731522664</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.2259740259740259</v>
+        <v>0.04876033057851359</v>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
-        <v>2.609341588255432</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0.2204215976661796</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>-0.4177489177489235</v>
-      </c>
-      <c r="AW27" t="inlineStr"/>
+        <v>-1.581818181818178</v>
+      </c>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="n">
+        <v>-1355417.911597259</v>
+      </c>
       <c r="AX27" t="n">
-        <v>12092619.04761905</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>2.824733379795305</v>
-      </c>
+        <v>-2739586.776859504</v>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="n">
-        <v>5.229623996479006</v>
-      </c>
+      <c r="BA27" t="n">
+        <v>-0.9380165289256155</v>
+      </c>
+      <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="n">
-        <v>1.047224086256588</v>
+        <v>-0.4431689164297872</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -3884,32 +3910,32 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45521.65625</v>
       </c>
       <c r="C28" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="D28" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="G28" t="n">
         <v>77</v>
       </c>
       <c r="H28" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3918,26 +3944,26 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3960,48 +3986,48 @@
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
+      <c r="AK28" t="n">
+        <v>6.047473147137211</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-1.817373737373714</v>
+      </c>
       <c r="AM28" t="n">
-        <v>-2.73092833092835</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>3.04947089947089</v>
-      </c>
+        <v>0.5603030303030303</v>
+      </c>
+      <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="n">
-        <v>1.999254449254437</v>
-      </c>
-      <c r="AP28" t="inlineStr"/>
+        <v>0.3394183358208125</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>4.231001319944824</v>
+      </c>
       <c r="AQ28" t="n">
-        <v>-354771.688076809</v>
+        <v>-0.243652360568035</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.0962000962000964</v>
+        <v>-0.4493939393939463</v>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
-        <v>0.582364166800204</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>-0.1019257415784218</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>-2.265945165945173</v>
-      </c>
-      <c r="AW28" t="inlineStr"/>
+        <v>4.8531313131313</v>
+      </c>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="n">
+        <v>15394079.72707261</v>
+      </c>
       <c r="AX28" t="n">
-        <v>-1010428.691678692</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>2.443070063141676</v>
-      </c>
+        <v>21702176.76767677</v>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="inlineStr"/>
-      <c r="BB28" t="n">
-        <v>-1.545112193234061</v>
-      </c>
+      <c r="BA28" t="n">
+        <v>4.536565656565656</v>
+      </c>
+      <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="n">
-        <v>-1.799888180167269</v>
+        <v>-0.5295242175838091</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -4010,32 +4036,32 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C29" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="F29" t="n">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="G29" t="n">
         <v>77</v>
       </c>
       <c r="H29" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -4044,26 +4070,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>54</v>
       </c>
       <c r="M29" t="n">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -4085,49 +4111,51 @@
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
+      <c r="AJ29" t="n">
+        <v>80.78818181818183</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>-0.8927444784876712</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>-0.9442424242424465</v>
+      </c>
       <c r="AM29" t="n">
-        <v>-0.4767676767676789</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.585353535353477</v>
-      </c>
+        <v>0.1599999999999999</v>
+      </c>
+      <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="n">
-        <v>1.038888888888891</v>
-      </c>
-      <c r="AP29" t="inlineStr"/>
+        <v>0.02882625506538572</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.5109650575432312</v>
+      </c>
       <c r="AQ29" t="n">
-        <v>212118.5200668897</v>
+        <v>1.52630408928681</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.06363636363636371</v>
+        <v>2.817676767676772</v>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
-        <v>2.705324332135945</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0.1178387835996533</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>-1.379292929292927</v>
-      </c>
-      <c r="AW29" t="inlineStr"/>
+        <v>-0.4752525252525288</v>
+      </c>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="n">
+        <v>-50945.92457868892</v>
+      </c>
       <c r="AX29" t="n">
-        <v>485429.2929292931</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>-0.02803497942386457</v>
-      </c>
+        <v>-270019.1919191917</v>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="n">
-        <v>-0.3094565905556266</v>
-      </c>
+      <c r="BA29" t="n">
+        <v>0.8898989898989953</v>
+      </c>
+      <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="n">
-        <v>-0.4784587169852834</v>
+        <v>0.1672802960851527</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -4136,32 +4164,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C30" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
         <v>77</v>
       </c>
       <c r="H30" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -4170,27 +4198,23 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>162</v>
+        <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-1</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -4200,8 +4224,12 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-2</v>
+      </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -4210,50 +4238,52 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
+      <c r="AI30" t="n">
+        <v>68.59876543209877</v>
+      </c>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
+      <c r="AK30" t="n">
+        <v>6.39161779276796</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.008092031425349</v>
+      </c>
       <c r="AM30" t="n">
-        <v>-2.683116883116881</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>-2.072727272727292</v>
-      </c>
+        <v>0.3212121212121211</v>
+      </c>
+      <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="n">
-        <v>-3.354545454545445</v>
-      </c>
-      <c r="AP30" t="inlineStr"/>
+        <v>0.2364075119926512</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>5.267080425078873</v>
+      </c>
       <c r="AQ30" t="n">
-        <v>-498289.3468611063</v>
+        <v>0.4046196033068838</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>-0.1485858585858537</v>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
-        <v>0.1482647020289107</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>-0.03507692307692345</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0.6740259740259731</v>
-      </c>
-      <c r="AW30" t="inlineStr"/>
+        <v>6.621896745230103</v>
+      </c>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="n">
+        <v>2109283.78822416</v>
+      </c>
       <c r="AX30" t="n">
-        <v>-1386201.298701299</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>-1.375597569347207</v>
-      </c>
+        <v>2025760.381593715</v>
+      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
-      <c r="BB30" t="n">
-        <v>-3.681237848893453</v>
-      </c>
+      <c r="BA30" t="n">
+        <v>4.644399551066215</v>
+      </c>
+      <c r="BB30" t="inlineStr"/>
       <c r="BC30" t="n">
-        <v>-2.281750585460806</v>
+        <v>-0.04906580691410056</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -4262,32 +4292,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>EL1P0u6m</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="F31" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="G31" t="n">
         <v>77</v>
       </c>
       <c r="H31" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -4296,21 +4326,21 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="M31" t="n">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
@@ -4336,47 +4366,23 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="n">
-        <v>13.47705627705628</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>-1.976623376623337</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>11.85454545454546</v>
-      </c>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="n">
-        <v>14953910.78719008</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.6999999999999997</v>
-      </c>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="n">
-        <v>-2.56472595296799</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0.5124838611680715</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>-0.05800865800865296</v>
-      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="n">
-        <v>33745692.64069264</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.695879630258432</v>
-      </c>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="inlineStr"/>
-      <c r="BB31" t="n">
-        <v>11.41315354639826</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0.02926701183532998</v>
-      </c>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
@@ -4384,32 +4390,32 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C32" t="n">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="D32" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="F32" t="n">
-        <v>58</v>
+        <v>178</v>
       </c>
       <c r="G32" t="n">
         <v>77</v>
       </c>
       <c r="H32" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -4418,23 +4424,27 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="M32" t="n">
-        <v>171</v>
+        <v>38</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-1</v>
+      </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>-1</v>
+      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -4455,49 +4465,51 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
+      <c r="AJ32" t="n">
+        <v>71.34686868686867</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-0.0003939578939622379</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>-0.7754208754208776</v>
+      </c>
       <c r="AM32" t="n">
-        <v>5.019047619047626</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2.197546897546914</v>
-      </c>
+        <v>-0.08473625140291818</v>
+      </c>
+      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="n">
-        <v>5.704473304473311</v>
-      </c>
-      <c r="AP32" t="inlineStr"/>
+        <v>0.1237123370456703</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.849104455215567</v>
+      </c>
       <c r="AQ32" t="n">
-        <v>1902769.268650221</v>
+        <v>-2.895334973668355</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.03896103896103909</v>
+        <v>-0.2389450056116686</v>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
-        <v>2.714418641323419</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0.131577417291703</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>-1.23116883116883</v>
-      </c>
-      <c r="AW32" t="inlineStr"/>
+        <v>-0.4277216610550028</v>
+      </c>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="n">
+        <v>277843.2362390696</v>
+      </c>
       <c r="AX32" t="n">
-        <v>3200440.115440115</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>4.485076980632542</v>
-      </c>
+        <v>-175168.3501683499</v>
+      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
-      <c r="BB32" t="n">
-        <v>4.000093962474921</v>
-      </c>
+      <c r="BA32" t="n">
+        <v>-1.175533108866446</v>
+      </c>
+      <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="n">
-        <v>-0.7567356218149897</v>
+        <v>2.68650828595273</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -4506,32 +4518,32 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45514.5625</v>
+        <v>45521.5625</v>
       </c>
       <c r="C33" t="n">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E33" t="n">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="F33" t="n">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="G33" t="n">
         <v>77</v>
       </c>
       <c r="H33" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -4540,21 +4552,23 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="M33" t="n">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
+        <v>-4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-1</v>
+      </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
@@ -4576,27 +4590,53 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
+      <c r="AI33" t="n">
+        <v>70.45454545454545</v>
+      </c>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
+      <c r="AK33" t="n">
+        <v>-5.633068960583032</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.212878787878822</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>-0.5702020202020202</v>
+      </c>
       <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>-0.4583960897606372</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-6.312907035033803</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>2.82915065220584</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>-1.58510101010101</v>
+      </c>
       <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
+      <c r="AT33" t="n">
+        <v>-3.98989898989899</v>
+      </c>
       <c r="AU33" t="inlineStr"/>
       <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
+      <c r="AW33" t="n">
+        <v>-9242613.455347564</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>-9545328.282828284</v>
+      </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
+      <c r="BA33" t="n">
+        <v>-6.529040404040401</v>
+      </c>
       <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr"/>
+      <c r="BC33" t="n">
+        <v>-0.1219726254633287</v>
+      </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
@@ -4604,32 +4644,32 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45514.54166666666</v>
+        <v>45521.5625</v>
       </c>
       <c r="C34" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E34" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F34" t="n">
-        <v>193</v>
+        <v>63</v>
       </c>
       <c r="G34" t="n">
         <v>77</v>
       </c>
       <c r="H34" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -4638,26 +4678,26 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>38</v>
+        <v>223</v>
       </c>
       <c r="M34" t="n">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="N34" t="n">
-        <v>-8</v>
+        <v>-19</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="P34" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4678,50 +4718,52 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
+      <c r="AI34" t="n">
+        <v>63.375</v>
+      </c>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
+      <c r="AK34" t="n">
+        <v>-7.397116684111566</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.223636363636416</v>
+      </c>
       <c r="AM34" t="n">
-        <v>1.712727272727278</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>4.721186868686857</v>
-      </c>
+        <v>-1.234297520661157</v>
+      </c>
+      <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="n">
-        <v>2.651035353535363</v>
-      </c>
-      <c r="AP34" t="inlineStr"/>
+        <v>-0.4773903306128366</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>-8.692263711944022</v>
+      </c>
       <c r="AQ34" t="n">
-        <v>842174.1760051541</v>
+        <v>2.42218493744582</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.08363636363636373</v>
+        <v>-1.90487603305785</v>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>7.104986857345551</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0.1271259175607002</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>-0.8361616161616148</v>
-      </c>
-      <c r="AW34" t="inlineStr"/>
+        <v>-7.187685950413211</v>
+      </c>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="n">
+        <v>-20456591.8585535</v>
+      </c>
       <c r="AX34" t="n">
-        <v>665252.5252525252</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>3.541578551882893</v>
-      </c>
+        <v>-33939380.16528925</v>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
-      <c r="BB34" t="n">
-        <v>5.077983071276549</v>
-      </c>
+      <c r="BA34" t="n">
+        <v>-9.794462809917363</v>
+      </c>
+      <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="n">
-        <v>2.274174340152598</v>
+        <v>-0.5637997948816391</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -4730,32 +4772,32 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45520.64583333334</v>
       </c>
       <c r="C35" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="F35" t="n">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="G35" t="n">
         <v>77</v>
       </c>
       <c r="H35" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -4764,19 +4806,27 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="M35" t="n">
         <v>240</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -4786,8 +4836,12 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4796,50 +4850,54 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
+      <c r="AI35" t="n">
+        <v>69.98601398601399</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>69.889898989899</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-2.283436038747027</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>-0.06848484848492831</v>
+      </c>
       <c r="AM35" t="n">
-        <v>5.520779220779218</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0.03614718614716139</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="n">
-        <v>7.714935064935077</v>
-      </c>
-      <c r="AP35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-4.268141187647913</v>
+      </c>
       <c r="AQ35" t="n">
-        <v>3124087.955958427</v>
+        <v>-0.02491778261256172</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.1967532467532465</v>
+        <v>-0.8424242424242401</v>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>-2.722161909480718</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0.2932180018049582</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>-3.460389610389608</v>
-      </c>
-      <c r="AW35" t="inlineStr"/>
+        <v>-3.158484848484846</v>
+      </c>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="n">
+        <v>-817667.002276741</v>
+      </c>
       <c r="AX35" t="n">
-        <v>6327061.688311689</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>8.150466398872197</v>
-      </c>
+        <v>-1147527.272727273</v>
+      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr"/>
-      <c r="BA35" t="inlineStr"/>
-      <c r="BB35" t="n">
-        <v>6.320338429686245</v>
-      </c>
+      <c r="BA35" t="n">
+        <v>-3.434545454545443</v>
+      </c>
+      <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="n">
-        <v>0.5418003132133578</v>
+        <v>-1.673615830566604</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -4848,23 +4906,23 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45516.67708333334</v>
       </c>
       <c r="C36" t="n">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E36" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F36" t="n">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="G36" t="n">
         <v>77</v>
@@ -4886,23 +4944,15 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="M36" t="n">
-        <v>196</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -4924,48 +4974,36 @@
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
+      <c r="AK36" t="n">
+        <v>3.53269609700645</v>
+      </c>
       <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="n">
-        <v>7.30346320346321</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0.4352813852813995</v>
-      </c>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="n">
-        <v>8.716666666666669</v>
-      </c>
-      <c r="AP36" t="inlineStr"/>
+        <v>0.1367241379310347</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>8.537350637867881</v>
+      </c>
       <c r="AQ36" t="n">
-        <v>2331684.463882171</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0.2142857142857142</v>
-      </c>
+        <v>3.347430845017044</v>
+      </c>
+      <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="n">
-        <v>2.295216405402726</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0.335388155262105</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>-0.2534632034632018</v>
-      </c>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="n">
-        <v>5026668.831168831</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>5.859522730187095</v>
-      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="n">
+        <v>1939007.06707086</v>
+      </c>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="n">
-        <v>5.715853236624767</v>
-      </c>
+      <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="n">
-        <v>0.3590758428975391</v>
+        <v>4.417824302134647</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
@@ -4974,23 +5012,23 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45516.65625</v>
       </c>
       <c r="C37" t="n">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="G37" t="n">
         <v>77</v>
@@ -5012,15 +5050,23 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="M37" t="n">
-        <v>265</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -5042,36 +5088,48 @@
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
+      <c r="AK37" t="n">
+        <v>5.091865286015448</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.820437710437716</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.2162738496071828</v>
+      </c>
       <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
+      <c r="AO37" t="n">
+        <v>0.2364075119926512</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>6.078070922236037</v>
+      </c>
       <c r="AQ37" t="n">
-        <v>1939279.189453559</v>
-      </c>
-      <c r="AR37" t="inlineStr"/>
+        <v>-0.3674574554368633</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>-0.2127833894500526</v>
+      </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>0.2504650749189068</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0.08389088968920899</v>
-      </c>
+        <v>4.242884399551087</v>
+      </c>
+      <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr"/>
-      <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="n">
-        <v>5.609189898181498</v>
-      </c>
+      <c r="AW37" t="n">
+        <v>2073205.741178613</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1518291.245791246</v>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="inlineStr"/>
-      <c r="BB37" t="n">
-        <v>3.419794806811609</v>
-      </c>
+      <c r="BA37" t="n">
+        <v>2.748103254769902</v>
+      </c>
+      <c r="BB37" t="inlineStr"/>
       <c r="BC37" t="n">
-        <v>-2.209026054866392</v>
+        <v>1.000277134095501</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
@@ -5080,23 +5138,23 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45516.5625</v>
       </c>
       <c r="C38" t="n">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E38" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="G38" t="n">
         <v>77</v>
@@ -5118,17 +5176,17 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="M38" t="n">
-        <v>31</v>
+        <v>267</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
@@ -5152,50 +5210,908 @@
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
+      <c r="AK38" t="n">
+        <v>4.621695348130132</v>
+      </c>
       <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="n">
-        <v>6.503872053872058</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>3.460990860990876</v>
-      </c>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="n">
-        <v>6.778018278018266</v>
-      </c>
-      <c r="AP38" t="inlineStr"/>
+        <v>0.08224931590149009</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-1.950083307996351</v>
+      </c>
       <c r="AQ38" t="n">
-        <v>2980193.501754784</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.2064935064935065</v>
-      </c>
+        <v>1.097234417756198</v>
+      </c>
+      <c r="AR38" t="inlineStr"/>
       <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="n">
-        <v>1.348599842246188</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0.1315624927811692</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0.4142857142857181</v>
-      </c>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="n">
-        <v>3979582.130832131</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>7.977680508076205</v>
-      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="n">
+        <v>807385.1778656123</v>
+      </c>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="n">
-        <v>6.344963595557402</v>
-      </c>
+      <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="n">
-        <v>-0.7414208063736858</v>
+        <v>-5.636925509273333</v>
       </c>
       <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C39" t="n">
+        <v>41</v>
+      </c>
+      <c r="D39" t="n">
+        <v>21</v>
+      </c>
+      <c r="E39" t="n">
+        <v>111</v>
+      </c>
+      <c r="F39" t="n">
+        <v>180</v>
+      </c>
+      <c r="G39" t="n">
+        <v>77</v>
+      </c>
+      <c r="H39" t="n">
+        <v>773</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>194</v>
+      </c>
+      <c r="M39" t="n">
+        <v>73</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="n">
+        <v>4.006611436900045</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.466262626262647</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>-0.02020202020202011</v>
+      </c>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="n">
+        <v>-0.1237123370456703</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.6780446896684538</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>3.151182829978438</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>-1.767777777777784</v>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>4.761414141414164</v>
+      </c>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="n">
+        <v>1168445.795135325</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2919146.464646465</v>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="n">
+        <v>3.718585858585868</v>
+      </c>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="n">
+        <v>-3.420309037831945</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C40" t="n">
+        <v>48</v>
+      </c>
+      <c r="D40" t="n">
+        <v>56</v>
+      </c>
+      <c r="E40" t="n">
+        <v>51</v>
+      </c>
+      <c r="F40" t="n">
+        <v>165</v>
+      </c>
+      <c r="G40" t="n">
+        <v>77</v>
+      </c>
+      <c r="H40" t="n">
+        <v>773</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>63</v>
+      </c>
+      <c r="M40" t="n">
+        <v>80</v>
+      </c>
+      <c r="N40" t="n">
+        <v>8</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="n">
+        <v>3.199836399283441</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>4.169393939393927</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.2481818181818183</v>
+      </c>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="n">
+        <v>0.1935295681270914</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>5.080885805275642</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>2.885303425552451</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>-0.2954545454545432</v>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>8.096363636363634</v>
+      </c>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="n">
+        <v>4284683.627062971</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>12069202.02020202</v>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="n">
+        <v>8.128686868686856</v>
+      </c>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="n">
+        <v>0.6164399232772944</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C41" t="n">
+        <v>24</v>
+      </c>
+      <c r="D41" t="n">
+        <v>48</v>
+      </c>
+      <c r="E41" t="n">
+        <v>103</v>
+      </c>
+      <c r="F41" t="n">
+        <v>187</v>
+      </c>
+      <c r="G41" t="n">
+        <v>77</v>
+      </c>
+      <c r="H41" t="n">
+        <v>773</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>228</v>
+      </c>
+      <c r="M41" t="n">
+        <v>80</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="n">
+        <v>2.300602888976684</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.761593714927017</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.1034118967452302</v>
+      </c>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="n">
+        <v>-0.05241219736714098</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>-0.8758213404994137</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.05298544926216664</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>-2.014915824915832</v>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>1.657003367003355</v>
+      </c>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="n">
+        <v>-61511.01013553748</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>-1073521.885521885</v>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="n">
+        <v>-2.799775533108871</v>
+      </c>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="n">
+        <v>-1.181015818909245</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C42" t="n">
+        <v>87</v>
+      </c>
+      <c r="D42" t="n">
+        <v>36</v>
+      </c>
+      <c r="E42" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" t="n">
+        <v>153</v>
+      </c>
+      <c r="G42" t="n">
+        <v>77</v>
+      </c>
+      <c r="H42" t="n">
+        <v>773</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>54</v>
+      </c>
+      <c r="M42" t="n">
+        <v>240</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="n">
+        <v>0.1898324490413899</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.724242424242391</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.06464646464646462</v>
+      </c>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="n">
+        <v>0.1042002147074614</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-0.04566370067576031</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>2.268213231347289</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>-1.538888888888888</v>
+      </c>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="n">
+        <v>1.308585858585857</v>
+      </c>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="n">
+        <v>358043.4696588081</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>525429.2929292931</v>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="n">
+        <v>-0.564646464646458</v>
+      </c>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="n">
+        <v>-0.4150312426882472</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C43" t="n">
+        <v>120</v>
+      </c>
+      <c r="D43" t="n">
+        <v>51</v>
+      </c>
+      <c r="E43" t="n">
+        <v>94</v>
+      </c>
+      <c r="F43" t="n">
+        <v>74</v>
+      </c>
+      <c r="G43" t="n">
+        <v>77</v>
+      </c>
+      <c r="H43" t="n">
+        <v>773</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>162</v>
+      </c>
+      <c r="M43" t="n">
+        <v>151</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="n">
+        <v>-1.143856204227106</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>-1.786433566433573</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="n">
+        <v>-0.04231307154384112</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>-3.404913275649122</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.6527582159315841</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.4961538461538453</v>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>-3.507552447552456</v>
+      </c>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="n">
+        <v>-460562.3602673612</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>-1396041.258741259</v>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="n">
+        <v>-2.966013986013976</v>
+      </c>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="n">
+        <v>-2.154294048875816</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C44" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" t="n">
+        <v>33</v>
+      </c>
+      <c r="E44" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" t="n">
+        <v>69</v>
+      </c>
+      <c r="G44" t="n">
+        <v>77</v>
+      </c>
+      <c r="H44" t="n">
+        <v>773</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>102</v>
+      </c>
+      <c r="M44" t="n">
+        <v>147</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="n">
+        <v>9.402396369927715</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>-2.341515151515154</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0.7100000000000002</v>
+      </c>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="n">
+        <v>0.552191083770031</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>11.22808068925053</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>-2.557786796428189</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.02676767676768321</v>
+      </c>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="n">
+        <v>12.05838383838385</v>
+      </c>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="n">
+        <v>14824499.85413968</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>33933626.26262626</v>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="n">
+        <v>13.77808080808082</v>
+      </c>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="n">
+        <v>0.1158684224585151</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C45" t="n">
+        <v>142</v>
+      </c>
+      <c r="D45" t="n">
+        <v>23</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>58</v>
+      </c>
+      <c r="G45" t="n">
+        <v>77</v>
+      </c>
+      <c r="H45" t="n">
+        <v>773</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>99</v>
+      </c>
+      <c r="M45" t="n">
+        <v>171</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="n">
+        <v>3.712450296616964</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2.331060606060674</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0.04545454545454541</v>
+      </c>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="n">
+        <v>0.1366392866392867</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>3.91470908720909</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>3.014277065527068</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>-1.422727272727268</v>
+      </c>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="n">
+        <v>5.787878787878782</v>
+      </c>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="n">
+        <v>1730888.176638176</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>3289318.181818182</v>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="n">
+        <v>4.971212121212105</v>
+      </c>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="n">
+        <v>-0.2966278782945508</v>
+      </c>
+      <c r="BD45" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD45"/>
+  <dimension ref="A1:BD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,23 +712,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -750,94 +750,110 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63</v>
+        <v>227</v>
       </c>
       <c r="M2" t="n">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="N2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>6</v>
+      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.166666666666667</v>
+      </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>67.94949494949496</v>
+        <v>77.52996632996633</v>
       </c>
       <c r="AJ2" t="n">
-        <v>72.15454545454546</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-2.817205447414679</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-0.9651048951049006</v>
-      </c>
+        <v>74.28377525252525</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>-0.2916783216783219</v>
+        <v>5.219065656565675</v>
       </c>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>-0.1895018158240251</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>-2.931196967849502</v>
+        <v>-0.5902542300462414</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.558063040344678</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.05839160839160584</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>-0.1793192257556488</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>1704229.511019283</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-2.253986013986008</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>0.002433425160697889</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2.318584309937563</v>
+      </c>
       <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>-7686396.441251528</v>
-      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-5574601.398601398</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+        <v>547150.6776843681</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-1.076552695395527</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.7745179063360901</v>
+      </c>
       <c r="BA2" t="n">
-        <v>-2.228811188811193</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>2.286202938475654</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.603064738292019</v>
+      </c>
       <c r="BC2" t="n">
-        <v>-0.5409925563644009</v>
+        <v>0.9785420237648452</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -846,23 +862,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -884,22 +900,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="M3" t="n">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -914,58 +930,64 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>71.03611111111113</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>72.2583164983165</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>6.962481244144342</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-1.206585081585075</v>
-      </c>
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>0.6348484848484848</v>
+        <v>4.142563131313096</v>
       </c>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
-        <v>0.5202832329242575</v>
-      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>7.130471246356834</v>
+        <v>1.135362621113643</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.1167385776855951</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.384790209790207</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>-0.1987713846192498</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>8831279.461279459</v>
+      </c>
       <c r="AT3" t="n">
-        <v>4.949417249417237</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>-0.3001641414141414</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.9109013195181745</v>
+      </c>
       <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="n">
-        <v>9957761.567015752</v>
-      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>9822243.589743592</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+        <v>-1928833.502517153</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-0.5261744577882226</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.307453703703704</v>
+      </c>
       <c r="BA3" t="n">
-        <v>6.43292540792541</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+        <v>1.778901515151517</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.171123737373748</v>
+      </c>
       <c r="BC3" t="n">
-        <v>-0.7737368355341303</v>
+        <v>-0.1144362609233838</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -974,29 +996,29 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>GUXb5YQq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
       </c>
       <c r="H4" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1008,26 +1030,26 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>124</v>
+        <v>190</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="N4" t="n">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1049,49 +1071,51 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="n">
-        <v>6.65528255319559</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-1.723636363636388</v>
-      </c>
+      <c r="AJ4" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>1.413636363636364</v>
+        <v>0.1604895104895832</v>
       </c>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>0.8034183256357164</v>
-      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>10.73580513045731</v>
+        <v>0.6062646367010984</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.1614972772799206</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.944545454545459</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>0.003205128205128194</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>1234949.300699301</v>
+      </c>
       <c r="AT4" t="n">
-        <v>6.882727272727266</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.8442656045180996</v>
+      </c>
       <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="n">
-        <v>21456964.51109277</v>
-      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>34633181.81818182</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+        <v>629586.6067515106</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.640996876033661</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.170069930069932</v>
+      </c>
       <c r="BA4" t="n">
-        <v>10.73</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+        <v>2.851538461538453</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.230629370629359</v>
+      </c>
       <c r="BC4" t="n">
-        <v>3.738508599291208</v>
+        <v>2.294813853123202</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1100,29 +1124,29 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>WIX2NXnS</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
       </c>
       <c r="H5" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1134,27 +1158,23 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="M5" t="n">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="N5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1168,58 +1188,54 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>68</v>
+        <v>70.11099632690542</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>2.652878273568803</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-0.3595041322314216</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.1826446280991736</v>
-      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>-0.1362484380259315</v>
-      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>1.253094596035766</v>
+        <v>1.846021241830073</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2.656239420804638</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.6157024793388466</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>0.1685950413223054</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>-2.188481559290395</v>
+      </c>
       <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="n">
-        <v>665603.2398855281</v>
-      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>1170785.123966942</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+        <v>-1183002.585200747</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.003681139122313937</v>
+      </c>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="n">
-        <v>0.3297520661156881</v>
-      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>-0.9744789585710301</v>
+        <v>-3.775271942110166</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1228,23 +1244,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>jqIIP2Cb</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1266,23 +1282,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="M6" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1292,68 +1304,58 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-2</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="n">
-        <v>70.95432098765433</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>7.001744382569882</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.2447727272727604</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.1490909090909092</v>
-      </c>
+        <v>67.87</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>0.1671894927659499</v>
-      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>4.721666220919303</v>
+        <v>-1.60574633828503</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.166737703002326</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-2.370909090909091</v>
-      </c>
+        <v>-0.1921886472660466</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>6.274318181818174</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>-5.445755991514517</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="n">
-        <v>1493340.43294634</v>
-      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>1122479.545454546</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+        <v>-1172488.039308473</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.376822901900301</v>
+      </c>
       <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="n">
-        <v>2.803409090909099</v>
-      </c>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>-1.132070792965429</v>
+        <v>0.6453635734750236</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -1362,23 +1364,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>fHO9ROsn</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C7" t="n">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1400,67 +1402,89 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>267</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>268</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>68.36101010101011</v>
+      </c>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="n">
-        <v>2.291231304926953</v>
-      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>0.1303978630065585</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.277944953597135</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.551512545425624</v>
-      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="n">
-        <v>1323139.105459758</v>
-      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
-        <v>5.859432234432237</v>
-      </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1468,23 +1492,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>v5l07LdU</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C8" t="n">
         <v>102</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -1506,94 +1530,96 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="M8" t="n">
-        <v>31</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="n">
+        <v>197</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-7</v>
+      </c>
       <c r="Y8" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>70.22027972027972</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>71.35525252525252</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.580513003488264</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-0.9542312008979081</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>-0.6704514426103572</v>
+        <v>-0.5615689011843017</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.212662816027915</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-0.6116161616161584</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="n">
-        <v>1.187250280583626</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>0.05149080264465056</v>
+      </c>
       <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>92685.09134085965</v>
-      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>210329.0684624016</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+        <v>343397.7694314234</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2.98596197961583</v>
+      </c>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>0.3175308641975505</v>
-      </c>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>-1.195239684436832</v>
+        <v>3.5957191739884</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -1602,29 +1628,29 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.5625</v>
       </c>
       <c r="C9" t="n">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F9" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
       </c>
       <c r="H9" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1636,23 +1662,27 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="M9" t="n">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
       <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1672,27 +1702,53 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>73.36931818181819</v>
+      </c>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>0.03514692378331574</v>
+      </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>2.06309416074123</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.3518154938743174</v>
+      </c>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>1205456.841138659</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.06717171717171722</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-1.30920201802553</v>
+      </c>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>109509.2342298217</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2.307398418574884</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.137167125803487</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.01675849403120822</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.7697199265381016</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0.2322978546507812</v>
+      </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
@@ -1700,29 +1756,29 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.5625</v>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" t="n">
+        <v>56</v>
+      </c>
+      <c r="F10" t="n">
         <v>15</v>
-      </c>
-      <c r="E10" t="n">
-        <v>123</v>
-      </c>
-      <c r="F10" t="n">
-        <v>166</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
       </c>
       <c r="H10" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1734,23 +1790,27 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="M10" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -1764,56 +1824,68 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="n">
-        <v>-4.006217479006082</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-1.69084175084177</v>
-      </c>
+      <c r="AI10" t="n">
+        <v>69.93658008658008</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70.81818181818181</v>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
-        <v>0.1049382716049383</v>
+        <v>-0.0220597584234099</v>
       </c>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>-3.527149144884021</v>
+        <v>-0.4032480669210941</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.2558478563100834</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.006722783389453</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+        <v>0.2676963131699428</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>5726916.719643994</v>
+      </c>
       <c r="AT10" t="n">
-        <v>-4.333692480359161</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
+        <v>0.2407501589319769</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.620894635628929</v>
+      </c>
       <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="n">
-        <v>-1446289.031374394</v>
-      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>-2743978.114478115</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+        <v>7194801.438642818</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.7223782477123599</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.6810553083280304</v>
+      </c>
       <c r="BA10" t="n">
-        <v>-2.543052749719422</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
+        <v>3.160521296884937</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.17889383343929</v>
+      </c>
       <c r="BC10" t="n">
-        <v>0.7338007518792153</v>
+        <v>2.970661242011261</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -1822,29 +1894,29 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45535.65625</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
       </c>
       <c r="H11" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1856,26 +1928,26 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1886,68 +1958,68 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1</v>
+      </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>68.59876543209877</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>68.4549494949495</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-2.564590493376741</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-0.7020202020202646</v>
-      </c>
+        <v>69.75646464646465</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
-        <v>0.02020202020202011</v>
+        <v>-0.4791750841751536</v>
       </c>
       <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
-        <v>0.1237123370456703</v>
-      </c>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
-        <v>-1.559575786979153</v>
+        <v>-2.187700848075536</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.9355128815092542</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-0.4055555555555515</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+        <v>0.2388434164149267</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-16150436.02693603</v>
+      </c>
       <c r="AT11" t="n">
-        <v>-2.39444444444446</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
+        <v>-0.05974747474747488</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-2.744433455856779</v>
+      </c>
       <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="n">
-        <v>-596430.810332984</v>
-      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>-1025555.555555556</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+        <v>-6612572.174946629</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.140680739148127</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.355117845117846</v>
+      </c>
       <c r="BA11" t="n">
-        <v>-3.031313131313127</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
+        <v>-2.970235690235697</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-4.206700336700337</v>
+      </c>
       <c r="BC11" t="n">
-        <v>1.158789198813356</v>
+        <v>-0.006336433187115631</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -1956,29 +2028,29 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.60416666666</v>
+        <v>45535.65625</v>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
         <v>77</v>
       </c>
       <c r="H12" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1990,20 +2062,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="M12" t="n">
-        <v>224</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
@@ -2025,51 +2099,51 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>67.01010101010101</v>
+        <v>71.46363636363637</v>
       </c>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="n">
-        <v>-6.924043655446681</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>-1.444141414141427</v>
-      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="n">
-        <v>-0.1612121212121211</v>
+        <v>-2.666124885215794</v>
       </c>
       <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="n">
-        <v>-0.2075812569272655</v>
-      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="n">
-        <v>-4.904440942390195</v>
+        <v>-2.867170628776876</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.9966628418519576</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.209696969696967</v>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+        <v>0.4050622503798935</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>31904977.50229568</v>
+      </c>
       <c r="AT12" t="n">
-        <v>-6.506464646464664</v>
-      </c>
-      <c r="AU12" t="inlineStr"/>
+        <v>0.6715702479338848</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.452440118182338</v>
+      </c>
       <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="n">
-        <v>-2157500.636523966</v>
-      </c>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>-2142594.94949495</v>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+        <v>12852004.18940369</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.1806970496030011</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.932662993572084</v>
+      </c>
       <c r="BA12" t="n">
-        <v>-3.446868686868669</v>
-      </c>
-      <c r="BB12" t="inlineStr"/>
+        <v>11.01708907254361</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.929393939393961</v>
+      </c>
       <c r="BC12" t="n">
-        <v>0.1388302979955292</v>
+        <v>7.674773454964878</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -2078,29 +2152,29 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>21OYHBAk</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="G13" t="n">
         <v>77</v>
       </c>
       <c r="H13" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2112,23 +2186,27 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="M13" t="n">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="N13" t="n">
-        <v>-17</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2142,58 +2220,68 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>73.43674242424242</v>
-      </c>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="n">
-        <v>-8.555568695573498</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.3419191919192031</v>
-      </c>
+        <v>68.84302112029386</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>65.23113636363635</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="n">
-        <v>-0.743838383838384</v>
+        <v>0.07289256198347971</v>
       </c>
       <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="n">
-        <v>-0.4287476892404425</v>
-      </c>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="n">
-        <v>-7.878065401229648</v>
+        <v>3.016418804718001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.1530747406109754</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-0.665252525252523</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+        <v>0.03067810691723749</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>-322703.305785124</v>
+      </c>
       <c r="AT13" t="n">
-        <v>-8.633333333333326</v>
-      </c>
-      <c r="AU13" t="inlineStr"/>
+        <v>0.1599999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-2.034431779162134</v>
+      </c>
       <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="n">
-        <v>-18824955.94225509</v>
-      </c>
+      <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="n">
-        <v>-32115520.20202021</v>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+        <v>-112552.6400390235</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.326614171746698</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.65793388429752</v>
+      </c>
       <c r="BA13" t="n">
-        <v>-10.72484848484848</v>
-      </c>
-      <c r="BB13" t="inlineStr"/>
+        <v>0.8245454545454578</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-1.05801652892562</v>
+      </c>
       <c r="BC13" t="n">
-        <v>0.6018855109821253</v>
+        <v>1.096276855061419</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -2202,29 +2290,29 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C14" t="n">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="F14" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="G14" t="n">
         <v>77</v>
       </c>
       <c r="H14" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2236,90 +2324,120 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>254</v>
+        <v>202</v>
       </c>
       <c r="M14" t="n">
-        <v>48</v>
+        <v>151</v>
       </c>
       <c r="N14" t="n">
-        <v>-23</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-19</v>
+      </c>
+      <c r="T14" t="n">
+        <v>19</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X14" t="n">
         <v>-2</v>
       </c>
-      <c r="P14" t="n">
-        <v>-10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="n">
-        <v>-4.647603690858261</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.65136975818794</v>
-      </c>
+      <c r="AJ14" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="n">
-        <v>-0.688544536271809</v>
+        <v>0.9280467007739617</v>
       </c>
       <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="n">
-        <v>-0.7226153653968179</v>
-      </c>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="n">
-        <v>-5.645385867424679</v>
+        <v>-0.4234691856377708</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.09954191581329</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>-1.748974594429139</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+        <v>0.009889879719608086</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>3330516.200970747</v>
+      </c>
       <c r="AT14" t="n">
-        <v>-2.707698194061834</v>
-      </c>
-      <c r="AU14" t="inlineStr"/>
+        <v>0.1431523022432115</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.053392916250601</v>
+      </c>
       <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="n">
-        <v>-12931898.87869197</v>
-      </c>
+      <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="n">
-        <v>-13061801.34680135</v>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
+        <v>1763444.435769465</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-3.126810362836284</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-1.058992522628884</v>
+      </c>
       <c r="BA14" t="n">
-        <v>-4.157790021426379</v>
-      </c>
-      <c r="BB14" t="inlineStr"/>
+        <v>3.479030565394197</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.995461104552021</v>
+      </c>
       <c r="BC14" t="n">
-        <v>-1.110334613348563</v>
+        <v>0.5672157407175575</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -2328,14 +2446,14 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45527.64583333334</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -2344,7 +2462,7 @@
         <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
         <v>77</v>
@@ -2366,19 +2484,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="M15" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2396,56 +2514,68 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="n">
-        <v>0.1792291262471082</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>3.314233241505974</v>
-      </c>
+      <c r="AI15" t="n">
+        <v>67.81784511784512</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>69.28451178451178</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.9247586980920346</v>
       </c>
       <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="n">
-        <v>-0.431862519464616</v>
+        <v>-0.5943565188943296</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.732712034139325</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>-1.708631772268138</v>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+        <v>0.007692307692307665</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>121939.6745230076</v>
+      </c>
       <c r="AT15" t="n">
-        <v>0.7447199265380959</v>
-      </c>
-      <c r="AU15" t="inlineStr"/>
+        <v>0.01909090909090905</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.4827192859263789</v>
+      </c>
       <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="n">
-        <v>-195391.3025693221</v>
-      </c>
+      <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="n">
-        <v>56919.19191919174</v>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
+        <v>21057.38383152569</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.6135342653786573</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.8344949494949496</v>
+      </c>
       <c r="BA15" t="n">
-        <v>-0.5790633608815483</v>
-      </c>
-      <c r="BB15" t="inlineStr"/>
+        <v>0.5888945005611674</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.2036139169472619</v>
+      </c>
       <c r="BC15" t="n">
-        <v>-0.4125488396019783</v>
+        <v>-0.3432954316214989</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -2454,29 +2584,29 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="F16" t="n">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
         <v>77</v>
       </c>
       <c r="H16" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2488,88 +2618,122 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-13</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>68.88834498834498</v>
+      </c>
       <c r="AJ16" t="n">
-        <v>68.15454545454546</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>8.91534620783159</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>4.950882759216114</v>
-      </c>
+        <v>70.40206611570247</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
-        <v>0.7411313994647331</v>
+        <v>-1.471136363636361</v>
       </c>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="n">
-        <v>0.5431710215183396</v>
-      </c>
+      <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="n">
-        <v>6.535526614950712</v>
+        <v>-0.1571226415334195</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.6247532497825148</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.05622248122247342</v>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+        <v>0.1033411033411034</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>486420.4545454546</v>
+      </c>
       <c r="AT16" t="n">
-        <v>10.44818052318054</v>
-      </c>
-      <c r="AU16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.983839215026862</v>
+      </c>
       <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="n">
-        <v>13065393.51073116</v>
-      </c>
+      <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="n">
-        <v>26936113.7011137</v>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
+        <v>392906.2785041046</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.1612262573641274</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.3345454545454487</v>
+      </c>
       <c r="BA16" t="n">
-        <v>9.424369766036421</v>
-      </c>
-      <c r="BB16" t="inlineStr"/>
+        <v>2.455227272727285</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>3.228863636363641</v>
+      </c>
       <c r="BC16" t="n">
-        <v>-1.225805823739964</v>
+        <v>2.389816165930014</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -2578,23 +2742,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45523.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C17" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>77</v>
@@ -2616,19 +2780,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="M17" t="n">
-        <v>239</v>
+        <v>55</v>
       </c>
       <c r="N17" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -2646,56 +2810,64 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="n">
-        <v>-4.006907119017484</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>-2.540559440559434</v>
-      </c>
+      <c r="AI17" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>78.55727272727272</v>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
-        <v>-0.5398601398601401</v>
+        <v>1.377685950413223</v>
       </c>
       <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="n">
-        <v>-0.3007820680496265</v>
-      </c>
+      <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="n">
-        <v>-6.720152785774857</v>
+        <v>2.608819499205111</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-3.919959208634737</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>-1.790209790209794</v>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+        <v>0.08860531051440135</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>6752975.206611572</v>
+      </c>
       <c r="AT17" t="n">
-        <v>-3.841258741258741</v>
-      </c>
-      <c r="AU17" t="inlineStr"/>
+        <v>0.2487603305785127</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.2976648587683</v>
+      </c>
       <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="n">
-        <v>-10821912.99744477</v>
-      </c>
+      <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="n">
-        <v>-13582692.30769231</v>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
+        <v>4056428.43130108</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-1.770989053092499</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.5396694214876092</v>
+      </c>
       <c r="BA17" t="n">
-        <v>-6.152447552447555</v>
-      </c>
-      <c r="BB17" t="inlineStr"/>
+        <v>2.997520661157012</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.471074380165291</v>
+      </c>
       <c r="BC17" t="n">
-        <v>-2.124285181064444</v>
+        <v>1.70564804196151</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -2704,23 +2876,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C18" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="G18" t="n">
         <v>77</v>
@@ -2742,22 +2914,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>241</v>
+        <v>95</v>
       </c>
       <c r="M18" t="n">
         <v>250</v>
       </c>
       <c r="N18" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2778,50 +2950,52 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>78.30699300699301</v>
+      </c>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="n">
-        <v>-6.053703107237581</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.793636363636324</v>
-      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.03460743801653621</v>
       </c>
       <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="n">
-        <v>-0.8262053527570767</v>
-      </c>
+      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="n">
-        <v>-5.902823074116185</v>
+        <v>-0.6013235376983346</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.2795260199570748</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>-0.9372727272727275</v>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+        <v>-0.1095278724274225</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>1590805.785123968</v>
+      </c>
       <c r="AT18" t="n">
-        <v>-4.859999999999999</v>
-      </c>
-      <c r="AU18" t="inlineStr"/>
+        <v>-0.1735537190082646</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.5645823461895247</v>
+      </c>
       <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="n">
-        <v>-13687718.22168891</v>
-      </c>
+      <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="n">
-        <v>-17727272.72727273</v>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
+        <v>-86052.6764256903</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-2.582383499558912</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-1.356198347107441</v>
+      </c>
       <c r="BA18" t="n">
-        <v>-6.484545454545454</v>
-      </c>
-      <c r="BB18" t="inlineStr"/>
+        <v>-0.1488636363636431</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.008161157024801</v>
+      </c>
       <c r="BC18" t="n">
-        <v>0.5211965110240939</v>
+        <v>-1.885980935273295</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -2830,29 +3004,29 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45535.54166666666</v>
       </c>
       <c r="C19" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>193</v>
       </c>
       <c r="G19" t="n">
         <v>77</v>
       </c>
       <c r="H19" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2864,92 +3038,122 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="M19" t="n">
-        <v>151</v>
+        <v>268</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-8</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2</v>
       </c>
-      <c r="P19" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="AA19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>65.23113636363635</v>
+      </c>
       <c r="AJ19" t="n">
-        <v>67.02000000000001</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>7.357223343262774</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>-0.7963157213157217</v>
-      </c>
+        <v>68.74000000000001</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="n">
-        <v>0.7381313131313132</v>
+        <v>2.552800734618927</v>
       </c>
       <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="n">
-        <v>0.7523791514378557</v>
-      </c>
+      <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="n">
-        <v>8.97950453202256</v>
+        <v>4.25835980379307</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.4738651437846215</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.876120176120175</v>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+        <v>0.1434532906818879</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>714439.8530762163</v>
+      </c>
       <c r="AT19" t="n">
-        <v>5.194030044030029</v>
-      </c>
-      <c r="AU19" t="inlineStr"/>
+        <v>0.1188552188552192</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.095660807443849</v>
+      </c>
       <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="n">
-        <v>14583889.23023524</v>
-      </c>
+      <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="n">
-        <v>15428060.08806009</v>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
+        <v>1175266.567317234</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.333847904611801</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-3.484213345576986</v>
+      </c>
       <c r="BA19" t="n">
-        <v>7.51061901061901</v>
-      </c>
-      <c r="BB19" t="inlineStr"/>
+        <v>0.6862871135598283</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.663414447505346</v>
+      </c>
       <c r="BC19" t="n">
-        <v>0.5301586758896164</v>
+        <v>3.689121875473504</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
@@ -2958,29 +3162,29 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45534.65625</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E20" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
         <v>77</v>
       </c>
       <c r="H20" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2992,23 +3196,27 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>239</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
       <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3022,58 +3230,64 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>67.42323232323233</v>
-      </c>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="n">
-        <v>-0.1280161534443494</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0.58727272727279</v>
-      </c>
+        <v>72.03295454545454</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>74.06110537190082</v>
+      </c>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
-        <v>-0.1490909090909092</v>
+        <v>-4.1732867132867</v>
       </c>
       <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="n">
-        <v>-0.1671894927659499</v>
-      </c>
+      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="n">
-        <v>-1.195485655898793</v>
+        <v>-4.216831979985784</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.250187716378093</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0.3909090909090907</v>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+        <v>0.5036243998785803</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>20859580.41958042</v>
+      </c>
       <c r="AT20" t="n">
-        <v>1.475454545454568</v>
-      </c>
-      <c r="AU20" t="inlineStr"/>
+        <v>0.8555944055944054</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.643829979632656</v>
+      </c>
       <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="n">
-        <v>49983.43124821316</v>
-      </c>
+      <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="n">
-        <v>2195000</v>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
+        <v>10599102.89704721</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.646832113878936</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.108881118881115</v>
+      </c>
       <c r="BA20" t="n">
-        <v>2.987272727272739</v>
-      </c>
-      <c r="BB20" t="inlineStr"/>
+        <v>4.513916083916087</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>3.050559440559439</v>
+      </c>
       <c r="BC20" t="n">
-        <v>-1.686118138501239</v>
+        <v>4.038577245868211</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -3082,29 +3296,29 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45534.5625</v>
       </c>
       <c r="C21" t="n">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="F21" t="n">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="G21" t="n">
         <v>77</v>
       </c>
       <c r="H21" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3116,19 +3330,27 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="M21" t="n">
-        <v>267</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3149,37 +3371,51 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="n">
-        <v>-2.31823826334697</v>
-      </c>
+      <c r="AJ21" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AM21" t="n">
+        <v>-1.38650793650794</v>
+      </c>
       <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="n">
-        <v>-6.170239533011269</v>
+        <v>-3.10065423739232</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.5929347826087223</v>
+        <v>-0.1334582573507423</v>
       </c>
       <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-10488754.09943592</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-0.246904105995015</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-3.72729458120898</v>
+      </c>
       <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="n">
-        <v>-817326.8301746562</v>
-      </c>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>-4157362.913029947</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.715711899095858</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.8064016791289532</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-6.152676111767036</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-4.753286107831556</v>
+      </c>
       <c r="BC21" t="n">
-        <v>-3.009571256038647</v>
+        <v>-4.433871272480388</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -3188,23 +3424,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C22" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="G22" t="n">
         <v>77</v>
@@ -3226,78 +3462,118 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M22" t="n">
-        <v>31</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="n">
-        <v>-6.384684417096963</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>-5.110399449035839</v>
-      </c>
+      <c r="AI22" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>68.81666666666666</v>
+      </c>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="n">
-        <v>-0.2272727272727273</v>
+        <v>-0.9985858585858978</v>
       </c>
       <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="n">
-        <v>-0.1262877158379407</v>
-      </c>
+      <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="n">
-        <v>-4.661759441208474</v>
+        <v>-2.712272157580998</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-5.453919881759077</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.088016528925614</v>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="n">
+        <v>-286823.2323232321</v>
+      </c>
       <c r="AT22" t="n">
-        <v>-6.625068870523407</v>
-      </c>
-      <c r="AU22" t="inlineStr"/>
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.490177326486162</v>
+      </c>
       <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="n">
-        <v>-2772414.687150819</v>
-      </c>
+      <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="n">
-        <v>-4028078.512396694</v>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
+        <v>263943.1809475927</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-0.1610907371495607</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.18949494949495</v>
+      </c>
       <c r="BA22" t="n">
-        <v>-5.686088154269981</v>
-      </c>
-      <c r="BB22" t="inlineStr"/>
+        <v>-0.604848484848489</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-0.9871717171717052</v>
+      </c>
       <c r="BC22" t="n">
-        <v>1.42665827851236</v>
+        <v>1.932301246139474</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -3306,23 +3582,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C23" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="F23" t="n">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="G23" t="n">
         <v>77</v>
@@ -3344,10 +3620,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="M23" t="n">
-        <v>267</v>
+        <v>187</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -3362,12 +3638,8 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -3404,23 +3676,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C24" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F24" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
         <v>77</v>
@@ -3442,86 +3714,96 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>67</v>
+        <v>228</v>
       </c>
       <c r="M24" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>-1</v>
       </c>
-      <c r="O24" t="n">
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-12</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-4</v>
       </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AA24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-3</v>
+      </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="n">
-        <v>-0.2796706844774519</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>-3.599145299145277</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>-0.08671328671328693</v>
-      </c>
+      <c r="AJ24" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="n">
-        <v>-0.1303978630065585</v>
-      </c>
+      <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="n">
-        <v>-2.919958248943772</v>
+        <v>2.564346678962067</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-3.177685384931834</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>-0.7808857808857823</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="n">
-        <v>-1.544366744366741</v>
-      </c>
-      <c r="AU24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="n">
+        <v>2.798509197355344</v>
+      </c>
       <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="n">
-        <v>-619920.9984638728</v>
-      </c>
+      <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="n">
-        <v>-596305.3613053614</v>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+        <v>1186289.730568577</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>-1.408184201838051</v>
+      </c>
       <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="n">
-        <v>-1.568065268065254</v>
-      </c>
+      <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="n">
-        <v>-2.92950504228282</v>
+        <v>2.423725270456046</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -3530,29 +3812,29 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="E25" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="G25" t="n">
         <v>77</v>
       </c>
       <c r="H25" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3564,27 +3846,19 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>124</v>
+        <v>228</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-3</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -3596,89 +3870,87 @@
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
+      <c r="AA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-3</v>
+      </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="n">
-        <v>-3.793878229899889</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.971818181818179</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>-0.5736363636363637</v>
-      </c>
+      <c r="AJ25" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="n">
-        <v>-0.5118471684261157</v>
-      </c>
+      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="n">
-        <v>-5.24970640384727</v>
+        <v>-4.449884398760815</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.910730703478436</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>-1.259090909090911</v>
-      </c>
+        <v>-0.03067810691723749</v>
+      </c>
+      <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="n">
-        <v>-6.010909090909095</v>
-      </c>
-      <c r="AU25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="n">
+        <v>1.278276253029105</v>
+      </c>
       <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="n">
-        <v>-12428700.10498474</v>
-      </c>
+      <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="n">
-        <v>-30504409.09090909</v>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+        <v>-223429.3110038533</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>-2.505796144613079</v>
+      </c>
       <c r="AZ25" t="inlineStr"/>
-      <c r="BA25" t="n">
-        <v>-7.815454545454557</v>
-      </c>
+      <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="n">
-        <v>-0.835851507453679</v>
+        <v>-3.031588533637731</v>
       </c>
       <c r="BD25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C26" t="n">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="G26" t="n">
         <v>77</v>
       </c>
       <c r="H26" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3690,26 +3962,26 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="M26" t="n">
-        <v>266</v>
+        <v>143</v>
       </c>
       <c r="N26" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>1</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3732,48 +4004,48 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="n">
-        <v>3.279644234116674</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>-1.303305785123939</v>
-      </c>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="n">
-        <v>0.2140495867768599</v>
+        <v>0.9249380165289267</v>
       </c>
       <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="n">
-        <v>0.130071290563269</v>
-      </c>
+      <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="n">
-        <v>0.3268449268749833</v>
+        <v>0.0822762061097535</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.444302914581556</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>-0.4537190082644642</v>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="n">
+        <v>-281501.0330578513</v>
+      </c>
       <c r="AT26" t="n">
-        <v>2.566115702479351</v>
-      </c>
-      <c r="AU26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>-3.316718350883505</v>
+      </c>
       <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="n">
-        <v>3760315.510724925</v>
-      </c>
+      <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="n">
-        <v>6059318.181818182</v>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
+        <v>-142996.2812175332</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2.428790630744093</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.6042975206611523</v>
+      </c>
       <c r="BA26" t="n">
-        <v>1.724793388429745</v>
-      </c>
-      <c r="BB26" t="inlineStr"/>
+        <v>-1.814318181818194</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-2.220516528925614</v>
+      </c>
       <c r="BC26" t="n">
-        <v>-2.367817123022178</v>
+        <v>-0.08756875544723641</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -3782,29 +4054,29 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="G27" t="n">
         <v>77</v>
       </c>
       <c r="H27" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3816,17 +4088,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="M27" t="n">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3835,7 +4107,7 @@
         <v>5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3856,52 +4128,52 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="n">
-        <v>67.51060606060607</v>
-      </c>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="n">
-        <v>-2.060821593865057</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0.114049586776872</v>
-      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="n">
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="n">
-        <v>-0.3165289256198347</v>
+        <v>0.8706958473625548</v>
       </c>
       <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="n">
-        <v>-0.1353895862591517</v>
-      </c>
+      <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="n">
-        <v>-1.635386095386096</v>
+        <v>1.435461877304022</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.1535870731522664</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.04876033057851359</v>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+        <v>-0.1033411033411034</v>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="n">
+        <v>-377121.4927048259</v>
+      </c>
       <c r="AT27" t="n">
-        <v>-1.581818181818178</v>
-      </c>
-      <c r="AU27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>-1.639849527665319</v>
+      </c>
       <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="n">
-        <v>-1355417.911597259</v>
-      </c>
+      <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="n">
-        <v>-2739586.776859504</v>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
+        <v>-373444.4320007476</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>-0.6523446222393616</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>-0.169040404040409</v>
+      </c>
       <c r="BA27" t="n">
-        <v>-0.9380165289256155</v>
-      </c>
-      <c r="BB27" t="inlineStr"/>
+        <v>-1.158894500561161</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-1.76179573512907</v>
+      </c>
       <c r="BC27" t="n">
-        <v>-0.4431689164297872</v>
+        <v>-1.662199781699783</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -3910,29 +4182,29 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C28" t="n">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="F28" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G28" t="n">
         <v>77</v>
       </c>
       <c r="H28" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -3944,90 +4216,116 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="N28" t="n">
-        <v>20</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="n">
-        <v>6.047473147137211</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>-1.817373737373714</v>
-      </c>
+      <c r="AJ28" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="n">
-        <v>0.5603030303030303</v>
+        <v>-5.406978879706145</v>
       </c>
       <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="n">
-        <v>0.3394183358208125</v>
-      </c>
+      <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="n">
-        <v>4.231001319944824</v>
+        <v>-5.494154506232803</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.243652360568035</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>-0.4493939393939463</v>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+        <v>-0.1215800623802874</v>
+      </c>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="n">
+        <v>-3873503.21395776</v>
+      </c>
       <c r="AT28" t="n">
-        <v>4.8531313131313</v>
-      </c>
-      <c r="AU28" t="inlineStr"/>
+        <v>-0.1980104071013165</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>-7.75966074176533</v>
+      </c>
       <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="n">
-        <v>15394079.72707261</v>
-      </c>
+      <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="n">
-        <v>21702176.76767677</v>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
+        <v>-2673137.165405254</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.388786909409102</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2.221678910315273</v>
+      </c>
       <c r="BA28" t="n">
-        <v>4.536565656565656</v>
-      </c>
-      <c r="BB28" t="inlineStr"/>
+        <v>-5.157361493725119</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>-6.714929599020508</v>
+      </c>
       <c r="BC28" t="n">
-        <v>-0.5295242175838091</v>
+        <v>-5.439365194955528</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -4036,23 +4334,23 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="F29" t="n">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="G29" t="n">
         <v>77</v>
@@ -4074,88 +4372,118 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="M29" t="n">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="N29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="U29" t="n">
         <v>-4</v>
       </c>
-      <c r="O29" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="V29" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD29" t="n">
         <v>-1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>65.46250000000001</v>
+      </c>
       <c r="AJ29" t="n">
-        <v>80.78818181818183</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>-0.8927444784876712</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>-0.9442424242424465</v>
-      </c>
+        <v>65.625</v>
+      </c>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="n">
-        <v>0.1599999999999999</v>
+        <v>1.03278236914602</v>
       </c>
       <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="n">
-        <v>0.02882625506538572</v>
-      </c>
+      <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="n">
-        <v>0.5109650575432312</v>
+        <v>-0.2033715057769712</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.52630408928681</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.817676767676772</v>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+        <v>0.04192980102860311</v>
+      </c>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="n">
+        <v>1082020.202020202</v>
+      </c>
       <c r="AT29" t="n">
-        <v>-0.4752525252525288</v>
-      </c>
-      <c r="AU29" t="inlineStr"/>
+        <v>0.1273645546372817</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.067352160186346</v>
+      </c>
       <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="n">
-        <v>-50945.92457868892</v>
-      </c>
+      <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="n">
-        <v>-270019.1919191917</v>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
+        <v>623686.1709878943</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>-0.2491396538879407</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.153259871441701</v>
+      </c>
       <c r="BA29" t="n">
-        <v>0.8898989898989953</v>
-      </c>
-      <c r="BB29" t="inlineStr"/>
+        <v>2.363728191000931</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.611570247933898</v>
+      </c>
       <c r="BC29" t="n">
-        <v>0.1672802960851527</v>
+        <v>0.9340753682536018</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -4164,23 +4492,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C30" t="n">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="F30" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="G30" t="n">
         <v>77</v>
@@ -4202,88 +4530,118 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="N30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>21</v>
+      </c>
+      <c r="T30" t="n">
+        <v>-21</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>6</v>
+      </c>
       <c r="Y30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1</v>
       </c>
-      <c r="Z30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
+      <c r="AC30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>68.59876543209877</v>
-      </c>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="n">
-        <v>6.39161779276796</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.008092031425349</v>
-      </c>
+        <v>68.98333333333333</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>74.31363636363636</v>
+      </c>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="n">
-        <v>0.3212121212121211</v>
+        <v>0.4269605142332011</v>
       </c>
       <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="n">
-        <v>0.2364075119926512</v>
-      </c>
+      <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="n">
-        <v>5.267080425078873</v>
+        <v>1.831351731595447</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.4046196033068838</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>-0.1485858585858537</v>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+        <v>-0.007692307692307665</v>
+      </c>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="n">
+        <v>2556151.40036731</v>
+      </c>
       <c r="AT30" t="n">
-        <v>6.621896745230103</v>
-      </c>
-      <c r="AU30" t="inlineStr"/>
+        <v>-0.01909090909090905</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4.796585177400914</v>
+      </c>
       <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="n">
-        <v>2109283.78822416</v>
-      </c>
+      <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="n">
-        <v>2025760.381593715</v>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
+        <v>1250288.837032507</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>-1.741312966519995</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>-2.720376492194671</v>
+      </c>
       <c r="BA30" t="n">
-        <v>4.644399551066215</v>
-      </c>
-      <c r="BB30" t="inlineStr"/>
+        <v>2.994632690541778</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>5.700752984389325</v>
+      </c>
       <c r="BC30" t="n">
-        <v>-0.04906580691410056</v>
+        <v>2.204362900543472</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -4292,23 +4650,23 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C31" t="n">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="F31" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="G31" t="n">
         <v>77</v>
@@ -4330,59 +4688,119 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="M31" t="n">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-1</v>
+      </c>
       <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AI31" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>67.89545454545454</v>
+      </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
+      <c r="AM31" t="n">
+        <v>2.748240648240596</v>
+      </c>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
+      <c r="AP31" t="n">
+        <v>2.675590233411555</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.1152906100111066</v>
+      </c>
       <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
+      <c r="AS31" t="n">
+        <v>-585389.0553890553</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.07337662337662332</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>-0.3319505223148127</v>
+      </c>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr"/>
+      <c r="AX31" t="n">
+        <v>39575.8281407766</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.502685332487058</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.6314019314019284</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>-0.9471805971805907</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>-1.676834276834285</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.094801035438891</v>
+      </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
@@ -4390,29 +4808,29 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45530.65625</v>
       </c>
       <c r="C32" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E32" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F32" t="n">
-        <v>178</v>
+        <v>42</v>
       </c>
       <c r="G32" t="n">
         <v>77</v>
       </c>
       <c r="H32" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4424,26 +4842,26 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="M32" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>-17</v>
       </c>
       <c r="O32" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P32" t="n">
         <v>-1</v>
       </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
       <c r="Q32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4464,52 +4882,52 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="n">
-        <v>71.34686868686867</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>-0.0003939578939622379</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>-0.7754208754208776</v>
-      </c>
+      <c r="AI32" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="n">
-        <v>-0.08473625140291818</v>
+        <v>-2.228391873278213</v>
       </c>
       <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="n">
-        <v>0.1237123370456703</v>
-      </c>
+      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="n">
-        <v>2.849104455215567</v>
+        <v>-1.157286721245526</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-2.895334973668355</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>-0.2389450056116686</v>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+        <v>-0.7271046137522112</v>
+      </c>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="n">
+        <v>-25319205.31068258</v>
+      </c>
       <c r="AT32" t="n">
-        <v>-0.4277216610550028</v>
-      </c>
-      <c r="AU32" t="inlineStr"/>
+        <v>-0.6472968319559229</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>-6.206667618655615</v>
+      </c>
       <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="n">
-        <v>277843.2362390696</v>
-      </c>
+      <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="n">
-        <v>-175168.3501683499</v>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
+        <v>-12234905.61305908</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>-0.5543059816486604</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>-0.7147134220997842</v>
+      </c>
       <c r="BA32" t="n">
-        <v>-1.175533108866446</v>
-      </c>
-      <c r="BB32" t="inlineStr"/>
+        <v>-7.324007116620734</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>-7.233901515151516</v>
+      </c>
       <c r="BC32" t="n">
-        <v>2.68650828595273</v>
+        <v>-5.609954695804234</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -4518,23 +4936,23 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C33" t="n">
+        <v>24</v>
+      </c>
+      <c r="D33" t="n">
         <v>85</v>
       </c>
-      <c r="D33" t="n">
-        <v>36</v>
-      </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F33" t="n">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="G33" t="n">
         <v>77</v>
@@ -4556,86 +4974,114 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="M33" t="n">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="N33" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>9</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V33" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
         <v>-1</v>
       </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
+      <c r="AA33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>70.45454545454545</v>
-      </c>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="n">
-        <v>-5.633068960583032</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.212878787878822</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>75.33475378787878</v>
+      </c>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="n">
-        <v>-0.5702020202020202</v>
+        <v>3.111627640036744</v>
       </c>
       <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="n">
-        <v>-0.4583960897606372</v>
-      </c>
+      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="n">
-        <v>-6.312907035033803</v>
+        <v>-0.319833077380963</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2.82915065220584</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>-1.58510101010101</v>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+        <v>-0.0722030700957903</v>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="n">
+        <v>434601.4118457292</v>
+      </c>
       <c r="AT33" t="n">
-        <v>-3.98989898989899</v>
-      </c>
-      <c r="AU33" t="inlineStr"/>
+        <v>0.1346648301193758</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.779940996990831</v>
+      </c>
       <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="n">
-        <v>-9242613.455347564</v>
-      </c>
+      <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="n">
-        <v>-9545328.282828284</v>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
+        <v>-1473.671220222488</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>-0.7095064691233191</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>-0.3695592286501395</v>
+      </c>
       <c r="BA33" t="n">
-        <v>-6.529040404040401</v>
-      </c>
-      <c r="BB33" t="inlineStr"/>
+        <v>1.145707070707061</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>2.313808539944901</v>
+      </c>
       <c r="BC33" t="n">
-        <v>-0.1219726254633287</v>
+        <v>0.01104309908907908</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -4644,23 +5090,23 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C34" t="n">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E34" t="n">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>77</v>
@@ -4682,22 +5128,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>223</v>
+        <v>99</v>
       </c>
       <c r="M34" t="n">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="N34" t="n">
-        <v>-19</v>
+        <v>17</v>
       </c>
       <c r="O34" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4718,52 +5164,50 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="n">
-        <v>63.375</v>
-      </c>
+      <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="n">
-        <v>-7.397116684111566</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.223636363636416</v>
-      </c>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="n">
-        <v>-1.234297520661157</v>
+        <v>-1.853450413223101</v>
       </c>
       <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="n">
-        <v>-0.4773903306128366</v>
-      </c>
+      <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="n">
-        <v>-8.692263711944022</v>
+        <v>0.6679386916010515</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.42218493744582</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>-1.90487603305785</v>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+        <v>0.8497862631908168</v>
+      </c>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="n">
+        <v>16962179.75206611</v>
+      </c>
       <c r="AT34" t="n">
-        <v>-7.187685950413211</v>
-      </c>
-      <c r="AU34" t="inlineStr"/>
+        <v>1.054669421487604</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>5.816963620334761</v>
+      </c>
       <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="n">
-        <v>-20456591.8585535</v>
-      </c>
+      <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="n">
-        <v>-33939380.16528925</v>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
+        <v>14672747.01003867</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0.4927709267273741</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0.8453305785123959</v>
+      </c>
       <c r="BA34" t="n">
-        <v>-9.794462809917363</v>
-      </c>
-      <c r="BB34" t="inlineStr"/>
+        <v>6.427520661157004</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.594710743801642</v>
+      </c>
       <c r="BC34" t="n">
-        <v>-0.5637997948816391</v>
+        <v>6.701296206360141</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -4772,29 +5216,29 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45520.64583333334</v>
+        <v>45529.65625</v>
       </c>
       <c r="C35" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D35" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E35" t="n">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>77</v>
       </c>
       <c r="H35" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4806,23 +5250,23 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="M35" t="n">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="N35" t="n">
-        <v>-5</v>
+        <v>11</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
@@ -4836,12 +5280,8 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4851,53 +5291,51 @@
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>69.98601398601399</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>69.889898989899</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>-2.283436038747027</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>-0.06848484848492831</v>
-      </c>
+        <v>67.8</v>
+      </c>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>-3.307438016528891</v>
       </c>
       <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
+      <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="n">
-        <v>-4.268141187647913</v>
+        <v>-3.537998793449106</v>
       </c>
       <c r="AQ35" t="n">
-        <v>-0.02491778261256172</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>-0.8424242424242401</v>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+        <v>0.3104683394598959</v>
+      </c>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="n">
+        <v>23846033.05785124</v>
+      </c>
       <c r="AT35" t="n">
-        <v>-3.158484848484846</v>
-      </c>
-      <c r="AU35" t="inlineStr"/>
+        <v>0.4479338842975209</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.009442190711397</v>
+      </c>
       <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="n">
-        <v>-817667.002276741</v>
-      </c>
+      <c r="AW35" t="inlineStr"/>
       <c r="AX35" t="n">
-        <v>-1147527.272727273</v>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
+        <v>8268656.74503216</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.826825898487471</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.738016528925623</v>
+      </c>
       <c r="BA35" t="n">
-        <v>-3.434545454545443</v>
-      </c>
-      <c r="BB35" t="inlineStr"/>
+        <v>5.646280991735537</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>2.890909090909091</v>
+      </c>
       <c r="BC35" t="n">
-        <v>-1.673615830566604</v>
+        <v>4.50303342235604</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -4906,32 +5344,32 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45516.67708333334</v>
+        <v>45529.64583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E36" t="n">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="G36" t="n">
         <v>77</v>
       </c>
       <c r="H36" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -4940,14 +5378,14 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="M36" t="n">
-        <v>267</v>
+        <v>151</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -4973,37 +5411,39 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="n">
-        <v>3.53269609700645</v>
-      </c>
+      <c r="AJ36" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="n">
-        <v>0.1367241379310347</v>
-      </c>
+      <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="n">
-        <v>8.537350637867881</v>
+        <v>-0.1865268620268523</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.347430845017044</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
+      <c r="AU36" t="n">
+        <v>-2.476695767195764</v>
+      </c>
       <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="n">
-        <v>1939007.06707086</v>
-      </c>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="n">
+        <v>385934.4042531543</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>5.199494098494096</v>
+      </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="n">
-        <v>4.417824302134647</v>
+        <v>3.786026251526252</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
@@ -5012,32 +5452,32 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45529.64583333334</v>
       </c>
       <c r="C37" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="G37" t="n">
         <v>77</v>
       </c>
       <c r="H37" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -5046,91 +5486,89 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="M37" t="n">
-        <v>38</v>
-      </c>
-      <c r="N37" t="n">
+        <v>268</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U37" t="n">
         <v>-4</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
+      <c r="V37" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z37" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
+      <c r="AA37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
+      <c r="AI37" t="n">
+        <v>71.36363636363636</v>
+      </c>
       <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="n">
-        <v>5.091865286015448</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.820437710437716</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.2162738496071828</v>
-      </c>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="n">
-        <v>0.2364075119926512</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>6.078070922236037</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>-0.3674574554368633</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>-0.2127833894500526</v>
-      </c>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="n">
-        <v>4.242884399551087</v>
-      </c>
+      <c r="AT37" t="inlineStr"/>
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="n">
-        <v>2073205.741178613</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1518291.245791246</v>
-      </c>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="n">
-        <v>2.748103254769902</v>
-      </c>
+      <c r="BA37" t="inlineStr"/>
       <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="n">
-        <v>1.000277134095501</v>
-      </c>
+      <c r="BC37" t="inlineStr"/>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
@@ -5138,57 +5576,61 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45516.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C38" t="n">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="D38" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="E38" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="G38" t="n">
         <v>77</v>
       </c>
       <c r="H38" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>91</v>
+      </c>
+      <c r="M38" t="n">
+        <v>239</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>102</v>
-      </c>
-      <c r="M38" t="n">
-        <v>267</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -5202,44 +5644,64 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
+      <c r="AC38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>-1</v>
+      </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="n">
-        <v>4.621695348130132</v>
-      </c>
+      <c r="AI38" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>72.03295454545454</v>
+      </c>
+      <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
+      <c r="AM38" t="n">
+        <v>-1.176923076923089</v>
+      </c>
       <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="n">
-        <v>0.08224931590149009</v>
-      </c>
+      <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="n">
-        <v>-1.950083307996351</v>
+        <v>-1.632381566870862</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.097234417756198</v>
+        <v>-0.2092702715606767</v>
       </c>
       <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
+      <c r="AS38" t="n">
+        <v>-5890089.001907183</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>-0.2778766687857599</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>-2.752778295228595</v>
+      </c>
       <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="n">
-        <v>807385.1778656123</v>
-      </c>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="n">
+        <v>-7670871.849001984</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>-0.6624761262313754</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.0874761602034333</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>-2.217736808645896</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>-2.487539732994279</v>
+      </c>
       <c r="BC38" t="n">
-        <v>-5.636925509273333</v>
+        <v>-3.128945708421554</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
@@ -5248,60 +5710,60 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45529.5625</v>
       </c>
       <c r="C39" t="n">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="F39" t="n">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="G39" t="n">
         <v>77</v>
       </c>
       <c r="H39" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>186</v>
+      </c>
+      <c r="M39" t="n">
+        <v>204</v>
+      </c>
+      <c r="N39" t="n">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>194</v>
-      </c>
-      <c r="M39" t="n">
-        <v>73</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3</v>
-      </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5323,49 +5785,51 @@
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="n">
-        <v>4.006611436900045</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.466262626262647</v>
-      </c>
+      <c r="AJ39" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="n">
-        <v>-0.02020202020202011</v>
+        <v>-0.923981573981564</v>
       </c>
       <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="n">
-        <v>-0.1237123370456703</v>
-      </c>
+      <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="n">
-        <v>0.6780446896684538</v>
+        <v>-0.1569594031675763</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.151182829978438</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>-1.767777777777784</v>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+        <v>0.5104853420916944</v>
+      </c>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="n">
+        <v>10022199.74469975</v>
+      </c>
       <c r="AT39" t="n">
-        <v>4.761414141414164</v>
-      </c>
-      <c r="AU39" t="inlineStr"/>
+        <v>0.6017038517038513</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6.913714444311751</v>
+      </c>
       <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="n">
-        <v>1168445.795135325</v>
-      </c>
+      <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="n">
-        <v>2919146.464646465</v>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
+        <v>9920911.024466714</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>-0.5890392451726392</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.087456987456985</v>
+      </c>
       <c r="BA39" t="n">
-        <v>3.718585858585868</v>
-      </c>
-      <c r="BB39" t="inlineStr"/>
+        <v>6.457825507825518</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>5.252014652014651</v>
+      </c>
       <c r="BC39" t="n">
-        <v>-3.420309037831945</v>
+        <v>7.176820518546464</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
@@ -5374,57 +5838,61 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45528.65625</v>
       </c>
       <c r="C40" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="G40" t="n">
         <v>77</v>
       </c>
       <c r="H40" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>97</v>
+      </c>
+      <c r="M40" t="n">
+        <v>189</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>63</v>
-      </c>
-      <c r="M40" t="n">
-        <v>80</v>
-      </c>
-      <c r="N40" t="n">
-        <v>8</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -5444,50 +5912,52 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
+      <c r="AI40" t="n">
+        <v>68</v>
+      </c>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="n">
-        <v>3.199836399283441</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>4.169393939393927</v>
-      </c>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="n">
-        <v>0.2481818181818183</v>
+        <v>-0.5066115702479692</v>
       </c>
       <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="n">
-        <v>0.1935295681270914</v>
-      </c>
+      <c r="AO40" t="inlineStr"/>
       <c r="AP40" t="n">
-        <v>5.080885805275642</v>
+        <v>-2.650363292575605</v>
       </c>
       <c r="AQ40" t="n">
-        <v>2.885303425552451</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>-0.2954545454545432</v>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+        <v>-0.106361897551156</v>
+      </c>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="n">
+        <v>982851.2396694217</v>
+      </c>
       <c r="AT40" t="n">
-        <v>8.096363636363634</v>
-      </c>
-      <c r="AU40" t="inlineStr"/>
+        <v>0.1685950413223138</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.653680695547678</v>
+      </c>
       <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="n">
-        <v>4284683.627062971</v>
-      </c>
+      <c r="AW40" t="inlineStr"/>
       <c r="AX40" t="n">
-        <v>12069202.02020202</v>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
+        <v>834516.7729755333</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>-0.8989290618446617</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>-0.6404958677685926</v>
+      </c>
       <c r="BA40" t="n">
-        <v>8.128686868686856</v>
-      </c>
-      <c r="BB40" t="inlineStr"/>
+        <v>0.2049586776859513</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0.0429752066115725</v>
+      </c>
       <c r="BC40" t="n">
-        <v>0.6164399232772944</v>
+        <v>1.28294831530124</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
@@ -5496,32 +5966,32 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E41" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="F41" t="n">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="G41" t="n">
         <v>77</v>
       </c>
       <c r="H41" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -5530,26 +6000,26 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M41" t="n">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O41" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q41" t="n">
         <v>2</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5572,48 +6042,48 @@
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="n">
-        <v>2.300602888976684</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.761593714927017</v>
-      </c>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
       <c r="AM41" t="n">
-        <v>0.1034118967452302</v>
+        <v>-1.381590909090875</v>
       </c>
       <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="n">
-        <v>-0.05241219736714098</v>
-      </c>
+      <c r="AO41" t="inlineStr"/>
       <c r="AP41" t="n">
-        <v>-0.8758213404994137</v>
+        <v>-0.279196003674258</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.05298544926216664</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>-2.014915824915832</v>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+        <v>0.8180428315645705</v>
+      </c>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="n">
+        <v>34468409.09090909</v>
+      </c>
       <c r="AT41" t="n">
-        <v>1.657003367003355</v>
-      </c>
-      <c r="AU41" t="inlineStr"/>
+        <v>1.395454545454546</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>6.643161341074389</v>
+      </c>
       <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="n">
-        <v>-61511.01013553748</v>
-      </c>
+      <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="n">
-        <v>-1073521.885521885</v>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
+        <v>21430435.08641117</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>3.946874870700956</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>3.971818181818183</v>
+      </c>
       <c r="BA41" t="n">
-        <v>-2.799775533108871</v>
-      </c>
-      <c r="BB41" t="inlineStr"/>
+        <v>10.78795454545455</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>6.822499999999991</v>
+      </c>
       <c r="BC41" t="n">
-        <v>-1.181015818909245</v>
+        <v>10.94913407204712</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
@@ -5622,32 +6092,32 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C42" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D42" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="F42" t="n">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="G42" t="n">
         <v>77</v>
       </c>
       <c r="H42" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -5656,90 +6126,98 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>54</v>
+        <v>202</v>
       </c>
       <c r="M42" t="n">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W42" t="n">
+        <v>8</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="n">
-        <v>0.1898324490413899</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.724242424242391</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.06464646464646462</v>
-      </c>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="n">
-        <v>0.1042002147074614</v>
-      </c>
+      <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="n">
-        <v>-0.04566370067576031</v>
+        <v>1.992134768723957</v>
       </c>
       <c r="AQ42" t="n">
-        <v>2.268213231347289</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>-1.538888888888888</v>
-      </c>
+        <v>0.1283856179358429</v>
+      </c>
+      <c r="AR42" t="inlineStr"/>
       <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="n">
-        <v>1.308585858585857</v>
-      </c>
-      <c r="AU42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="n">
+        <v>3.867403765649655</v>
+      </c>
       <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="n">
-        <v>358043.4696588081</v>
-      </c>
+      <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="n">
-        <v>525429.2929292931</v>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+        <v>1513547.466408598</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>-0.1479000305874401</v>
+      </c>
       <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="n">
-        <v>-0.564646464646458</v>
-      </c>
+      <c r="BA42" t="inlineStr"/>
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="n">
-        <v>-0.4150312426882472</v>
+        <v>2.113859933308959</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
@@ -5748,32 +6226,32 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>4QCyHCDr</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C43" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E43" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="F43" t="n">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="G43" t="n">
         <v>77</v>
       </c>
       <c r="H43" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -5782,27 +6260,23 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="M43" t="n">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
-      <c r="O43" t="n">
-        <v>-1</v>
-      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -5824,48 +6298,48 @@
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="n">
-        <v>-1.143856204227106</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>-1.786433566433573</v>
-      </c>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>-1.211101928374632</v>
       </c>
       <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="n">
-        <v>-0.04231307154384112</v>
-      </c>
+      <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="n">
-        <v>-3.404913275649122</v>
+        <v>-0.1822772290164494</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.6527582159315841</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0.4961538461538453</v>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="n">
+        <v>-2237964.531680441</v>
+      </c>
       <c r="AT43" t="n">
-        <v>-3.507552447552456</v>
-      </c>
-      <c r="AU43" t="inlineStr"/>
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>-3.401212885228759</v>
+      </c>
       <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="n">
-        <v>-460562.3602673612</v>
-      </c>
+      <c r="AW43" t="inlineStr"/>
       <c r="AX43" t="n">
-        <v>-1396041.258741259</v>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
+        <v>-1137108.822393481</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.134542146547133</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>2.030881542699721</v>
+      </c>
       <c r="BA43" t="n">
-        <v>-2.966013986013976</v>
-      </c>
-      <c r="BB43" t="inlineStr"/>
+        <v>-1.914329660238749</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>-3.934490358126709</v>
+      </c>
       <c r="BC43" t="n">
-        <v>-2.154294048875816</v>
+        <v>-2.192254273947</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
@@ -5874,32 +6348,32 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="D44" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F44" t="n">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="G44" t="n">
         <v>77</v>
       </c>
       <c r="H44" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -5908,86 +6382,96 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="M44" t="n">
-        <v>147</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>-3</v>
+      </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
+      <c r="AI44" t="n">
+        <v>68.66666666666667</v>
+      </c>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="n">
-        <v>9.402396369927715</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>-2.341515151515154</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.7100000000000002</v>
-      </c>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="n">
-        <v>0.552191083770031</v>
-      </c>
+      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="n">
-        <v>11.22808068925053</v>
+        <v>4.418381732139494</v>
       </c>
       <c r="AQ44" t="n">
-        <v>-2.557786796428189</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0.02676767676768321</v>
-      </c>
+        <v>0.1184957382162348</v>
+      </c>
+      <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="n">
-        <v>12.05838383838385</v>
-      </c>
-      <c r="AU44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="n">
+        <v>2.664010849399048</v>
+      </c>
       <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="n">
-        <v>14824499.85413968</v>
-      </c>
+      <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="n">
-        <v>33933626.26262626</v>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+        <v>1279790.530639133</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>4.556688110026624</v>
+      </c>
       <c r="AZ44" t="inlineStr"/>
-      <c r="BA44" t="n">
-        <v>13.77808080808082</v>
-      </c>
+      <c r="BA44" t="inlineStr"/>
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="n">
-        <v>0.1158684224585151</v>
+        <v>7.566088637035847</v>
       </c>
       <c r="BD44" t="n">
         <v>0</v>
@@ -5996,122 +6480,1238 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>CSXdOfL8</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C45" t="n">
         <v>142</v>
       </c>
       <c r="D45" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F45" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="G45" t="n">
         <v>77</v>
       </c>
       <c r="H45" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>162</v>
+      </c>
+      <c r="M45" t="n">
+        <v>187</v>
+      </c>
+      <c r="N45" t="n">
+        <v>6</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>99</v>
-      </c>
-      <c r="M45" t="n">
-        <v>171</v>
-      </c>
-      <c r="N45" t="n">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>-8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-7</v>
+      </c>
+      <c r="X45" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA45" t="n">
         <v>2</v>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>-3</v>
+      </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="n">
-        <v>3.712450296616964</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.331060606060674</v>
-      </c>
+      <c r="AJ45" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="n">
-        <v>0.04545454545454541</v>
+        <v>-0.4758103764921771</v>
       </c>
       <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="n">
-        <v>0.1366392866392867</v>
-      </c>
+      <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="n">
-        <v>3.91470908720909</v>
+        <v>1.243376043909421</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.014277065527068</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>-1.422727272727268</v>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+        <v>0.1502588462374435</v>
+      </c>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="n">
+        <v>1083615.358126722</v>
+      </c>
       <c r="AT45" t="n">
-        <v>5.787878787878782</v>
-      </c>
-      <c r="AU45" t="inlineStr"/>
+        <v>0.1373737373737376</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>6.613966656078645</v>
+      </c>
       <c r="AV45" t="inlineStr"/>
-      <c r="AW45" t="n">
-        <v>1730888.176638176</v>
-      </c>
+      <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="n">
-        <v>3289318.181818182</v>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
+        <v>1352378.698495235</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>-1.123155851622833</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>-1.689146005509645</v>
+      </c>
       <c r="BA45" t="n">
-        <v>4.971212121212105</v>
-      </c>
-      <c r="BB45" t="inlineStr"/>
+        <v>3.2729958677686</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>5.947513774104678</v>
+      </c>
       <c r="BC45" t="n">
-        <v>-0.2966278782945508</v>
+        <v>4.535318135142305</v>
       </c>
       <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C46" t="n">
+        <v>41</v>
+      </c>
+      <c r="D46" t="n">
+        <v>51</v>
+      </c>
+      <c r="E46" t="n">
+        <v>94</v>
+      </c>
+      <c r="F46" t="n">
+        <v>43</v>
+      </c>
+      <c r="G46" t="n">
+        <v>77</v>
+      </c>
+      <c r="H46" t="n">
+        <v>774</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>190</v>
+      </c>
+      <c r="M46" t="n">
+        <v>31</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W46" t="n">
+        <v>4</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="n">
+        <v>70.18333333333334</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>70.4040404040404</v>
+      </c>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="n">
+        <v>-0.32449750025512</v>
+      </c>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="n">
+        <v>-1.360615441880356</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="n">
+        <v>172202.0712172226</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>1.972728663521963</v>
+      </c>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="n">
+        <v>123534.4347141762</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>-1.615219751140604</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>-0.1007116620752946</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0.51798540965207</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0.7534486276910428</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>-0.6400476287829946</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>126</v>
+      </c>
+      <c r="F47" t="n">
+        <v>153</v>
+      </c>
+      <c r="G47" t="n">
+        <v>77</v>
+      </c>
+      <c r="H47" t="n">
+        <v>774</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>76</v>
+      </c>
+      <c r="M47" t="n">
+        <v>143</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>68</v>
+      </c>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="n">
+        <v>-0.1732167832168443</v>
+      </c>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="n">
+        <v>-0.3841723401087904</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0.1001359751359752</v>
+      </c>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="n">
+        <v>-1011131.118881119</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>-2.572684981437476</v>
+      </c>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="n">
+        <v>-654322.7541689081</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0.3927435687067806</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>-0.3355244755244726</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>-2.756993006993</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>-2.451538461538462</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>-2.233728512537866</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45528.60416666666</v>
+      </c>
+      <c r="C48" t="n">
+        <v>41</v>
+      </c>
+      <c r="D48" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" t="n">
+        <v>69</v>
+      </c>
+      <c r="F48" t="n">
+        <v>75</v>
+      </c>
+      <c r="G48" t="n">
+        <v>77</v>
+      </c>
+      <c r="H48" t="n">
+        <v>774</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>154</v>
+      </c>
+      <c r="M48" t="n">
+        <v>31</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="n">
+        <v>-1.40901744719929</v>
+      </c>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="n">
+        <v>1.894138060475797</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>-0.1615105403488091</v>
+      </c>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="n">
+        <v>-2206837.832874197</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>-0.1047382920110194</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>-6.399032244543619</v>
+      </c>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="n">
+        <v>-1945621.22830462</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0.2701190465133791</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>3.589522497704312</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>-2.997860422405878</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>-6.396584022038581</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>-4.285547892887251</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C49" t="n">
+        <v>126</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>120</v>
+      </c>
+      <c r="F49" t="n">
+        <v>102</v>
+      </c>
+      <c r="G49" t="n">
+        <v>77</v>
+      </c>
+      <c r="H49" t="n">
+        <v>771</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>227</v>
+      </c>
+      <c r="M49" t="n">
+        <v>204</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="n">
+        <v>2.710185185185196</v>
+      </c>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="n">
+        <v>0.7163668682360935</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>-0.6893982302775088</v>
+      </c>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="n">
+        <v>-13134872.9721457</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>-0.6801423324150597</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>-4.724157270129226</v>
+      </c>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="n">
+        <v>-12629224.16964497</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>-0.8944483961036518</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>-1.731756963575144</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>-4.207652280379548</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>-2.757835935108659</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>-5.49054488513805</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C50" t="n">
+        <v>67</v>
+      </c>
+      <c r="D50" t="n">
+        <v>36</v>
+      </c>
+      <c r="E50" t="n">
+        <v>17</v>
+      </c>
+      <c r="F50" t="n">
+        <v>31</v>
+      </c>
+      <c r="G50" t="n">
+        <v>77</v>
+      </c>
+      <c r="H50" t="n">
+        <v>771</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>186</v>
+      </c>
+      <c r="M50" t="n">
+        <v>38</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-17</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="n">
+        <v>0.5624242424242141</v>
+      </c>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="n">
+        <v>-0.4721016541725476</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>-0.4138400604819368</v>
+      </c>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="n">
+        <v>-31407393.93939394</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>-0.7230303030303031</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>-8.64158246647834</v>
+      </c>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="n">
+        <v>-20127219.2715042</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0.5718925537552515</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>-0.8316161616161573</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>-10.74373737373737</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>-8.553434343434361</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>-8.290109757392372</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C51" t="n">
+        <v>24</v>
+      </c>
+      <c r="D51" t="n">
+        <v>14</v>
+      </c>
+      <c r="E51" t="n">
+        <v>49</v>
+      </c>
+      <c r="F51" t="n">
+        <v>193</v>
+      </c>
+      <c r="G51" t="n">
+        <v>77</v>
+      </c>
+      <c r="H51" t="n">
+        <v>774</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>154</v>
+      </c>
+      <c r="M51" t="n">
+        <v>268</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="n">
+        <v>3.352929292929332</v>
+      </c>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="n">
+        <v>3.698966476759921</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0.0008867521367521558</v>
+      </c>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="n">
+        <v>-137936.868686869</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0.0005723905723906686</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0.3084031246531254</v>
+      </c>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="n">
+        <v>-136592.9008431183</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>-0.6377971979711141</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>-1.464158249158249</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>-0.7014814814814798</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0.3865824915825016</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>-0.461875307060069</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C52" t="n">
+        <v>63</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>32</v>
+      </c>
+      <c r="F52" t="n">
+        <v>187</v>
+      </c>
+      <c r="G52" t="n">
+        <v>77</v>
+      </c>
+      <c r="H52" t="n">
+        <v>771</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>243</v>
+      </c>
+      <c r="M52" t="n">
+        <v>69</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="n">
+        <v>321</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>5.103219696969717</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>334</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0.2742880738024667</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>0.5143990066021598</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>26681573.02188552</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>0.7486742424242427</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>9.018790578000804</v>
+      </c>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="n">
+        <v>12932560.27136374</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>-1.65943581153757</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0.04269781144781248</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>9.300063131313109</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>10.34741161616162</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>6.238265520781724</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45523.5625</v>
+      </c>
+      <c r="C53" t="n">
+        <v>35</v>
+      </c>
+      <c r="D53" t="n">
+        <v>84</v>
+      </c>
+      <c r="E53" t="n">
+        <v>40</v>
+      </c>
+      <c r="F53" t="n">
+        <v>30</v>
+      </c>
+      <c r="G53" t="n">
+        <v>77</v>
+      </c>
+      <c r="H53" t="n">
+        <v>771</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>95</v>
+      </c>
+      <c r="M53" t="n">
+        <v>239</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>-236</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>-2.791695804195825</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>-60300000</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>-252</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>-3.937635976311526</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>-0.3144184316859902</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>-13608828.67132867</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>-0.5398601398601401</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>-3.999331361441733</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>-10831332.18936396</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>-2.30004275682202</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>-1.862937062937068</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>-6.274038461538467</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>-3.771940559440552</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>-6.910556826178905</v>
+      </c>
+      <c r="BD53" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD45"/>
+  <dimension ref="A1:BD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,23 +712,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -750,94 +750,118 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="M2" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="N2" t="n">
-        <v>-3</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-9</v>
+      </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-11</v>
+      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1</v>
+      </c>
       <c r="AI2" t="n">
-        <v>67.94949494949496</v>
+        <v>72.375</v>
       </c>
       <c r="AJ2" t="n">
-        <v>72.15454545454546</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-2.817205447414679</v>
-      </c>
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-0.9651048951049006</v>
+        <v>1.05843936427047</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.2916783216783219</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>-0.2191362231877498</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1730318.318283005</v>
+      </c>
       <c r="AO2" t="n">
-        <v>-0.1895018158240251</v>
+        <v>-0.4427894327894322</v>
       </c>
       <c r="AP2" t="n">
-        <v>-2.931196967849502</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1.558063040344678</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.05839160839160584</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>-0.331899766899767</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>3.113310023310035</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-2.253986013986008</v>
+        <v>0.9298599087084511</v>
       </c>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>-0.05079903081303883</v>
+      </c>
       <c r="AW2" t="n">
-        <v>-7686396.441251528</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-5574601.398601398</v>
-      </c>
+        <v>8704756.216006216</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>1.656888111888108</v>
+      </c>
       <c r="BA2" t="n">
-        <v>-2.228811188811193</v>
+        <v>-0.5026953094892797</v>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>-0.5409925563644009</v>
+        <v>4.119131701631687</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -846,23 +870,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
         <v>120</v>
       </c>
-      <c r="D3" t="n">
-        <v>19</v>
-      </c>
-      <c r="E3" t="n">
-        <v>56</v>
-      </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -884,88 +908,110 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>227</v>
       </c>
       <c r="M3" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>10</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.833333333333333</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>77.52996632996633</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>72.2583164983165</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>6.962481244144342</v>
-      </c>
+        <v>73.75505050505051</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-1.206585081585075</v>
+        <v>-0.7301828035303686</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.6348484848484848</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>-0.184284836276815</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>439074.9110436016</v>
+      </c>
       <c r="AO3" t="n">
-        <v>0.5202832329242575</v>
+        <v>-0.8615549433731253</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.130471246356834</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.1167385776855951</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.384790209790207</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>-0.03491225385164776</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>3.495194367921655</v>
+      </c>
       <c r="AT3" t="n">
-        <v>4.949417249417237</v>
+        <v>2.322059086190109</v>
       </c>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>0.8569870725432338</v>
+      </c>
       <c r="AW3" t="n">
-        <v>9957761.567015752</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9822243.589743592</v>
-      </c>
+        <v>1519588.307315579</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>2.137437506376884</v>
+      </c>
       <c r="BA3" t="n">
-        <v>6.43292540792541</v>
+        <v>-1.143632007030398</v>
       </c>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-0.7737368355341303</v>
+        <v>5.39421997755332</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -974,29 +1020,29 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>fHO9ROsn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
       </c>
       <c r="H4" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1008,91 +1054,93 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>268</v>
       </c>
       <c r="N4" t="n">
-        <v>21</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3333333333333335</v>
+      </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>68.36101010101011</v>
+      </c>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="n">
-        <v>6.65528255319559</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-1.723636363636388</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.413636363636364</v>
-      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>0.8034183256357164</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10.73580513045731</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-0.1614972772799206</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.944545454545459</v>
-      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>6.882727272727266</v>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="n">
-        <v>21456964.51109277</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>34633181.81818182</v>
-      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>10.73</v>
-      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="n">
-        <v>3.738508599291208</v>
-      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
@@ -1100,29 +1148,29 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>WIX2NXnS</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
       </c>
       <c r="H5" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1134,40 +1182,44 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="M5" t="n">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="N5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1175,52 +1227,40 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>68</v>
+        <v>70.11099632690542</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>2.652878273568803</v>
-      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-0.3595041322314216</v>
+        <v>1.846021241830101</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1826446280991736</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>-0.1362484380259315</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.253094596035766</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-2.656239420804638</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.6157024793388466</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1183002.585200747</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>0.1685950413223054</v>
+        <v>-2.188481559290395</v>
       </c>
       <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="n">
-        <v>665603.2398855281</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1170785.123966942</v>
-      </c>
+      <c r="AV5" t="n">
+        <v>-3.775271942110166</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>0.3297520661156881</v>
+        <v>-0.003681139122313937</v>
       </c>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="n">
-        <v>-0.9744789585710301</v>
-      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
@@ -1228,23 +1268,23 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CSXdOfL8</t>
+          <t>GUXb5YQq</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1266,22 +1306,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="M6" t="n">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1292,12 +1332,8 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-2</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1306,54 +1342,52 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="n">
-        <v>70.95432098765433</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>7.001744382569882</v>
-      </c>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-0.2447727272727604</v>
+        <v>0.6062646367010984</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1490909090909092</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>0.003205128205128194</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>629586.6067515106</v>
+      </c>
       <c r="AO6" t="n">
-        <v>0.1671894927659499</v>
+        <v>0.170069930069932</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.721666220919303</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.166737703002326</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-2.370909090909091</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>3.230629370629359</v>
+      </c>
       <c r="AT6" t="n">
-        <v>6.274318181818174</v>
+        <v>0.8442656045180996</v>
       </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>2.294813853123202</v>
+      </c>
       <c r="AW6" t="n">
-        <v>1493340.43294634</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1122479.545454546</v>
-      </c>
+        <v>1234949.300699301</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>2.851538461538453</v>
+      </c>
       <c r="BA6" t="n">
-        <v>2.803409090909099</v>
+        <v>1.640996876033661</v>
       </c>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>-1.132070792965429</v>
+        <v>0.1604895104895832</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -1362,23 +1396,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CEhO9e6F</t>
+          <t>jqIIP2Cb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C7" t="n">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="F7" t="n">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1400,28 +1434,40 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="M7" t="n">
-        <v>267</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
@@ -1429,38 +1475,40 @@
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="n">
-        <v>2.291231304926953</v>
-      </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>0.1303978630065585</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.277944953597135</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.551512545425624</v>
-      </c>
+      <c r="AJ7" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>-1.60574633828503</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.1921886472660466</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1172488.039308473</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>-5.445755991514517</v>
+      </c>
       <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="n">
-        <v>1323139.105459758</v>
-      </c>
+      <c r="AV7" t="n">
+        <v>0.6453635734750236</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>4.376822901900301</v>
+      </c>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="n">
-        <v>5.859432234432237</v>
-      </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1468,23 +1516,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0IkylEqd</t>
+          <t>v5l07LdU</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.64583333334</v>
       </c>
       <c r="C8" t="n">
         <v>102</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -1506,95 +1554,97 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="M8" t="n">
-        <v>31</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="n">
+        <v>197</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>-5.5</v>
+      </c>
       <c r="Y8" t="n">
-        <v>0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.333333333333333</v>
+      </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-2</v>
+      </c>
       <c r="AI8" t="n">
-        <v>70.22027972027972</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>71.35525252525252</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.580513003488264</v>
-      </c>
+        <v>71.36363636363636</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>-0.9542312008979081</v>
+        <v>-0.5615689011843017</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.6704514426103572</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-1.212662816027915</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-0.6116161616161584</v>
-      </c>
+      <c r="AN8" t="n">
+        <v>343397.7694314232</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>1.187250280583626</v>
+        <v>0.05149080264465056</v>
       </c>
       <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>92685.09134085965</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>210329.0684624016</v>
-      </c>
+      <c r="AV8" t="n">
+        <v>3.5957191739884</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>0.3175308641975505</v>
+        <v>2.98596197961583</v>
       </c>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="n">
-        <v>-1.195239684436832</v>
-      </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
@@ -1602,29 +1652,29 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ptW4MYkL</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.5625</v>
       </c>
       <c r="C9" t="n">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>196</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
       </c>
       <c r="H9" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1636,63 +1686,103 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="M9" t="n">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
       <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>69.93658008658008</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>70.81818181818181</v>
+      </c>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>-0.4032480669210941</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.2676963131699428</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>7194801.438642818</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.6810553083280304</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.2407501589319769</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>2.17889383343929</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.620894635628929</v>
+      </c>
       <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>2.970661242011261</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5726916.719643994</v>
+      </c>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>3.160521296884937</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.7223782477123599</v>
+      </c>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>-0.0220597584234099</v>
+      </c>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
@@ -1700,29 +1790,29 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4QCyHCDr</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45536.5625</v>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
       </c>
       <c r="H10" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1734,23 +1824,27 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="M10" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -1770,50 +1864,52 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>73.36931818181819</v>
+      </c>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="n">
-        <v>-4.006217479006082</v>
-      </c>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>-1.69084175084177</v>
+        <v>2.06309416074123</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1049382716049383</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>0.3518154938743174</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>109509.2342298217</v>
+      </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1.137167125803487</v>
       </c>
       <c r="AP10" t="n">
-        <v>-3.527149144884021</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-0.2558478563100834</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.006722783389453</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+        <v>0.06717171717171722</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>0.7697199265381016</v>
+      </c>
       <c r="AT10" t="n">
-        <v>-4.333692480359161</v>
+        <v>-1.30920201802553</v>
       </c>
       <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-0.2322978546507812</v>
+      </c>
       <c r="AW10" t="n">
-        <v>-1446289.031374394</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-2743978.114478115</v>
-      </c>
+        <v>1205456.841138659</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>0.01675849403120822</v>
+      </c>
       <c r="BA10" t="n">
-        <v>-2.543052749719422</v>
+        <v>2.307398418574884</v>
       </c>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>0.7338007518792153</v>
+        <v>0.03514692378331574</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -1822,29 +1918,29 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CxyB0iT1</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45528.64583333334</v>
+        <v>45535.65625</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="F11" t="n">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
       </c>
       <c r="H11" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1856,26 +1952,26 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1886,14 +1982,14 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-1</v>
+      </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
@@ -1901,53 +1997,53 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>68.59876543209877</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>68.4549494949495</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-2.564590493376741</v>
-      </c>
+        <v>69.75646464646465</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>-0.7020202020202646</v>
+        <v>-2.187700848075508</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.02020202020202011</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>0.2388434164149267</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-6612572.174946629</v>
+      </c>
       <c r="AO11" t="n">
-        <v>0.1237123370456703</v>
+        <v>1.355117845117846</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1.559575786979153</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-0.9355128815092542</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-0.4055555555555515</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+        <v>-0.05974747474747488</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-4.206700336700337</v>
+      </c>
       <c r="AT11" t="n">
-        <v>-2.39444444444446</v>
+        <v>-2.744433455856779</v>
       </c>
       <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-0.006336433187115631</v>
+      </c>
       <c r="AW11" t="n">
-        <v>-596430.810332984</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>-1025555.555555556</v>
-      </c>
+        <v>-16150436.02693603</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>-2.970235690235697</v>
+      </c>
       <c r="BA11" t="n">
-        <v>-3.031313131313127</v>
+        <v>2.140680739148127</v>
       </c>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="n">
-        <v>1.158789198813356</v>
+        <v>-0.4791750841751536</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -1956,29 +2052,29 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.60416666666</v>
+        <v>45535.65625</v>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
         <v>77</v>
       </c>
       <c r="H12" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1990,20 +2086,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="M12" t="n">
-        <v>224</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
@@ -2025,51 +2123,51 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>67.01010101010101</v>
+        <v>71.46363636363637</v>
       </c>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="n">
-        <v>-6.924043655446681</v>
-      </c>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>-1.444141414141427</v>
+        <v>-2.867170628776876</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.1612121212121211</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
+        <v>0.4050622503798935</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12852004.18940369</v>
+      </c>
       <c r="AO12" t="n">
-        <v>-0.2075812569272655</v>
+        <v>1.932662993572084</v>
       </c>
       <c r="AP12" t="n">
-        <v>-4.904440942390195</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.9966628418519576</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.209696969696967</v>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+        <v>0.6715702479338848</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>6.929393939393961</v>
+      </c>
       <c r="AT12" t="n">
-        <v>-6.506464646464664</v>
+        <v>5.452440118182338</v>
       </c>
       <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>7.674773454964878</v>
+      </c>
       <c r="AW12" t="n">
-        <v>-2157500.636523966</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-2142594.94949495</v>
-      </c>
+        <v>31904977.50229568</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>11.01708907254361</v>
+      </c>
       <c r="BA12" t="n">
-        <v>-3.446868686868669</v>
+        <v>0.1806970496030011</v>
       </c>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="n">
-        <v>0.1388302979955292</v>
+        <v>-2.666124885215794</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -2078,29 +2176,29 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>21OYHBAk</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="G13" t="n">
         <v>77</v>
       </c>
       <c r="H13" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2112,36 +2210,48 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="M13" t="n">
-        <v>224</v>
+        <v>143</v>
       </c>
       <c r="N13" t="n">
-        <v>-17</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
@@ -2149,51 +2259,53 @@
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>73.43674242424242</v>
-      </c>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="n">
-        <v>-8.555568695573498</v>
-      </c>
+        <v>68.84302112029386</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>65.23113636363635</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.3419191919192031</v>
+        <v>3.016418804718029</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.743838383838384</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
+        <v>0.03067810691723749</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-112552.6400390235</v>
+      </c>
       <c r="AO13" t="n">
-        <v>-0.4287476892404425</v>
+        <v>3.65793388429752</v>
       </c>
       <c r="AP13" t="n">
-        <v>-7.878065401229648</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-0.1530747406109754</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-0.665252525252523</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+        <v>0.1599999999999999</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>-1.05801652892562</v>
+      </c>
       <c r="AT13" t="n">
-        <v>-8.633333333333326</v>
+        <v>-2.034431779162134</v>
       </c>
       <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>1.096276855061419</v>
+      </c>
       <c r="AW13" t="n">
-        <v>-18824955.94225509</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-32115520.20202021</v>
-      </c>
+        <v>-322703.305785124</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.8245454545454578</v>
+      </c>
       <c r="BA13" t="n">
-        <v>-10.72484848484848</v>
+        <v>1.326614171746698</v>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="n">
-        <v>0.6018855109821253</v>
+        <v>0.07289256198347971</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -2202,29 +2314,29 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dtLQNtsB</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C14" t="n">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
         <v>77</v>
       </c>
       <c r="H14" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2236,90 +2348,102 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="M14" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="N14" t="n">
-        <v>-23</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5</v>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="n">
-        <v>-4.647603690858261</v>
-      </c>
+      <c r="AI14" t="n">
+        <v>67.81784511784512</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>69.28451178451178</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>2.65136975818794</v>
+        <v>-0.5943565188943296</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.688544536271809</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
+        <v>0.007692307692307665</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>21057.38383152569</v>
+      </c>
       <c r="AO14" t="n">
-        <v>-0.7226153653968179</v>
+        <v>0.8344949494949496</v>
       </c>
       <c r="AP14" t="n">
-        <v>-5.645385867424679</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.09954191581329</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>-1.748974594429139</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+        <v>0.01909090909090905</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>0.2036139169472619</v>
+      </c>
       <c r="AT14" t="n">
-        <v>-2.707698194061834</v>
+        <v>0.4827192859263789</v>
       </c>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>-0.3432954316214989</v>
+      </c>
       <c r="AW14" t="n">
-        <v>-12931898.87869197</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>-13061801.34680135</v>
-      </c>
+        <v>121939.6745230076</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>0.5888945005611674</v>
+      </c>
       <c r="BA14" t="n">
-        <v>-4.157790021426379</v>
+        <v>-0.6135342653786608</v>
       </c>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
-        <v>-1.110334613348563</v>
+        <v>0.9247586980920346</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -2328,23 +2452,23 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>CGH1PgIF</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45527.64583333334</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
         <v>77</v>
@@ -2366,86 +2490,116 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>126</v>
+        <v>202</v>
       </c>
       <c r="M15" t="n">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>-1</v>
       </c>
-      <c r="P15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>8</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-4</v>
+      </c>
       <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="n">
-        <v>0.1792291262471082</v>
-      </c>
+      <c r="AJ15" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>3.314233241505974</v>
+        <v>-0.4234691856377708</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="inlineStr"/>
+        <v>0.009889879719607864</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1763444.435769465</v>
+      </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>-1.058992522628884</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.431862519464616</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>4.732712034139325</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>-1.708631772268138</v>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+        <v>0.1431523022432115</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>3.995461104552021</v>
+      </c>
       <c r="AT15" t="n">
-        <v>0.7447199265380959</v>
+        <v>4.053392916250601</v>
       </c>
       <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>0.5672157407175575</v>
+      </c>
       <c r="AW15" t="n">
-        <v>-195391.3025693221</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>56919.19191919174</v>
-      </c>
+        <v>3330516.200970747</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>3.479030565394197</v>
+      </c>
       <c r="BA15" t="n">
-        <v>-0.5790633608815483</v>
+        <v>-3.126810362836284</v>
       </c>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
-        <v>-0.4125488396019783</v>
+        <v>0.9280467007739901</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -2454,29 +2608,29 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>Ofy73Ced</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45535.64583333334</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="F16" t="n">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
         <v>77</v>
       </c>
       <c r="H16" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2488,88 +2642,122 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1</v>
+      </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>68.88834498834498</v>
+      </c>
       <c r="AJ16" t="n">
-        <v>68.15454545454546</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>8.91534620783159</v>
-      </c>
+        <v>70.40206611570247</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
-        <v>4.950882759216114</v>
+        <v>-0.1571226415334195</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.7411313994647331</v>
-      </c>
-      <c r="AN16" t="inlineStr"/>
+        <v>0.1033411033411034</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>392906.2785041046</v>
+      </c>
       <c r="AO16" t="n">
-        <v>0.5431710215183396</v>
+        <v>-0.3345454545454487</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.535526614950712</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.6247532497825148</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.05622248122247342</v>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>3.228863636363641</v>
+      </c>
       <c r="AT16" t="n">
-        <v>10.44818052318054</v>
+        <v>2.983839215026862</v>
       </c>
       <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>2.389816165930014</v>
+      </c>
       <c r="AW16" t="n">
-        <v>13065393.51073116</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>26936113.7011137</v>
-      </c>
+        <v>486420.4545454546</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
       <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
+      <c r="AZ16" t="n">
+        <v>2.455227272727285</v>
+      </c>
       <c r="BA16" t="n">
-        <v>9.424369766036421</v>
+        <v>-0.1612262573641274</v>
       </c>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="n">
-        <v>-1.225805823739964</v>
+        <v>-1.471136363636361</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -2578,23 +2766,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45523.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C17" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>77</v>
@@ -2616,19 +2804,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>102</v>
+        <v>227</v>
       </c>
       <c r="M17" t="n">
-        <v>239</v>
+        <v>55</v>
       </c>
       <c r="N17" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -2644,58 +2832,66 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="n">
-        <v>-4.006907119017484</v>
-      </c>
+      <c r="AI17" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>78.55727272727272</v>
+      </c>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>-2.540559440559434</v>
+        <v>2.608819499205111</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.5398601398601401</v>
-      </c>
-      <c r="AN17" t="inlineStr"/>
+        <v>0.08860531051440135</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>4056428.43130108</v>
+      </c>
       <c r="AO17" t="n">
-        <v>-0.3007820680496265</v>
+        <v>-0.5396694214876092</v>
       </c>
       <c r="AP17" t="n">
-        <v>-6.720152785774857</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>-3.919959208634737</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>-1.790209790209794</v>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+        <v>0.2487603305785127</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>3.471074380165291</v>
+      </c>
       <c r="AT17" t="n">
-        <v>-3.841258741258741</v>
+        <v>3.2976648587683</v>
       </c>
       <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>1.70564804196151</v>
+      </c>
       <c r="AW17" t="n">
-        <v>-10821912.99744477</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>-13582692.30769231</v>
-      </c>
+        <v>6752975.206611572</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
+      <c r="AZ17" t="n">
+        <v>2.997520661157012</v>
+      </c>
       <c r="BA17" t="n">
-        <v>-6.152447552447555</v>
+        <v>-1.770989053092499</v>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="n">
-        <v>-2.124285181064444</v>
+        <v>1.377685950413223</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -2704,23 +2900,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C18" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="G18" t="n">
         <v>77</v>
@@ -2742,22 +2938,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>241</v>
+        <v>95</v>
       </c>
       <c r="M18" t="n">
         <v>250</v>
       </c>
       <c r="N18" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="O18" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2778,50 +2974,52 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>76.90000000000001</v>
+      </c>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="n">
-        <v>-6.053703107237581</v>
-      </c>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>1.793636363636324</v>
+        <v>-0.6918096398586613</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="AN18" t="inlineStr"/>
+        <v>-0.115765413542434</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-55628.53160742205</v>
+      </c>
       <c r="AO18" t="n">
-        <v>-0.8262053527570767</v>
+        <v>-1.355371900826444</v>
       </c>
       <c r="AP18" t="n">
-        <v>-5.902823074116185</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.2795260199570748</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>-0.9372727272727275</v>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+        <v>-0.1735537190082646</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>2.010330578512409</v>
+      </c>
       <c r="AT18" t="n">
-        <v>-4.859999999999999</v>
+        <v>0.6088112887330226</v>
       </c>
       <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>-1.924883999294309</v>
+      </c>
       <c r="AW18" t="n">
-        <v>-13687718.22168891</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>-17727272.72727273</v>
-      </c>
+        <v>1595247.933884298</v>
+      </c>
+      <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
+      <c r="AZ18" t="n">
+        <v>-0.1632231404958731</v>
+      </c>
       <c r="BA18" t="n">
-        <v>-6.484545454545454</v>
+        <v>-2.628120443981942</v>
       </c>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="n">
-        <v>0.5211965110240939</v>
+        <v>-0.1508264462809734</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -2830,29 +3028,29 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>v3JgRFm3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45535.54166666666</v>
       </c>
       <c r="C19" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>193</v>
       </c>
       <c r="G19" t="n">
         <v>77</v>
       </c>
       <c r="H19" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2864,92 +3062,122 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="M19" t="n">
-        <v>151</v>
+        <v>268</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65.23113636363635</v>
+      </c>
       <c r="AJ19" t="n">
-        <v>67.02000000000001</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>7.357223343262774</v>
-      </c>
+        <v>68.74000000000001</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>-0.7963157213157217</v>
+        <v>4.25835980379307</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.7381313131313132</v>
-      </c>
-      <c r="AN19" t="inlineStr"/>
+        <v>0.1434532906818879</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1175266.567317234</v>
+      </c>
       <c r="AO19" t="n">
-        <v>0.7523791514378557</v>
+        <v>-3.484213345576986</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.97950453202256</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.4738651437846215</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.876120176120175</v>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+        <v>0.118855218855219</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>4.663414447505346</v>
+      </c>
       <c r="AT19" t="n">
-        <v>5.194030044030029</v>
+        <v>5.095660807443849</v>
       </c>
       <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>3.689121875473504</v>
+      </c>
       <c r="AW19" t="n">
-        <v>14583889.23023524</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>15428060.08806009</v>
-      </c>
+        <v>714439.8530762163</v>
+      </c>
+      <c r="AX19" t="inlineStr"/>
       <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
+      <c r="AZ19" t="n">
+        <v>0.6862871135598283</v>
+      </c>
       <c r="BA19" t="n">
-        <v>7.51061901061901</v>
+        <v>-0.333847904611801</v>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="n">
-        <v>0.5301586758896164</v>
+        <v>2.552800734618984</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
@@ -2958,29 +3186,29 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45534.65625</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E20" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
         <v>77</v>
       </c>
       <c r="H20" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2992,23 +3220,27 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="O20" t="n">
+        <v>5</v>
+      </c>
       <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3020,8 +3252,12 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+      <c r="AA20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
@@ -3029,51 +3265,53 @@
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>67.42323232323233</v>
-      </c>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="n">
-        <v>-0.1280161534443494</v>
-      </c>
+        <v>72.01859504132231</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>73.98212809917356</v>
+      </c>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.58727272727279</v>
+        <v>-4.156263204474328</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0.1490909090909092</v>
-      </c>
-      <c r="AN20" t="inlineStr"/>
+        <v>0.5199947734575063</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>10845701.11836059</v>
+      </c>
       <c r="AO20" t="n">
-        <v>-0.1671894927659499</v>
+        <v>2.077012987012989</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1.195485655898793</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.250187716378093</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0.3909090909090907</v>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+        <v>0.8655844155844155</v>
+      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>3.15220779220779</v>
+      </c>
       <c r="AT20" t="n">
-        <v>1.475454545454568</v>
+        <v>2.648070815198139</v>
       </c>
       <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
+      <c r="AV20" t="n">
+        <v>4.162812977797444</v>
+      </c>
       <c r="AW20" t="n">
-        <v>49983.43124821316</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>2195000</v>
-      </c>
+        <v>21244220.77922078</v>
+      </c>
+      <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>4.614415584415582</v>
+      </c>
       <c r="BA20" t="n">
-        <v>2.987272727272739</v>
+        <v>1.753072090435442</v>
       </c>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="n">
-        <v>-1.686118138501239</v>
+        <v>-4.230779220779198</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -3082,29 +3320,29 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>IXMN9zkI</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45534.5625</v>
       </c>
       <c r="C21" t="n">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="F21" t="n">
-        <v>199</v>
+        <v>72</v>
       </c>
       <c r="G21" t="n">
         <v>77</v>
       </c>
       <c r="H21" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -3116,19 +3354,27 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="M21" t="n">
-        <v>267</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3149,37 +3395,51 @@
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="n">
-        <v>-2.31823826334697</v>
-      </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
+      <c r="AJ21" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="n">
+        <v>-3.10065423739232</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-0.1334582573507423</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-4157362.913029947</v>
+      </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>-0.8064016791289532</v>
       </c>
       <c r="AP21" t="n">
-        <v>-6.170239533011269</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.5929347826087223</v>
-      </c>
+        <v>-0.246904105995015</v>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-4.753286107831556</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-3.72729458120898</v>
+      </c>
       <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
+      <c r="AV21" t="n">
+        <v>-4.433871272480388</v>
+      </c>
       <c r="AW21" t="n">
-        <v>-817326.8301746562</v>
+        <v>-10488754.09943592</v>
       </c>
       <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>-6.152676111767036</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.715711899095858</v>
+      </c>
       <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="n">
-        <v>-3.009571256038647</v>
+        <v>-1.38650793650794</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -3188,23 +3448,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C22" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="G22" t="n">
         <v>77</v>
@@ -3226,10 +3486,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="M22" t="n">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -3256,49 +3516,25 @@
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="n">
-        <v>-6.384684417096963</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>-5.110399449035839</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>-0.2272727272727273</v>
-      </c>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="n">
-        <v>-0.1262877158379407</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>-4.661759441208474</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>-5.453919881759077</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.088016528925614</v>
-      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="n">
-        <v>-6.625068870523407</v>
-      </c>
+      <c r="AT22" t="inlineStr"/>
       <c r="AU22" t="inlineStr"/>
       <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="n">
-        <v>-2772414.687150819</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>-4028078.512396694</v>
-      </c>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="n">
-        <v>-5.686088154269981</v>
-      </c>
+      <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="n">
-        <v>1.42665827851236</v>
-      </c>
+      <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
@@ -3306,14 +3542,14 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C23" t="n">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="D23" t="n">
         <v>34</v>
@@ -3322,7 +3558,7 @@
         <v>135</v>
       </c>
       <c r="F23" t="n">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
         <v>77</v>
@@ -3344,57 +3580,95 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="M23" t="n">
-        <v>267</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>162</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-12</v>
+      </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Z23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-3</v>
+      </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-4</v>
+      </c>
       <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AJ23" t="n">
+        <v>70.7</v>
+      </c>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
+      <c r="AL23" t="n">
+        <v>2.564346678962039</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1186289.730568577</v>
+      </c>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
       <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
+      <c r="AT23" t="n">
+        <v>2.798509197355344</v>
+      </c>
       <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
+      <c r="AV23" t="n">
+        <v>2.423725270456046</v>
+      </c>
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
+      <c r="BA23" t="n">
+        <v>-1.408184201838051</v>
+      </c>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="n">
@@ -3404,14 +3678,14 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45532.64583333334</v>
       </c>
       <c r="C24" t="n">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="D24" t="n">
         <v>77</v>
@@ -3420,7 +3694,7 @@
         <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="G24" t="n">
         <v>77</v>
@@ -3442,86 +3716,118 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="M24" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
       </c>
       <c r="O24" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
       <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB24" t="n">
         <v>-2</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="n">
-        <v>-0.2796706844774519</v>
-      </c>
+      <c r="AE24" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>69.45454545454545</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>68.81666666666666</v>
+      </c>
+      <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="n">
-        <v>-3.599145299145277</v>
+        <v>-2.712272157580998</v>
       </c>
       <c r="AM24" t="n">
-        <v>-0.08671328671328693</v>
-      </c>
-      <c r="AN24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>263943.1809475925</v>
+      </c>
       <c r="AO24" t="n">
-        <v>-0.1303978630065585</v>
+        <v>0.18949494949495</v>
       </c>
       <c r="AP24" t="n">
-        <v>-2.919958248943772</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>-3.177685384931834</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>-0.7808857808857823</v>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="n">
+        <v>-0.9871717171717052</v>
+      </c>
       <c r="AT24" t="n">
-        <v>-1.544366744366741</v>
+        <v>1.490177326486162</v>
       </c>
       <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
+      <c r="AV24" t="n">
+        <v>1.932301246139474</v>
+      </c>
       <c r="AW24" t="n">
-        <v>-619920.9984638728</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>-596305.3613053614</v>
-      </c>
+        <v>-286823.2323232321</v>
+      </c>
+      <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
+      <c r="AZ24" t="n">
+        <v>-0.604848484848489</v>
+      </c>
       <c r="BA24" t="n">
-        <v>-1.568065268065254</v>
+        <v>-0.1610907371495607</v>
       </c>
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="n">
-        <v>-2.92950504228282</v>
+        <v>-0.9985858585858978</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -3530,29 +3836,29 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="E25" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="G25" t="n">
         <v>77</v>
       </c>
       <c r="H25" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3564,121 +3870,147 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="M25" t="n">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="N25" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-4</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-5</v>
       </c>
-      <c r="Q25" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AA25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2</v>
+      </c>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2</v>
+      </c>
       <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="n">
-        <v>-3.793878229899889</v>
-      </c>
+      <c r="AJ25" t="n">
+        <v>66.88888888888889</v>
+      </c>
+      <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>1.971818181818179</v>
+        <v>-5.494154506232803</v>
       </c>
       <c r="AM25" t="n">
-        <v>-0.5736363636363637</v>
-      </c>
-      <c r="AN25" t="inlineStr"/>
+        <v>-0.1215800623802874</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-2673137.165405254</v>
+      </c>
       <c r="AO25" t="n">
-        <v>-0.5118471684261157</v>
+        <v>2.221678910315273</v>
       </c>
       <c r="AP25" t="n">
-        <v>-5.24970640384727</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.910730703478436</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>-1.259090909090911</v>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+        <v>-0.1980104071013165</v>
+      </c>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="n">
+        <v>-6.714929599020508</v>
+      </c>
       <c r="AT25" t="n">
-        <v>-6.010909090909095</v>
+        <v>-7.75966074176533</v>
       </c>
       <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
+      <c r="AV25" t="n">
+        <v>-5.439365194955528</v>
+      </c>
       <c r="AW25" t="n">
-        <v>-12428700.10498474</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>-30504409.09090909</v>
-      </c>
+        <v>-3873503.21395776</v>
+      </c>
+      <c r="AX25" t="inlineStr"/>
       <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
+      <c r="AZ25" t="n">
+        <v>-5.157361493725119</v>
+      </c>
       <c r="BA25" t="n">
-        <v>-7.815454545454557</v>
+        <v>1.388786909409102</v>
       </c>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="n">
-        <v>-0.835851507453679</v>
+        <v>-5.406978879706202</v>
       </c>
       <c r="BD25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>tWk1tTtf</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C26" t="n">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="G26" t="n">
         <v>77</v>
       </c>
       <c r="H26" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3690,26 +4022,26 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="M26" t="n">
-        <v>266</v>
+        <v>143</v>
       </c>
       <c r="N26" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>1</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3732,48 +4064,48 @@
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="n">
-        <v>3.279644234116674</v>
-      </c>
+      <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>-1.303305785123939</v>
+        <v>0.08227620610978192</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.2140495867768599</v>
-      </c>
-      <c r="AN26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-142996.2812175332</v>
+      </c>
       <c r="AO26" t="n">
-        <v>0.130071290563269</v>
+        <v>0.6042975206611523</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.3268449268749833</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.444302914581556</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>-0.4537190082644642</v>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="n">
+        <v>-2.220516528925614</v>
+      </c>
       <c r="AT26" t="n">
-        <v>2.566115702479351</v>
+        <v>-3.316718350883505</v>
       </c>
       <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
+      <c r="AV26" t="n">
+        <v>-0.08756875544723641</v>
+      </c>
       <c r="AW26" t="n">
-        <v>3760315.510724925</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>6059318.181818182</v>
-      </c>
+        <v>-281501.0330578513</v>
+      </c>
+      <c r="AX26" t="inlineStr"/>
       <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
+      <c r="AZ26" t="n">
+        <v>-1.814318181818194</v>
+      </c>
       <c r="BA26" t="n">
-        <v>1.724793388429745</v>
+        <v>2.428790630744093</v>
       </c>
       <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="n">
-        <v>-2.367817123022178</v>
+        <v>0.9249380165289267</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -3782,29 +4114,29 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>v3ivyY4E</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>143</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="G27" t="n">
         <v>77</v>
       </c>
       <c r="H27" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3816,27 +4148,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="M27" t="n">
-        <v>163</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -3848,61 +4172,57 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AA27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-3</v>
+      </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="n">
-        <v>67.51060606060607</v>
-      </c>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="n">
-        <v>-2.060821593865057</v>
-      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.114049586776872</v>
+        <v>-4.449884398760815</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.3165289256198347</v>
-      </c>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="n">
-        <v>-0.1353895862591517</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>-1.635386095386096</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.1535870731522664</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.04876033057851359</v>
-      </c>
+        <v>-0.03067810691723749</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-223429.3110038533</v>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
-        <v>-1.581818181818178</v>
+        <v>1.278276253029105</v>
       </c>
       <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="n">
-        <v>-1355417.911597259</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>-2739586.776859504</v>
-      </c>
+      <c r="AV27" t="n">
+        <v>-3.031588533637731</v>
+      </c>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
-        <v>-0.9380165289256155</v>
+        <v>-2.505796144613079</v>
       </c>
       <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="n">
-        <v>-0.4431689164297872</v>
-      </c>
+      <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
@@ -3910,29 +4230,29 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>Eql9v7B6</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C28" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="G28" t="n">
         <v>77</v>
       </c>
       <c r="H28" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -3944,90 +4264,122 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>serie a</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="M28" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>-1</v>
+      </c>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="n">
-        <v>6.047473147137211</v>
-      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>65.46250000000001</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>65.625</v>
+      </c>
+      <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>-1.817373737373714</v>
+        <v>-0.2033715057769712</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.5603030303030303</v>
-      </c>
-      <c r="AN28" t="inlineStr"/>
+        <v>0.04192980102860311</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>623686.1709878943</v>
+      </c>
       <c r="AO28" t="n">
-        <v>0.3394183358208125</v>
+        <v>1.153259871441701</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.231001319944824</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>-0.243652360568035</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>-0.4493939393939463</v>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+        <v>0.1273645546372819</v>
+      </c>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="n">
+        <v>1.611570247933898</v>
+      </c>
       <c r="AT28" t="n">
-        <v>4.8531313131313</v>
+        <v>1.067352160186346</v>
       </c>
       <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
+      <c r="AV28" t="n">
+        <v>0.9340753682536018</v>
+      </c>
       <c r="AW28" t="n">
-        <v>15394079.72707261</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>21702176.76767677</v>
-      </c>
+        <v>1082020.202020202</v>
+      </c>
+      <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
+      <c r="AZ28" t="n">
+        <v>2.363728191000931</v>
+      </c>
       <c r="BA28" t="n">
-        <v>4.536565656565656</v>
+        <v>-0.2491396538879407</v>
       </c>
       <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="n">
-        <v>-0.5295242175838091</v>
+        <v>1.03278236914602</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -4036,23 +4388,23 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>W0WITkcl</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="F29" t="n">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="G29" t="n">
         <v>77</v>
@@ -4074,22 +4426,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="M29" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="N29" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -4112,50 +4464,50 @@
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="n">
-        <v>80.78818181818183</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>-0.8927444784876712</v>
-      </c>
+        <v>65.77777777777777</v>
+      </c>
+      <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>-0.9442424242424465</v>
+        <v>1.435461877304022</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.1599999999999999</v>
-      </c>
-      <c r="AN29" t="inlineStr"/>
+        <v>-0.1033411033411034</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>-373444.4320007476</v>
+      </c>
       <c r="AO29" t="n">
-        <v>0.02882625506538572</v>
+        <v>-0.169040404040409</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.5109650575432312</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.52630408928681</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.817676767676772</v>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="n">
+        <v>-1.76179573512907</v>
+      </c>
       <c r="AT29" t="n">
-        <v>-0.4752525252525288</v>
+        <v>-1.639849527665319</v>
       </c>
       <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
+      <c r="AV29" t="n">
+        <v>-1.662199781699783</v>
+      </c>
       <c r="AW29" t="n">
-        <v>-50945.92457868892</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>-270019.1919191917</v>
-      </c>
+        <v>-377121.4927048259</v>
+      </c>
+      <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
+      <c r="AZ29" t="n">
+        <v>-1.158894500561161</v>
+      </c>
       <c r="BA29" t="n">
-        <v>0.8898989898989953</v>
+        <v>-0.6523446222393616</v>
       </c>
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="n">
-        <v>0.1672802960851527</v>
+        <v>0.8706958473625548</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -4164,23 +4516,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>EL5MmBlK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C30" t="n">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="F30" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="G30" t="n">
         <v>77</v>
@@ -4202,88 +4554,118 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="N30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-2</v>
+      </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+        <v>-21</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-1</v>
+      </c>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AI30" t="n">
-        <v>68.59876543209877</v>
-      </c>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="n">
-        <v>6.39161779276796</v>
-      </c>
+        <v>68.98333333333333</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>74.31363636363636</v>
+      </c>
+      <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>1.008092031425349</v>
+        <v>1.831351731595447</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.3212121212121211</v>
-      </c>
-      <c r="AN30" t="inlineStr"/>
+        <v>-0.007692307692307665</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1250288.837032507</v>
+      </c>
       <c r="AO30" t="n">
-        <v>0.2364075119926512</v>
+        <v>-2.720376492194671</v>
       </c>
       <c r="AP30" t="n">
-        <v>5.267080425078873</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.4046196033068838</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>-0.1485858585858537</v>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+        <v>-0.01909090909090905</v>
+      </c>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="n">
+        <v>5.700752984389325</v>
+      </c>
       <c r="AT30" t="n">
-        <v>6.621896745230103</v>
+        <v>4.796585177400914</v>
       </c>
       <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
+      <c r="AV30" t="n">
+        <v>2.204362900543472</v>
+      </c>
       <c r="AW30" t="n">
-        <v>2109283.78822416</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2025760.381593715</v>
-      </c>
+        <v>2556151.40036731</v>
+      </c>
+      <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
+      <c r="AZ30" t="n">
+        <v>2.994632690541778</v>
+      </c>
       <c r="BA30" t="n">
-        <v>4.644399551066215</v>
+        <v>-1.741312966519992</v>
       </c>
       <c r="BB30" t="inlineStr"/>
       <c r="BC30" t="n">
-        <v>-0.04906580691410056</v>
+        <v>0.4269605142332011</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -4292,23 +4674,23 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>YPSZP7dD</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45531.64583333334</v>
       </c>
       <c r="C31" t="n">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="F31" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="G31" t="n">
         <v>77</v>
@@ -4330,59 +4712,119 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="M31" t="n">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-1</v>
+      </c>
       <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>67.89545454545454</v>
+      </c>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
+      <c r="AL31" t="n">
+        <v>2.675590233411555</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.1152906100111069</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>39575.8281407766</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.6314019314019284</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.07337662337662332</v>
+      </c>
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
+      <c r="AS31" t="n">
+        <v>-1.676834276834285</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>-0.3319505223148127</v>
+      </c>
       <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
+      <c r="AV31" t="n">
+        <v>1.094801035438891</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>-585389.0553890555</v>
+      </c>
       <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
+      <c r="AZ31" t="n">
+        <v>-0.9471805971805907</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.502685332487058</v>
+      </c>
       <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr"/>
+      <c r="BC31" t="n">
+        <v>2.748240648240568</v>
+      </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
@@ -4390,29 +4832,29 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45530.65625</v>
       </c>
       <c r="C32" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E32" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="F32" t="n">
-        <v>178</v>
+        <v>42</v>
       </c>
       <c r="G32" t="n">
         <v>77</v>
       </c>
       <c r="H32" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4424,26 +4866,26 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="M32" t="n">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>-17</v>
       </c>
       <c r="O32" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P32" t="n">
         <v>-1</v>
       </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
       <c r="Q32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4464,52 +4906,52 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="n">
-        <v>71.34686868686867</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>-0.0003939578939622379</v>
-      </c>
+      <c r="AI32" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>-0.7754208754208776</v>
+        <v>-1.080363464402353</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.08473625140291818</v>
-      </c>
-      <c r="AN32" t="inlineStr"/>
+        <v>-0.7067397751837112</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>-12433420.79729322</v>
+      </c>
       <c r="AO32" t="n">
-        <v>0.1237123370456703</v>
+        <v>-0.579377693014056</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.849104455215567</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>-2.895334973668355</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>-0.2389450056116686</v>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+        <v>-0.6155612064702973</v>
+      </c>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="n">
+        <v>-7.176087801087803</v>
+      </c>
       <c r="AT32" t="n">
-        <v>-0.4277216610550028</v>
+        <v>-6.225626207845892</v>
       </c>
       <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
+      <c r="AV32" t="n">
+        <v>-5.673591925914579</v>
+      </c>
       <c r="AW32" t="n">
-        <v>277843.2362390696</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>-175168.3501683499</v>
-      </c>
+        <v>-25192682.06540934</v>
+      </c>
+      <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
+      <c r="AZ32" t="n">
+        <v>-7.201993713357325</v>
+      </c>
       <c r="BA32" t="n">
-        <v>-1.175533108866446</v>
+        <v>-0.5777851299476033</v>
       </c>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="n">
-        <v>2.68650828595273</v>
+        <v>-2.204960443596804</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -4518,23 +4960,23 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C33" t="n">
+        <v>63</v>
+      </c>
+      <c r="D33" t="n">
         <v>85</v>
       </c>
-      <c r="D33" t="n">
-        <v>36</v>
-      </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F33" t="n">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="G33" t="n">
         <v>77</v>
@@ -4556,86 +4998,118 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="M33" t="n">
-        <v>239</v>
+        <v>148</v>
       </c>
       <c r="N33" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
+      <c r="W33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-4</v>
+      </c>
       <c r="AI33" t="n">
-        <v>70.45454545454545</v>
-      </c>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="n">
-        <v>-5.633068960583032</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>74.54166666666666</v>
+      </c>
+      <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>1.212878787878822</v>
+        <v>-0.4597616508650901</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.5702020202020202</v>
-      </c>
-      <c r="AN33" t="inlineStr"/>
+        <v>-0.07716868061695648</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>-109549.4378609895</v>
+      </c>
       <c r="AO33" t="n">
-        <v>-0.4583960897606372</v>
+        <v>-0.4565962656871747</v>
       </c>
       <c r="AP33" t="n">
-        <v>-6.312907035033803</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>2.82915065220584</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>-1.58510101010101</v>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+        <v>0.09731915110703016</v>
+      </c>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="n">
+        <v>2.205938169574537</v>
+      </c>
       <c r="AT33" t="n">
-        <v>-3.98989898989899</v>
+        <v>1.783415773243377</v>
       </c>
       <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
+      <c r="AV33" t="n">
+        <v>-0.1105118521325323</v>
+      </c>
       <c r="AW33" t="n">
-        <v>-9242613.455347564</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>-9545328.282828284</v>
-      </c>
+        <v>249960.2081420254</v>
+      </c>
+      <c r="AX33" t="inlineStr"/>
       <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
+      <c r="AZ33" t="n">
+        <v>0.9969416386082912</v>
+      </c>
       <c r="BA33" t="n">
-        <v>-6.529040404040401</v>
+        <v>-0.7765857807581895</v>
       </c>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="n">
-        <v>-0.1219726254633287</v>
+        <v>3.286781961024388</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -4644,23 +5118,23 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C34" t="n">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E34" t="n">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>77</v>
@@ -4682,22 +5156,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="M34" t="n">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="N34" t="n">
-        <v>-19</v>
+        <v>11</v>
       </c>
       <c r="O34" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4719,51 +5193,51 @@
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>63.375</v>
+        <v>67.8</v>
       </c>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="n">
-        <v>-7.397116684111566</v>
-      </c>
+      <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>1.223636363636416</v>
+        <v>-3.537998793449106</v>
       </c>
       <c r="AM34" t="n">
-        <v>-1.234297520661157</v>
-      </c>
-      <c r="AN34" t="inlineStr"/>
+        <v>0.3104683394598959</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>8268656.74503216</v>
+      </c>
       <c r="AO34" t="n">
-        <v>-0.4773903306128366</v>
+        <v>1.738016528925623</v>
       </c>
       <c r="AP34" t="n">
-        <v>-8.692263711944022</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>2.42218493744582</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>-1.90487603305785</v>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+        <v>0.4479338842975209</v>
+      </c>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="n">
+        <v>2.890909090909091</v>
+      </c>
       <c r="AT34" t="n">
-        <v>-7.187685950413211</v>
+        <v>1.009442190711397</v>
       </c>
       <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
+      <c r="AV34" t="n">
+        <v>4.50303342235604</v>
+      </c>
       <c r="AW34" t="n">
-        <v>-20456591.8585535</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>-33939380.16528925</v>
-      </c>
+        <v>23846033.05785124</v>
+      </c>
+      <c r="AX34" t="inlineStr"/>
       <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
+      <c r="AZ34" t="n">
+        <v>5.646280991735537</v>
+      </c>
       <c r="BA34" t="n">
-        <v>-9.794462809917363</v>
+        <v>1.826825898487471</v>
       </c>
       <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="n">
-        <v>-0.5637997948816391</v>
+        <v>-3.307438016528891</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -4772,29 +5246,29 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45520.64583333334</v>
+        <v>45529.65625</v>
       </c>
       <c r="C35" t="n">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="D35" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E35" t="n">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="F35" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>77</v>
       </c>
       <c r="H35" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4806,26 +5280,26 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="M35" t="n">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="N35" t="n">
-        <v>-5</v>
+        <v>17</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4836,12 +5310,8 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4850,54 +5320,50 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="n">
-        <v>69.98601398601399</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>69.889898989899</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>-2.283436038747027</v>
-      </c>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>-0.06848484848492831</v>
+        <v>0.6679386916010515</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="inlineStr"/>
+        <v>0.8497862631908168</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>14672747.01003867</v>
+      </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>0.8453305785123959</v>
       </c>
       <c r="AP35" t="n">
-        <v>-4.268141187647913</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>-0.02491778261256172</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>-0.8424242424242401</v>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+        <v>1.054669421487604</v>
+      </c>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="n">
+        <v>4.594710743801642</v>
+      </c>
       <c r="AT35" t="n">
-        <v>-3.158484848484846</v>
+        <v>5.816963620334761</v>
       </c>
       <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
+      <c r="AV35" t="n">
+        <v>6.701296206360141</v>
+      </c>
       <c r="AW35" t="n">
-        <v>-817667.002276741</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>-1147527.272727273</v>
-      </c>
+        <v>16962179.75206611</v>
+      </c>
+      <c r="AX35" t="inlineStr"/>
       <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
+      <c r="AZ35" t="n">
+        <v>6.427520661157004</v>
+      </c>
       <c r="BA35" t="n">
-        <v>-3.434545454545443</v>
+        <v>0.4927709267273741</v>
       </c>
       <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="n">
-        <v>-1.673615830566604</v>
+        <v>-1.853450413223101</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -4906,32 +5372,32 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>KvdW7ZzS</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45516.67708333334</v>
+        <v>45529.64583333334</v>
       </c>
       <c r="C36" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E36" t="n">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="G36" t="n">
         <v>77</v>
       </c>
       <c r="H36" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -4940,14 +5406,14 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="M36" t="n">
-        <v>267</v>
+        <v>151</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -4973,38 +5439,40 @@
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="n">
-        <v>3.53269609700645</v>
-      </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="n">
-        <v>0.1367241379310347</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>8.537350637867881</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>3.347430845017044</v>
-      </c>
+      <c r="AJ36" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="n">
+        <v>-0.1865268620268523</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>385934.4042531543</v>
+      </c>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="inlineStr"/>
       <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>-2.476695767195764</v>
+      </c>
       <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="n">
-        <v>1939007.06707086</v>
-      </c>
+      <c r="AV36" t="n">
+        <v>3.786026251526252</v>
+      </c>
+      <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
+      <c r="BA36" t="n">
+        <v>5.199494098494096</v>
+      </c>
       <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="n">
-        <v>4.417824302134647</v>
-      </c>
+      <c r="BC36" t="inlineStr"/>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
@@ -5012,32 +5480,32 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>hCxNBHy3</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45529.64583333334</v>
       </c>
       <c r="C37" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="G37" t="n">
         <v>77</v>
       </c>
       <c r="H37" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -5046,91 +5514,89 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="M37" t="n">
-        <v>38</v>
-      </c>
-      <c r="N37" t="n">
+        <v>268</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-13</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>-4</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+      <c r="X37" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
+      <c r="AE37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>71.36363636363636</v>
+      </c>
       <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="n">
-        <v>5.091865286015448</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.820437710437716</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.2162738496071828</v>
-      </c>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="n">
-        <v>0.2364075119926512</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>6.078070922236037</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>-0.3674574554368633</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>-0.2127833894500526</v>
-      </c>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="n">
-        <v>4.242884399551087</v>
-      </c>
+      <c r="AT37" t="inlineStr"/>
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="n">
-        <v>2073205.741178613</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1518291.245791246</v>
-      </c>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="n">
-        <v>2.748103254769902</v>
-      </c>
+      <c r="BA37" t="inlineStr"/>
       <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="n">
-        <v>1.000277134095501</v>
-      </c>
+      <c r="BC37" t="inlineStr"/>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
@@ -5138,57 +5604,61 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45516.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C38" t="n">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D38" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F38" t="n">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="G38" t="n">
         <v>77</v>
       </c>
       <c r="H38" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>186</v>
+      </c>
+      <c r="M38" t="n">
+        <v>204</v>
+      </c>
+      <c r="N38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>102</v>
-      </c>
-      <c r="M38" t="n">
-        <v>267</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
       <c r="P38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -5209,37 +5679,51 @@
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="n">
-        <v>4.621695348130132</v>
-      </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
+      <c r="AJ38" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="n">
+        <v>-0.1569594031675763</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.5104853420916944</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>9920911.024466714</v>
+      </c>
       <c r="AO38" t="n">
-        <v>0.08224931590149009</v>
+        <v>1.087456987456985</v>
       </c>
       <c r="AP38" t="n">
-        <v>-1.950083307996351</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.097234417756198</v>
-      </c>
+        <v>0.6017038517038513</v>
+      </c>
+      <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
+      <c r="AS38" t="n">
+        <v>5.252014652014651</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>6.913714444311751</v>
+      </c>
       <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
+      <c r="AV38" t="n">
+        <v>7.176820518546464</v>
+      </c>
       <c r="AW38" t="n">
-        <v>807385.1778656123</v>
+        <v>10022199.74469975</v>
       </c>
       <c r="AX38" t="inlineStr"/>
       <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
+      <c r="AZ38" t="n">
+        <v>6.457825507825518</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>-0.5890392451726392</v>
+      </c>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="n">
-        <v>-5.636925509273333</v>
+        <v>-0.923981573981564</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
@@ -5248,124 +5732,152 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45529.5625</v>
       </c>
       <c r="C39" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E39" t="n">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="F39" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="G39" t="n">
         <v>77</v>
       </c>
       <c r="H39" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>91</v>
+      </c>
+      <c r="M39" t="n">
+        <v>64</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P39" t="n">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>194</v>
-      </c>
-      <c r="M39" t="n">
-        <v>73</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>-18</v>
+      </c>
+      <c r="T39" t="n">
         <v>2</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+      <c r="W39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="n">
-        <v>4.006611436900045</v>
-      </c>
+      <c r="AE39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>2.466262626262647</v>
+        <v>-1.571812791359406</v>
       </c>
       <c r="AM39" t="n">
-        <v>-0.02020202020202011</v>
-      </c>
-      <c r="AN39" t="inlineStr"/>
+        <v>-0.1928998979817507</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>-7424273.627688604</v>
+      </c>
       <c r="AO39" t="n">
-        <v>-0.1237123370456703</v>
+        <v>0.05560802833530687</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.6780446896684538</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>3.151182829978438</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>-1.767777777777784</v>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+        <v>-0.2678866587957498</v>
+      </c>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="n">
+        <v>-2.385891381345928</v>
+      </c>
       <c r="AT39" t="n">
-        <v>4.761414141414164</v>
+        <v>-2.748537459663112</v>
       </c>
       <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
+      <c r="AV39" t="n">
+        <v>-3.004709976492322</v>
+      </c>
       <c r="AW39" t="n">
-        <v>1168445.795135325</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>2919146.464646465</v>
-      </c>
+        <v>-5505448.642266823</v>
+      </c>
+      <c r="AX39" t="inlineStr"/>
       <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
+      <c r="AZ39" t="n">
+        <v>-2.1172373081464</v>
+      </c>
       <c r="BA39" t="n">
-        <v>3.718585858585868</v>
+        <v>-0.55623614967487</v>
       </c>
       <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="n">
-        <v>-3.420309037831945</v>
+        <v>-1.234415584415586</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
@@ -5374,32 +5886,32 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45528.65625</v>
       </c>
       <c r="C40" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E40" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F40" t="n">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="G40" t="n">
         <v>77</v>
       </c>
       <c r="H40" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -5408,23 +5920,27 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>63</v>
+        <v>223</v>
       </c>
       <c r="M40" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
       <c r="P40" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -5446,48 +5962,48 @@
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="n">
-        <v>3.199836399283441</v>
-      </c>
+      <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>4.169393939393927</v>
+        <v>-0.1887099015139313</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.2481818181818183</v>
-      </c>
-      <c r="AN40" t="inlineStr"/>
+        <v>0.824280372679582</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>21400010.94159291</v>
+      </c>
       <c r="AO40" t="n">
-        <v>0.1935295681270914</v>
+        <v>3.970991735537186</v>
       </c>
       <c r="AP40" t="n">
-        <v>5.080885805275642</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>2.885303425552451</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>-0.2954545454545432</v>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+        <v>1.395454545454546</v>
+      </c>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="n">
+        <v>6.820330578512383</v>
+      </c>
       <c r="AT40" t="n">
-        <v>8.096363636363634</v>
+        <v>6.598932398530891</v>
       </c>
       <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
+      <c r="AV40" t="n">
+        <v>10.98803713606813</v>
+      </c>
       <c r="AW40" t="n">
-        <v>4284683.627062971</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>12069202.02020202</v>
-      </c>
+        <v>34463966.94214876</v>
+      </c>
+      <c r="AX40" t="inlineStr"/>
       <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
+      <c r="AZ40" t="n">
+        <v>10.80231404958678</v>
+      </c>
       <c r="BA40" t="n">
-        <v>8.128686868686856</v>
+        <v>3.992611815123986</v>
       </c>
       <c r="BB40" t="inlineStr"/>
       <c r="BC40" t="n">
-        <v>0.6164399232772944</v>
+        <v>-1.265371900826437</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
@@ -5496,60 +6012,60 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="F41" t="n">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="G41" t="n">
         <v>77</v>
       </c>
       <c r="H41" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>97</v>
+      </c>
+      <c r="M41" t="n">
+        <v>189</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>228</v>
-      </c>
-      <c r="M41" t="n">
-        <v>80</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2</v>
-      </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5570,50 +6086,52 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
+      <c r="AI41" t="n">
+        <v>68</v>
+      </c>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="n">
-        <v>2.300602888976684</v>
-      </c>
+      <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>2.761593714927017</v>
+        <v>-2.650363292575605</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.1034118967452302</v>
-      </c>
-      <c r="AN41" t="inlineStr"/>
+        <v>-0.106361897551156</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>834516.7729755333</v>
+      </c>
       <c r="AO41" t="n">
-        <v>-0.05241219736714098</v>
+        <v>-0.6404958677685926</v>
       </c>
       <c r="AP41" t="n">
-        <v>-0.8758213404994137</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.05298544926216664</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>-2.014915824915832</v>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+        <v>0.1685950413223138</v>
+      </c>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="n">
+        <v>0.0429752066115725</v>
+      </c>
       <c r="AT41" t="n">
-        <v>1.657003367003355</v>
+        <v>2.653680695547678</v>
       </c>
       <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
+      <c r="AV41" t="n">
+        <v>1.28294831530124</v>
+      </c>
       <c r="AW41" t="n">
-        <v>-61511.01013553748</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>-1073521.885521885</v>
-      </c>
+        <v>982851.2396694217</v>
+      </c>
+      <c r="AX41" t="inlineStr"/>
       <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
+      <c r="AZ41" t="n">
+        <v>0.2049586776859513</v>
+      </c>
       <c r="BA41" t="n">
-        <v>-2.799775533108871</v>
+        <v>-0.8989290618446617</v>
       </c>
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="n">
-        <v>-1.181015818909245</v>
+        <v>-0.5066115702479692</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
@@ -5622,20 +6140,20 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>CxyB0iT1</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C42" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F42" t="n">
         <v>153</v>
@@ -5644,35 +6162,35 @@
         <v>77</v>
       </c>
       <c r="H42" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>76</v>
+      </c>
+      <c r="M42" t="n">
+        <v>143</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>54</v>
-      </c>
-      <c r="M42" t="n">
-        <v>240</v>
-      </c>
-      <c r="N42" t="n">
-        <v>4</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>7</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -5680,66 +6198,98 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>11</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="n">
-        <v>0.1898324490413899</v>
-      </c>
+      <c r="AE42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>67.33333333333333</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>68</v>
+      </c>
+      <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="n">
-        <v>1.724242424242391</v>
+        <v>-0.3841723401087904</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.06464646464646462</v>
-      </c>
-      <c r="AN42" t="inlineStr"/>
+        <v>0.1001359751359752</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-654322.7541689081</v>
+      </c>
       <c r="AO42" t="n">
-        <v>0.1042002147074614</v>
+        <v>-0.3355244755244726</v>
       </c>
       <c r="AP42" t="n">
-        <v>-0.04566370067576031</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>2.268213231347289</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>-1.538888888888888</v>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="n">
+        <v>-2.451538461538462</v>
+      </c>
       <c r="AT42" t="n">
-        <v>1.308585858585857</v>
+        <v>-2.572684981437476</v>
       </c>
       <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="inlineStr"/>
+      <c r="AV42" t="n">
+        <v>-2.233728512537866</v>
+      </c>
       <c r="AW42" t="n">
-        <v>358043.4696588081</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>525429.2929292931</v>
-      </c>
+        <v>-1011131.118881119</v>
+      </c>
+      <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
+      <c r="AZ42" t="n">
+        <v>-2.756993006993</v>
+      </c>
       <c r="BA42" t="n">
-        <v>-0.564646464646458</v>
+        <v>0.3927435687067806</v>
       </c>
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="n">
-        <v>-0.4150312426882472</v>
+        <v>-0.1732167832168443</v>
       </c>
       <c r="BD42" t="n">
         <v>0</v>
@@ -5748,14 +6298,14 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>0IkylEqd</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C43" t="n">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="D43" t="n">
         <v>51</v>
@@ -5764,16 +6314,16 @@
         <v>94</v>
       </c>
       <c r="F43" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="G43" t="n">
         <v>77</v>
       </c>
       <c r="H43" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -5782,90 +6332,122 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="M43" t="n">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>-1</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>7</v>
+      </c>
+      <c r="X43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-3</v>
+      </c>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="n">
-        <v>-1.143856204227106</v>
-      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>70.18333333333334</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>70.4040404040404</v>
+      </c>
+      <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>-1.786433566433573</v>
+        <v>-1.360615441880384</v>
       </c>
       <c r="AM43" t="n">
         <v>0</v>
       </c>
-      <c r="AN43" t="inlineStr"/>
+      <c r="AN43" t="n">
+        <v>123534.4347141762</v>
+      </c>
       <c r="AO43" t="n">
-        <v>-0.04231307154384112</v>
+        <v>-0.1007116620752946</v>
       </c>
       <c r="AP43" t="n">
-        <v>-3.404913275649122</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.6527582159315841</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0.4961538461538453</v>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="n">
+        <v>0.7534486276910428</v>
+      </c>
       <c r="AT43" t="n">
-        <v>-3.507552447552456</v>
+        <v>1.972728663521963</v>
       </c>
       <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
+      <c r="AV43" t="n">
+        <v>-0.6400476287829946</v>
+      </c>
       <c r="AW43" t="n">
-        <v>-460562.3602673612</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>-1396041.258741259</v>
-      </c>
+        <v>172202.0712172226</v>
+      </c>
+      <c r="AX43" t="inlineStr"/>
       <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
+      <c r="AZ43" t="n">
+        <v>0.51798540965207</v>
+      </c>
       <c r="BA43" t="n">
-        <v>-2.966013986013976</v>
+        <v>-1.615219751140604</v>
       </c>
       <c r="BB43" t="inlineStr"/>
       <c r="BC43" t="n">
-        <v>-2.154294048875816</v>
+        <v>-0.32449750025512</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
@@ -5874,32 +6456,32 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>CEhO9e6F</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="D44" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F44" t="n">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="G44" t="n">
         <v>77</v>
       </c>
       <c r="H44" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -5908,87 +6490,97 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="M44" t="n">
-        <v>147</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-2</v>
+      </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>5</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>-3</v>
+      </c>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>68.66666666666667</v>
+      </c>
       <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="n">
-        <v>9.402396369927715</v>
-      </c>
+      <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>-2.341515151515154</v>
+        <v>4.418381732139494</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.7100000000000002</v>
-      </c>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="n">
-        <v>0.552191083770031</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>11.22808068925053</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>-2.557786796428189</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0.02676767676768321</v>
-      </c>
+        <v>0.118495738216235</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1279790.530639133</v>
+      </c>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>12.05838383838385</v>
+        <v>2.664010849399048</v>
       </c>
       <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="n">
-        <v>14824499.85413968</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>33933626.26262626</v>
-      </c>
+      <c r="AV44" t="n">
+        <v>7.566088637035847</v>
+      </c>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
-        <v>13.77808080808082</v>
+        <v>4.556688110026624</v>
       </c>
       <c r="BB44" t="inlineStr"/>
-      <c r="BC44" t="n">
-        <v>0.1158684224585151</v>
-      </c>
+      <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="n">
         <v>0</v>
       </c>
@@ -5996,32 +6588,32 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>ptW4MYkL</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45528.64583333334</v>
       </c>
       <c r="C45" t="n">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F45" t="n">
-        <v>58</v>
+        <v>196</v>
       </c>
       <c r="G45" t="n">
         <v>77</v>
       </c>
       <c r="H45" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -6030,88 +6622,874 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="M45" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="n">
+        <v>-5</v>
+      </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
+      <c r="W45" t="n">
+        <v>2</v>
+      </c>
+      <c r="X45" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>-1</v>
+      </c>
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="n">
-        <v>3.712450296616964</v>
-      </c>
+      <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>2.331060606060674</v>
+        <v>1.992134768723986</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.04545454545454541</v>
-      </c>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="n">
-        <v>0.1366392866392867</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>3.91470908720909</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>3.014277065527068</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>-1.422727272727268</v>
-      </c>
+        <v>0.1283856179358429</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1513547.466408598</v>
+      </c>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
-        <v>5.787878787878782</v>
+        <v>3.867403765649655</v>
       </c>
       <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
-      <c r="AW45" t="n">
-        <v>1730888.176638176</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>3289318.181818182</v>
-      </c>
+      <c r="AV45" t="n">
+        <v>2.113859933308959</v>
+      </c>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
-        <v>4.971212121212105</v>
+        <v>-0.1479000305874401</v>
       </c>
       <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="n">
-        <v>-0.2966278782945508</v>
-      </c>
+      <c r="BC45" t="inlineStr"/>
       <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" t="n">
+        <v>123</v>
+      </c>
+      <c r="F46" t="n">
+        <v>166</v>
+      </c>
+      <c r="G46" t="n">
+        <v>77</v>
+      </c>
+      <c r="H46" t="n">
+        <v>774</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>76</v>
+      </c>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="n">
+        <v>-0.1822772290164494</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>-1137108.82239348</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>2.030881542699721</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="n">
+        <v>-3.934490358126709</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>-3.401212885228759</v>
+      </c>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="n">
+        <v>-2.192254273947</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>-2237964.531680441</v>
+      </c>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="n">
+        <v>-1.914329660238749</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>1.134542146547133</v>
+      </c>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="n">
+        <v>-1.211101928374632</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C47" t="n">
+        <v>142</v>
+      </c>
+      <c r="D47" t="n">
+        <v>48</v>
+      </c>
+      <c r="E47" t="n">
+        <v>103</v>
+      </c>
+      <c r="F47" t="n">
+        <v>28</v>
+      </c>
+      <c r="G47" t="n">
+        <v>77</v>
+      </c>
+      <c r="H47" t="n">
+        <v>774</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>162</v>
+      </c>
+      <c r="M47" t="n">
+        <v>187</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T47" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="n">
+        <v>1.243376043909421</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0.1502588462374435</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1352378.698495235</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>-1.689146005509645</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0.1373737373737374</v>
+      </c>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="n">
+        <v>5.947513774104678</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>6.613966656078645</v>
+      </c>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="n">
+        <v>4.535318135142305</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>1083615.358126722</v>
+      </c>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="n">
+        <v>3.2729958677686</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>-1.123155851622833</v>
+      </c>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="n">
+        <v>-0.4758103764921771</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45528.60416666666</v>
+      </c>
+      <c r="C48" t="n">
+        <v>41</v>
+      </c>
+      <c r="D48" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" t="n">
+        <v>69</v>
+      </c>
+      <c r="F48" t="n">
+        <v>75</v>
+      </c>
+      <c r="G48" t="n">
+        <v>77</v>
+      </c>
+      <c r="H48" t="n">
+        <v>774</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>154</v>
+      </c>
+      <c r="M48" t="n">
+        <v>31</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="n">
+        <v>66.81818181818181</v>
+      </c>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="n">
+        <v>1.894138060475797</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>-0.1615105403488091</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>-1945621.22830462</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>3.589522497704312</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>-0.1047382920110194</v>
+      </c>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="n">
+        <v>-6.396584022038581</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>-6.399032244543619</v>
+      </c>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="n">
+        <v>-4.285547892887251</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>-2206837.832874197</v>
+      </c>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="n">
+        <v>-2.997860422405878</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0.2701190465133791</v>
+      </c>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="n">
+        <v>-1.40901744719929</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C49" t="n">
+        <v>67</v>
+      </c>
+      <c r="D49" t="n">
+        <v>36</v>
+      </c>
+      <c r="E49" t="n">
+        <v>17</v>
+      </c>
+      <c r="F49" t="n">
+        <v>31</v>
+      </c>
+      <c r="G49" t="n">
+        <v>77</v>
+      </c>
+      <c r="H49" t="n">
+        <v>771</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>186</v>
+      </c>
+      <c r="M49" t="n">
+        <v>38</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-17</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="n">
+        <v>-0.4721016541725191</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>-0.4138400604819368</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>-20127219.2715042</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>-0.8316161616161573</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>-0.7230303030303031</v>
+      </c>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="n">
+        <v>-8.553434343434361</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>-8.64158246647834</v>
+      </c>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="n">
+        <v>-8.290109757392372</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>-31407393.93939394</v>
+      </c>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="n">
+        <v>-10.74373737373737</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>0.5718925537552515</v>
+      </c>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="n">
+        <v>0.5624242424242141</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C50" t="n">
+        <v>126</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>120</v>
+      </c>
+      <c r="F50" t="n">
+        <v>102</v>
+      </c>
+      <c r="G50" t="n">
+        <v>77</v>
+      </c>
+      <c r="H50" t="n">
+        <v>771</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>227</v>
+      </c>
+      <c r="M50" t="n">
+        <v>204</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="n">
+        <v>0.7163668682360935</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>-0.6893982302775088</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>-12629224.16964497</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>-1.731756963575144</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>-0.6801423324150597</v>
+      </c>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="n">
+        <v>-2.757835935108659</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>-4.724157270129226</v>
+      </c>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="n">
+        <v>-5.49054488513805</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>-13134872.9721457</v>
+      </c>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="n">
+        <v>-4.207652280379548</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>-0.8944483961036518</v>
+      </c>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="n">
+        <v>2.710185185185196</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C51" t="n">
+        <v>24</v>
+      </c>
+      <c r="D51" t="n">
+        <v>14</v>
+      </c>
+      <c r="E51" t="n">
+        <v>49</v>
+      </c>
+      <c r="F51" t="n">
+        <v>193</v>
+      </c>
+      <c r="G51" t="n">
+        <v>77</v>
+      </c>
+      <c r="H51" t="n">
+        <v>774</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>154</v>
+      </c>
+      <c r="M51" t="n">
+        <v>268</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="n">
+        <v>70.36363636363636</v>
+      </c>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="n">
+        <v>3.698966476759921</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0.0008867521367521558</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>-136592.9008431183</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>-1.464158249158249</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0.0005723905723906686</v>
+      </c>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="n">
+        <v>0.3865824915825016</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0.3084031246531254</v>
+      </c>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="n">
+        <v>-0.461875307060069</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>-137936.868686869</v>
+      </c>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="n">
+        <v>-0.7014814814814798</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>-0.6377971979711177</v>
+      </c>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="n">
+        <v>3.352929292929389</v>
+      </c>
+      <c r="BD51" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,44 +520,44 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_n_matches_last_days_home</t>
+          <t>dif_mean_last_match_goals</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_n_matches_last_days_home_against</t>
+          <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
@@ -580,140 +580,130 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
       <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -722,23 +712,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -760,19 +750,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="M2" t="n">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -780,139 +770,123 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>0.5700000000000001</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.1400000000000001</v>
-      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.5800000000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>2</v>
       </c>
-      <c r="AA2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="AD2" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="AE2" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.5</v>
+        <v>-9</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5</v>
+        <v>-11</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1</v>
+        <v>72.375</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1.5</v>
+        <v>72.27272727272727</v>
       </c>
       <c r="AK2" t="n">
-        <v>73.59999999999999</v>
+        <v>-0.5026953094892797</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.90000000000001</v>
+        <v>-0.2191362231877498</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.992611815123986</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>10.98803713606813</v>
-      </c>
+        <v>-0.331899766899767</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>1.395454545454546</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-3</v>
-      </c>
+        <v>8704756.216006216</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-1.265371900826437</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>3.970991735537186</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>34463966.94214876</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
+        <v>-0.4427894327894322</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>21400010.94159291</v>
+        <v>3.113310023310035</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.666666666666668</v>
+        <v>-1730318.318283005</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.598932398530891</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>172</v>
-      </c>
+        <v>1.656888111888108</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>1.333333333333333</v>
+        <v>1.05843936427047</v>
       </c>
       <c r="AZ2" t="n">
-        <v>171</v>
+        <v>4.119131701631687</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.824280372679582</v>
+        <v>-0.05079903081303883</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.820330578512383</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.1887099015139313</v>
-      </c>
+        <v>0.9298599087084511</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>136900000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>10.80231404958678</v>
-      </c>
-      <c r="BF2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="F3" t="n">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -934,163 +908,139 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>97</v>
+        <v>254</v>
       </c>
       <c r="M3" t="n">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="N3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.83</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-7</v>
+        <v>0.74</v>
       </c>
       <c r="Z3" t="n">
-        <v>-6.5</v>
+        <v>-0.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>16</v>
+        <v>-2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>-16</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AE3" t="n">
-        <v>-7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.5</v>
+        <v>79</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>73.75505050505051</v>
       </c>
       <c r="AK3" t="n">
-        <v>69.40909090909091</v>
+        <v>-1.093853189385047</v>
       </c>
       <c r="AL3" t="n">
-        <v>73.36931818181819</v>
+        <v>-0.1865803702904087</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.8989290618446617</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.28294831530124</v>
-      </c>
+        <v>-0.03835578002244655</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>0.1685950413223138</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-6</v>
-      </c>
+        <v>1463341.75084175</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-0.5066115702479692</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0.6404958677685926</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>982851.2396694217</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-2</v>
-      </c>
+        <v>-0.8150673400673405</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>834516.7729755333</v>
+        <v>3.417508417508429</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>466572.0514082243</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.653680695547678</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-115</v>
-      </c>
+        <v>2.135578002244657</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0.647721139789752</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-152</v>
+        <v>5.290432098765422</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.106361897551156</v>
+        <v>0.9330782762909848</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0429752066115725</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-2.650363292575605</v>
-      </c>
+        <v>2.342071268557319</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>-550000</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.2049586776859513</v>
-      </c>
-      <c r="BF3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1115,16 +1065,20 @@
         <v>186</v>
       </c>
       <c r="M4" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="N4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
       <c r="P4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1133,134 +1087,98 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-0.2399999999999998</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>69.93658008658008</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.5</v>
+        <v>70.81818181818181</v>
       </c>
       <c r="AK4" t="n">
-        <v>73.40000000000001</v>
+        <v>-0.7223782477123599</v>
       </c>
       <c r="AL4" t="n">
-        <v>75.59999999999999</v>
+        <v>0.2676963131699428</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.5718925537552515</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-8.290109757392372</v>
-      </c>
+        <v>0.2407501589319769</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-0.7230303030303031</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-2.5</v>
-      </c>
+        <v>5726916.719643994</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>0.5624242424242141</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-0.8316161616161573</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-31407393.93939394</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
+        <v>0.6810553083280304</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>-20127219.2715042</v>
+        <v>2.17889383343929</v>
       </c>
       <c r="AV4" t="n">
-        <v>-5.5</v>
+        <v>7194801.438642818</v>
       </c>
       <c r="AW4" t="n">
-        <v>-8.64158246647834</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>69</v>
-      </c>
+        <v>3.160521296884937</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>-1</v>
+        <v>-0.4032480669210941</v>
       </c>
       <c r="AZ4" t="n">
-        <v>76</v>
+        <v>-0.0220597584234099</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.4138400604819368</v>
+        <v>2.970661242011261</v>
       </c>
       <c r="BB4" t="n">
-        <v>-8.553434343434361</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-0.4721016541725191</v>
-      </c>
+        <v>2.620894635628929</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-10.74373737373737</v>
-      </c>
-      <c r="BF4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C5" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1282,140 +1200,1784 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M5" t="n">
-        <v>204</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
-        <v>-23</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>-10</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>73.36931818181819</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>2.307398418574884</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3518154938743174</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.06717171717171722</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>1205456.841138659</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>1.137167125803487</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>0.7697199265381016</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>109509.2342298217</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.01675849403120822</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>2.06309416074123</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.03514692378331574</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.2322978546507812</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-1.30920201802553</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C6" t="n">
+        <v>117</v>
+      </c>
+      <c r="D6" t="n">
+        <v>55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>66</v>
+      </c>
+      <c r="F6" t="n">
+        <v>31</v>
+      </c>
+      <c r="G6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>771</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>254</v>
+      </c>
+      <c r="M6" t="n">
+        <v>96</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="V6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>0.2200000000000002</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
         <v>-1</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="n">
         <v>-3</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AE6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>69.55555555555556</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.100753155650178</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2227540088524074</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.07219749947022636</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>-17003895.24616798</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>1.462329589602327</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>-4.26287349014622</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-6995724.231104091</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-2.966228720774183</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>-1.745136997082028</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.5085470085470547</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.3062353952514201</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-2.837270656710004</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C7" t="n">
+        <v>117</v>
+      </c>
+      <c r="D7" t="n">
+        <v>33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" t="n">
+        <v>77</v>
+      </c>
+      <c r="H7" t="n">
+        <v>771</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>110</v>
+      </c>
+      <c r="M7" t="n">
+        <v>96</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>71.46363636363637</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>0.2923619949635992</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4012203796901967</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.6768595041322318</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>31852915.51882461</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>2.118365472910927</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>6.76666666666668</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12779978.7425277</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>11.03535353535354</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>-2.593562232342379</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-2.657116620752987</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7.612933825190467</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.32338014836148</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C8" t="n">
+        <v>58</v>
+      </c>
+      <c r="D8" t="n">
+        <v>84</v>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>97</v>
+      </c>
+      <c r="G8" t="n">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>771</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>95</v>
+      </c>
+      <c r="M8" t="n">
+        <v>250</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="n">
+        <v>-2.628120443981942</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.115765413542434</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.1735537190082646</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>1595247.933884298</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>-1.355371900826444</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>2.010330578512409</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-55628.53160742205</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.1632231404958731</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>-0.6918096398586613</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.1508264462809734</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-1.924883999294309</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.6088112887330226</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C9" t="n">
+        <v>39</v>
+      </c>
+      <c r="D9" t="n">
+        <v>67</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>771</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>227</v>
+      </c>
+      <c r="M9" t="n">
+        <v>55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" t="n">
         <v>2</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>73.45454545454545</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>78.55727272727272</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.770989053092499</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08860531051440135</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.2487603305785127</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>6752975.206611572</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>-0.5396694214876092</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>3.471074380165291</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4056428.43130108</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.997520661157012</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>2.608819499205111</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.377685950413223</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.70564804196151</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3.2976648587683</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C10" t="n">
+        <v>74</v>
+      </c>
+      <c r="D10" t="n">
+        <v>41</v>
+      </c>
+      <c r="E10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
+        <v>77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>771</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>223</v>
+      </c>
+      <c r="M10" t="n">
+        <v>64</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>73.98212809917356</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.753072090435442</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.5199947734575063</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.8655844155844155</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>21244220.77922078</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>2.077012987012989</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>3.15220779220779</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10845701.11836059</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.614415584415582</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>-4.156263204474328</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-4.230779220779198</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.162812977797444</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.648070815198139</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45534.5625</v>
+      </c>
+      <c r="C11" t="n">
+        <v>67</v>
+      </c>
+      <c r="D11" t="n">
+        <v>62</v>
+      </c>
+      <c r="E11" t="n">
+        <v>52</v>
+      </c>
+      <c r="F11" t="n">
+        <v>72</v>
+      </c>
+      <c r="G11" t="n">
+        <v>77</v>
+      </c>
+      <c r="H11" t="n">
+        <v>771</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>124</v>
+      </c>
+      <c r="M11" t="n">
+        <v>38</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.715711899095858</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1334582573507423</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.246904105995015</v>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>-10488754.09943592</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-0.8064016791289532</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>-4.753286107831556</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-4157362.913029947</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-6.152676111767036</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>-3.10065423739232</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-1.38650793650794</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-4.433871272480388</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-3.72729458120898</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45530.65625</v>
+      </c>
+      <c r="C12" t="n">
+        <v>52</v>
+      </c>
+      <c r="D12" t="n">
+        <v>49</v>
+      </c>
+      <c r="E12" t="n">
+        <v>116</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H12" t="n">
+        <v>771</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>110</v>
+      </c>
+      <c r="M12" t="n">
+        <v>148</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-17</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="n">
+        <v>-0.5777851299476033</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.7067397751837112</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.6155612064702973</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-108100000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-25192682.06540934</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.579377693014056</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-341</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.400000000000006</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-7.176087801087803</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-12433420.79729322</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-7.201993713357325</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-3.199999999999999</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-1.080363464402353</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-2.204960443596804</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-5.673591925914579</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-6.225626207845892</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-329</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45530.5625</v>
+      </c>
+      <c r="C13" t="n">
+        <v>29</v>
+      </c>
+      <c r="D13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>64</v>
+      </c>
+      <c r="F13" t="n">
+        <v>187</v>
+      </c>
+      <c r="G13" t="n">
+        <v>77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>771</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>99</v>
+      </c>
+      <c r="M13" t="n">
+        <v>148</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.1699999999999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>78</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>74.54166666666666</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.7765857807581895</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.07716868061695648</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.09731915110703016</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>249960.2081420254</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.4565962656871747</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.205938169574537</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-109549.4378609895</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.9969416386082912</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.4597616508650901</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.286781961024388</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.1105118521325323</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.783415773243377</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>UilLdutJ</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C14" t="n">
+        <v>131</v>
+      </c>
+      <c r="D14" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>140</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>771</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>99</v>
+      </c>
+      <c r="M14" t="n">
+        <v>55</v>
+      </c>
+      <c r="N14" t="n">
+        <v>17</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="n">
+        <v>0.4927709267273741</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.8497862631908168</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.054669421487604</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-9625000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>16962179.75206611</v>
+      </c>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>0.8453305785123959</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-287</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>4.594710743801642</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>14672747.01003867</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.427520661157004</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="n">
+        <v>0.6679386916010515</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-1.853450413223101</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.701296206360141</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.816963620334761</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-280</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2uc40Ntf</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C15" t="n">
+        <v>87</v>
+      </c>
+      <c r="D15" t="n">
+        <v>33</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>771</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>110</v>
+      </c>
+      <c r="M15" t="n">
+        <v>268</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="n">
+        <v>1.826825898487471</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.3104683394598959</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.4479338842975209</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-29400000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>23846033.05785124</v>
+      </c>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>1.738016528925623</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-237</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>2.890909090909091</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8268656.74503216</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.646280991735537</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="n">
+        <v>-3.537998793449106</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-3.307438016528891</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.50303342235604</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.009442190711397</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-216</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M7MVoOR0</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5625</v>
+      </c>
+      <c r="C16" t="n">
+        <v>120</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>56</v>
+      </c>
+      <c r="F16" t="n">
+        <v>74</v>
+      </c>
+      <c r="G16" t="n">
+        <v>77</v>
+      </c>
+      <c r="H16" t="n">
+        <v>771</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>186</v>
+      </c>
+      <c r="M16" t="n">
+        <v>204</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.5890392451726392</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.5104853420916944</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.6017038517038513</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>21875000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>10022199.74469975</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.087456987456985</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.166666666666657</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.252014652014651</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9920911.024466714</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.457825507825518</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.8333333333333321</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.1569594031675763</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.923981573981564</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.176820518546464</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.913714444311751</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-54</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dbt7KrYP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5625</v>
+      </c>
+      <c r="C17" t="n">
+        <v>103</v>
+      </c>
+      <c r="D17" t="n">
+        <v>56</v>
+      </c>
+      <c r="E17" t="n">
+        <v>51</v>
+      </c>
+      <c r="F17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" t="n">
+        <v>77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>771</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>91</v>
+      </c>
+      <c r="M17" t="n">
+        <v>64</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.55623614967487</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.1928998979817507</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.2678866587957498</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-24400000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-5505448.642266823</v>
+      </c>
+      <c r="AP17" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AH5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>75.27272727272727</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-0.8944483961036518</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-5.49054488513805</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-0.6801423324150597</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="AQ17" t="n">
+        <v>0.05560802833530687</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-2.385891381345928</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-7424273.627688604</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-2.1172373081464</v>
+      </c>
+      <c r="AX17" t="n">
         <v>-4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>2.710185185185196</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-1.731756963575144</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-13134872.9721457</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-12629224.16964497</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-4.724157270129226</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>84</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>83</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-0.6893982302775088</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-2.757835935108659</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.7163668682360935</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>18900000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-4.207652280379548</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="AY17" t="n">
+        <v>-1.571812791359406</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-1.234415584415586</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-3.004709976492322</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-2.748537459663112</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-27</v>
+      </c>
+      <c r="BD17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -771,10 +771,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>0.1699999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="U2" t="n">
         <v>6</v>
@@ -782,87 +782,91 @@
       <c r="V2" t="n">
         <v>-1</v>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" t="n">
-        <v>0.1699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AG2" t="n">
         <v>-2</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AH2" t="n">
         <v>2</v>
       </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-11</v>
-      </c>
       <c r="AI2" t="n">
-        <v>72.375</v>
+        <v>72.69358356290175</v>
       </c>
       <c r="AJ2" t="n">
-        <v>72.27272727272727</v>
-      </c>
-      <c r="AK2" t="n">
+        <v>72.20123966942148</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>1.656888111888108</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
         <v>-0.5026953094892797</v>
       </c>
-      <c r="AL2" t="n">
-        <v>-0.2191362231877498</v>
-      </c>
-      <c r="AM2" t="n">
+      <c r="AO2" t="n">
+        <v>3.113310023310035</v>
+      </c>
+      <c r="AP2" t="n">
         <v>-0.331899766899767</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>8704756.216006216</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-0.4427894327894322</v>
+        <v>4.119131701631687</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>-0.2191362231877498</v>
+      </c>
       <c r="AU2" t="n">
-        <v>3.113310023310035</v>
+        <v>-1730318.318283005</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1730318.318283005</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.656888111888108</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>-0.05079903081303883</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>-0.4427894327894322</v>
+      </c>
       <c r="AY2" t="n">
         <v>1.05843936427047</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>4.119131701631687</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-0.05079903081303883</v>
-      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
+        <v>8704756.216006216</v>
+      </c>
+      <c r="BC2" t="n">
         <v>0.9298599087084511</v>
       </c>
-      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -925,98 +929,98 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>0.7250000000000001</v>
       </c>
       <c r="T3" t="n">
+        <v>0.7199999999999998</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>4.833333333333334</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
         <v>-2</v>
       </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-2.333333333333333</v>
-      </c>
       <c r="AE3" t="n">
-        <v>5.5</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>3.166666666666666</v>
       </c>
       <c r="AG3" t="n">
-        <v>6</v>
+        <v>-10</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.5</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
-        <v>79</v>
+        <v>77.13636363636363</v>
       </c>
       <c r="AJ3" t="n">
         <v>73.75505050505051</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="n">
+        <v>2.135578002244657</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="n">
         <v>-1.093853189385047</v>
       </c>
-      <c r="AL3" t="n">
-        <v>-0.1865803702904087</v>
-      </c>
-      <c r="AM3" t="n">
+      <c r="AO3" t="n">
+        <v>3.417508417508429</v>
+      </c>
+      <c r="AP3" t="n">
         <v>-0.03835578002244655</v>
       </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
-        <v>1463341.75084175</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-0.8150673400673405</v>
+        <v>5.290432098765422</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>-0.1865803702904087</v>
+      </c>
       <c r="AU3" t="n">
-        <v>3.417508417508429</v>
+        <v>466572.0514082243</v>
       </c>
       <c r="AV3" t="n">
-        <v>466572.0514082243</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.135578002244657</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>0.9330782762909848</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>-0.8150673400673405</v>
+      </c>
       <c r="AY3" t="n">
         <v>-0.647721139789752</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>5.290432098765422</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.9330782762909848</v>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
+        <v>1463341.75084175</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.342071268557319</v>
       </c>
-      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
@@ -1082,79 +1086,103 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2</v>
+      </c>
       <c r="AI4" t="n">
-        <v>69.93658008658008</v>
+        <v>69.74606782106781</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70.81818181818181</v>
-      </c>
-      <c r="AK4" t="n">
+        <v>69.40909090909091</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="n">
+        <v>3.160521296884937</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="n">
         <v>-0.7223782477123599</v>
       </c>
-      <c r="AL4" t="n">
-        <v>0.2676963131699428</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="AO4" t="n">
+        <v>2.17889383343929</v>
+      </c>
+      <c r="AP4" t="n">
         <v>0.2407501589319769</v>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>5726916.719643994</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>0.6810553083280304</v>
+        <v>-0.0220597584234099</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>0.2676963131699428</v>
+      </c>
       <c r="AU4" t="n">
-        <v>2.17889383343929</v>
+        <v>7194801.438642818</v>
       </c>
       <c r="AV4" t="n">
-        <v>7194801.438642818</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.160521296884937</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>2.970661242011261</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>0.6810553083280304</v>
+      </c>
       <c r="AY4" t="n">
         <v>-0.4032480669210941</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>-0.0220597584234099</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.970661242011261</v>
-      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
+        <v>5726916.719643994</v>
+      </c>
+      <c r="BC4" t="n">
         <v>2.620894635628929</v>
       </c>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
@@ -1220,69 +1248,99 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0.1100000000000003</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="n">
         <v>73.36931818181819</v>
       </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
+      <c r="AJ5" t="n">
+        <v>80.45708041958042</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>0.01675849403120822</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
         <v>2.307398418574884</v>
       </c>
-      <c r="AL5" t="n">
-        <v>0.3518154938743174</v>
-      </c>
-      <c r="AM5" t="n">
+      <c r="AO5" t="n">
+        <v>0.7697199265381016</v>
+      </c>
+      <c r="AP5" t="n">
         <v>0.06717171717171722</v>
       </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>1205456.841138659</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>1.137167125803487</v>
+        <v>0.03514692378331574</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>0.3518154938743174</v>
+      </c>
       <c r="AU5" t="n">
-        <v>0.7697199265381016</v>
+        <v>109509.2342298217</v>
       </c>
       <c r="AV5" t="n">
-        <v>109509.2342298217</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.01675849403120822</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>-0.2322978546507812</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>1.137167125803487</v>
+      </c>
       <c r="AY5" t="n">
         <v>2.06309416074123</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>0.03514692378331574</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-0.2322978546507812</v>
-      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
+        <v>1205456.841138659</v>
+      </c>
+      <c r="BC5" t="n">
         <v>-1.30920201802553</v>
       </c>
-      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
@@ -1349,98 +1407,102 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>-0.3299999999999998</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.8600000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="AB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>0.2200000000000002</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
       <c r="AD6" t="n">
-        <v>-3</v>
+        <v>-0.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>4</v>
+        <v>-2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>3</v>
       </c>
       <c r="AG6" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="AI6" t="n">
-        <v>69.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>69.55555555555556</v>
-      </c>
-      <c r="AK6" t="n">
+        <v>72.57777777777778</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>-2.966228720774183</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
         <v>2.100753155650178</v>
       </c>
-      <c r="AL6" t="n">
-        <v>0.2227540088524074</v>
-      </c>
-      <c r="AM6" t="n">
+      <c r="AO6" t="n">
+        <v>-4.26287349014622</v>
+      </c>
+      <c r="AP6" t="n">
         <v>-0.07219749947022636</v>
       </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>-17003895.24616798</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>1.462329589602327</v>
+        <v>-0.5085470085470547</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0.2227540088524074</v>
+      </c>
       <c r="AU6" t="n">
-        <v>-4.26287349014622</v>
+        <v>-6995724.231104091</v>
       </c>
       <c r="AV6" t="n">
-        <v>-6995724.231104091</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-2.966228720774183</v>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+        <v>-0.3062353952514201</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1.462329589602327</v>
+      </c>
       <c r="AY6" t="n">
         <v>-1.745136997082028</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>-0.5085470085470547</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-0.3062353952514201</v>
-      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
+        <v>-17003895.24616798</v>
+      </c>
+      <c r="BC6" t="n">
         <v>-2.837270656710004</v>
       </c>
-      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
@@ -1502,69 +1564,103 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5049999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-8.333333333333334</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-29</v>
+      </c>
       <c r="AI7" t="n">
-        <v>71.46363636363637</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="n">
+        <v>72.22575757575758</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>76.16666666666667</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="n">
+        <v>11.03535353535354</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
         <v>0.2923619949635992</v>
       </c>
-      <c r="AL7" t="n">
-        <v>0.4012203796901967</v>
-      </c>
-      <c r="AM7" t="n">
+      <c r="AO7" t="n">
+        <v>6.76666666666668</v>
+      </c>
+      <c r="AP7" t="n">
         <v>0.6768595041322318</v>
       </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>31852915.51882461</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>2.118365472910927</v>
+        <v>-2.657116620752987</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0.4012203796901967</v>
+      </c>
       <c r="AU7" t="n">
-        <v>6.76666666666668</v>
+        <v>12779978.7425277</v>
       </c>
       <c r="AV7" t="n">
-        <v>12779978.7425277</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>11.03535353535354</v>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+        <v>7.612933825190467</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>2.118365472910927</v>
+      </c>
       <c r="AY7" t="n">
         <v>-2.593562232342379</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>-2.657116620752987</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.612933825190467</v>
-      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
+        <v>31852915.51882461</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5.32338014836148</v>
       </c>
-      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1630,69 +1726,99 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0.4099999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5.5</v>
+      </c>
       <c r="AI8" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="n">
+      <c r="AJ8" t="n">
+        <v>74.59243827160495</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="n">
+        <v>-0.1632231404958731</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
         <v>-2.628120443981942</v>
       </c>
-      <c r="AL8" t="n">
-        <v>-0.115765413542434</v>
-      </c>
-      <c r="AM8" t="n">
+      <c r="AO8" t="n">
+        <v>2.010330578512409</v>
+      </c>
+      <c r="AP8" t="n">
         <v>-0.1735537190082646</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>1595247.933884298</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>-1.355371900826444</v>
+        <v>-0.1508264462809734</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>-0.115765413542434</v>
+      </c>
       <c r="AU8" t="n">
-        <v>2.010330578512409</v>
+        <v>-55628.53160742205</v>
       </c>
       <c r="AV8" t="n">
-        <v>-55628.53160742205</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-0.1632231404958731</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+        <v>-1.924883999294309</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-1.355371900826444</v>
+      </c>
       <c r="AY8" t="n">
         <v>-0.6918096398586613</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>-0.1508264462809734</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-1.924883999294309</v>
-      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
+        <v>1595247.933884298</v>
+      </c>
+      <c r="BC8" t="n">
         <v>0.6088112887330226</v>
       </c>
-      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
@@ -1758,75 +1884,103 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-26</v>
+      </c>
       <c r="AI9" t="n">
-        <v>73.45454545454545</v>
+        <v>77.11404958677686</v>
       </c>
       <c r="AJ9" t="n">
-        <v>78.55727272727272</v>
-      </c>
-      <c r="AK9" t="n">
+        <v>72.63356902356902</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
+        <v>2.997520661157012</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
         <v>-1.770989053092499</v>
       </c>
-      <c r="AL9" t="n">
-        <v>0.08860531051440135</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="AO9" t="n">
+        <v>3.471074380165291</v>
+      </c>
+      <c r="AP9" t="n">
         <v>0.2487603305785127</v>
       </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
-        <v>6752975.206611572</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>-0.5396694214876092</v>
+        <v>1.377685950413223</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0.08860531051440135</v>
+      </c>
       <c r="AU9" t="n">
-        <v>3.471074380165291</v>
+        <v>4056428.43130108</v>
       </c>
       <c r="AV9" t="n">
-        <v>4056428.43130108</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.997520661157012</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+        <v>1.70564804196151</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>-0.5396694214876092</v>
+      </c>
       <c r="AY9" t="n">
         <v>2.608819499205111</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>1.377685950413223</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.70564804196151</v>
-      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
+        <v>6752975.206611572</v>
+      </c>
+      <c r="BC9" t="n">
         <v>3.2976648587683</v>
       </c>
-      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
@@ -1892,69 +2046,99 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
+      <c r="AA10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>73.59999999999999</v>
+      </c>
       <c r="AJ10" t="n">
         <v>73.98212809917356</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="n">
+        <v>4.614415584415582</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
         <v>1.753072090435442</v>
       </c>
-      <c r="AL10" t="n">
-        <v>0.5199947734575063</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AO10" t="n">
+        <v>3.15220779220779</v>
+      </c>
+      <c r="AP10" t="n">
         <v>0.8655844155844155</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
-        <v>21244220.77922078</v>
-      </c>
-      <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="n">
-        <v>2.077012987012989</v>
+        <v>-4.230779220779198</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0.5199947734575063</v>
+      </c>
       <c r="AU10" t="n">
-        <v>3.15220779220779</v>
+        <v>10845701.11836059</v>
       </c>
       <c r="AV10" t="n">
-        <v>10845701.11836059</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.614415584415582</v>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+        <v>4.162812977797444</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>2.077012987012989</v>
+      </c>
       <c r="AY10" t="n">
         <v>-4.156263204474328</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>-4.230779220779198</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.162812977797444</v>
-      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
+        <v>21244220.77922078</v>
+      </c>
+      <c r="BC10" t="n">
         <v>2.648070815198139</v>
       </c>
-      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
@@ -2020,69 +2204,99 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3800000000000003</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>73.93146853146854</v>
+      </c>
       <c r="AJ11" t="n">
-        <v>81.45454545454545</v>
-      </c>
-      <c r="AK11" t="n">
+        <v>75.35367965367965</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="n">
+        <v>-6.152676111767036</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
         <v>0.715711899095858</v>
       </c>
-      <c r="AL11" t="n">
-        <v>-0.1334582573507423</v>
-      </c>
-      <c r="AM11" t="n">
+      <c r="AO11" t="n">
+        <v>-4.753286107831556</v>
+      </c>
+      <c r="AP11" t="n">
         <v>-0.246904105995015</v>
       </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
-        <v>-10488754.09943592</v>
-      </c>
-      <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="n">
-        <v>-0.8064016791289532</v>
+        <v>-1.38650793650794</v>
       </c>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>-0.1334582573507423</v>
+      </c>
       <c r="AU11" t="n">
-        <v>-4.753286107831556</v>
+        <v>-4157362.913029947</v>
       </c>
       <c r="AV11" t="n">
-        <v>-4157362.913029947</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-6.152676111767036</v>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+        <v>-4.433871272480388</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>-0.8064016791289532</v>
+      </c>
       <c r="AY11" t="n">
         <v>-3.10065423739232</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>-1.38650793650794</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-4.433871272480388</v>
-      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
+        <v>-10488754.09943592</v>
+      </c>
+      <c r="BC11" t="n">
         <v>-3.72729458120898</v>
       </c>
-      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
         <v>0</v>
       </c>
@@ -2148,82 +2362,112 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>12</v>
+      </c>
       <c r="AI12" t="n">
         <v>80.7</v>
       </c>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>72.375</v>
+      </c>
       <c r="AK12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-7.201993713357325</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AN12" t="n">
         <v>-0.5777851299476033</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AO12" t="n">
+        <v>-7.176087801087803</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.6155612064702973</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-2.204960443596804</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-108100000</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.400000000000006</v>
+      </c>
+      <c r="AT12" t="n">
         <v>-0.7067397751837112</v>
       </c>
-      <c r="AM12" t="n">
-        <v>-0.6155612064702973</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-108100000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-25192682.06540934</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
+        <v>-12433420.79729322</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-5.673591925914579</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-329</v>
+      </c>
+      <c r="AX12" t="n">
         <v>-0.579377693014056</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-341</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.400000000000006</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-7.176087801087803</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-12433420.79729322</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-7.201993713357325</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-3.199999999999999</v>
       </c>
       <c r="AY12" t="n">
         <v>-1.080363464402353</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-2.204960443596804</v>
+        <v>-3.199999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>-5.673591925914579</v>
+        <v>-341</v>
       </c>
       <c r="BB12" t="n">
+        <v>-25192682.06540934</v>
+      </c>
+      <c r="BC12" t="n">
         <v>-6.225626207845892</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-329</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -2291,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2</v>
+        <v>-0.1699999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
@@ -2302,19 +2546,19 @@
       <c r="V13" t="n">
         <v>-4</v>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-0.1699999999999999</v>
-      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
-        <v>-3</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
         <v>2</v>
@@ -2323,16 +2567,16 @@
         <v>-2.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>-3</v>
       </c>
       <c r="AH13" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
         <v>78</v>
@@ -2341,61 +2585,61 @@
         <v>74.54166666666666</v>
       </c>
       <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.9969416386082912</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
         <v>-0.7765857807581895</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AO13" t="n">
+        <v>2.205938169574537</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.09731915110703016</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.286781961024388</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AT13" t="n">
         <v>-0.07716868061695648</v>
       </c>
-      <c r="AM13" t="n">
-        <v>0.09731915110703016</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>249960.2081420254</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="n">
+      <c r="AU13" t="n">
+        <v>-109549.4378609895</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.1105118521325323</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AX13" t="n">
         <v>-0.4565962656871747</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.205938169574537</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-109549.4378609895</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.9969416386082912</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
       </c>
       <c r="AY13" t="n">
         <v>-0.4597616508650901</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.286781961024388</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0.1105118521325323</v>
+        <v>-1</v>
       </c>
       <c r="BB13" t="n">
+        <v>249960.2081420254</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.783415773243377</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-1</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -2462,74 +2706,106 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>69.67171717171718</v>
+      </c>
       <c r="AK14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>6.427520661157004</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="n">
         <v>0.4927709267273741</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AO14" t="n">
+        <v>4.594710743801642</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.054669421487604</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-1.853450413223101</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-9625000</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
         <v>0.8497862631908168</v>
       </c>
-      <c r="AM14" t="n">
-        <v>1.054669421487604</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>-9625000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>16962179.75206611</v>
-      </c>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="n">
+      <c r="AU14" t="n">
+        <v>14672747.01003867</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6.701296206360141</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-280</v>
+      </c>
+      <c r="AX14" t="n">
         <v>0.8453305785123959</v>
       </c>
-      <c r="AR14" t="n">
-        <v>-287</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="n">
-        <v>4.594710743801642</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>14672747.01003867</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>6.427520661157004</v>
-      </c>
-      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="n">
         <v>0.6679386916010515</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>-1.853450413223101</v>
-      </c>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
-        <v>6.701296206360141</v>
+        <v>-287</v>
       </c>
       <c r="BB14" t="n">
+        <v>16962179.75206611</v>
+      </c>
+      <c r="BC14" t="n">
         <v>5.816963620334761</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>-280</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -2596,76 +2872,106 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>5</v>
+      </c>
       <c r="AI15" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="AJ15" t="inlineStr"/>
+        <v>70.77500000000001</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>73.45454545454545</v>
+      </c>
       <c r="AK15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>5.646280991735537</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
         <v>1.826825898487471</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AO15" t="n">
+        <v>2.890909090909091</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.4479338842975209</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-3.307438016528891</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-29400000</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
         <v>0.3104683394598959</v>
       </c>
-      <c r="AM15" t="n">
-        <v>0.4479338842975209</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>-29400000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>23846033.05785124</v>
-      </c>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="n">
+      <c r="AU15" t="n">
+        <v>8268656.74503216</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.50303342235604</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-216</v>
+      </c>
+      <c r="AX15" t="n">
         <v>1.738016528925623</v>
       </c>
-      <c r="AR15" t="n">
-        <v>-237</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="n">
-        <v>2.890909090909091</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8268656.74503216</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.646280991735537</v>
-      </c>
-      <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="n">
         <v>-3.537998793449106</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>-3.307438016528891</v>
-      </c>
+      <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
-        <v>4.50303342235604</v>
+        <v>-237</v>
       </c>
       <c r="BB15" t="n">
+        <v>23846033.05785124</v>
+      </c>
+      <c r="BC15" t="n">
         <v>1.009442190711397</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>-216</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -2732,82 +3038,112 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.6200000000000001</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-2</v>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>69.55555555555556</v>
+      </c>
       <c r="AJ16" t="n">
         <v>72.7</v>
       </c>
       <c r="AK16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6.457825507825518</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
         <v>-0.5890392451726392</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AO16" t="n">
+        <v>5.252014652014651</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.6017038517038513</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.923981573981564</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>21875000</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>9.166666666666657</v>
+      </c>
+      <c r="AT16" t="n">
         <v>0.5104853420916944</v>
       </c>
-      <c r="AM16" t="n">
-        <v>0.6017038517038513</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>21875000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>10022199.74469975</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
+      <c r="AU16" t="n">
+        <v>9920911.024466714</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7.176820518546464</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-54</v>
+      </c>
+      <c r="AX16" t="n">
         <v>1.087456987456985</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>-64</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.166666666666657</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.252014652014651</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9920911.024466714</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6.457825507825518</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>-0.8333333333333321</v>
       </c>
       <c r="AY16" t="n">
         <v>-0.1569594031675763</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0.923981573981564</v>
+        <v>-0.8333333333333321</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.176820518546464</v>
+        <v>-64</v>
       </c>
       <c r="BB16" t="n">
+        <v>10022199.74469975</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6.913714444311751</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>-54</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -2875,107 +3211,111 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
         <v>-2</v>
       </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>7</v>
+        <v>-17.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>-1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AH17" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>66.40000000000001</v>
+        <v>73.92727272727274</v>
       </c>
       <c r="AJ17" t="n">
         <v>71.875</v>
       </c>
       <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-2.1172373081464</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AN17" t="n">
         <v>-0.55623614967487</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AO17" t="n">
+        <v>-2.385891381345928</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.2678866587957498</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-1.234415584415586</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-24400000</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AT17" t="n">
         <v>-0.1928998979817507</v>
       </c>
-      <c r="AM17" t="n">
-        <v>-0.2678866587957498</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>-24400000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>-5505448.642266823</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="AU17" t="n">
+        <v>-7424273.627688604</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-3.004709976492322</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AX17" t="n">
         <v>0.05560802833530687</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>-2.385891381345928</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>-7424273.627688604</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>-2.1172373081464</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>-4</v>
       </c>
       <c r="AY17" t="n">
         <v>-1.571812791359406</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-1.234415584415586</v>
+        <v>-4</v>
       </c>
       <c r="BA17" t="n">
-        <v>-3.004709976492322</v>
+        <v>-11</v>
       </c>
       <c r="BB17" t="n">
+        <v>-5505448.642266823</v>
+      </c>
+      <c r="BC17" t="n">
         <v>-2.748537459663112</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>-27</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD17"/>
+  <dimension ref="A1:BD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,74 +520,74 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -771,46 +771,42 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.1699999999999999</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AF2" t="n">
         <v>-0.5800000000000001</v>
-      </c>
-      <c r="U2" t="n">
-        <v>6</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-11</v>
       </c>
       <c r="AG2" t="n">
         <v>-2</v>
@@ -822,50 +818,50 @@
         <v>72.69358356290175</v>
       </c>
       <c r="AJ2" t="n">
-        <v>72.20123966942148</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>72.27272727272727</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.4427894327894322</v>
+      </c>
       <c r="AL2" t="n">
-        <v>1.656888111888108</v>
+        <v>-0.2191362231877498</v>
       </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
+        <v>8704756.216006216</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>1.656888111888108</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.05843936427047</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.119131701631687</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>0.9298599087084511</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-0.05079903081303883</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-1730318.318283005</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>3.113310023310035</v>
+      </c>
+      <c r="BB2" t="n">
         <v>-0.5026953094892797</v>
       </c>
-      <c r="AO2" t="n">
-        <v>3.113310023310035</v>
-      </c>
-      <c r="AP2" t="n">
+      <c r="BC2" t="n">
         <v>-0.331899766899767</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4.119131701631687</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>-0.2191362231877498</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-1730318.318283005</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-0.05079903081303883</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>-0.4427894327894322</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.05843936427047</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>8704756.216006216</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.9298599087084511</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -929,42 +925,42 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>4.833333333333334</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.7250000000000001</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AF3" t="n">
         <v>0.7199999999999998</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.833333333333333</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>4.833333333333334</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.666666666666666</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3.166666666666666</v>
       </c>
       <c r="AG3" t="n">
         <v>-10</v>
@@ -978,48 +974,48 @@
       <c r="AJ3" t="n">
         <v>73.75505050505051</v>
       </c>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>-0.8150673400673405</v>
+      </c>
       <c r="AL3" t="n">
-        <v>2.135578002244657</v>
+        <v>-0.1865803702904087</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
+        <v>1463341.75084175</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>2.135578002244657</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.647721139789752</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.290432098765422</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>2.342071268557319</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>0.9330782762909848</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>466572.0514082243</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="n">
+        <v>3.417508417508429</v>
+      </c>
+      <c r="BB3" t="n">
         <v>-1.093853189385047</v>
       </c>
-      <c r="AO3" t="n">
-        <v>3.417508417508429</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="BC3" t="n">
         <v>-0.03835578002244655</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.290432098765422</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="n">
-        <v>-0.1865803702904087</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>466572.0514082243</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.9330782762909848</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>-0.8150673400673405</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-0.647721139789752</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>1463341.75084175</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.342071268557319</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1035,7 +1031,7 @@
         <v>45536.5625</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
@@ -1066,10 +1062,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="M4" t="n">
-        <v>55</v>
+        <v>235</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -1087,101 +1083,101 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.46</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5</v>
+        <v>-0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>5.166666666666666</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>7</v>
+        <v>0.3350000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>-4.166666666666664</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="AI4" t="n">
-        <v>69.74606782106781</v>
+        <v>69.77777777777777</v>
       </c>
       <c r="AJ4" t="n">
-        <v>69.40909090909091</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>70.77272727272727</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.6175685425685415</v>
+      </c>
       <c r="AL4" t="n">
-        <v>3.160521296884937</v>
+        <v>0.242699100825235</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>-0.7223782477123599</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.17889383343929</v>
-      </c>
+        <v>6001111.111111113</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>0.2407501589319769</v>
+        <v>3.188636363636377</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.0220597584234099</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>-0.3212259736350802</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.0870490620490898</v>
+      </c>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>0.2676963131699428</v>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>7194801.438642818</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.970661242011261</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>2.706803883754375</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>2.878163096580252</v>
+      </c>
       <c r="AX4" t="n">
-        <v>0.6810553083280304</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-0.4032480669210941</v>
-      </c>
+        <v>7231570.974917667</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>2.304653679653683</v>
+      </c>
       <c r="BB4" t="n">
-        <v>5726916.719643994</v>
+        <v>-0.845468987634824</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.620894635628929</v>
+        <v>0.2060245310245306</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1228,7 +1224,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>223</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
         <v>8</v>
@@ -1249,97 +1245,101 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1100000000000003</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.49</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.5</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.833333333333333</v>
+      </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>-0.3333333333333334</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6666666666666667</v>
+        <v>3.833333333333334</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.8333333333333333</v>
+        <v>-3</v>
       </c>
       <c r="AE5" t="n">
-        <v>5</v>
+        <v>-0.6499999999999997</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2</v>
+        <v>-0.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-4.333333333333336</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.333333333333336</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.36931818181819</v>
+        <v>73.00378787878788</v>
       </c>
       <c r="AJ5" t="n">
         <v>80.45708041958042</v>
       </c>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>1.180348943985308</v>
+      </c>
       <c r="AL5" t="n">
-        <v>0.01675849403120822</v>
+        <v>0.3526943454149336</v>
       </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>2.307398418574884</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.7697199265381016</v>
-      </c>
+        <v>1143910.69788797</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>0.06717171717171722</v>
+        <v>0.05601469237832646</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.03514692378331574</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>2.091360012536484</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.0404499540863128</v>
+      </c>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="n">
-        <v>0.3518154938743174</v>
-      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>109509.2342298217</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.2322978546507812</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>-1.30817441001264</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>-0.1931698094933267</v>
+      </c>
       <c r="AX5" t="n">
-        <v>1.137167125803487</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2.06309416074123</v>
-      </c>
+        <v>117037.8820525873</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>0.7853535353535364</v>
+      </c>
       <c r="BB5" t="n">
-        <v>1205456.841138659</v>
+        <v>2.286326459488219</v>
       </c>
       <c r="BC5" t="n">
-        <v>-1.30920201802553</v>
+        <v>0.06655188246097343</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1407,46 +1407,46 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
         <v>-0.3299999999999998</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AF6" t="n">
         <v>-0.8600000000000001</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>3</v>
       </c>
       <c r="AG6" t="n">
         <v>5</v>
@@ -1460,48 +1460,48 @@
       <c r="AJ6" t="n">
         <v>72.57777777777778</v>
       </c>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>1.462329589602327</v>
+      </c>
       <c r="AL6" t="n">
-        <v>-2.966228720774183</v>
+        <v>0.2227540088524074</v>
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
+        <v>-17003895.24616798</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>-2.966228720774183</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.745136997082028</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.5085470085470547</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>-2.837270656710004</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>-0.3062353952514201</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-6995724.231104091</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>-4.26287349014622</v>
+      </c>
+      <c r="BB6" t="n">
         <v>2.100753155650178</v>
       </c>
-      <c r="AO6" t="n">
-        <v>-4.26287349014622</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="BC6" t="n">
         <v>-0.07219749947022636</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.5085470085470547</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="n">
-        <v>0.2227540088524074</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-6995724.231104091</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.3062353952514201</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>1.462329589602327</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-1.745136997082028</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>-17003895.24616798</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-2.837270656710004</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -1565,46 +1565,46 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-8.333333333333334</v>
+      </c>
+      <c r="AE7" t="n">
         <v>-0.46</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AF7" t="n">
         <v>0.5049999999999999</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.833333333333333</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>9.166666666666666</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-8.333333333333334</v>
       </c>
       <c r="AG7" t="n">
         <v>29</v>
@@ -1613,53 +1613,53 @@
         <v>-29</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.22575757575758</v>
+        <v>70.77500000000001</v>
       </c>
       <c r="AJ7" t="n">
         <v>76.16666666666667</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AK7" t="n">
+        <v>2.118365472910927</v>
+      </c>
       <c r="AL7" t="n">
-        <v>11.03535353535354</v>
+        <v>0.4012203796901967</v>
       </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
+        <v>31852915.51882461</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>11.03535353535354</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-2.593562232342379</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-2.657116620752987</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>5.32338014836148</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>7.612933825190467</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12779978.7425277</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>6.76666666666668</v>
+      </c>
+      <c r="BB7" t="n">
         <v>0.2923619949635992</v>
       </c>
-      <c r="AO7" t="n">
-        <v>6.76666666666668</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="BC7" t="n">
         <v>0.6768595041322318</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-2.657116620752987</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="n">
-        <v>0.4012203796901967</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>12779978.7425277</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7.612933825190467</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>2.118365472910927</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-2.593562232342379</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>31852915.51882461</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.32338014836148</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -1668,23 +1668,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45535.5625</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -1706,19 +1706,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>95</v>
+        <v>227</v>
       </c>
       <c r="M8" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1727,97 +1727,97 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4099999999999999</v>
+        <v>-1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+        <v>-1.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1666666666666667</v>
+        <v>6.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.8333333333333334</v>
+        <v>-1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>-3</v>
+        <v>0.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>-5.5</v>
+        <v>26</v>
       </c>
       <c r="AH8" t="n">
-        <v>5.5</v>
+        <v>-26</v>
       </c>
       <c r="AI8" t="n">
-        <v>76.90000000000001</v>
+        <v>73.45454545454545</v>
       </c>
       <c r="AJ8" t="n">
-        <v>74.59243827160495</v>
-      </c>
-      <c r="AK8" t="inlineStr"/>
+        <v>69.67171717171718</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.5396694214876092</v>
+      </c>
       <c r="AL8" t="n">
-        <v>-0.1632231404958731</v>
+        <v>0.08860531051440135</v>
       </c>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>-2.628120443981942</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2.010330578512409</v>
-      </c>
+        <v>6752975.206611572</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>-0.1735537190082646</v>
+        <v>2.997520661157012</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.1508264462809734</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+        <v>2.608819499205111</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.377685950413223</v>
+      </c>
       <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="n">
-        <v>-0.115765413542434</v>
-      </c>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>-55628.53160742205</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-1.924883999294309</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
+        <v>3.2976648587683</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>1.70564804196151</v>
+      </c>
       <c r="AX8" t="n">
-        <v>-1.355371900826444</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-0.6918096398586613</v>
-      </c>
+        <v>4056428.43130108</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>3.471074380165291</v>
+      </c>
       <c r="BB8" t="n">
-        <v>1595247.933884298</v>
+        <v>-1.770989053092499</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.6088112887330226</v>
+        <v>0.2487603305785127</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -1826,23 +1826,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
         <v>45535.5625</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="M9" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
       </c>
       <c r="O9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1885,13 +1885,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="T9" t="n">
-        <v>0.43</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1900,86 +1900,86 @@
         <v>-1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AC9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AC9" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.3333333333333334</v>
-      </c>
       <c r="AE9" t="n">
-        <v>6.5</v>
+        <v>0.0149999999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1.5</v>
+        <v>0.8399999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>-6.666666666666664</v>
       </c>
       <c r="AH9" t="n">
-        <v>-26</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.11404958677686</v>
+        <v>80.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>72.63356902356902</v>
-      </c>
-      <c r="AK9" t="inlineStr"/>
+        <v>74.59243827160495</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.373201714110802</v>
+      </c>
       <c r="AL9" t="n">
-        <v>2.997520661157012</v>
+        <v>-0.1209633644716102</v>
       </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>-1.770989053092499</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>3.471074380165291</v>
-      </c>
+        <v>1599181.205999389</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>0.2487603305785127</v>
+        <v>-0.1740319865320004</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.377685950413223</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
+        <v>-0.5794406021852865</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.4432774716865708</v>
+      </c>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="n">
-        <v>0.08860531051440135</v>
-      </c>
+      <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>4056428.43130108</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.70564804196151</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
+        <v>0.6193529513789002</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>-2.015143131592524</v>
+      </c>
       <c r="AX9" t="n">
-        <v>-0.5396694214876092</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>2.608819499205111</v>
-      </c>
+        <v>-49765.20917114615</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>2.031814355677994</v>
+      </c>
       <c r="BB9" t="n">
-        <v>6752975.206611572</v>
+        <v>-2.681585441527446</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.2976648587683</v>
+        <v>-0.1735537190082646</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>45534.65625</v>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D10" t="n">
         <v>41</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="M10" t="n">
         <v>64</v>
@@ -2047,97 +2047,97 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="AA10" t="n">
-        <v>-10</v>
+        <v>-0.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1</v>
+        <v>-4.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
       <c r="AE10" t="n">
-        <v>4</v>
+        <v>-0.835</v>
       </c>
       <c r="AF10" t="n">
-        <v>-9</v>
+        <v>-0.6299999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>-15</v>
+        <v>-9.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>73.59999999999999</v>
+        <v>72.74444444444444</v>
       </c>
       <c r="AJ10" t="n">
-        <v>73.98212809917356</v>
-      </c>
-      <c r="AK10" t="inlineStr"/>
+        <v>73.65972222222223</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.201873278236913</v>
+      </c>
       <c r="AL10" t="n">
-        <v>4.614415584415582</v>
+        <v>0.5372603429849805</v>
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="n">
-        <v>1.753072090435442</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>3.15220779220779</v>
-      </c>
+        <v>21284435.26170798</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>0.8655844155844155</v>
+        <v>4.759008264462793</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-4.230779220779198</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
+        <v>-4.08999842883901</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-4.30986225895316</v>
+      </c>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>0.5199947734575063</v>
-      </c>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="n">
-        <v>10845701.11836059</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.162812977797444</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
+        <v>2.662928855899878</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>4.234473844459359</v>
+      </c>
       <c r="AX10" t="n">
-        <v>2.077012987012989</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-4.156263204474328</v>
-      </c>
+        <v>10973105.98543164</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>3.205123966942139</v>
+      </c>
       <c r="BB10" t="n">
-        <v>21244220.77922078</v>
+        <v>1.741623992218194</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.648070815198139</v>
+        <v>0.8928374655647382</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
         <v>45534.5625</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="D11" t="n">
         <v>62</v>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="M11" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="N11" t="n">
         <v>4</v>
@@ -2205,97 +2205,97 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.03</v>
+        <v>-2</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3800000000000003</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11" t="n">
         <v>2</v>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.333333333333333</v>
+      </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
         <v>3</v>
       </c>
-      <c r="AC11" t="n">
-        <v>-1.333333333333333</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.666666666666667</v>
+        <v>-8.333333333333334</v>
       </c>
       <c r="AE11" t="n">
-        <v>7.5</v>
+        <v>-1.625</v>
       </c>
       <c r="AF11" t="n">
-        <v>-6.5</v>
+        <v>-1.015</v>
       </c>
       <c r="AG11" t="n">
-        <v>-4.5</v>
+        <v>-2.666666666666664</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.5</v>
+        <v>2.666666666666664</v>
       </c>
       <c r="AI11" t="n">
-        <v>73.93146853146854</v>
+        <v>73.6888888888889</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75.35367965367965</v>
-      </c>
-      <c r="AK11" t="inlineStr"/>
+        <v>74.98484848484848</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.8519360269360305</v>
+      </c>
       <c r="AL11" t="n">
-        <v>-6.152676111767036</v>
+        <v>-0.1216650216541857</v>
       </c>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>0.715711899095858</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-4.753286107831556</v>
-      </c>
+        <v>-10309681.81818182</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
-        <v>-0.246904105995015</v>
+        <v>-6.094713804713805</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.38650793650794</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
+        <v>-2.868834768400291</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.469191919191928</v>
+      </c>
       <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="n">
-        <v>-0.1334582573507423</v>
-      </c>
+      <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="n">
-        <v>-4157362.913029947</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-4.433871272480388</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
+        <v>-3.6536741218641</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>-4.376690792344917</v>
+      </c>
       <c r="AX11" t="n">
-        <v>-0.8064016791289532</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-3.10065423739232</v>
-      </c>
+        <v>-4126247.598044208</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>-4.613939393939404</v>
+      </c>
       <c r="BB11" t="n">
-        <v>-10488754.09943592</v>
+        <v>0.7086853030228824</v>
       </c>
       <c r="BC11" t="n">
-        <v>-3.72729458120898</v>
+        <v>-0.2477946127946127</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -2363,42 +2363,42 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
         <v>0.6499999999999999</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AF12" t="n">
         <v>1.07</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13</v>
       </c>
       <c r="AG12" t="n">
         <v>-12</v>
@@ -2413,61 +2413,61 @@
         <v>72.375</v>
       </c>
       <c r="AK12" t="n">
-        <v>-4</v>
+        <v>-0.579377693014056</v>
       </c>
       <c r="AL12" t="n">
+        <v>-0.7067397751837112</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-25192682.06540934</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-254</v>
+      </c>
+      <c r="AP12" t="n">
         <v>-7.201993713357325</v>
       </c>
-      <c r="AM12" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="n">
+        <v>-1.080363464402353</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-2.204960443596804</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-253</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-6.225626207845892</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-94600000</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-5.673591925914579</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-12433420.79729322</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-7.176087801087803</v>
+      </c>
+      <c r="BB12" t="n">
         <v>-0.5777851299476033</v>
       </c>
-      <c r="AO12" t="n">
-        <v>-7.176087801087803</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="BC12" t="n">
         <v>-0.6155612064702973</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-2.204960443596804</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-108100000</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.400000000000006</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-0.7067397751837112</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-12433420.79729322</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-5.673591925914579</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-329</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-0.579377693014056</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-1.080363464402353</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-3.199999999999999</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-341</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-25192682.06540934</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-6.225626207845892</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -2535,42 +2535,42 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE13" t="n">
         <v>0.5800000000000001</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AF13" t="n">
         <v>-0.1699999999999999</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-2</v>
       </c>
       <c r="AG13" t="n">
         <v>-3</v>
@@ -2585,739 +2585,63 @@
         <v>74.54166666666666</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0.4565962656871747</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.9969416386082912</v>
+        <v>-0.07716868061695648</v>
       </c>
       <c r="AM13" t="n">
         <v>1</v>
       </c>
       <c r="AN13" t="n">
+        <v>249960.2081420254</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.9969416386082912</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.4597616508650901</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.286781961024388</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.783415773243377</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.1105118521325323</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-109549.4378609895</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.205938169574537</v>
+      </c>
+      <c r="BB13" t="n">
         <v>-0.7765857807581895</v>
       </c>
-      <c r="AO13" t="n">
-        <v>2.205938169574537</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="BC13" t="n">
         <v>0.09731915110703016</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>3.286781961024388</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-0.07716868061695648</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-109549.4378609895</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-0.1105118521325323</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-0.4565962656871747</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>-0.4597616508650901</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>249960.2081420254</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.783415773243377</v>
-      </c>
       <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>UilLdutJ</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C14" t="n">
-        <v>131</v>
-      </c>
-      <c r="D14" t="n">
-        <v>55</v>
-      </c>
-      <c r="E14" t="n">
-        <v>140</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>77</v>
-      </c>
-      <c r="H14" t="n">
-        <v>771</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>99</v>
-      </c>
-      <c r="M14" t="n">
-        <v>55</v>
-      </c>
-      <c r="N14" t="n">
-        <v>17</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>72.27272727272727</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>69.67171717171718</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>6.427520661157004</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="n">
-        <v>0.4927709267273741</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>4.594710743801642</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.054669421487604</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>-1.853450413223101</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>-9625000</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="n">
-        <v>0.8497862631908168</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>14672747.01003867</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6.701296206360141</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-280</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0.8453305785123959</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0.6679386916010515</v>
-      </c>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="n">
-        <v>-287</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>16962179.75206611</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.816963620334761</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2uc40Ntf</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C15" t="n">
-        <v>87</v>
-      </c>
-      <c r="D15" t="n">
-        <v>33</v>
-      </c>
-      <c r="E15" t="n">
-        <v>15</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>77</v>
-      </c>
-      <c r="H15" t="n">
-        <v>771</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>110</v>
-      </c>
-      <c r="M15" t="n">
-        <v>268</v>
-      </c>
-      <c r="N15" t="n">
-        <v>11</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>70.77500000000001</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>73.45454545454545</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>5.646280991735537</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="n">
-        <v>1.826825898487471</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>2.890909090909091</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.4479338842975209</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>-3.307438016528891</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>-29400000</v>
-      </c>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="n">
-        <v>0.3104683394598959</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8268656.74503216</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.50303342235604</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>-216</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.738016528925623</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-3.537998793449106</v>
-      </c>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="n">
-        <v>-237</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>23846033.05785124</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.009442190711397</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>M7MVoOR0</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45529.5625</v>
-      </c>
-      <c r="C16" t="n">
-        <v>120</v>
-      </c>
-      <c r="D16" t="n">
-        <v>19</v>
-      </c>
-      <c r="E16" t="n">
-        <v>56</v>
-      </c>
-      <c r="F16" t="n">
-        <v>74</v>
-      </c>
-      <c r="G16" t="n">
-        <v>77</v>
-      </c>
-      <c r="H16" t="n">
-        <v>771</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>186</v>
-      </c>
-      <c r="M16" t="n">
-        <v>204</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.6200000000000001</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>69.55555555555556</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>6.457825507825518</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>-0.5890392451726392</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>5.252014652014651</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0.6017038517038513</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>-0.923981573981564</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>21875000</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.166666666666657</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.5104853420916944</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>9920911.024466714</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>7.176820518546464</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>-54</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.087456987456985</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>-0.1569594031675763</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>-0.8333333333333321</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>-64</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>10022199.74469975</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>6.913714444311751</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dbt7KrYP</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45529.5625</v>
-      </c>
-      <c r="C17" t="n">
-        <v>103</v>
-      </c>
-      <c r="D17" t="n">
-        <v>56</v>
-      </c>
-      <c r="E17" t="n">
-        <v>51</v>
-      </c>
-      <c r="F17" t="n">
-        <v>30</v>
-      </c>
-      <c r="G17" t="n">
-        <v>77</v>
-      </c>
-      <c r="H17" t="n">
-        <v>771</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>91</v>
-      </c>
-      <c r="M17" t="n">
-        <v>64</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.8799999999999999</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>73.92727272727274</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>71.875</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>-2.1172373081464</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>-0.55623614967487</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>-2.385891381345928</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>-0.2678866587957498</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>-1.234415584415586</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>-24400000</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>-0.1928998979817507</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>-7424273.627688604</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>-3.004709976492322</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>-27</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.05560802833530687</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>-1.571812791359406</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>-11</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>-5505448.642266823</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>-2.748537459663112</v>
-      </c>
-      <c r="BD17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -771,24 +771,28 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>0.1699999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-9</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1</v>
+        <v>-11</v>
       </c>
       <c r="AA2" t="n">
         <v>3</v>
@@ -796,23 +800,19 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="n">
         <v>-1</v>
       </c>
-      <c r="AD2" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.1699999999999999</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-0.5800000000000001</v>
-      </c>
       <c r="AG2" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="AI2" t="n">
         <v>72.69358356290175</v>
@@ -821,48 +821,48 @@
         <v>72.27272727272727</v>
       </c>
       <c r="AK2" t="n">
+        <v>-0.5026953094892797</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-0.331899766899767</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
         <v>-0.4427894327894322</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>4.119131701631687</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>-1730318.318283005</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.113310023310035</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.656888111888108</v>
+      </c>
+      <c r="AW2" t="n">
         <v>-0.2191362231877498</v>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
+      <c r="AX2" t="n">
+        <v>0.9298599087084511</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8704756.216006216</v>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>1.656888111888108</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.05843936427047</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.119131701631687</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>0.9298599087084511</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>-0.05079903081303883</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-1730318.318283005</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>3.113310023310035</v>
+        <v>1.05843936427047</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.5026953094892797</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.331899766899767</v>
-      </c>
+        <v>-0.05079903081303883</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -925,24 +925,28 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>-2</v>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>4.833333333333334</v>
+        <v>0.7250000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>3.666666666666666</v>
+        <v>0.7199999999999998</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>3.333333333333334</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.666666666666667</v>
+        <v>3.166666666666666</v>
       </c>
       <c r="AA3" t="n">
         <v>1.833333333333333</v>
@@ -950,23 +954,19 @@
       <c r="AB3" t="n">
         <v>-1.833333333333333</v>
       </c>
-      <c r="AC3" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.166666666666666</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>0.7250000000000001</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7199999999999998</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AG3" t="n">
-        <v>-10</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>3.666666666666666</v>
       </c>
       <c r="AI3" t="n">
         <v>77.13636363636363</v>
@@ -975,48 +975,48 @@
         <v>73.75505050505051</v>
       </c>
       <c r="AK3" t="n">
+        <v>-1.093853189385047</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.03835578002244655</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
         <v>-0.8150673400673405</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>5.290432098765422</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>466572.0514082243</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.417508417508429</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.135578002244657</v>
+      </c>
+      <c r="AW3" t="n">
         <v>-0.1865803702904087</v>
       </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="n">
+      <c r="AX3" t="n">
+        <v>2.342071268557319</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1463341.75084175</v>
       </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>2.135578002244657</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.647721139789752</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>5.290432098765422</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="n">
-        <v>2.342071268557319</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="n">
-        <v>0.9330782762909848</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>466572.0514082243</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>3.417508417508429</v>
+        <v>-0.647721139789752</v>
       </c>
       <c r="BB3" t="n">
-        <v>-1.093853189385047</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-0.03835578002244655</v>
-      </c>
+        <v>0.9330782762909848</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
@@ -1083,28 +1083,28 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
+        <v>-4.166666666666664</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.166666666666664</v>
+      </c>
+      <c r="U4" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="U4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
-        <v>-2.333333333333334</v>
+        <v>0.6</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>0.3350000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.166666666666666</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.833333333333333</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AA4" t="n">
         <v>0.1666666666666667</v>
@@ -1113,22 +1113,22 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6</v>
+        <v>5.166666666666666</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3350000000000001</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4.166666666666664</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.166666666666664</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>69.77777777777777</v>
@@ -1137,48 +1137,48 @@
         <v>70.77272727272727</v>
       </c>
       <c r="AK4" t="n">
+        <v>-0.845468987634824</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2060245310245306</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
         <v>0.6175685425685415</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0.0870490620490898</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>7231570.974917667</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.304653679653683</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.188636363636377</v>
+      </c>
+      <c r="AW4" t="n">
         <v>0.242699100825235</v>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="n">
+      <c r="AX4" t="n">
+        <v>2.706803883754375</v>
+      </c>
+      <c r="AY4" t="n">
         <v>6001111.111111113</v>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>3.188636363636377</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-0.3212259736350802</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.0870490620490898</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="n">
-        <v>2.706803883754375</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="n">
-        <v>2.878163096580252</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7231570.974917667</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>2.304653679653683</v>
+        <v>-0.3212259736350802</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.845468987634824</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.2060245310245306</v>
-      </c>
+        <v>2.878163096580252</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
@@ -1245,28 +1245,28 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>-1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>-0.6499999999999997</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3333333333333339</v>
+        <v>-0.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.666666666666667</v>
+        <v>3.833333333333334</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.833333333333333</v>
+        <v>-3</v>
       </c>
       <c r="AA5" t="n">
         <v>-0.6666666666666667</v>
@@ -1275,22 +1275,22 @@
         <v>-0.3333333333333334</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.833333333333334</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.6499999999999997</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.2</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4.333333333333336</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.333333333333336</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="AI5" t="n">
         <v>73.00378787878788</v>
@@ -1299,48 +1299,48 @@
         <v>80.45708041958042</v>
       </c>
       <c r="AK5" t="n">
+        <v>2.286326459488219</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.06655188246097343</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
         <v>1.180348943985308</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>0.0404499540863128</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>117037.8820525873</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.7853535353535364</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.05601469237832646</v>
+      </c>
+      <c r="AW5" t="n">
         <v>0.3526943454149336</v>
       </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="n">
+      <c r="AX5" t="n">
+        <v>-1.30817441001264</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1143910.69788797</v>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>0.05601469237832646</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2.091360012536484</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.0404499540863128</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="n">
-        <v>-1.30817441001264</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="n">
-        <v>-0.1931698094933267</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>117037.8820525873</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>0.7853535353535364</v>
+        <v>2.091360012536484</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.286326459488219</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.06655188246097343</v>
-      </c>
+        <v>-0.1931698094933267</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
@@ -1407,28 +1407,28 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>-0.3299999999999998</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.5</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
         <v>0.5</v>
@@ -1437,22 +1437,22 @@
         <v>-0.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.3299999999999998</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.8600000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>-5</v>
+        <v>5.5</v>
       </c>
       <c r="AI6" t="n">
         <v>71.59999999999999</v>
@@ -1461,48 +1461,48 @@
         <v>72.57777777777778</v>
       </c>
       <c r="AK6" t="n">
+        <v>2.100753155650178</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.07219749947022636</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
         <v>1.462329589602327</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>-0.5085470085470547</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>-6995724.231104091</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-4.26287349014622</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-2.966228720774183</v>
+      </c>
+      <c r="AW6" t="n">
         <v>0.2227540088524074</v>
       </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="n">
+      <c r="AX6" t="n">
+        <v>-2.837270656710004</v>
+      </c>
+      <c r="AY6" t="n">
         <v>-17003895.24616798</v>
       </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
-        <v>-2.966228720774183</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-1.745136997082028</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-0.5085470085470547</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="n">
-        <v>-2.837270656710004</v>
-      </c>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="n">
-        <v>-0.3062353952514201</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-6995724.231104091</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>-4.26287349014622</v>
+        <v>-1.745136997082028</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.100753155650178</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.07219749947022636</v>
-      </c>
+        <v>-0.3062353952514201</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
@@ -1565,28 +1565,28 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-29</v>
+      </c>
+      <c r="U7" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="U7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>-0.46</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1666666666666661</v>
+        <v>0.5049999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.833333333333333</v>
+        <v>-8.333333333333334</v>
       </c>
       <c r="AA7" t="n">
         <v>-0.5</v>
@@ -1595,22 +1595,22 @@
         <v>0.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.166666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>-8.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.46</v>
+        <v>0.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5049999999999999</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="AG7" t="n">
-        <v>29</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>-29</v>
+        <v>0.1666666666666661</v>
       </c>
       <c r="AI7" t="n">
         <v>70.77500000000001</v>
@@ -1619,48 +1619,48 @@
         <v>76.16666666666667</v>
       </c>
       <c r="AK7" t="n">
+        <v>0.2923619949635992</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.6768595041322318</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
         <v>2.118365472910927</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-2.657116620752987</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>12779978.7425277</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.76666666666668</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11.03535353535354</v>
+      </c>
+      <c r="AW7" t="n">
         <v>0.4012203796901967</v>
       </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="n">
+      <c r="AX7" t="n">
+        <v>5.32338014836148</v>
+      </c>
+      <c r="AY7" t="n">
         <v>31852915.51882461</v>
       </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
-        <v>11.03535353535354</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-2.593562232342379</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-2.657116620752987</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="n">
-        <v>5.32338014836148</v>
-      </c>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="n">
-        <v>7.612933825190467</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12779978.7425277</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>6.76666666666668</v>
+        <v>-2.593562232342379</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.2923619949635992</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.6768595041322318</v>
-      </c>
+        <v>7.612933825190467</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1727,24 +1727,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>26</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-26</v>
+      </c>
+      <c r="U8" t="n">
         <v>-1</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.5</v>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-1.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>-1</v>
@@ -1752,23 +1756,19 @@
       <c r="AB8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>-1.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-26</v>
       </c>
       <c r="AI8" t="n">
         <v>73.45454545454545</v>
@@ -1777,48 +1777,48 @@
         <v>69.67171717171718</v>
       </c>
       <c r="AK8" t="n">
+        <v>-1.770989053092499</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2487603305785127</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
         <v>-0.5396694214876092</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>1.377685950413223</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>4056428.43130108</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.471074380165291</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.997520661157012</v>
+      </c>
+      <c r="AW8" t="n">
         <v>0.08860531051440135</v>
       </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
+      <c r="AX8" t="n">
+        <v>3.2976648587683</v>
+      </c>
+      <c r="AY8" t="n">
         <v>6752975.206611572</v>
       </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>2.997520661157012</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2.608819499205111</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.377685950413223</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="n">
-        <v>3.2976648587683</v>
-      </c>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>1.70564804196151</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4056428.43130108</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
-        <v>3.471074380165291</v>
+        <v>2.608819499205111</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.770989053092499</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.2487603305785127</v>
-      </c>
+        <v>1.70564804196151</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
@@ -1885,28 +1885,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>-6.666666666666664</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.666666666666664</v>
+      </c>
+      <c r="U9" t="n">
         <v>-0.6666666666666667</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>-1</v>
+        <v>0.0149999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>0.8399999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.666666666666667</v>
+        <v>-1.5</v>
       </c>
       <c r="AA9" t="n">
         <v>-0.8333333333333334</v>
@@ -1915,22 +1915,22 @@
         <v>1.833333333333333</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0149999999999999</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.8399999999999999</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AG9" t="n">
-        <v>-6.666666666666664</v>
+        <v>-1</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.666666666666664</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>80.25</v>
@@ -1939,48 +1939,48 @@
         <v>74.59243827160495</v>
       </c>
       <c r="AK9" t="n">
+        <v>-2.681585441527446</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.1735537190082646</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
         <v>-1.373201714110802</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>-0.4432774716865708</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>-49765.20917114615</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.031814355677994</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0.1740319865320004</v>
+      </c>
+      <c r="AW9" t="n">
         <v>-0.1209633644716102</v>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
+      <c r="AX9" t="n">
+        <v>0.6193529513789002</v>
+      </c>
+      <c r="AY9" t="n">
         <v>1599181.205999389</v>
       </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>-0.1740319865320004</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-0.5794406021852865</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-0.4432774716865708</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="n">
-        <v>0.6193529513789002</v>
-      </c>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="n">
-        <v>-2.015143131592524</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-49765.20917114615</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
-        <v>2.031814355677994</v>
+        <v>-0.5794406021852865</v>
       </c>
       <c r="BB9" t="n">
-        <v>-2.681585441527446</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.1735537190082646</v>
-      </c>
+        <v>-2.015143131592524</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
@@ -2047,24 +2047,28 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="U10" t="n">
         <v>0.5</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>-1</v>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>-7</v>
+        <v>-0.835</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>-0.6299999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1</v>
+        <v>-4.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.5</v>
+        <v>-6</v>
       </c>
       <c r="AA10" t="n">
         <v>-0.5</v>
@@ -2072,23 +2076,19 @@
       <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-6</v>
-      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>-0.835</v>
+        <v>-1</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.6299999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>9.5</v>
+        <v>-7</v>
       </c>
       <c r="AH10" t="n">
-        <v>-9.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI10" t="n">
         <v>72.74444444444444</v>
@@ -2097,48 +2097,48 @@
         <v>73.65972222222223</v>
       </c>
       <c r="AK10" t="n">
+        <v>1.741623992218194</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.8928374655647382</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
         <v>2.201873278236913</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>-4.30986225895316</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>10973105.98543164</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.205123966942139</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.759008264462793</v>
+      </c>
+      <c r="AW10" t="n">
         <v>0.5372603429849805</v>
       </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
+      <c r="AX10" t="n">
+        <v>2.662928855899878</v>
+      </c>
+      <c r="AY10" t="n">
         <v>21284435.26170798</v>
       </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
-        <v>4.759008264462793</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-4.08999842883901</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-4.30986225895316</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="n">
-        <v>2.662928855899878</v>
-      </c>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="n">
-        <v>4.234473844459359</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10973105.98543164</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
-        <v>3.205123966942139</v>
+        <v>-4.089998428838982</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.741623992218194</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.8928374655647382</v>
-      </c>
+        <v>4.234473844459359</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
@@ -2205,24 +2205,28 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
+        <v>-2.666666666666664</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.666666666666664</v>
+      </c>
+      <c r="U11" t="n">
         <v>-2</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>2</v>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>7</v>
+        <v>-1.625</v>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>-1.015</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.333333333333333</v>
+        <v>-8.333333333333334</v>
       </c>
       <c r="AA11" t="n">
         <v>-1.333333333333333</v>
@@ -2230,23 +2234,19 @@
       <c r="AB11" t="n">
         <v>1</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-8.333333333333334</v>
-      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>-1.625</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AF11" t="n">
-        <v>-1.015</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="AG11" t="n">
-        <v>-2.666666666666664</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.666666666666664</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
         <v>73.6888888888889</v>
@@ -2255,48 +2255,48 @@
         <v>74.98484848484848</v>
       </c>
       <c r="AK11" t="n">
+        <v>0.7086853030228824</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.2477946127946127</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
         <v>-0.8519360269360305</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-1.469191919191928</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>-4126247.598044208</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-4.613939393939404</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-6.094713804713805</v>
+      </c>
+      <c r="AW11" t="n">
         <v>-0.1216650216541857</v>
       </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="n">
+      <c r="AX11" t="n">
+        <v>-3.6536741218641</v>
+      </c>
+      <c r="AY11" t="n">
         <v>-10309681.81818182</v>
       </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="n">
-        <v>-6.094713804713805</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-2.868834768400291</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-1.469191919191928</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="n">
-        <v>-3.6536741218641</v>
-      </c>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="n">
-        <v>-4.376690792344917</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>-4126247.598044208</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
-        <v>-4.613939393939404</v>
+        <v>-2.868834768400291</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.7086853030228824</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.2477946127946127</v>
-      </c>
+        <v>-4.376690792344917</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
         <v>0</v>
       </c>
@@ -2363,24 +2363,28 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
+        <v>-12</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12</v>
+      </c>
+      <c r="U12" t="n">
         <v>-1.5</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>1.5</v>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.5</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
         <v>-1</v>
@@ -2388,23 +2392,19 @@
       <c r="AB12" t="n">
         <v>1</v>
       </c>
-      <c r="AC12" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>13</v>
-      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>0.6499999999999999</v>
+        <v>-5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.07</v>
+        <v>3.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>-12</v>
+        <v>2.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
         <v>80.7</v>
@@ -2413,61 +2413,61 @@
         <v>72.375</v>
       </c>
       <c r="AK12" t="n">
+        <v>-0.5777851299476033</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.6155612064702973</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-94600000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO12" t="n">
         <v>-0.579377693014056</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AP12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-2.204960443596804</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-253</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-12433420.79729322</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-7.176087801087803</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-7.201993713357325</v>
+      </c>
+      <c r="AW12" t="n">
         <v>-0.7067397751837112</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AX12" t="n">
+        <v>-6.225626207845892</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-25192682.06540934</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-254</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-1.080363464402353</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-5.673591925914579</v>
+      </c>
+      <c r="BC12" t="n">
         <v>-2</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-25192682.06540934</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-254</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-7.201993713357325</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-1.080363464402353</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-2.204960443596804</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-253</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-6.225626207845892</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-94600000</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-5.673591925914579</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-12433420.79729322</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-7.176087801087803</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-0.5777851299476033</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-0.6155612064702973</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -2535,24 +2535,28 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>-2.5</v>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>5.5</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>-0.1699999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AA13" t="n">
         <v>1</v>
@@ -2560,23 +2564,19 @@
       <c r="AB13" t="n">
         <v>-2</v>
       </c>
-      <c r="AC13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-2</v>
-      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>0.5800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1699999999999999</v>
+        <v>-4</v>
       </c>
       <c r="AG13" t="n">
-        <v>-3</v>
+        <v>5.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
         <v>78</v>
@@ -2585,61 +2585,61 @@
         <v>74.54166666666666</v>
       </c>
       <c r="AK13" t="n">
+        <v>-0.7765857807581895</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.09731915110703016</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AO13" t="n">
         <v>-0.4565962656871747</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.286781961024388</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-109549.4378609895</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.205938169574537</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.9969416386082912</v>
+      </c>
+      <c r="AW13" t="n">
         <v>-0.07716868061695648</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AX13" t="n">
+        <v>1.783415773243377</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>249960.2081420254</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.4597616508650901</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.1105118521325323</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>249960.2081420254</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.9969416386082912</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-0.4597616508650901</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.286781961024388</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.783415773243377</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-0.1105118521325323</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-109549.4378609895</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.205938169574537</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-0.7765857807581895</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0.09731915110703016</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD13"/>
+  <dimension ref="A1:BD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,74 +530,74 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,92 +610,92 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -719,7 +719,7 @@
         <v>45536.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="M2" t="n">
-        <v>250</v>
+        <v>103</v>
       </c>
       <c r="N2" t="n">
         <v>15</v>
@@ -771,97 +771,101 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X2" t="n">
         <v>-2</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Y2" t="n">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.1699999999999999</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.5800000000000001</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB2" t="n">
         <v>-1</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>-0.7150000000000003</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1</v>
+        <v>-1.515</v>
       </c>
       <c r="AG2" t="n">
-        <v>5</v>
+        <v>-9.5</v>
       </c>
       <c r="AH2" t="n">
         <v>-9</v>
       </c>
       <c r="AI2" t="n">
-        <v>72.69358356290175</v>
+        <v>72.52083333333334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>72.27272727272727</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-0.5026953094892797</v>
-      </c>
+        <v>71.72727272727272</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-0.331899766899767</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>0.3117499784555804</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.181932223651627</v>
+      </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-0.4427894327894322</v>
+        <v>-0.6188246097337036</v>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>4.119131701631687</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+        <v>-0.1392881996937838</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.11062018789292</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.54622448258813</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-1730318.318283005</v>
+        <v>0.8659940943117732</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.113310023310035</v>
+        <v>8745670.8695345</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.656888111888108</v>
+        <v>-0.3746238609874974</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.2191362231877498</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.9298599087084511</v>
-      </c>
+        <v>-1117895.421189511</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>8704756.216006216</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>1.05843936427047</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-0.05079903081303883</v>
-      </c>
+        <v>4.095401568128807</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.512099935567136</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
         <v>0</v>
@@ -877,7 +881,7 @@
         <v>45536.65625</v>
       </c>
       <c r="C3" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -925,97 +929,97 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-10</v>
+        <v>-10.66666666666666</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>10.66666666666666</v>
       </c>
       <c r="U3" t="n">
+        <v>4.666666666666668</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="W3" t="n">
         <v>2</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>-2</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.7250000000000001</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.7199999999999998</v>
-      </c>
       <c r="Y3" t="n">
-        <v>3.333333333333334</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.166666666666666</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.833333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.833333333333333</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.8699999999999997</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1</v>
       </c>
-      <c r="AF3" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.833333333333334</v>
-      </c>
       <c r="AH3" t="n">
-        <v>3.666666666666666</v>
+        <v>3.333333333333332</v>
       </c>
       <c r="AI3" t="n">
         <v>77.13636363636363</v>
       </c>
       <c r="AJ3" t="n">
-        <v>73.75505050505051</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-1.093853189385047</v>
-      </c>
+        <v>73.93686868686869</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-0.03835578002244655</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>0.8732346149018753</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.176357428249285</v>
+      </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>-0.8150673400673405</v>
+        <v>-0.7721969696969708</v>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>5.290432098765422</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+        <v>-1.135099898904485</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.19371212121213</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.941565656565658</v>
+      </c>
       <c r="AT3" t="n">
-        <v>466572.0514082243</v>
+        <v>2.359849332244465</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.417508417508429</v>
+        <v>1256878.787878788</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.135578002244657</v>
+        <v>-0.05573232323232324</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.1865803702904087</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.342071268557319</v>
-      </c>
+        <v>365435.3851956483</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>1463341.75084175</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="n">
-        <v>-0.647721139789752</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.9330782762909848</v>
-      </c>
+        <v>5.280555555555537</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.9310393232897809</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1089,22 +1093,22 @@
         <v>4.166666666666664</v>
       </c>
       <c r="U4" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="W4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.3350000000000001</v>
-      </c>
       <c r="Y4" t="n">
-        <v>5.333333333333333</v>
+        <v>5.166666666666666</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.333333333333333</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="AA4" t="n">
         <v>0.1666666666666667</v>
@@ -1119,16 +1123,16 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.166666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.833333333333333</v>
+        <v>0.3350000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.333333333333334</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AI4" t="n">
         <v>69.77777777777777</v>
@@ -1136,48 +1140,48 @@
       <c r="AJ4" t="n">
         <v>70.77272727272727</v>
       </c>
-      <c r="AK4" t="n">
-        <v>-0.845468987634824</v>
-      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.2060245310245306</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+        <v>2.858328559624482</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.2299949509274091</v>
+      </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>0.6175685425685415</v>
+        <v>0.6585465040010483</v>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>0.0870490620490898</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+        <v>-0.9127024526400298</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.379240456513187</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.320110192837461</v>
+      </c>
       <c r="AT4" t="n">
-        <v>7231570.974917667</v>
+        <v>2.717778528528413</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.304653679653683</v>
+        <v>6160560.146923785</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.188636363636377</v>
+        <v>0.2076085530630982</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.242699100825235</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.706803883754375</v>
-      </c>
+        <v>7227891.533956234</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>6001111.111111113</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>-0.3212259736350802</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.878163096580252</v>
-      </c>
+        <v>0.2193493375311846</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.2370551918111801</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1193,7 +1197,7 @@
         <v>45536.5625</v>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D5" t="n">
         <v>48</v>
@@ -1227,7 +1231,7 @@
         <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
@@ -1245,34 +1249,34 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.333333333333336</v>
+        <v>-3.333333333333336</v>
       </c>
       <c r="T5" t="n">
-        <v>4.333333333333336</v>
+        <v>3.333333333333336</v>
       </c>
       <c r="U5" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.6499999999999997</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.833333333333334</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.3333333333333334</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1281,65 +1285,65 @@
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.666666666666667</v>
+        <v>0.1750000000000003</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.833333333333333</v>
+        <v>-0.2649999999999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>4.666666666666668</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.3333333333333339</v>
+        <v>-1</v>
       </c>
       <c r="AI5" t="n">
         <v>73.00378787878788</v>
       </c>
       <c r="AJ5" t="n">
-        <v>80.45708041958042</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.286326459488219</v>
-      </c>
+        <v>79.91249999999999</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.06655188246097343</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>-0.2106851694964575</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.3179255026926595</v>
+      </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1.180348943985308</v>
+        <v>1.173456152433424</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>0.0404499540863128</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+        <v>2.080675812477285</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.7253883532292633</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.008360116314676702</v>
+      </c>
       <c r="AT5" t="n">
-        <v>117037.8820525873</v>
+        <v>-1.184084003324188</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.7853535353535364</v>
+        <v>1026030.188246096</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.05601469237832646</v>
+        <v>0.07951867156412584</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.3526943454149336</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-1.30817441001264</v>
-      </c>
+        <v>137305.1009788145</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>1143910.69788797</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="n">
-        <v>2.091360012536484</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-0.1931698094933267</v>
-      </c>
+        <v>0.1648167278848973</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.065157583429624</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1413,22 +1417,22 @@
         <v>-5</v>
       </c>
       <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W6" t="n">
         <v>1</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="W6" t="n">
-        <v>-0.3299999999999998</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.8600000000000001</v>
-      </c>
       <c r="Y6" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>-1.5</v>
       </c>
       <c r="AA6" t="n">
         <v>0.5</v>
@@ -1443,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-0.3299999999999998</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.5</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
         <v>71.59999999999999</v>
@@ -1460,48 +1464,48 @@
       <c r="AJ6" t="n">
         <v>72.57777777777778</v>
       </c>
-      <c r="AK6" t="n">
-        <v>2.100753155650178</v>
-      </c>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>-0.07219749947022636</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
+        <v>-0.4367162606865094</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.1995173087993456</v>
+      </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>1.462329589602327</v>
+        <v>1.539738292011023</v>
       </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>-0.5085470085470547</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+        <v>1.987029255599051</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-4.220546372819101</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-2.894123048668519</v>
+      </c>
       <c r="AT6" t="n">
-        <v>-6995724.231104091</v>
+        <v>-2.903636675321451</v>
       </c>
       <c r="AU6" t="n">
-        <v>-4.26287349014622</v>
+        <v>-16976379.70615244</v>
       </c>
       <c r="AV6" t="n">
-        <v>-2.966228720774183</v>
+        <v>-0.06776859504132204</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2227540088524074</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-2.837270656710004</v>
-      </c>
+        <v>-7303279.296525573</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
-        <v>-17003895.24616798</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="n">
-        <v>-1.745136997082028</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-0.3062353952514201</v>
-      </c>
+        <v>-0.5078282828283136</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-1.827319815534878</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
         <v>0</v>
@@ -1548,7 +1552,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
         <v>96</v>
@@ -1565,101 +1569,101 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="T7" t="n">
-        <v>-29</v>
+        <v>-19</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1666666666666667</v>
+        <v>2.333333333333332</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.46</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5049999999999999</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.166666666666666</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="Z7" t="n">
-        <v>-8.333333333333334</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.5</v>
+        <v>-0.125</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1.833333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1666666666666661</v>
+        <v>-7.666666666666667</v>
       </c>
       <c r="AI7" t="n">
-        <v>70.77500000000001</v>
+        <v>72.36515151515151</v>
       </c>
       <c r="AJ7" t="n">
         <v>76.16666666666667</v>
       </c>
-      <c r="AK7" t="n">
-        <v>0.2923619949635992</v>
-      </c>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.6768595041322318</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
+        <v>7.550055037311679</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.4072809857508028</v>
+      </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>2.118365472910927</v>
+        <v>2.052249770431587</v>
       </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>-2.657116620752987</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+        <v>0.3597862373878407</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.737741046831971</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10.95849403122131</v>
+      </c>
       <c r="AT7" t="n">
-        <v>12779978.7425277</v>
+        <v>5.21277408775542</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.76666666666668</v>
+        <v>31748370.06427915</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.03535353535354</v>
+        <v>0.6537190082644628</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.4012203796901967</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.32338014836148</v>
-      </c>
+        <v>12614959.80313376</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="n">
-        <v>31852915.51882461</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="n">
-        <v>-2.593562232342379</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.612933825190467</v>
-      </c>
+        <v>-2.456290174472002</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-2.590531929312078</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
         <v>0</v>
@@ -1675,7 +1679,7 @@
         <v>45535.5625</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="D8" t="n">
         <v>67</v>
@@ -1706,10 +1710,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>227</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
@@ -1727,97 +1731,101 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="T8" t="n">
-        <v>-26</v>
+        <v>-26.5</v>
       </c>
       <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
         <v>-1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>0.5</v>
       </c>
-      <c r="W8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>-0.1050000000000002</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>-0.3149999999999999</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-1.5</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.45454545454545</v>
+        <v>76.95454545454545</v>
       </c>
       <c r="AJ8" t="n">
-        <v>69.67171717171718</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-1.770989053092499</v>
-      </c>
+        <v>72.85521885521887</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.2487603305785127</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
+        <v>1.887665977062539</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.09787052453719114</v>
+      </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>-0.5396694214876092</v>
+        <v>-0.3421487603305806</v>
       </c>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>1.377685950413223</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+        <v>-1.556251472027334</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.317217630853989</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.114531680440763</v>
+      </c>
       <c r="AT8" t="n">
-        <v>4056428.43130108</v>
+        <v>3.276104366046894</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.471074380165291</v>
+        <v>6599552.341597796</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.997520661157012</v>
+        <v>0.2589531680440773</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.08860531051440135</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.2976648587683</v>
-      </c>
+        <v>3957872.962060821</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="n">
-        <v>6752975.206611572</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>2.608819499205111</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.70564804196151</v>
-      </c>
+        <v>1.356749311294749</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.709128577361355</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
         <v>0</v>
@@ -1833,7 +1841,7 @@
         <v>45535.5625</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>84</v>
@@ -1867,7 +1875,7 @@
         <v>179</v>
       </c>
       <c r="M9" t="n">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
@@ -1885,34 +1893,34 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-6.666666666666664</v>
+        <v>-6.333333333333329</v>
       </c>
       <c r="T9" t="n">
-        <v>6.666666666666664</v>
+        <v>6.333333333333329</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="W9" t="n">
         <v>-0.6666666666666667</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="W9" t="n">
-        <v>0.0149999999999999</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.8399999999999999</v>
-      </c>
       <c r="Y9" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.5</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.833333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1921,65 +1929,65 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>-0.1650000000000001</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.666666666666667</v>
+        <v>0.7849999999999997</v>
       </c>
       <c r="AG9" t="n">
-        <v>-1</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AI9" t="n">
         <v>80.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>74.59243827160495</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-2.681585441527446</v>
-      </c>
+        <v>75.5625</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>-0.1735537190082646</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
+        <v>-2.007339653674094</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.1431553327842681</v>
+      </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>-1.373201714110802</v>
+        <v>-1.351851851851848</v>
       </c>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>-0.4432774716865708</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+        <v>-2.774851147724188</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.988425925925938</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.2194865319865471</v>
+      </c>
       <c r="AT9" t="n">
-        <v>-49765.20917114615</v>
+        <v>0.6568424467706961</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.031814355677994</v>
+        <v>1502882.996632997</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.1740319865320004</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.1209633644716102</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.6193529513789002</v>
-      </c>
+        <v>-21884.02434384124</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="n">
-        <v>1599181.205999389</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="n">
-        <v>-0.5794406021852865</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-2.015143131592524</v>
-      </c>
+        <v>-0.5507154882155021</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0.6918363056729504</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
         <v>0</v>
@@ -2053,22 +2061,22 @@
         <v>-9.5</v>
       </c>
       <c r="U10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W10" t="n">
         <v>0.5</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>-1</v>
       </c>
-      <c r="W10" t="n">
-        <v>-0.835</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.6299999999999999</v>
-      </c>
       <c r="Y10" t="n">
-        <v>-4.5</v>
+        <v>-1</v>
       </c>
       <c r="Z10" t="n">
-        <v>-6</v>
+        <v>-0.5</v>
       </c>
       <c r="AA10" t="n">
         <v>-0.5</v>
@@ -2079,16 +2087,16 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>-1</v>
+        <v>-0.835</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.5</v>
+        <v>-0.6299999999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>-7</v>
+        <v>-4.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.5</v>
+        <v>-6</v>
       </c>
       <c r="AI10" t="n">
         <v>72.74444444444444</v>
@@ -2097,48 +2105,62 @@
         <v>73.65972222222223</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.741623992218194</v>
+        <v>-72</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.8928374655647382</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
+        <v>4.365915615900093</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.5419168047273635</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
       <c r="AO10" t="n">
-        <v>2.201873278236913</v>
-      </c>
-      <c r="AP10" t="inlineStr"/>
+        <v>2.260920897284535</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>66300000</v>
+      </c>
       <c r="AQ10" t="n">
-        <v>-4.30986225895316</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+        <v>1.815686912006786</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.192266824084996</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.799527744982285</v>
+      </c>
       <c r="AT10" t="n">
-        <v>10973105.98543164</v>
+        <v>2.727019032842009</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.205123966942139</v>
+        <v>21266794.56906729</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.759008264462793</v>
+        <v>0.9127508854781581</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.5372603429849805</v>
+        <v>11194653.50172602</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.662928855899878</v>
+        <v>0.4166666666666679</v>
       </c>
       <c r="AY10" t="n">
-        <v>21284435.26170798</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
+        <v>-4.288606847697736</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-4.145096170220398</v>
+      </c>
       <c r="BA10" t="n">
-        <v>-4.089998428838982</v>
+        <v>-7.25</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.234473844459359</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
+        <v>-80</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.5833333333333335</v>
+      </c>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
@@ -2211,22 +2233,22 @@
         <v>2.666666666666664</v>
       </c>
       <c r="U11" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.625</v>
+        <v>-2</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.015</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>3</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="Z11" t="n">
-        <v>-8.333333333333334</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="AA11" t="n">
         <v>-1.333333333333333</v>
@@ -2237,16 +2259,16 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>1.333333333333333</v>
+        <v>-1.625</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.333333333333333</v>
+        <v>-1.015</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>-8.333333333333334</v>
       </c>
       <c r="AI11" t="n">
         <v>73.6888888888889</v>
@@ -2255,393 +2277,63 @@
         <v>74.98484848484848</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.7086853030228824</v>
+        <v>-11</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.2477946127946127</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
+        <v>-4.340723833730735</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.1361451143533892</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
       <c r="AO11" t="n">
-        <v>-0.8519360269360305</v>
-      </c>
-      <c r="AP11" t="inlineStr"/>
+        <v>-0.853780226507503</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-38875000</v>
+      </c>
       <c r="AQ11" t="n">
-        <v>-1.469191919191928</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
+        <v>0.7362016920515515</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-4.596951331496783</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-6.052488521579434</v>
+      </c>
       <c r="AT11" t="n">
-        <v>-4126247.598044208</v>
+        <v>-3.613646991805666</v>
       </c>
       <c r="AU11" t="n">
-        <v>-4.613939393939404</v>
+        <v>-10277142.02632384</v>
       </c>
       <c r="AV11" t="n">
-        <v>-6.094713804713805</v>
+        <v>-0.2357881848790939</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.1216650216541857</v>
+        <v>-4135958.258926415</v>
       </c>
       <c r="AX11" t="n">
-        <v>-3.6536741218641</v>
+        <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>-10309681.81818182</v>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
+        <v>-1.587205387205415</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-2.715608322379865</v>
+      </c>
       <c r="BA11" t="n">
-        <v>-2.868834768400291</v>
+        <v>-10.66666666666666</v>
       </c>
       <c r="BB11" t="n">
-        <v>-4.376690792344917</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
+        <v>-20</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
       <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fZZxp2dD</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45530.65625</v>
-      </c>
-      <c r="C12" t="n">
-        <v>52</v>
-      </c>
-      <c r="D12" t="n">
-        <v>49</v>
-      </c>
-      <c r="E12" t="n">
-        <v>116</v>
-      </c>
-      <c r="F12" t="n">
-        <v>42</v>
-      </c>
-      <c r="G12" t="n">
-        <v>77</v>
-      </c>
-      <c r="H12" t="n">
-        <v>771</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>110</v>
-      </c>
-      <c r="M12" t="n">
-        <v>148</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-17</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-12</v>
-      </c>
-      <c r="T12" t="n">
-        <v>12</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.6499999999999999</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>72.375</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-0.5777851299476033</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>-0.6155612064702973</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-94600000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>-0.579377693014056</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-2.204960443596804</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-253</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-12433420.79729322</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-7.176087801087803</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-7.201993713357325</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-0.7067397751837112</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-6.225626207845892</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-25192682.06540934</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-254</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-1.080363464402353</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-5.673591925914579</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0hYMmpcl</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45530.5625</v>
-      </c>
-      <c r="C13" t="n">
-        <v>29</v>
-      </c>
-      <c r="D13" t="n">
-        <v>85</v>
-      </c>
-      <c r="E13" t="n">
-        <v>64</v>
-      </c>
-      <c r="F13" t="n">
-        <v>187</v>
-      </c>
-      <c r="G13" t="n">
-        <v>77</v>
-      </c>
-      <c r="H13" t="n">
-        <v>771</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>99</v>
-      </c>
-      <c r="M13" t="n">
-        <v>148</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.5800000000000001</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.1699999999999999</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>78</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>74.54166666666666</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>-0.7765857807581895</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.09731915110703016</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-0.4565962656871747</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>3.286781961024388</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-109549.4378609895</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.205938169574537</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.9969416386082912</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-0.07716868061695648</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.783415773243377</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>249960.2081420254</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-0.4597616508650901</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-0.1105118521325323</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD11"/>
+  <dimension ref="A1:BD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -719,7 +719,7 @@
         <v>45536.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -771,52 +771,52 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U2" t="n">
         <v>-7.5</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>7.5</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-6</v>
-      </c>
       <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
       </c>
       <c r="Z2" t="n">
         <v>-2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>-0.7150000000000003</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1</v>
+        <v>-1.515</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-9.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5</v>
+        <v>-9</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.7150000000000003</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.515</v>
+        <v>-2</v>
       </c>
       <c r="AG2" t="n">
-        <v>-9.5</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="AI2" t="n">
         <v>72.52083333333334</v>
@@ -824,49 +824,57 @@
       <c r="AJ2" t="n">
         <v>71.72727272727272</v>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>0.3117499784555804</v>
-      </c>
+      <c r="AK2" t="n">
+        <v>0.24365343097638</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>-0.181932223651627</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>3.152651515151518</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.8577196962850593</v>
+      </c>
       <c r="AO2" t="n">
-        <v>-0.6188246097337036</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>1.395521885521873</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.388821548821549</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>-0.1392881996937838</v>
+        <v>-0.1848734150576647</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.11062018789292</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.54622448258813</v>
-      </c>
+        <v>-0.7415740740740695</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>0.8659940943117732</v>
+        <v>-0.1574965443591623</v>
       </c>
       <c r="AU2" t="n">
-        <v>8745670.8695345</v>
+        <v>1.477255518770249</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.3746238609874974</v>
+        <v>325</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1117895.421189511</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>8159649.831649829</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>320</v>
+      </c>
       <c r="AY2" t="n">
-        <v>4.095401568128807</v>
+        <v>3.981729797979767</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.512099935567136</v>
+        <v>-1054301.433946898</v>
       </c>
       <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>96000000</v>
+      </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -881,7 +889,7 @@
         <v>45536.65625</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -929,48 +937,48 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="U3" t="n">
         <v>-10.66666666666666</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>10.66666666666666</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8699999999999997</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.333333333333332</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AG3" t="n">
         <v>4.666666666666668</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>2.333333333333332</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-1.333333333333334</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.8699999999999997</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>3.333333333333332</v>
       </c>
       <c r="AI3" t="n">
         <v>77.13636363636363</v>
@@ -978,49 +986,57 @@
       <c r="AJ3" t="n">
         <v>73.93686868686869</v>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="n">
-        <v>0.8732346149018753</v>
-      </c>
+      <c r="AK3" t="n">
+        <v>0.7587092633958719</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-0.176357428249285</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>3.193421589633701</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.371499500847918</v>
+      </c>
       <c r="AO3" t="n">
-        <v>-0.7721969696969708</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>1.854218957249245</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.07095449443934299</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>-1.135099898904485</v>
+        <v>-0.1835623703369578</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.19371212121213</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.941565656565658</v>
-      </c>
+        <v>-0.8908249158249184</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>2.359849332244465</v>
+        <v>-1.249892413290812</v>
       </c>
       <c r="AU3" t="n">
-        <v>1256878.787878788</v>
+        <v>-1.039973013320633</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.05573232323232324</v>
+        <v>229</v>
       </c>
       <c r="AW3" t="n">
-        <v>365435.3851956483</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>1152100.8060402</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>224</v>
+      </c>
       <c r="AY3" t="n">
-        <v>5.280555555555537</v>
+        <v>5.418202224262814</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.9310393232897809</v>
+        <v>333953.3405850739</v>
       </c>
       <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>23800000</v>
+      </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
@@ -1035,7 +1051,7 @@
         <v>45536.5625</v>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
@@ -1087,52 +1103,52 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="U4" t="n">
         <v>-4.166666666666664</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>4.166666666666664</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3350000000000001</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>5.166666666666666</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="AG4" t="n">
         <v>-2.333333333333334</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AH4" t="n">
         <v>3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5.166666666666666</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.833333333333333</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.3350000000000001</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.333333333333333</v>
       </c>
       <c r="AI4" t="n">
         <v>69.77777777777777</v>
@@ -1140,49 +1156,63 @@
       <c r="AJ4" t="n">
         <v>70.77272727272727</v>
       </c>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>2.875601492801295</v>
+      </c>
       <c r="AL4" t="n">
-        <v>2.858328559624482</v>
+        <v>-6</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.2299949509274091</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>2.416486543759291</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.679583275345223</v>
+      </c>
       <c r="AO4" t="n">
-        <v>0.6585465040010483</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>3.246450519177785</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.1836547291092745</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>-0.9127024526400298</v>
+        <v>0.2484560745621152</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.379240456513187</v>
+        <v>0.5790704245249643</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.320110192837461</v>
+        <v>-3</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.717778528528413</v>
+        <v>-0.8411861708681094</v>
       </c>
       <c r="AU4" t="n">
-        <v>6160560.146923785</v>
+        <v>-0.2788552587338415</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2076085530630982</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>7227891.533956234</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>6184957.97132161</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5</v>
+      </c>
       <c r="AY4" t="n">
-        <v>0.2193493375311846</v>
+        <v>0.2525605707424177</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.2370551918111801</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
+        <v>7131639.119699867</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18100000</v>
+      </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
@@ -1197,7 +1227,7 @@
         <v>45536.5625</v>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>48</v>
@@ -1249,52 +1279,52 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U5" t="n">
         <v>-3.333333333333336</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>3.333333333333336</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1750000000000003</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.2649999999999999</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.666666666666668</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="AG5" t="n">
         <v>3.666666666666666</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AH5" t="n">
         <v>1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.6666666666666661</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.1750000000000003</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.2649999999999999</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.666666666666668</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1</v>
       </c>
       <c r="AI5" t="n">
         <v>73.00378787878788</v>
@@ -1302,49 +1332,63 @@
       <c r="AJ5" t="n">
         <v>79.91249999999999</v>
       </c>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>-0.1463130061659683</v>
+      </c>
       <c r="AL5" t="n">
-        <v>-0.2106851694964575</v>
+        <v>1.199999999999989</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.3179255026926595</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>0.7113177226813576</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1.139505048328573</v>
+      </c>
       <c r="AO5" t="n">
-        <v>1.173456152433424</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>0.0264003673094777</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.08351698806244223</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>2.080675812477285</v>
+        <v>0.3143154938743173</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.7253883532292633</v>
+        <v>1.163154269972448</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.008360116314676702</v>
+        <v>-1.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1.184084003324188</v>
+        <v>2.119443873120346</v>
       </c>
       <c r="AU5" t="n">
-        <v>1026030.188246096</v>
+        <v>2.028169918316962</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.07951867156412584</v>
+        <v>322</v>
       </c>
       <c r="AW5" t="n">
-        <v>137305.1009788145</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>1035365.013774104</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>278</v>
+      </c>
       <c r="AY5" t="n">
-        <v>0.1648167278848973</v>
+        <v>0.2332185491275993</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.065157583429624</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
+        <v>172026.2796843681</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>21350000</v>
+      </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
@@ -1359,7 +1403,7 @@
         <v>45535.65625</v>
       </c>
       <c r="C6" t="n">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="D6" t="n">
         <v>55</v>
@@ -1411,52 +1455,52 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U6" t="n">
         <v>5</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>-5</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.3299999999999998</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.8600000000000001</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
         <v>5.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-0.3299999999999998</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-0.8600000000000001</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>3</v>
       </c>
       <c r="AI6" t="n">
         <v>71.59999999999999</v>
@@ -1464,49 +1508,63 @@
       <c r="AJ6" t="n">
         <v>72.57777777777778</v>
       </c>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>-0.5877605697202313</v>
+      </c>
       <c r="AL6" t="n">
-        <v>-0.4367162606865094</v>
+        <v>-7</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1995173087993456</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>-4.096189164370983</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-2.911219302475175</v>
+      </c>
       <c r="AO6" t="n">
-        <v>1.539738292011023</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>-2.734582185491277</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.07385674931129516</v>
+      </c>
       <c r="AQ6" t="n">
-        <v>1.987029255599051</v>
+        <v>0.1829676471968962</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.220546372819101</v>
+        <v>1.522038567493119</v>
       </c>
       <c r="AS6" t="n">
-        <v>-2.894123048668519</v>
+        <v>-9</v>
       </c>
       <c r="AT6" t="n">
-        <v>-2.903636675321451</v>
+        <v>1.87753562201846</v>
       </c>
       <c r="AU6" t="n">
-        <v>-16976379.70615244</v>
+        <v>-1.917525638497125</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.06776859504132204</v>
+        <v>-5</v>
       </c>
       <c r="AW6" t="n">
-        <v>-7303279.296525573</v>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+        <v>-16414895.77594123</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-11</v>
+      </c>
       <c r="AY6" t="n">
-        <v>-0.5078282828283136</v>
+        <v>-0.4921303948576963</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.827319815534878</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
+        <v>-7763471.857371988</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-4300000</v>
+      </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
@@ -1521,7 +1579,7 @@
         <v>45535.65625</v>
       </c>
       <c r="C7" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="D7" t="n">
         <v>33</v>
@@ -1569,52 +1627,52 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>19</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>-19</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-7.666666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.333333333333334</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
         <v>2.333333333333332</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.125</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>7.333333333333334</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-7.666666666666667</v>
       </c>
       <c r="AI7" t="n">
         <v>72.36515151515151</v>
@@ -1622,49 +1680,57 @@
       <c r="AJ7" t="n">
         <v>76.16666666666667</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="n">
-        <v>7.550055037311679</v>
-      </c>
+      <c r="AK7" t="n">
+        <v>7.504971590163009</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
-        <v>0.4072809857508028</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>6.830771349862275</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5.152218672960885</v>
+      </c>
       <c r="AO7" t="n">
-        <v>2.052249770431587</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>11.09376492194673</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.6484297520661157</v>
+      </c>
       <c r="AQ7" t="n">
-        <v>0.3597862373878407</v>
+        <v>0.4115074718251146</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.737741046831971</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>10.95849403122131</v>
-      </c>
+        <v>2.085739210284665</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>5.21277408775542</v>
+        <v>0.4058135997195507</v>
       </c>
       <c r="AU7" t="n">
-        <v>31748370.06427915</v>
+        <v>-2.541063402669636</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.6537190082644628</v>
+        <v>-153</v>
       </c>
       <c r="AW7" t="n">
-        <v>12614959.80313376</v>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+        <v>31811694.67401285</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-146</v>
+      </c>
       <c r="AY7" t="n">
-        <v>-2.456290174472002</v>
+        <v>-2.415803489439867</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-2.590531929312078</v>
+        <v>12571900.63462513</v>
       </c>
       <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-8900000</v>
+      </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1679,7 +1745,7 @@
         <v>45535.5625</v>
       </c>
       <c r="C8" t="n">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
         <v>67</v>
@@ -1731,52 +1797,52 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="U8" t="n">
         <v>26.5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>-26.5</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-1.833333333333333</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.1050000000000002</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.3149999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AG8" t="n">
         <v>4</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
         <v>-1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-1.833333333333333</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.1050000000000002</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.3149999999999999</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-2.333333333333334</v>
       </c>
       <c r="AI8" t="n">
         <v>76.95454545454545</v>
@@ -1784,49 +1850,63 @@
       <c r="AJ8" t="n">
         <v>72.85521885521887</v>
       </c>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="n">
+        <v>1.80606297499088</v>
+      </c>
       <c r="AL8" t="n">
-        <v>1.887665977062539</v>
+        <v>-6.25</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.09787052453719114</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>3.358677685950411</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3.199141157808882</v>
+      </c>
       <c r="AO8" t="n">
-        <v>-0.3421487603305806</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>3.137190082644636</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.2661157024793388</v>
+      </c>
       <c r="AQ8" t="n">
-        <v>-1.556251472027334</v>
+        <v>0.09754802923768469</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.317217630853989</v>
+        <v>-0.3446280991735584</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.114531680440763</v>
+        <v>-3.416666666666668</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.276104366046894</v>
+        <v>-1.585172771150827</v>
       </c>
       <c r="AU8" t="n">
-        <v>6599552.341597796</v>
+        <v>2.742590849067341</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2589531680440773</v>
+        <v>101</v>
       </c>
       <c r="AW8" t="n">
-        <v>3957872.962060821</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+        <v>6582148.76033058</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>80</v>
+      </c>
       <c r="AY8" t="n">
-        <v>1.356749311294749</v>
+        <v>1.331404958677695</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.709128577361355</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
+        <v>3713158.522970122</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>27675000</v>
+      </c>
       <c r="BD8" t="n">
         <v>0</v>
       </c>
@@ -1841,7 +1921,7 @@
         <v>45535.5625</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
         <v>84</v>
@@ -1893,52 +1973,52 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U9" t="n">
         <v>-6.333333333333329</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>6.333333333333329</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.1650000000000001</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7849999999999997</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>4.666666666666666</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.1650000000000001</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.7849999999999997</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-2.666666666666666</v>
       </c>
       <c r="AI9" t="n">
         <v>80.25</v>
@@ -1946,394 +2026,58 @@
       <c r="AJ9" t="n">
         <v>75.5625</v>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="n">
-        <v>-2.007339653674094</v>
-      </c>
+      <c r="AK9" t="n">
+        <v>-2.081197572305769</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
-        <v>-0.1431553327842681</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>1.888200183654732</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.8234110595546724</v>
+      </c>
       <c r="AO9" t="n">
-        <v>-1.351851851851848</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+        <v>-0.2229109274563683</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1570247933884299</v>
+      </c>
       <c r="AQ9" t="n">
-        <v>-2.774851147724188</v>
+        <v>-0.1617575689798669</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.988425925925938</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.2194865319865471</v>
-      </c>
+        <v>-1.259871441689622</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>0.6568424467706961</v>
+        <v>-2.966186259558995</v>
       </c>
       <c r="AU9" t="n">
-        <v>1502882.996632997</v>
+        <v>-0.4486108478405129</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.1666666666666667</v>
+        <v>78</v>
       </c>
       <c r="AW9" t="n">
-        <v>-21884.02434384124</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+        <v>1464302.112029385</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>70</v>
+      </c>
       <c r="AY9" t="n">
-        <v>-0.5507154882155021</v>
+        <v>-0.5925160697887861</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.6918363056729504</v>
+        <v>-5362.509315537289</v>
       </c>
       <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3400000</v>
+      </c>
       <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WdSjHeFt</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C10" t="n">
-        <v>103</v>
-      </c>
-      <c r="D10" t="n">
-        <v>41</v>
-      </c>
-      <c r="E10" t="n">
-        <v>45</v>
-      </c>
-      <c r="F10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G10" t="n">
-        <v>77</v>
-      </c>
-      <c r="H10" t="n">
-        <v>771</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>179</v>
-      </c>
-      <c r="M10" t="n">
-        <v>64</v>
-      </c>
-      <c r="N10" t="n">
-        <v>19</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="n">
-        <v>-0.835</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-0.6299999999999999</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>72.74444444444444</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>73.65972222222223</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-72</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>4.365915615900093</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.5419168047273635</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>2.260920897284535</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>66300000</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.815686912006786</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.192266824084996</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.799527744982285</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.727019032842009</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>21266794.56906729</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.9127508854781581</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>11194653.50172602</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.4166666666666679</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-4.288606847697736</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-4.145096170220398</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>-80</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.5833333333333335</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>EaryFQkA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45534.5625</v>
-      </c>
-      <c r="C11" t="n">
-        <v>103</v>
-      </c>
-      <c r="D11" t="n">
-        <v>62</v>
-      </c>
-      <c r="E11" t="n">
-        <v>52</v>
-      </c>
-      <c r="F11" t="n">
-        <v>72</v>
-      </c>
-      <c r="G11" t="n">
-        <v>77</v>
-      </c>
-      <c r="H11" t="n">
-        <v>771</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>21</v>
-      </c>
-      <c r="M11" t="n">
-        <v>64</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-2.666666666666664</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.666666666666664</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="n">
-        <v>-1.625</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-1.015</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-8.333333333333334</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>73.6888888888889</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>74.98484848484848</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-4.340723833730735</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-0.1361451143533892</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-0.853780226507503</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-38875000</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.7362016920515515</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-4.596951331496783</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-6.052488521579434</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-3.613646991805666</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-10277142.02632384</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-0.2357881848790939</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-4135958.258926415</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-1.587205387205415</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-2.715608322379865</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-10.66666666666666</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>-20</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="BD11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD5"/>
+  <dimension ref="A1:BD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,23 +712,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45551.65625</v>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
         <v>55</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -750,19 +750,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -771,110 +771,102 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-9.5</v>
+        <v>0.4566666666666668</v>
       </c>
       <c r="T2" t="n">
-        <v>-9</v>
+        <v>-0.4899999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-7.5</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.666666666666666</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5</v>
+        <v>-2.333333333333334</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.5</v>
+        <v>21.66666666666666</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2</v>
+        <v>-21.66666666666666</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.5</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AB2" t="n">
-        <v>-6</v>
+        <v>0.6666666666666679</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.7150000000000003</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.515</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>72.52083333333334</v>
+        <v>74.48333333333333</v>
       </c>
       <c r="AJ2" t="n">
-        <v>71.72727272727272</v>
+        <v>77.70833333333333</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8577196962850593</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-0.1574965443591623</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.395521885521873</v>
-      </c>
+        <v>0.3800099206349203</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>320</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>8159649.831649829</v>
-      </c>
+        <v>0.4541666666666668</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>96000000</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-0.388821548821549</v>
+        <v>3.845436507936498</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.1848734150576647</v>
+        <v>3.937748015873012</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.981729797979767</v>
+        <v>-0.008482142857140218</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>7601387.648809524</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.7415740740740695</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>325</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.24365343097638</v>
-      </c>
+        <v>5.834722222222211</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>-1054301.433946898</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>-1.6215277777778</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>15315208.33333333</v>
+      </c>
       <c r="BA2" t="n">
-        <v>3.152651515151518</v>
+        <v>1.309027777777775</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.477255518770249</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>4.038194444444443</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.8861607142856656</v>
+      </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -882,23 +874,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45551.5625</v>
       </c>
       <c r="C3" t="n">
         <v>102</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -920,123 +912,119 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>254</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>148</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>1.156666666666667</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.2866666666666664</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.333333333333332</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-10.66666666666666</v>
-      </c>
-      <c r="V3" t="n">
-        <v>10.66666666666666</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.6666666666666643</v>
+      </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>4.666666666666664</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2</v>
+        <v>-4.666666666666664</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.666666666666668</v>
+        <v>-5</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.333333333333332</v>
+        <v>-1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8699999999999997</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.6666666666666665</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
+        <v>79.41818181818182</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>77.13636363636363</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>73.93686868686869</v>
-      </c>
       <c r="AK3" t="n">
-        <v>2.371499500847918</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-1.249892413290812</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.854218957249245</v>
-      </c>
+        <v>0.04026636708701958</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>224</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1152100.8060402</v>
-      </c>
+        <v>0.02499999999999991</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>23800000</v>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-0.07095449443934299</v>
+        <v>-0.4932721234079906</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.1835623703369578</v>
+        <v>-3.789518711964362</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.418202224262814</v>
+        <v>-2.433214324926283</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>-803322.6574753756</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.8908249158249184</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>229</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0.7587092633958719</v>
-      </c>
+        <v>-3.705744949494942</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>333953.3405850739</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>-0.1827020202019867</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-1115290.404040404</v>
+      </c>
       <c r="BA3" t="n">
-        <v>3.193421589633701</v>
+        <v>-2.611300505050504</v>
       </c>
       <c r="BB3" t="n">
-        <v>-1.039973013320633</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>0.6865530303030454</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1.880077482903573</v>
+      </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
@@ -1044,23 +1032,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45550.65625</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1085,133 +1073,119 @@
         <v>21</v>
       </c>
       <c r="M4" t="n">
-        <v>235</v>
+        <v>64</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5.333333333333333</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="T4" t="n">
-        <v>2.333333333333333</v>
+        <v>-0.2399999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-4.166666666666664</v>
+        <v>-3.666666666666667</v>
       </c>
       <c r="V4" t="n">
-        <v>4.166666666666664</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.5</v>
+        <v>-6.999999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.333333333333332</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-6.666666666666664</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3333333333333333</v>
+        <v>6.666666666666664</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.333333333333334</v>
+        <v>5.666666666666668</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>0.6666666666666661</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.6</v>
+        <v>-2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3350000000000001</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1666666666666667</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.166666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>69.77777777777777</v>
+        <v>73.27272727272727</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70.77272727272727</v>
+        <v>73.99629629629629</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.754255414987597</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-0.8604145763772237</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>3.238544536271803</v>
-      </c>
+        <v>-0.4065629418890289</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>6123649.37251301</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>18100000</v>
-      </c>
+        <v>-1.122727272727273</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>0.1852540557086009</v>
+        <v>-6.217749490847311</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.2332819013887002</v>
+        <v>-6.710965513954648</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.2943373125191613</v>
+        <v>0.5226034533099799</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>-22010975.96545966</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.6166513621059018</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.888443306653784</v>
-      </c>
+        <v>-11.50454545454544</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>7171765.039259768</v>
+        <v>1.249242424242425</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-37363712.12121212</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.340243342516075</v>
+        <v>-3.4530303030303</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.1713516980838676</v>
+        <v>-8.270454545454541</v>
       </c>
       <c r="BC4" t="n">
-        <v>-6</v>
+        <v>-1.993554603608942</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1220,23 +1194,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45550.54166666666</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E5" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1258,138 +1232,1092 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="M5" t="n">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="N5" t="n">
+        <v>-15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.6066666666666665</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.05333333333333301</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.666666666666668</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2</v>
       </c>
-      <c r="O5" t="n">
+      <c r="AA5" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>72.89015151515152</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.3098030237736122</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>-0.586363636363636</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>-4.701917390887971</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-6.749335033158573</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.4353443941679238</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-11017746.69162537</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-8.152272727272717</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>3.404545454545485</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-27182840.90909091</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-1.327272727272724</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-6.170454545454547</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.368778879072977</v>
+      </c>
+      <c r="BD5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" t="n">
+        <v>84</v>
+      </c>
+      <c r="G6" t="n">
+        <v>77</v>
+      </c>
+      <c r="H6" t="n">
+        <v>771</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>179</v>
+      </c>
+      <c r="M6" t="n">
+        <v>55</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.086666666666667</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8733333333333334</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="X6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-9.666666666666664</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9.666666666666664</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.333333333333332</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-10.33333333333333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>77.10648148148148</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>70.71851851851852</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1425620756055539</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>-0.007407407407407529</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-1.46638041507606</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.6015118858597077</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.153532425706345</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>34275.48618853278</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.077777777777769</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>2.68518518518519</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1029259.259259259</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.2518518518518533</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.4555555555555628</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.269869711608834</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C7" t="n">
+        <v>39</v>
+      </c>
+      <c r="D7" t="n">
+        <v>56</v>
+      </c>
+      <c r="E7" t="n">
+        <v>51</v>
+      </c>
+      <c r="F7" t="n">
+        <v>55</v>
+      </c>
+      <c r="G7" t="n">
+        <v>77</v>
+      </c>
+      <c r="H7" t="n">
+        <v>771</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>194</v>
+      </c>
+      <c r="M7" t="n">
+        <v>105</v>
+      </c>
+      <c r="N7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4366666666666665</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="n">
         <v>8</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Z7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>76.21515151515152</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>77.74242424242424</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.05137844611528819</v>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>0.3270833333333332</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1.520289694825294</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.498369852326903</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.13399307091257</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3196203.821440857</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.501388888888869</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>3.681249999999977</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5637708.333333334</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.552777777777777</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.0013888888888971</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.795491332497875</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.3125</v>
+      </c>
+      <c r="C8" t="n">
+        <v>55</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79</v>
+      </c>
+      <c r="F8" t="n">
+        <v>202</v>
+      </c>
+      <c r="G8" t="n">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>771</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>223</v>
+      </c>
+      <c r="M8" t="n">
+        <v>250</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.666666666666668</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.08333333333333304</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.1166666666666667</v>
+      </c>
+      <c r="U8" t="n">
         <v>-1</v>
       </c>
-      <c r="U5" t="n">
-        <v>-3.333333333333336</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3.333333333333336</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="V8" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>75.98989898989898</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>74.19318181818181</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.2196594427244583</v>
+      </c>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>-0.5925925925925928</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-7.196336429308559</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-4.937358101135203</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.282786377708984</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-15727867.13106295</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-4.67685185185185</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>2.536111111111097</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-15506782.40740741</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.585185185185189</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-3.463888888888874</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.218028895768811</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.65625</v>
+      </c>
+      <c r="C9" t="n">
+        <v>63</v>
+      </c>
+      <c r="D9" t="n">
+        <v>41</v>
+      </c>
+      <c r="E9" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" t="n">
+        <v>74</v>
+      </c>
+      <c r="G9" t="n">
+        <v>77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>771</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>124</v>
+      </c>
+      <c r="M9" t="n">
+        <v>38</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.206666666666667</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-6.333333333333334</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18.66666666666667</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-18.66666666666667</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.666666666666666</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AD9" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>74.51851851851852</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>76.68055555555556</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.4792397660818712</v>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
+        <v>0.6525252525252525</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>10.28946278740329</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11.67989175838146</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0.8874940975627439</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>28279868.14863245</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11.22045454545454</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="n">
+        <v>-0.4161616161615882</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>38074595.95959596</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-1.411616161616159</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10.85606060606059</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-1.646769096654623</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.54166666666</v>
+      </c>
+      <c r="C10" t="n">
+        <v>55</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G10" t="n">
+        <v>77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>771</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>227</v>
+      </c>
+      <c r="M10" t="n">
+        <v>250</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4433333333333334</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-22.33333333333334</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>75.45892255892255</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>73.79166666666667</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.5444444444444443</v>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="n">
+        <v>-0.2916666666666667</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>-5.836006807202452</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-8.849467501097934</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-1.823896574440052</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-16137987.00318401</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-8.438636363636363</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="n">
+        <v>-0.9280303030302832</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-26712348.48484848</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.01060606060606162</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-7.517424242424227</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-2.034049736495405</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C11" t="n">
+        <v>70</v>
+      </c>
+      <c r="D11" t="n">
+        <v>43</v>
+      </c>
+      <c r="E11" t="n">
+        <v>129</v>
+      </c>
+      <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0.1750000000000003</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.2649999999999999</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="G11" t="n">
+        <v>77</v>
+      </c>
+      <c r="H11" t="n">
+        <v>771</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>254</v>
+      </c>
+      <c r="M11" t="n">
+        <v>103</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.6166666666666665</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.1766666666666667</v>
+      </c>
+      <c r="U11" t="n">
         <v>-1</v>
       </c>
-      <c r="AG5" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.6666666666666661</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>73.00378787878788</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>79.91249999999999</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-1.139505048328573</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.119443873120346</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0264003673094777</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>278</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1035365.013774104</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1.199999999999999</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>21350000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.08351698806244223</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.3143154938743173</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.2332185491275993</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.163154269972448</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>322</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-0.1463130061659683</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>172026.2796843681</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.7113177226813576</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.028169918316962</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.199999999999989</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="V11" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-16.33333333333334</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16.33333333333333</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-7.333333333333332</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>74.72575757575758</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>74.48484848484848</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.05995670995671021</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
+        <v>-0.09659090909090939</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>-5.143950216450207</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.4528679653679717</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.445530303030303</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-1161069.264069263</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-2.756060606060601</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="n">
+        <v>-5.096969696969694</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-3395265.15151515</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.5405303030303052</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-3.92765151515151</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.3798051948051864</v>
+      </c>
+      <c r="BD11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD11"/>
+  <dimension ref="A1:BD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,23 +712,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45551.65625</v>
+        <v>45558.65625</v>
       </c>
       <c r="C2" t="n">
+        <v>102</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
-        <v>55</v>
-      </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -750,123 +750,119 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="M2" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
         <v>2</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.4566666666666668</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.4899999999999999</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3.666666666666666</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-2.333333333333334</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>21.66666666666666</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-21.66666666666666</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.6666666666666679</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.6666666666666667</v>
-      </c>
       <c r="AE2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-5.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.5</v>
+        <v>-5.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>74.48333333333333</v>
+        <v>78.30000000000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>77.70833333333333</v>
+        <v>73.45555555555556</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3800099206349203</v>
+        <v>2.690250396056996</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>0.4541666666666668</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>6576847.285175734</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>8544444.444444444</v>
+      </c>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0.05113117241263709</v>
+      </c>
       <c r="AR2" t="n">
-        <v>3.845436507936498</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3.937748015873012</v>
-      </c>
+        <v>5.899999999999977</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>-0.008482142857140218</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7601387.648809524</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.834722222222211</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
+        <v>-0.1555555555555561</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-1.527777777777779</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.194444444444443</v>
+      </c>
       <c r="AY2" t="n">
-        <v>-1.6215277777778</v>
+        <v>3.382925593666442</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15315208.33333333</v>
+        <v>-1.42551639340827</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.309027777777775</v>
+        <v>5.116721307868332</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.038194444444443</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.8861607142856656</v>
-      </c>
+        <v>4.649999999999991</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -874,23 +870,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>xIieTySH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45551.5625</v>
+        <v>45557.65625</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -912,143 +908,147 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>179</v>
+      </c>
+      <c r="M3" t="n">
+        <v>96</v>
+      </c>
+      <c r="N3" t="n">
         <v>8</v>
       </c>
-      <c r="M3" t="n">
-        <v>148</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>3</v>
+      </c>
       <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.156666666666667</v>
+        <v>-1</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2866666666666664</v>
+        <v>-2.5</v>
       </c>
       <c r="U3" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-1.085</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="V3" t="n">
+      <c r="Z3" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1</v>
       </c>
-      <c r="W3" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.6666666666666643</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.666666666666664</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-4.666666666666664</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AH3" t="n">
         <v>-1</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
       <c r="AI3" t="n">
-        <v>79.41818181818182</v>
+        <v>73.31666666666668</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77.13636363636363</v>
+        <v>72.48998316498316</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.04026636708701958</v>
+        <v>1.191556241428316</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>0.02499999999999991</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>-86685.5970116891</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>6405589.225589231</v>
+      </c>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>0.1910374365617333</v>
+      </c>
       <c r="AR3" t="n">
-        <v>-0.4932721234079906</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-3.789518711964362</v>
-      </c>
+        <v>-0.8949494949495431</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>-2.433214324926283</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-803322.6574753756</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-3.705744949494942</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
+        <v>0.8006734006734011</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>4.275420875420874</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.947138047138026</v>
+      </c>
       <c r="AY3" t="n">
-        <v>-0.1827020202019867</v>
+        <v>0.5767315946343956</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1115290.404040404</v>
+        <v>2.403350343887425</v>
       </c>
       <c r="BA3" t="n">
-        <v>-2.611300505050504</v>
+        <v>-1.033811563543011</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.6865530303030454</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-1.880077482903573</v>
-      </c>
+        <v>0.7454545454545496</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>WvDUsysB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45557.54166666666</v>
       </c>
       <c r="C4" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>175</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1070,123 +1070,123 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>148</v>
+      </c>
+      <c r="M4" t="n">
+        <v>148</v>
+      </c>
+      <c r="N4" t="n">
         <v>21</v>
       </c>
-      <c r="M4" t="n">
-        <v>64</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AC4" t="n">
         <v>-1</v>
       </c>
-      <c r="O4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1.366666666666667</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.2399999999999999</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-3.666666666666667</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-6.999999999999999</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.333333333333332</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-6.666666666666664</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>6.666666666666664</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5.666666666666668</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.6666666666666661</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-2</v>
-      </c>
       <c r="AD4" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.666666666666667</v>
+        <v>-4.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.5</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="AI4" t="n">
-        <v>73.27272727272727</v>
+        <v>74.61742424242425</v>
       </c>
       <c r="AJ4" t="n">
-        <v>73.99629629629629</v>
+        <v>74.09976851851852</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.4065629418890289</v>
+        <v>-3.907519315367807</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>-1.122727272727273</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>16099154.42791082</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>16584242.42424242</v>
+      </c>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0.6418578136129285</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-6.217749490847311</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-6.710965513954648</v>
-      </c>
+        <v>-2.443181818181813</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>0.5226034533099799</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-22010975.96545966</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-11.50454545454544</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>-0.4772727272727195</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.77272727272728</v>
+      </c>
       <c r="AY4" t="n">
-        <v>1.249242424242425</v>
+        <v>5.17711885478829</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-37363712.12121212</v>
+        <v>-0.69007161494374</v>
       </c>
       <c r="BA4" t="n">
-        <v>-3.4530303030303</v>
+        <v>5.418324872768622</v>
       </c>
       <c r="BB4" t="n">
-        <v>-8.270454545454541</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-1.993554603608942</v>
-      </c>
+        <v>4.74015151515151</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
@@ -1194,23 +1194,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C5" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1232,147 +1232,147 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="M5" t="n">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="N5" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6066666666666665</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.05333333333333301</v>
+        <v>-0.5</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.666666666666667</v>
+        <v>-0.8500000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6666666666666665</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-5.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>4.666666666666668</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.333333333333334</v>
+        <v>-4.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.666666666666666</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.333333333333333</v>
+        <v>-2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.8333333333333333</v>
+        <v>13.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.5</v>
+        <v>77.59696969696969</v>
       </c>
       <c r="AJ5" t="n">
-        <v>72.89015151515152</v>
+        <v>74.60690235690237</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.3098030237736122</v>
+        <v>-3.323035425968357</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-0.586363636363636</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>-2395258.410458232</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-3845530.303030304</v>
+      </c>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>0.2355242365081198</v>
+      </c>
       <c r="AR5" t="n">
-        <v>-4.701917390887971</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-6.749335033158573</v>
-      </c>
+        <v>-1.34318181818179</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>0.4353443941679238</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-11017746.69162537</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-8.152272727272717</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
+        <v>0.04696969696969688</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>0.007575757575761344</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-2.789393939393932</v>
+      </c>
       <c r="AY5" t="n">
-        <v>3.404545454545485</v>
+        <v>0.04922761833368838</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-27182840.90909091</v>
+        <v>2.76776670044099</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1.327272727272724</v>
+        <v>-2.455991441092635</v>
       </c>
       <c r="BB5" t="n">
-        <v>-6.170454545454547</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.368778879072977</v>
-      </c>
+        <v>-2.00378787878789</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45557.3125</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1394,123 +1394,123 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="M6" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="N6" t="n">
-        <v>-11</v>
+        <v>-22</v>
       </c>
       <c r="O6" t="n">
         <v>-3</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.086666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8733333333333334</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.666666666666667</v>
+        <v>-0.3699999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="Y6" t="n">
-        <v>-9.666666666666664</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.666666666666664</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.333333333333332</v>
+        <v>2.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>-10.33333333333333</v>
+        <v>-3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1</v>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-8</v>
       </c>
       <c r="AI6" t="n">
-        <v>77.10648148148148</v>
+        <v>73.14444444444445</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70.71851851851852</v>
+        <v>75.31458333333335</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1425620756055539</v>
+        <v>-0.1856476615172653</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="n">
-        <v>-0.007407407407407529</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+        <v>562562.0321707278</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-7055151.515151516</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>-0.01869830652439375</v>
+      </c>
       <c r="AR6" t="n">
-        <v>-1.46638041507606</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.6015118858597077</v>
-      </c>
+        <v>2.618181818181853</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>2.153532425706345</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>34275.48618853278</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.077777777777769</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
+        <v>-0.1848484848484853</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>-0.8151515151515163</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-3.066666666666663</v>
+      </c>
       <c r="AY6" t="n">
-        <v>2.68518518518519</v>
+        <v>-0.5314912140999155</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1029259.259259259</v>
+        <v>-1.851802303976218</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2518518518518533</v>
+        <v>2.122865371343636</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.4555555555555628</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.269869711608834</v>
-      </c>
+        <v>-0.9363636363636374</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
@@ -1518,23 +1518,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45556.65625</v>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1556,123 +1556,123 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>194</v>
+        <v>95</v>
       </c>
       <c r="M7" t="n">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>-11</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4366666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1899999999999999</v>
+        <v>-3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0.666666666666667</v>
+        <v>-0.7350000000000003</v>
       </c>
       <c r="V7" t="n">
-        <v>2.333333333333333</v>
+        <v>-0.3</v>
       </c>
       <c r="W7" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.6666666666666661</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>-5.333333333333334</v>
+        <v>-7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AD7" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.333333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1.666666666666667</v>
+        <v>-1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-5.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>76.21515151515152</v>
+        <v>77.27575757575757</v>
       </c>
       <c r="AJ7" t="n">
-        <v>77.74242424242424</v>
+        <v>78.30134680134681</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.05137844611528819</v>
+        <v>1.044889760633481</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="n">
-        <v>0.3270833333333332</v>
-      </c>
-      <c r="AO7" t="inlineStr"/>
+        <v>86064.50365043059</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1773194.444444444</v>
+      </c>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-0.07951345755693606</v>
+      </c>
       <c r="AR7" t="n">
-        <v>1.520289694825294</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.498369852326903</v>
-      </c>
+        <v>-2.292361111111092</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>1.13399307091257</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3196203.821440857</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.501388888888869</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>1.003472222222225</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.91458333333334</v>
+      </c>
       <c r="AY7" t="n">
-        <v>3.681249999999977</v>
+        <v>-0.1107245468744225</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5637708.333333334</v>
+        <v>-0.4317333188042554</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.552777777777777</v>
+        <v>0.3041455995060147</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0013888888888971</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.795491332497875</v>
-      </c>
+        <v>0.6187500000000057</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
@@ -1680,23 +1680,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45550.3125</v>
+        <v>45556.54166666666</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -1718,19 +1718,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="M8" t="n">
-        <v>250</v>
+        <v>196</v>
       </c>
       <c r="N8" t="n">
-        <v>-16</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
         <v>-2</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1739,126 +1739,126 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08333333333333304</v>
+        <v>-3</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1166666666666667</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC8" t="n">
         <v>-1</v>
       </c>
-      <c r="V8" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-4.666666666666668</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-20</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.666666666666668</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.6666666666666667</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.6666666666666666</v>
+        <v>-2</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-1.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.8333333333333333</v>
+        <v>-8.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.98989898989898</v>
+        <v>73.37146464646464</v>
       </c>
       <c r="AJ8" t="n">
-        <v>74.19318181818181</v>
+        <v>72.25378787878788</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.2196594427244583</v>
+        <v>0.2738921957671323</v>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="n">
-        <v>-0.5925925925925928</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
+        <v>11193260.16865079</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-2230505.05050505</v>
+      </c>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>0.05497685185185186</v>
+      </c>
       <c r="AR8" t="n">
-        <v>-7.196336429308559</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-4.937358101135203</v>
-      </c>
+        <v>4.031986531986547</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>2.282786377708984</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-15727867.13106295</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-4.67685185185185</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
+        <v>-0.3397306397306394</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>-2.825589225589223</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-1.611868686868675</v>
+      </c>
       <c r="AY8" t="n">
-        <v>2.536111111111097</v>
+        <v>2.829282407407405</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-15506782.40740741</v>
+        <v>-0.2022156084656039</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.585185185185189</v>
+        <v>2.831183862433875</v>
       </c>
       <c r="BB8" t="n">
-        <v>-3.463888888888874</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.218028895768811</v>
-      </c>
+        <v>1.646885521885523</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SQjcKLRk</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.65625</v>
+        <v>45556.41666666666</v>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
@@ -1880,123 +1880,123 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="M9" t="n">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.206666666666667</v>
-      </c>
       <c r="T9" t="n">
-        <v>0.2533333333333334</v>
+        <v>4.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.333333333333334</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="W9" t="n">
-        <v>4.333333333333332</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.333333333333334</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.66666666666667</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="Z9" t="n">
-        <v>-18.66666666666667</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AA9" t="n">
-        <v>-4</v>
+        <v>-0.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5.666666666666666</v>
+        <v>3.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.333333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.6666666666666667</v>
+        <v>3</v>
       </c>
       <c r="AG9" t="n">
         <v>-0.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>74.51851851851852</v>
+        <v>77.16913580246914</v>
       </c>
       <c r="AJ9" t="n">
-        <v>76.68055555555556</v>
+        <v>74.20202020202019</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.4792397660818712</v>
+        <v>-0.5908650622720586</v>
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="n">
-        <v>0.6525252525252525</v>
-      </c>
-      <c r="AO9" t="inlineStr"/>
+        <v>-2980371.696104071</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-3159255.05050505</v>
+      </c>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>-0.4406475748194014</v>
+      </c>
       <c r="AR9" t="n">
-        <v>10.28946278740329</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>11.67989175838146</v>
-      </c>
+        <v>0.1199494949494806</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>-0.8874940975627439</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>28279868.14863245</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11.22045454545454</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
+        <v>-0.1290404040404043</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>-0.6868686868686851</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-3.449242424242428</v>
+      </c>
       <c r="AY9" t="n">
-        <v>-0.4161616161615882</v>
+        <v>-4.426260007435459</v>
       </c>
       <c r="AZ9" t="n">
-        <v>38074595.95959596</v>
+        <v>-2.567953098859689</v>
       </c>
       <c r="BA9" t="n">
-        <v>-1.411616161616159</v>
+        <v>-1.054104170272225</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.85606060606059</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-1.646769096654623</v>
-      </c>
+        <v>-3.36666666666666</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
         <v>0</v>
       </c>
@@ -2004,23 +2004,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.54166666666</v>
+        <v>45555.65625</v>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
@@ -2042,123 +2042,123 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M10" t="n">
-        <v>250</v>
+        <v>38</v>
       </c>
       <c r="N10" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="O10" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="P10" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="Q10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.6949999999999998</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.7399999999999998</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="Y10" t="n">
         <v>-1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.4433333333333334</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-2.666666666666667</v>
-      </c>
-      <c r="V10" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="X10" t="n">
-        <v>9.666666666666666</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-22.33333333333334</v>
-      </c>
       <c r="Z10" t="n">
-        <v>22.33333333333333</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.666666666666666</v>
+        <v>-4</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>-9.5</v>
       </c>
       <c r="AC10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
         <v>-1</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
       <c r="AF10" t="n">
-        <v>0.3333333333333333</v>
+        <v>-2.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>-9</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.3333333333333335</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>75.45892255892255</v>
+        <v>77.08207070707071</v>
       </c>
       <c r="AJ10" t="n">
-        <v>73.79166666666667</v>
+        <v>72.87567340067339</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.5444444444444443</v>
+        <v>-0.2968019728174056</v>
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="n">
-        <v>-0.2916666666666667</v>
-      </c>
-      <c r="AO10" t="inlineStr"/>
+        <v>-3238961.489383043</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-6084236.111111111</v>
+      </c>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>-0.0572640222096743</v>
+      </c>
       <c r="AR10" t="n">
-        <v>-5.836006807202452</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-8.849467501097934</v>
-      </c>
+        <v>-1.297916666666623</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>-1.823896574440052</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-16137987.00318401</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-8.438636363636363</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
+        <v>-0.1819444444444447</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-1.547916666666669</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-2.756249999999994</v>
+      </c>
       <c r="AY10" t="n">
-        <v>-0.9280303030302832</v>
+        <v>-1.422667030719083</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-26712348.48484848</v>
+        <v>0.5787020664308962</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.01060606060606162</v>
+        <v>-0.9130630429829409</v>
       </c>
       <c r="BB10" t="n">
-        <v>-7.517424242424227</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-2.034049736495405</v>
-      </c>
+        <v>-0.4472222222222229</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
@@ -2166,23 +2166,23 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.41666666666</v>
+        <v>45555.5625</v>
       </c>
       <c r="C11" t="n">
         <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="E11" t="n">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
@@ -2204,120 +2204,1736 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>254</v>
+        <v>95</v>
       </c>
       <c r="M11" t="n">
         <v>103</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>-1</v>
+      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6166666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1766666666666667</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
+        <v>-0.4450000000000001</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="Y11" t="n">
         <v>-1</v>
       </c>
-      <c r="V11" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-16.33333333333334</v>
-      </c>
       <c r="Z11" t="n">
-        <v>16.33333333333333</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>-7.333333333333332</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.6666666666666661</v>
+        <v>-5</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.6666666666666667</v>
+        <v>-2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.5</v>
+        <v>26.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.5</v>
+        <v>-26.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>74.72575757575758</v>
+        <v>75.34284511784512</v>
       </c>
       <c r="AJ11" t="n">
-        <v>74.48484848484848</v>
+        <v>77.81498316498316</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.05995670995671021</v>
+        <v>1.743525546514689</v>
       </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>-0.09659090909090939</v>
-      </c>
-      <c r="AO11" t="inlineStr"/>
+        <v>-239912.8747158637</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1455795.454545455</v>
+      </c>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>0.3580891330891329</v>
+      </c>
       <c r="AR11" t="n">
-        <v>-5.143950216450207</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-0.4528679653679717</v>
-      </c>
+        <v>0.568181818181813</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>3.445530303030303</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-1161069.264069263</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-2.756060606060601</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
+        <v>0.06818181818181812</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>1.41363636363636</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.729545454545459</v>
+      </c>
       <c r="AY11" t="n">
-        <v>-5.096969696969694</v>
+        <v>0.8473002239306595</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-3395265.15151515</v>
+        <v>2.489388027431506</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.5405303030303052</v>
+        <v>-0.9276480564524121</v>
       </c>
       <c r="BB11" t="n">
-        <v>-3.92765151515151</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.3798051948051864</v>
-      </c>
+        <v>-0.6318181818181756</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45551.65625</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F12" t="n">
+        <v>171</v>
+      </c>
+      <c r="G12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H12" t="n">
+        <v>771</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>124</v>
+      </c>
+      <c r="M12" t="n">
+        <v>116</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.4566666666666668</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.4899999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>74.36666666666667</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>77.75984848484848</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-1.308765189488895</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="n">
+        <v>7463520.503436622</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>14901887.62626263</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>0.3669895382395385</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.69526515151523</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>0.4417929292929295</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>1.346401515151516</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>5.922916666666666</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.302938691425538</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.3944643806485928</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.100684286473765</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.608585858585869</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45551.5625</v>
+      </c>
+      <c r="C13" t="n">
+        <v>102</v>
+      </c>
+      <c r="D13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" t="n">
+        <v>175</v>
+      </c>
+      <c r="G13" t="n">
+        <v>77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>771</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>148</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.156666666666667</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.2866666666666664</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-4.666666666666666</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>6.333333333333336</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-6.333333333333336</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>79.22558922558922</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>75.8047138047138</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-1.950061350627209</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="n">
+        <v>-789109.9409328955</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1265063.131313131</v>
+      </c>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>0.04411658141517494</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.2035984848484418</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0.02499999999999991</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="n">
+        <v>-2.611300505050504</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-3.705744949494942</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-3.420082663500182</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-1.91055596151504</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-1.39369078066008</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.3547348484848527</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C14" t="n">
+        <v>65</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>63</v>
+      </c>
+      <c r="G14" t="n">
+        <v>77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>771</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>21</v>
+      </c>
+      <c r="M14" t="n">
+        <v>64</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.366666666666667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.2399999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-6.999999999999999</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.333333333333332</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>5.666666666666668</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-8.666666666666664</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>8.666666666666664</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>73.37878787878788</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>73.87272727272727</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-1.817986210649224</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="n">
+        <v>-21872240.18056219</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-37363712.12121212</v>
+      </c>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>-0.4168972633646546</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.802272727272765</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>-1.122727272727273</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>-3.4530303030303</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-11.50454545454544</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-6.87123248128681</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.3387266417157768</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-6.10022495620322</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-8.270454545454541</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45550.54166666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>126</v>
+      </c>
+      <c r="D15" t="n">
+        <v>85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>64</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21</v>
+      </c>
+      <c r="G15" t="n">
+        <v>77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>771</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>95</v>
+      </c>
+      <c r="M15" t="n">
+        <v>196</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.6066666666666665</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.05333333333333301</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.666666666666668</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>74.51481481481481</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>72.71969696969697</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.510944495319478</v>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>-10479778.59813797</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-27155568.18181818</v>
+      </c>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>-0.2721192002442006</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.454545454545467</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>-0.586363636363636</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>-1.327272727272724</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-8.10681818181817</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-6.458070054945068</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.6975351037851034</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-4.880619149369153</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-6.125</v>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C16" t="n">
+        <v>39</v>
+      </c>
+      <c r="D16" t="n">
+        <v>56</v>
+      </c>
+      <c r="E16" t="n">
+        <v>51</v>
+      </c>
+      <c r="F16" t="n">
+        <v>55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>77</v>
+      </c>
+      <c r="H16" t="n">
+        <v>771</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>194</v>
+      </c>
+      <c r="M16" t="n">
+        <v>105</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.4366666666666665</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.333333333333332</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>7.666666666666664</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-7.666666666666664</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>76.06363636363636</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>77.74242424242424</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.7320145307273549</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="n">
+        <v>3589072.669321526</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>5902777.777777778</v>
+      </c>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>0.07904432523997729</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.827777777777726</v>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0.3000000000000003</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>2.480555555555558</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.063888888888883</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.989162340964384</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.338466802711654</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.274166559349609</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.5083333333333258</v>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>84</v>
+      </c>
+      <c r="G17" t="n">
+        <v>77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>771</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>179</v>
+      </c>
+      <c r="M17" t="n">
+        <v>55</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.086666666666667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8733333333333334</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>76.84074074074074</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>70.71851851851852</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>4.625540823910427</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="n">
+        <v>342963.9141052198</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1560000</v>
+      </c>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>0.03844494877103588</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.733333333333348</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.23333333333332</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.058933216541917</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.172788262462173</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-1.792303710781979</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.4666666666666544</v>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zTBIR3ZF</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45550.3125</v>
+      </c>
+      <c r="C18" t="n">
+        <v>55</v>
+      </c>
+      <c r="D18" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" t="n">
+        <v>79</v>
+      </c>
+      <c r="F18" t="n">
+        <v>202</v>
+      </c>
+      <c r="G18" t="n">
+        <v>77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>771</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>223</v>
+      </c>
+      <c r="M18" t="n">
+        <v>250</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.08333333333333304</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.1166666666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.666666666666668</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>75.98989898989898</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>74.28409090909092</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>4.174526579371815</v>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="n">
+        <v>-14938419.21872417</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-15707083.33333333</v>
+      </c>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>-0.2366071149352882</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.127272727272754</v>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>-0.5393939393939391</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>1.490909090909085</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-4.63636363636364</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-4.911453388372891</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.426704886101177</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-7.22592499519746</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-3.724242424242419</v>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SQjcKLRk</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.65625</v>
+      </c>
+      <c r="C19" t="n">
+        <v>63</v>
+      </c>
+      <c r="D19" t="n">
+        <v>41</v>
+      </c>
+      <c r="E19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F19" t="n">
+        <v>74</v>
+      </c>
+      <c r="G19" t="n">
+        <v>77</v>
+      </c>
+      <c r="H19" t="n">
+        <v>771</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>124</v>
+      </c>
+      <c r="M19" t="n">
+        <v>38</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.206666666666667</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-4.666666666666666</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>18.33333333333334</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>74.38518518518518</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>76.60000000000001</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1.0716188212335</v>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="n">
+        <v>24796866.31165364</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>33494764.30976431</v>
+      </c>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>0.6043406756642051</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.8249999999999886</v>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0.6647306397306396</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="n">
+        <v>-1.385521885521886</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>10.79301346801348</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11.51771721551806</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.5850165355650567</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.829865766776862</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10.35757575757575</v>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>v1I9TP43</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45549.54166666666</v>
+      </c>
+      <c r="C20" t="n">
+        <v>55</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" t="n">
+        <v>77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>771</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>227</v>
+      </c>
+      <c r="M20" t="n">
+        <v>250</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.4433333333333334</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-23.33333333333334</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>75.30909090909091</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>74.04814814814814</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.5064732469623436</v>
+      </c>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="n">
+        <v>-21433125.8920729</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-26380858.58585859</v>
+      </c>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>-0.6851851851851853</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-1.145622895622893</v>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>-0.3148148148148147</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="n">
+        <v>0.0846801346801378</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-8.224494949494954</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-10.13465268628313</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-1.589637315180799</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-6.784154955350616</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-7.140067340067347</v>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>n7VN5MCd</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45549.41666666666</v>
+      </c>
+      <c r="C21" t="n">
+        <v>70</v>
+      </c>
+      <c r="D21" t="n">
+        <v>43</v>
+      </c>
+      <c r="E21" t="n">
+        <v>129</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>77</v>
+      </c>
+      <c r="H21" t="n">
+        <v>771</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>254</v>
+      </c>
+      <c r="M21" t="n">
+        <v>103</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.6166666666666665</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.1766666666666667</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-5.333333333333332</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-17.33333333333334</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17.33333333333333</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>74.69797979797981</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>74.54545454545455</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-1.330210292482406</v>
+      </c>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="n">
+        <v>-1974297.550427722</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-2911111.111111112</v>
+      </c>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="n">
+        <v>0.2144286987506825</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-3.439393939393881</v>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>0.1616161616161613</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="n">
+        <v>2.027777777777779</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-1.300505050505052</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.5302509694401039</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>3.15787239947117</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-4.70403342104251</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-2.962121212121218</v>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD8"/>
+  <dimension ref="A1:BD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,74 +530,74 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,23 +712,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45551.65625</v>
+        <v>45565.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -750,130 +750,122 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="M2" t="n">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4566666666666668</v>
+        <v>0.7950000000000002</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4899999999999999</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-5</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6666666666666667</v>
+        <v>11.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y2" t="n">
         <v>-1</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.6666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3333333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.333333333333333</v>
+        <v>-15</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>-4.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.666666666666668</v>
+        <v>4.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AH2" t="n">
-        <v>-20</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AI2" t="n">
-        <v>74.36666666666667</v>
+        <v>74.95947811447812</v>
       </c>
       <c r="AJ2" t="n">
-        <v>77.75984848484848</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+        <v>75.91727272727272</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-2.958333309202875</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.8889496558192178</v>
+      </c>
       <c r="AM2" t="n">
-        <v>-72</v>
+        <v>-1277868.686868686</v>
       </c>
       <c r="AN2" t="n">
-        <v>7463520.503436622</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.3944643806485928</v>
-      </c>
+        <v>-2.45085858585859</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>14901887.62626263</v>
+        <v>1.169242424242427</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.69526515151523</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.302938691425538</v>
-      </c>
+        <v>-1.733737830607382</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>-1400000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.346401515151516</v>
-      </c>
+        <v>-0.05272727272727273</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>-66</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.4417929292929295</v>
-      </c>
+        <v>-2.871868686868709</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>0.3669895382395385</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.100684286473765</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-1.308765189488895</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>-0.5174242424242266</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>-1.778124722298656</v>
+      </c>
       <c r="BA2" t="n">
-        <v>5.922916666666666</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.608585858585869</v>
-      </c>
+        <v>-0.257304984870202</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>-1</v>
+        <v>277106.9161434374</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
@@ -882,23 +874,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45551.5625</v>
+        <v>45564.65625</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -920,126 +912,122 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="M3" t="n">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
       <c r="P3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.156666666666667</v>
+        <v>1.695</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2866666666666664</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6666666666666666</v>
+        <v>-1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y3" t="n">
-        <v>-4.666666666666666</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB3" t="n">
         <v>-1</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
       <c r="AC3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>4.000000000000001</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6.333333333333336</v>
-      </c>
       <c r="AH3" t="n">
-        <v>-6.333333333333336</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>79.22558922558922</v>
+        <v>73.83943602693603</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75.8047138047138</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+        <v>77.5530303030303</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.9495129266868432</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.00779450018581</v>
+      </c>
       <c r="AM3" t="n">
-        <v>224</v>
+        <v>27341090.90909091</v>
       </c>
       <c r="AN3" t="n">
-        <v>-789109.9409328955</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-1.91055596151504</v>
-      </c>
+        <v>1.534545454545452</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-1265063.131313131</v>
+        <v>5.13636363636364</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.2035984848484418</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-3.420082663500182</v>
-      </c>
+        <v>3.84704637150287</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>10900000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-2.611300505050504</v>
-      </c>
+        <v>0.272727272727272</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>217</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.02499999999999991</v>
-      </c>
+        <v>8.481818181818184</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>0.04411658141517494</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-1.39369078066008</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-1.950061350627209</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>-1.578181818181832</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>0.4725135371874671</v>
+      </c>
       <c r="BA3" t="n">
-        <v>-3.705744949494942</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.3547348484848527</v>
-      </c>
+        <v>0.2548435260391786</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>3</v>
+        <v>9236907.764638742</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1048,23 +1036,23 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45564.54166666666</v>
       </c>
       <c r="C4" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1086,161 +1074,147 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="M4" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="O4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.366666666666667</v>
+        <v>-0.9550000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2399999999999999</v>
+        <v>-0.1100000000000001</v>
       </c>
       <c r="U4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="X4" t="n">
         <v>-2</v>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AG4" t="n">
         <v>0.3333333333333334</v>
       </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5.666666666666668</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.6666666666666661</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-6.999999999999999</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.333333333333332</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-8.666666666666664</v>
-      </c>
       <c r="AH4" t="n">
-        <v>8.666666666666664</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="AI4" t="n">
-        <v>73.37878787878788</v>
+        <v>76.2976430976431</v>
       </c>
       <c r="AJ4" t="n">
-        <v>73.87272727272727</v>
+        <v>76.35151515151516</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.5137649695194426</v>
       </c>
       <c r="AL4" t="n">
-        <v>-2</v>
+        <v>-5.825146817873801</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>-9751232.323232323</v>
       </c>
       <c r="AN4" t="n">
-        <v>-21872240.18056219</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.3387266417157768</v>
-      </c>
+        <v>-1.531666666666666</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-37363712.12121212</v>
+        <v>-3.88823232323233</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.802272727272765</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-6.87123248128681</v>
-      </c>
+        <v>-5.283924777978484</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>13600000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-3.4530303030303</v>
-      </c>
+        <v>-0.4944444444444445</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-1.122727272727273</v>
-      </c>
+        <v>-5.332626262626263</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>-0.4168972633646546</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-6.10022495620322</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-1.817986210649224</v>
-      </c>
+        <v>0.4752525252525004</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>4.5</v>
+        <v>-0.08113426132925383</v>
       </c>
       <c r="BA4" t="n">
-        <v>-11.50454545454544</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-8.270454545454541</v>
-      </c>
+        <v>-0.3492380192508069</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
+        <v>-7983636.445691751</v>
+      </c>
+      <c r="BD4" t="n">
         <v>1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1262,161 +1236,147 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>95</v>
+        <v>223</v>
       </c>
       <c r="M5" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="N5" t="n">
-        <v>-15</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.8199999999999998</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-2</v>
       </c>
-      <c r="P5" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.6066666666666665</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.05333333333333301</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="AC5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-1.333333333333333</v>
       </c>
-      <c r="V5" t="n">
-        <v>-0.6666666666666666</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-3.666666666666666</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-2.666666666666667</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>4.666666666666668</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2</v>
-      </c>
       <c r="AI5" t="n">
-        <v>74.51481481481481</v>
+        <v>74.89015151515152</v>
       </c>
       <c r="AJ5" t="n">
-        <v>72.71969696969697</v>
+        <v>76.48047138047137</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1</v>
+        <v>0.6562108953213084</v>
       </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>7.740355520718794</v>
       </c>
       <c r="AM5" t="n">
-        <v>4</v>
+        <v>19099154.04040404</v>
       </c>
       <c r="AN5" t="n">
-        <v>-10479778.59813797</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.6975351037851034</v>
-      </c>
+        <v>-0.5932323232323284</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-27155568.18181818</v>
+        <v>6.731060606060609</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.454545454545467</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-6.458070054945068</v>
-      </c>
+        <v>9.653498011332672</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>-11000000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-1.327272727272724</v>
-      </c>
+        <v>0.7014141414141413</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-0.586363636363636</v>
-      </c>
+        <v>7.673484848484847</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-0.2721192002442006</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-4.880619149369153</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.510944495319478</v>
-      </c>
+        <v>-1.22777777777776</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-13</v>
+        <v>-2.489662681902388</v>
       </c>
       <c r="BA5" t="n">
-        <v>-8.10681818181817</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-6.125</v>
-      </c>
+        <v>0.6494899303594954</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>18078376.44147424</v>
       </c>
       <c r="BD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1438,130 +1398,118 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="M6" t="n">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="N6" t="n">
-        <v>-11</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-3</v>
-      </c>
+        <v>-4</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.086666666666667</v>
+        <v>0.3799999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8733333333333334</v>
+        <v>-0.3599999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6666666666666667</v>
+        <v>9</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.666666666666668</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-10</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.333333333333333</v>
+        <v>3.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>6.666666666666666</v>
+        <v>-6.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>-11</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AI6" t="n">
-        <v>76.84074074074074</v>
+        <v>75.45681818181818</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70.71851851851852</v>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+        <v>75.55757575757575</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.158227931488803</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-1.612715953001981</v>
+      </c>
       <c r="AM6" t="n">
-        <v>249</v>
+        <v>1030944.444444445</v>
       </c>
       <c r="AN6" t="n">
-        <v>342963.9141052198</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>2.172788262462173</v>
-      </c>
+        <v>2.599444444444444</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>1560000</v>
+        <v>-1.445555555555558</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.733333333333348</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.058933216541917</v>
-      </c>
+        <v>1.674047996244795</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>59500000</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.3999999999999986</v>
-      </c>
+        <v>0.4411111111111117</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>234</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
+        <v>1.083888888888893</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>0.03844494877103588</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-1.792303710781979</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.625540823910427</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
+        <v>-2.168333333333322</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>-0.070374861599106</v>
+      </c>
       <c r="BA6" t="n">
-        <v>1.23333333333332</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0.4666666666666544</v>
-      </c>
+        <v>0.3607916987665269</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>3</v>
+        <v>1793007.58337772</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -1570,14 +1518,14 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45564.3125</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="D7" t="n">
         <v>56</v>
@@ -1586,7 +1534,7 @@
         <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1608,136 +1556,122 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>-13</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="P7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.245</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.2750000000000001</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>7</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.4366666666666665</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1899999999999999</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.3333333333333339</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-5</v>
-      </c>
       <c r="AF7" t="n">
-        <v>5.333333333333332</v>
+        <v>-7</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-7.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>76.06363636363636</v>
+        <v>71.34030303030302</v>
       </c>
       <c r="AJ7" t="n">
-        <v>77.74242424242424</v>
+        <v>75.86481481481481</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.5</v>
+        <v>-0.9936442687747054</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.5</v>
+        <v>-1.957081121776767</v>
       </c>
       <c r="AM7" t="n">
-        <v>6</v>
+        <v>-8986636.363636367</v>
       </c>
       <c r="AN7" t="n">
-        <v>3589072.669321526</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1.338466802711654</v>
-      </c>
+        <v>0.4409090909090878</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>5902777.777777778</v>
+        <v>-3.227272727272734</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.827777777777726</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>3.989162340964384</v>
-      </c>
+        <v>-2.778947487295312</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>42200000</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.480555555555558</v>
-      </c>
+        <v>-0.2322727272727274</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.3000000000000003</v>
-      </c>
+        <v>-3.054545454545448</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>0.07904432523997729</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.274166559349609</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.7320145307273549</v>
-      </c>
+        <v>3.170000000000016</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>4.5</v>
+        <v>1.793279126670427</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.063888888888883</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.5083333333333258</v>
-      </c>
+        <v>-0.3097169207603996</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-4074993.242988896</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -1746,23 +1680,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45550.3125</v>
+        <v>45563.65625</v>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>202</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -1784,132 +1718,2226 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>141</v>
+      </c>
+      <c r="M8" t="n">
+        <v>23</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.0950000000000002</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>70.98363636363636</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>78.13888888888889</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-2.279530162441908</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.01039310810182315</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-5722727.272727272</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.2909090909090892</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>-1.829545454545453</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-2.925470880450462</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>0.01136363636363691</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>-1.784090909090907</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>-1.838636363636397</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>-1.666082709259882</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.318906745477753</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
+        <v>-4844565.80983294</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>79</v>
+      </c>
+      <c r="F9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" t="n">
+        <v>77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>771</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>223</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
+        <v>157</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6350000000000002</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.605</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>73.26161616161616</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>75.74666666666667</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.650220330237353</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-7.122036893704873</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-25854431.81818182</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.339772727272724</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>-6.587373737373738</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-6.940273821809427</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-0.1664141414141409</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>-6.3433080808081</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>-1.708964646464693</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>1.080458204334406</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.2187319401444789</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>-17996776.36523908</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C10" t="n">
+        <v>87</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63</v>
+      </c>
+      <c r="G10" t="n">
+        <v>77</v>
+      </c>
+      <c r="H10" t="n">
+        <v>771</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>186</v>
+      </c>
+      <c r="M10" t="n">
+        <v>189</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.005000000000000115</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>73.90092592592593</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>76.60833333333333</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1.440273577658484</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-5.856706517054988</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-35283818.18181818</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-2.897272727272728</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>-8.467272727272729</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-8.027356547970371</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-1.468181818181818</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>-10.01363636363637</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>3.49818181818182</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>-0.4824285433236639</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.8688954310821317</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>-22872953.08006145</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.65625</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>41</v>
+      </c>
+      <c r="E11" t="n">
+        <v>23</v>
+      </c>
+      <c r="F11" t="n">
+        <v>55</v>
+      </c>
+      <c r="G11" t="n">
+        <v>77</v>
+      </c>
+      <c r="H11" t="n">
+        <v>771</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>91</v>
+      </c>
+      <c r="M11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4099999999999999</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>77.43181818181817</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>72.45483164983165</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.5637890403370278</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>8.366355796878068</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>30631819.44444445</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.4827777777777804</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="n">
+        <v>7.053888888888878</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10.29684492464206</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>0.7772222222222225</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>9.301111111111098</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>0.6816666666666436</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>-0.6266436998486995</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.5721957241394582</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>22806833.83359585</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C12" t="n">
+        <v>97</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F12" t="n">
+        <v>187</v>
+      </c>
+      <c r="G12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H12" t="n">
+        <v>771</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>63</v>
+      </c>
+      <c r="M12" t="n">
+        <v>239</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8633333333333331</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.7599999999999998</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-2.666666666666668</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1.333333333333336</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.333333333333336</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>78.69259259259259</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>73.9909090909091</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-1.100088143645067</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4.880197462720346</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>9369444.444444444</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1.661111111111111</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>4.958333333333329</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.299791650950112</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>-0.180555555555556</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>3.486111111111114</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>5.641666666666652</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>3.119509816556416</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.07228326355185666</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
+        <v>6634199.78929347</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>41</v>
+      </c>
+      <c r="E13" t="n">
+        <v>45</v>
+      </c>
+      <c r="F13" t="n">
+        <v>31</v>
+      </c>
+      <c r="G13" t="n">
+        <v>77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>771</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>54</v>
+      </c>
+      <c r="M13" t="n">
+        <v>204</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.2033333333333336</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.7233333333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>73.46666666666667</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>72.88518518518518</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>3.072512757915568</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-1.237097803092041</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4071868.686868683</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.875757575757572</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="n">
+        <v>0.6095959595959641</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.163853043801893</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>0.6459595959595958</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>2.470454545454544</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="n">
+        <v>-1.858080808080814</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>1.54671065933212</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.3337128600299955</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
+        <v>807159.7152847126</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>140</v>
+      </c>
+      <c r="F14" t="n">
+        <v>175</v>
+      </c>
+      <c r="G14" t="n">
+        <v>77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>771</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>223</v>
+      </c>
+      <c r="M14" t="n">
+        <v>268</v>
+      </c>
+      <c r="N14" t="n">
+        <v>21</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.06333333333333302</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.333333333333332</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-4.999999999999998</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>74.28409090909092</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>74.29259259259258</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.348410184231799</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>5.355339912644908</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>17073477.27272727</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.4118181818181803</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>4.710454545454553</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>5.576326726342714</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>4.64318181818183</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>-2.884545454545446</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>-3.339618485734235</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.6224767772721735</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
+        <v>16425986.81715769</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>97</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>771</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>54</v>
+      </c>
+      <c r="M15" t="n">
+        <v>239</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.003333333333333</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.08666666666666667</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.3333333333333321</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-14.33333333333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>76.98484848484848</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>75.09090909090909</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>3.029072208401296</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-2.886755386043248</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-4459363.636363637</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.1363636363636367</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="n">
+        <v>-2.045454545454547</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.04310825356553494</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>0.04636363636363638</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>-3.100909090909099</v>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>-1.71272727272725</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>-3.05537952177761</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.2327306813626153</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>-2193710.359792631</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45557.3125</v>
+      </c>
+      <c r="C16" t="n">
+        <v>131</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>56</v>
+      </c>
+      <c r="F16" t="n">
+        <v>102</v>
+      </c>
+      <c r="G16" t="n">
+        <v>77</v>
+      </c>
+      <c r="H16" t="n">
+        <v>771</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>63</v>
+      </c>
+      <c r="M16" t="n">
+        <v>116</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-22</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.1233333333333333</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.1066666666666669</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>7.999999999999998</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3.333333333333336</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-3.333333333333336</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>73.53333333333333</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-1.980333209463645</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.057704584063288</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-6840858.585858589</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.4674242424242436</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="n">
+        <v>-0.9244949494949424</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.629729521686059</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>-0.05782828282828301</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>-2.560101010101008</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>2.211111111111137</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="n">
+        <v>0.3581716612694379</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.06994965581922141</v>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
+        <v>114764.1167206373</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.65625</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>84</v>
+      </c>
+      <c r="E17" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24</v>
+      </c>
+      <c r="G17" t="n">
+        <v>77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>771</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>268</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-11</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.6733333333333331</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.003333333333333</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-8.999999999999998</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-4.333333333333333</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.999999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-2.666666666666668</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-3.666666666666664</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.666666666666664</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>77.10909090909091</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>78.22558922558922</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.2071091430816807</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.2380533217100691</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1689180.555555556</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.187777777777782</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.2750567261368246</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.02499999999999991</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="n">
+        <v>1.786666666666676</v>
+      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="n">
+        <v>-1.678888888888878</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="n">
+        <v>1.237825684104877</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.06361076604554872</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="n">
+        <v>42423.37325527333</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C18" t="n">
+        <v>58</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32</v>
+      </c>
+      <c r="F18" t="n">
+        <v>21</v>
+      </c>
+      <c r="G18" t="n">
+        <v>77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>771</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>97</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.9100000000000001</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-8.333333333333334</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-6.000000000000001</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-4.666666666666666</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>73.06161616161616</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>72.30681818181819</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.5113095238095227</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.673511904761909</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-1252749.999999996</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-2.619772727272725</v>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="n">
+        <v>1.669191919191917</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.240277777777791</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>-0.3026767676767674</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="n">
+        <v>-1.214873737373722</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>3.272601010101056</v>
+      </c>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="n">
+        <v>0.7867063492063266</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.04097222222222219</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
+        <v>9068792.162698412</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C19" t="n">
+        <v>52</v>
+      </c>
+      <c r="D19" t="n">
+        <v>62</v>
+      </c>
+      <c r="E19" t="n">
+        <v>52</v>
+      </c>
+      <c r="F19" t="n">
+        <v>123</v>
+      </c>
+      <c r="G19" t="n">
+        <v>77</v>
+      </c>
+      <c r="H19" t="n">
+        <v>771</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>91</v>
+      </c>
+      <c r="M19" t="n">
         <v>250</v>
       </c>
-      <c r="N8" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="N19" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O19" t="n">
         <v>-2</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.5166666666666669</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.006666666666666821</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V19" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.08333333333333304</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.1166666666666667</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="W19" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AB19" t="n">
         <v>0.6666666666666667</v>
       </c>
-      <c r="V8" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3.666666666666668</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AC19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG19" t="n">
         <v>-1</v>
       </c>
-      <c r="AD8" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>77.19259259259259</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>73.96868686868686</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-2.446584701309966</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.8543944473288718</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-2677222.222222222</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.7840404040403968</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="n">
+        <v>-2.824242424242428</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-4.281008005948379</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>-0.137777777777778</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>-3.012121212121201</v>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="n">
+        <v>-0.131313131313135</v>
+      </c>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="n">
+        <v>-1.280469827595454</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0.4314069487444101</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="n">
+        <v>-3024902.912438812</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>49</v>
+      </c>
+      <c r="E20" t="n">
+        <v>116</v>
+      </c>
+      <c r="F20" t="n">
+        <v>72</v>
+      </c>
+      <c r="G20" t="n">
+        <v>77</v>
+      </c>
+      <c r="H20" t="n">
+        <v>771</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>124</v>
+      </c>
+      <c r="M20" t="n">
+        <v>100</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-11</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.2266666666666665</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.1966666666666668</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-8.333333333333332</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-8.666666666666664</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>8.666666666666664</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>76.79924242424242</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>72.85530303030303</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.4215071076901715</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.9682686162045542</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-6037388.888888889</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-1.638333333333332</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="n">
+        <v>-0.4377777777777681</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-1.616679079120729</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>-0.2055555555555559</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>-2.845000000000013</v>
+      </c>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="n">
+        <v>-1.3183333333333</v>
+      </c>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>-0.5014415782539174</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.09381121776773926</v>
+      </c>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="n">
+        <v>-3436832.82787007</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45555.5625</v>
+      </c>
+      <c r="C21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D21" t="n">
+        <v>85</v>
+      </c>
+      <c r="E21" t="n">
+        <v>64</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>77</v>
+      </c>
+      <c r="H21" t="n">
+        <v>771</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>99</v>
+      </c>
+      <c r="M21" t="n">
+        <v>157</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.1033333333333331</v>
+      </c>
+      <c r="U21" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="V21" t="n">
         <v>-4.666666666666668</v>
       </c>
-      <c r="AF8" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>75.98989898989898</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>74.28409090909092</v>
-      </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
-        <v>397</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-14938419.21872417</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>2.426704886101177</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-15707083.33333333</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.127272727272754</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-4.911453388372891</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>29450000</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.490909090909085</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>350</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-0.5393939393939391</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-0.2366071149352882</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>-7.22592499519746</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.174526579371815</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>-4.63636363636364</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-3.724242424242419</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="W21" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.333333333333332</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>23.33333333333334</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-23.33333333333334</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>75.57239057239057</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>78.52794612794612</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.418961402337363</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-1.09723827086998</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1537545.454545454</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.403636363636362</v>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="n">
+        <v>-0.3054545454545519</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.5780580440682712</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>0.07272727272727275</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>1.947272727272747</v>
+      </c>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="n">
+        <v>0.4727272727272975</v>
+      </c>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>1.354297561394759</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.3191510450333979</v>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="n">
+        <v>-378183.0230842382</v>
+      </c>
+      <c r="BD21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV13"/>
+  <dimension ref="A1:BV15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,135 +690,135 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.65625</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -840,193 +840,191 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.119</v>
+        <v>-0.6918939393939396</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2500000000000001</v>
+        <v>-1.321678321678322</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.636363636363637</v>
+        <v>-1.075757575757575</v>
       </c>
       <c r="U2" t="n">
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>5.545454545454545</v>
+        <v>-3.053030303030303</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2727272727272727</v>
+        <v>-0.8409090909090908</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5</v>
+        <v>-0.5874125874125874</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.919642857142857</v>
+        <v>11.76625874125874</v>
       </c>
       <c r="AB2" t="n">
-        <v>-6.640518680013631</v>
+        <v>0.7690755264530953</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.479683630182052</v>
+        <v>419.0332202479278</v>
       </c>
       <c r="AD2" t="n">
-        <v>-281.3730118779358</v>
+        <v>-7.7984193162319</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>29.1111111111111</v>
+        <v>-1.444444444444457</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>-2.666666666666671</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.6666666666666679</v>
+        <v>4.833333333333336</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2.833333333333336</v>
+        <v>3.958041958041957</v>
       </c>
       <c r="AK2" t="n">
-        <v>-10</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
-        <v>12</v>
+        <v>-6.212121212121218</v>
       </c>
       <c r="AM2" t="n">
-        <v>-117.5</v>
+        <v>115.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>85.72727272727275</v>
+        <v>-68.84090909090918</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.8181818181818183</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1</v>
-      </c>
+        <v>-0.5555555555555556</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-0.2000000000000001</v>
+        <v>2</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.6666666666666679</v>
+        <v>-0.6666666666666661</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.333333333333336</v>
+        <v>-0.6573426573426584</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.329857397504455</v>
+        <v>0.8763157894736899</v>
       </c>
       <c r="AV2" t="n">
-        <v>-15.97570532697749</v>
+        <v>13.10741510587246</v>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>0.0413411382805357</v>
+        <v>0.03389857337468094</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0.4629629629629626</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-3.869312169312195</v>
-      </c>
+        <v>-0.1188811188811189</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>-2154.232804232804</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="n">
-        <v>4.43944341372913</v>
-      </c>
+        <v>-4.481643035962293</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-2.310615096827906</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-21064225.58922559</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-72585.26936026933</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>-1.640211640211632</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0.7877635797401865</v>
-      </c>
+        <v>-5.973737373737364</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
-        <v>3.424454335093699</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>0.2119361578623544</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
+        <v>-0.7210437710437816</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-2.917592592592587</v>
+      </c>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
+        <v>-4.045875420875433</v>
+      </c>
       <c r="BN2" t="n">
-        <v>1.619179894179908</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1024.839722450241</v>
-      </c>
+        <v>-49990.98650099795</v>
+      </c>
+      <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
-        <v>1469404.296105794</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>330248.0158730149</v>
-      </c>
+        <v>-0.4898685072026032</v>
+      </c>
+      <c r="BQ2" t="inlineStr"/>
       <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
+      <c r="BS2" t="n">
+        <v>-0.6216093233827849</v>
+      </c>
       <c r="BT2" t="n">
-        <v>4.346031746031748</v>
-      </c>
-      <c r="BU2" t="inlineStr"/>
+        <v>-3.245524567177881</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-7090989.024377186</v>
+      </c>
       <c r="BV2" t="n">
-        <v>-1.201975699370635</v>
+        <v>-1.008375420875421</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.54166666666</v>
       </c>
       <c r="C3" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -1048,193 +1046,197 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="M3" t="n">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.33</v>
+        <v>-0.27</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5997727272727276</v>
+        <v>0.1327272727272726</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.8406593406593403</v>
+        <v>0.2472527472527473</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.5</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2243589743589749</v>
+        <v>1.461538461538461</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8333333333333339</v>
+        <v>0.3333333333333339</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.230769230769232</v>
+        <v>7.153846153846153</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.5</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.07692307692307687</v>
+        <v>-0.7692307692307692</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3.25</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.2307692307692308</v>
+        <v>-0.8901098901098903</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.8417748917748926</v>
+        <v>-0.3245115995115992</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.301771573849002</v>
+        <v>-3.036970878543277</v>
       </c>
       <c r="AC3" t="n">
-        <v>283.0086223341783</v>
+        <v>145.3383813036054</v>
       </c>
       <c r="AD3" t="n">
-        <v>334.0237031990255</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>151.7082275327695</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>37</v>
+      </c>
       <c r="AF3" t="n">
-        <v>-16.13636363636364</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>-1.818181818181827</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>19</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-18.33636363636363</v>
+        <v>23.72727272727273</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.083333333333332</v>
+        <v>1.166666666666664</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-8.04395604395604</v>
+        <v>2.340659340659336</v>
       </c>
       <c r="AK3" t="n">
-        <v>-14</v>
+        <v>-22.66666666666667</v>
       </c>
       <c r="AL3" t="n">
-        <v>-26.88461538461539</v>
+        <v>-12.61538461538461</v>
       </c>
       <c r="AM3" t="n">
-        <v>-148.0000000000001</v>
+        <v>-251.3333333333333</v>
       </c>
       <c r="AN3" t="n">
-        <v>-246.75</v>
+        <v>-138.0769230769231</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5897435897435896</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-2</v>
-      </c>
+        <v>0.2564102564102559</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>-1.083333333333334</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.247252747252746</v>
+        <v>3.390109890109891</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.77423451305031</v>
+        <v>19.83487777496729</v>
       </c>
       <c r="AV3" t="n">
-        <v>12.66965210556458</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>3.811045170761716</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-0.04036845507433744</v>
+      </c>
       <c r="AX3" t="n">
-        <v>-0.04255568837141895</v>
+        <v>0.05558161054230655</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-0.4160353535353534</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>-1.779292929292922</v>
-      </c>
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-15916.79292929293</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="n">
-        <v>1.662192732023254</v>
-      </c>
+        <v>-1.33394223223172</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.310877179468374</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-6306177.398989899</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-21931.94444444445</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>-3.368518518518513</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>-0.9291438666374177</v>
-      </c>
+        <v>-3.043876262626242</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
-        <v>-3.709029219413949</v>
-      </c>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="n">
-        <v>0.02097678406960424</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
+        <v>-0.7970959595959357</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-0.9908459595959584</v>
+      </c>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="n">
+        <v>-2.33819444444444</v>
+      </c>
       <c r="BN3" t="n">
-        <v>-3.400252525252512</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-8345.347614659688</v>
-      </c>
+        <v>-11304.54554150561</v>
+      </c>
+      <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="n">
-        <v>-4052593.482151906</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>-6369690.65656566</v>
-      </c>
+        <v>-0.03557599807599798</v>
+      </c>
+      <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
+      <c r="BS3" t="n">
+        <v>-1.489262412740175</v>
+      </c>
       <c r="BT3" t="n">
-        <v>0.8512626262626206</v>
-      </c>
-      <c r="BU3" t="inlineStr"/>
+        <v>0.5297471528437967</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-2577388.207888436</v>
+      </c>
       <c r="BV3" t="n">
-        <v>-4.665426805666371</v>
+        <v>-0.1390151515151514</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1256,209 +1258,191 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.213333333333333</v>
+        <v>-1.496666666666667</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.708461538461538</v>
+        <v>-0.7167948717948714</v>
       </c>
       <c r="Q4" t="n">
         <v>-1</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.9846153846153847</v>
+        <v>-0.8571428571428572</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.666666666666666</v>
+        <v>-0.25</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09230769230769287</v>
+        <v>-1.313186813186814</v>
       </c>
       <c r="U4" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.887179487179488</v>
+        <v>-1.945054945054945</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.666666666666667</v>
+        <v>-2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2820512820512817</v>
+        <v>-1.230769230769231</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3</v>
+        <v>-3.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3692307692307693</v>
+        <v>-1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.915964590964592</v>
+        <v>-1.07834249084249</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3285462278556897</v>
+        <v>2.614332211419529</v>
       </c>
       <c r="AC4" t="n">
-        <v>-289.3481671119148</v>
+        <v>122.4942256076844</v>
       </c>
       <c r="AD4" t="n">
-        <v>-63.9349350936032</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-41</v>
-      </c>
+        <v>179.8997493995991</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-1.426573426573412</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-20</v>
-      </c>
+        <v>-26.36363636363636</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-10.3986013986014</v>
+        <v>-12.90909090909091</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.333333333333339</v>
+        <v>-1.416666666666668</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.538461538461537</v>
+        <v>-6.642857142857139</v>
       </c>
       <c r="AK4" t="n">
-        <v>-3.333333333333343</v>
+        <v>-15.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.8820512820512789</v>
+        <v>-20.8021978021978</v>
       </c>
       <c r="AM4" t="n">
-        <v>-30</v>
+        <v>-136.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>-17.21538461538461</v>
+        <v>-185.0604395604396</v>
       </c>
       <c r="AO4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4615384615384617</v>
+        <v>-0.4615384615384615</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>0.6666666666666666</v>
+        <v>-1.25</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.666666666666666</v>
+        <v>2.083333333333334</v>
       </c>
       <c r="AT4" t="n">
-        <v>-2.194871794871796</v>
+        <v>0.2142857142857135</v>
       </c>
       <c r="AU4" t="n">
-        <v>-10.37007832209071</v>
+        <v>-1.55908306304978</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.944892738274053</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.09223614936717688</v>
-      </c>
+        <v>12.62334109692243</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-0.03321989428002949</v>
+        <v>0.006363726310762929</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.75</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.08717948717948718</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-1.219402356902357</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-1.519234006734052</v>
-      </c>
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>-100191.3720538721</v>
+        <v>0.37369018477807</v>
       </c>
       <c r="BD4" t="n">
-        <v>-249000</v>
+        <v>-0.2632376101228964</v>
       </c>
       <c r="BE4" t="n">
-        <v>-48975000</v>
-      </c>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="n">
-        <v>0.209417707260954</v>
-      </c>
+        <v>-6296917.989417991</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-27662.56613756614</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>-4.719065656565661</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>-1.229997977486534</v>
-      </c>
+        <v>-3.290343915343925</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>-3.122621012981412</v>
+        <v>-0.384788359788331</v>
       </c>
       <c r="BK4" t="n">
-        <v>-222</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>-0.4153643457991283</v>
-      </c>
+        <v>-0.783333333333335</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>-3</v>
+        <v>-2.41507936507935</v>
       </c>
       <c r="BN4" t="n">
-        <v>-5.931060606060598</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-71110.30187013597</v>
-      </c>
+        <v>-30887.8445274333</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>-17696851.68742076</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-32208851.01010101</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>-241</v>
-      </c>
+        <v>-0.3878855444072837</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="n">
-        <v>-6</v>
+        <v>-5.337480439390987</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.4005471380471413</v>
-      </c>
-      <c r="BU4" t="inlineStr"/>
+        <v>-6.549655382764371</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-8174672.613418425</v>
+      </c>
       <c r="BV4" t="n">
-        <v>-3.133950151043962</v>
+        <v>-0.537037037037037</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.54166666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>202</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1480,213 +1464,191 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="M5" t="n">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.746666666666667</v>
+        <v>-0.7699999999999998</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6284615384615385</v>
+        <v>-1.251333333333334</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.5</v>
+        <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7692307692307692</v>
+        <v>-1.775</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9166666666666661</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.266666666666667</v>
+        <v>-3.116666666666666</v>
       </c>
       <c r="U5" t="n">
-        <v>-7.333333333333334</v>
+        <v>-11.33333333333334</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.76923076923077</v>
+        <v>-9.504166666666668</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.583333333333333</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.476923076923077</v>
+        <v>-1.241666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2.75</v>
+        <v>-1</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1</v>
+        <v>-1.175</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.988995215311006</v>
+        <v>-4.761363636363636</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.583296571122243</v>
+        <v>-0.3771482528264656</v>
       </c>
       <c r="AC5" t="n">
-        <v>197.8395530850846</v>
+        <v>-148.3655545626848</v>
       </c>
       <c r="AD5" t="n">
-        <v>125.7491661002368</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-41</v>
-      </c>
+        <v>-73.60818006682328</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-22.23333333333333</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-26</v>
-      </c>
+        <v>-39.69871794871794</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-12.46666666666666</v>
+        <v>-43.92307692307692</v>
       </c>
       <c r="AI5" t="n">
-        <v>-9.916666666666664</v>
+        <v>-18.33333333333333</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-9.676923076923075</v>
+        <v>-2.570833333333333</v>
       </c>
       <c r="AK5" t="n">
-        <v>-26.5</v>
+        <v>-40.66666666666667</v>
       </c>
       <c r="AL5" t="n">
-        <v>-10.71794871794872</v>
+        <v>-25.20833333333333</v>
       </c>
       <c r="AM5" t="n">
-        <v>-248.4166666666667</v>
+        <v>-324.3333333333333</v>
       </c>
       <c r="AN5" t="n">
-        <v>-94.20512820512812</v>
+        <v>-211.2291666666667</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.5833333333333333</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.4512820512820515</v>
+        <v>-0.1517857142857144</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
-        <v>-5.5</v>
+        <v>-0.6666666666666679</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.8923076923076909</v>
+        <v>-5.191666666666666</v>
       </c>
       <c r="AU5" t="n">
-        <v>27.76717223311903</v>
+        <v>23.23908514372911</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.498230486467072</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-0.03772005772005772</v>
-      </c>
+        <v>22.00417025908766</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-0.01394933868064398</v>
+        <v>-0.03346705741048973</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.5833333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.3538461538461539</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-1.121170033670034</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.097685185185156</v>
-      </c>
+        <v>-0.07083333333333333</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>-17185.43771043771</v>
+        <v>-1.889561083724175</v>
       </c>
       <c r="BD5" t="n">
-        <v>-15000</v>
+        <v>0.7216958420350501</v>
       </c>
       <c r="BE5" t="n">
-        <v>-100000</v>
+        <v>-15103910.98484848</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.43176600922596</v>
-      </c>
+        <v>-43895.49062049063</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>-4.213468013467988</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.916865928614385</v>
-      </c>
+        <v>-7.512987012987011</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>-4.842559271339312</v>
+        <v>-3.035281385281365</v>
       </c>
       <c r="BK5" t="n">
-        <v>206</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.6154290789831407</v>
-      </c>
+        <v>-0.2492784992784998</v>
+      </c>
+      <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>3</v>
+        <v>-6.874386724386724</v>
       </c>
       <c r="BN5" t="n">
-        <v>-5.59608585858588</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>-6045.139804523387</v>
-      </c>
+        <v>-25232.6593825029</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>-13804033.22585463</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-15392946.12794613</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>220</v>
-      </c>
+        <v>-0.4591989761931883</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>4</v>
+        <v>-4.239281841272359</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.150841750841753</v>
+        <v>-3.632266887701689</v>
       </c>
       <c r="BU5" t="n">
-        <v>1</v>
+        <v>-9160705.052974874</v>
       </c>
       <c r="BV5" t="n">
-        <v>-5.357223057368941</v>
+        <v>-0.62020202020202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45585.3125</v>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1708,215 +1670,191 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="M6" t="n">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.09666666666666701</v>
+        <v>-1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2601923076923078</v>
+        <v>-1.0475</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2307692307692308</v>
+        <v>-1.071428571428571</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.000000000000001</v>
+        <v>-2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1538461538461542</v>
+        <v>-3.027472527472527</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.333333333333334</v>
+        <v>-10.58333333333333</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1538461538461533</v>
+        <v>-10.68681318681319</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>-1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2307692307692306</v>
+        <v>-0.6208791208791211</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>-0.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4615384615384617</v>
+        <v>-0.4285714285714288</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.144444444444446</v>
+        <v>-3.347249278499278</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.697045023205501</v>
+        <v>-0.275102462692459</v>
       </c>
       <c r="AC6" t="n">
-        <v>-264.3489091792463</v>
+        <v>-325.3654639186395</v>
       </c>
       <c r="AD6" t="n">
-        <v>-187.9378911759189</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>29</v>
-      </c>
+        <v>-58.13029411271043</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>23.00000000000001</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>34</v>
-      </c>
+        <v>-56.24545454545455</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>18.18181818181818</v>
+        <v>-51.38181818181818</v>
       </c>
       <c r="AI6" t="n">
-        <v>-12.00000000000001</v>
+        <v>-10.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.6153846153846132</v>
+        <v>-18.64285714285715</v>
       </c>
       <c r="AK6" t="n">
-        <v>-13.33333333333333</v>
+        <v>-15</v>
       </c>
       <c r="AL6" t="n">
-        <v>15.38461538461539</v>
+        <v>-26.82417582417582</v>
       </c>
       <c r="AM6" t="n">
-        <v>-121.3333333333334</v>
+        <v>-102.6666666666667</v>
       </c>
       <c r="AN6" t="n">
-        <v>122.2307692307692</v>
+        <v>-241.0384615384615</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1.076923076923077</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.4615384615384615</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>0.7999999999999999</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.333333333333336</v>
+        <v>-6</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.1538461538461533</v>
+        <v>-3.857142857142859</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.859528202562259</v>
+        <v>17.33328071199925</v>
       </c>
       <c r="AV6" t="n">
-        <v>-10.4275186766583</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.03668406756642052</v>
-      </c>
+        <v>25.41042458660809</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>0.02759736259354513</v>
+        <v>-0.07081392925318672</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.1538461538461539</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0.5308080808080806</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.052741702741713</v>
-      </c>
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>21651.40692640692</v>
+        <v>0.9276346499716226</v>
       </c>
       <c r="BD6" t="n">
-        <v>230000</v>
+        <v>-2.651973104726725</v>
       </c>
       <c r="BE6" t="n">
-        <v>41025000</v>
+        <v>-21039509.37950938</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0.5671142211825426</v>
-      </c>
+        <v>-79984.45165945165</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="n">
-        <v>1.351202501202508</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.861118953510243</v>
-      </c>
+        <v>-9.45501443001443</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="n">
-        <v>4.231546207415775</v>
+        <v>2.19408369408373</v>
       </c>
       <c r="BK6" t="n">
-        <v>301</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.1669151138716358</v>
-      </c>
+        <v>-2.800829725829725</v>
+      </c>
+      <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="n">
-        <v>4</v>
+        <v>-6.373665223665213</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.777092352092353</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>16855.48923126563</v>
-      </c>
+        <v>-62826.1102874198</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="n">
-        <v>4096092.633298379</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5565569.985569988</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>306</v>
-      </c>
+        <v>-0.6862333654000319</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="n">
-        <v>4</v>
+        <v>-4.617849736146852</v>
       </c>
       <c r="BT6" t="n">
-        <v>2.384163059163065</v>
+        <v>-7.743976106421741</v>
       </c>
       <c r="BU6" t="n">
-        <v>-6.5</v>
+        <v>-11699401.6843496</v>
       </c>
       <c r="BV6" t="n">
-        <v>3.51684520448498</v>
+        <v>-0.9813131313131309</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.65625</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1938,209 +1876,191 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>223</v>
       </c>
       <c r="M7" t="n">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8130219780219783</v>
+        <v>0.4130769230769233</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6142857142857143</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.085714285714286</v>
+        <v>0.1153846153846145</v>
       </c>
       <c r="U7" t="n">
-        <v>12.66666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="V7" t="n">
-        <v>5.642857142857142</v>
+        <v>2.326923076923077</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.4166666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4476190476190477</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6857142857142855</v>
+        <v>-0.06593406593406592</v>
       </c>
       <c r="AA7" t="n">
-        <v>-11.43392857142857</v>
+        <v>13.21626984126984</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.551064790370408</v>
+        <v>-1.403185229241135</v>
       </c>
       <c r="AC7" t="n">
-        <v>-240.0895625417212</v>
+        <v>208.0301293486534</v>
       </c>
       <c r="AD7" t="n">
-        <v>-59.39450681130606</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>86</v>
-      </c>
+        <v>-115.9337339632394</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>46.96153846153847</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>34</v>
-      </c>
+        <v>-22.20909090909092</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>28.47435897435898</v>
+        <v>-13.42727272727273</v>
       </c>
       <c r="AI7" t="n">
-        <v>14.58333333333334</v>
+        <v>2.333333333333336</v>
       </c>
       <c r="AJ7" t="n">
-        <v>13.75714285714285</v>
+        <v>-2.593406593406595</v>
       </c>
       <c r="AK7" t="n">
-        <v>23.66666666666667</v>
+        <v>35</v>
       </c>
       <c r="AL7" t="n">
-        <v>33.24761904761904</v>
+        <v>-6.038461538461533</v>
       </c>
       <c r="AM7" t="n">
-        <v>208.9166666666666</v>
+        <v>383</v>
       </c>
       <c r="AN7" t="n">
-        <v>298.9857142857142</v>
+        <v>-44.28846153846155</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.416666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.3809523809523809</v>
+        <v>-1.141025641025641</v>
       </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.833333333333332</v>
+        <v>-4.666666666666667</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.033333333333337</v>
+        <v>-1.153846153846155</v>
       </c>
       <c r="AU7" t="n">
-        <v>-29.97985618659246</v>
+        <v>-15.25130772005772</v>
       </c>
       <c r="AV7" t="n">
-        <v>-29.25161916733127</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.02999945337076275</v>
-      </c>
+        <v>4.764687761870302</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>0.02336219197240378</v>
+        <v>-0.03203375057592261</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.280952380952381</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>-2.980952380952431</v>
-      </c>
+        <v>0.2032967032967034</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>27338.74458874459</v>
+        <v>1.563994708994727</v>
       </c>
       <c r="BD7" t="n">
-        <v>-43000</v>
+        <v>-0.7084038800705414</v>
       </c>
       <c r="BE7" t="n">
-        <v>-9800000</v>
-      </c>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="n">
-        <v>2.229290324543943</v>
-      </c>
+        <v>12428333.33333333</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>52233.33333333334</v>
+      </c>
+      <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="n">
-        <v>7.1943722943723</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>-0.7264297437667153</v>
-      </c>
+        <v>0.9916666666666742</v>
+      </c>
+      <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="n">
-        <v>6.899997430776423</v>
+        <v>3.51666666666668</v>
       </c>
       <c r="BK7" t="n">
-        <v>-148</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.5582940516273851</v>
-      </c>
+        <v>-1.616666666666667</v>
+      </c>
+      <c r="BL7" t="inlineStr"/>
       <c r="BM7" t="n">
-        <v>-2</v>
+        <v>2.266666666666652</v>
       </c>
       <c r="BN7" t="n">
-        <v>9.19567099567098</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>17808.32649713602</v>
-      </c>
+        <v>37522.23104056437</v>
+      </c>
+      <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="n">
-        <v>8366066.948098199</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>18784913.41991342</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>-153</v>
-      </c>
+        <v>0.07009700176366818</v>
+      </c>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="n">
-        <v>-2</v>
+        <v>1.398809523809518</v>
       </c>
       <c r="BT7" t="n">
-        <v>1.991991341991344</v>
-      </c>
-      <c r="BU7" t="inlineStr"/>
+        <v>1.638020282186929</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5907759.589947088</v>
+      </c>
       <c r="BV7" t="n">
-        <v>5.753129117259562</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.3125</v>
+        <v>45584.54166666666</v>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -2162,213 +2082,193 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>223</v>
+        <v>91</v>
       </c>
       <c r="M8" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2</v>
+        <v>2.02</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7004615384615386</v>
+        <v>1.11525641025641</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5999999999999999</v>
+        <v>1.553846153846154</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3333333333333335</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.266666666666667</v>
+        <v>2.266666666666667</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.666666666666667</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6666666666666661</v>
+        <v>8.25</v>
       </c>
       <c r="W8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.2</v>
+        <v>-0.7692307692307692</v>
       </c>
       <c r="AA8" t="n">
-        <v>-6.826573310948311</v>
+        <v>-4.811217948717948</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.463831937526984</v>
+        <v>-3.181698813524261</v>
       </c>
       <c r="AC8" t="n">
-        <v>-528.1166342978481</v>
+        <v>-293.7624982947076</v>
       </c>
       <c r="AD8" t="n">
-        <v>-252.0173884908619</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>41.5</v>
-      </c>
+        <v>-134.4012137418377</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>22.15384615384615</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>17.5</v>
-      </c>
+        <v>47.93636363636364</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>1.076923076923073</v>
+        <v>36.83636363636364</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3</v>
+        <v>-1.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-4.133333333333333</v>
+        <v>11.75384615384615</v>
       </c>
       <c r="AK8" t="n">
-        <v>30.83333333333334</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>18.8</v>
+        <v>31.56666666666668</v>
       </c>
       <c r="AM8" t="n">
-        <v>357.6666666666667</v>
+        <v>97.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>178.6666666666667</v>
+        <v>301.4166666666667</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5833333333333333</v>
+        <v>-1.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.2666666666666666</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
+        <v>-1.047619047619048</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
       <c r="AR8" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.9333333333333335</v>
       </c>
       <c r="AS8" t="n">
-        <v>-2.75</v>
+        <v>-4.499999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>-1.600000000000001</v>
+        <v>-0.2717948717948726</v>
       </c>
       <c r="AU8" t="n">
-        <v>-22.68617350124063</v>
+        <v>24.57402668603327</v>
       </c>
       <c r="AV8" t="n">
-        <v>-9.496146541729455</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-0.001117935212362454</v>
-      </c>
+        <v>-16.40910988850573</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>-0.02458534075445749</v>
+        <v>0.09069626106171055</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.4666666666666666</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.068181818181818</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.4568181818181642</v>
-      </c>
+        <v>-0.1128205128205128</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>83912.5</v>
+        <v>-1.240721166846271</v>
       </c>
       <c r="BD8" t="n">
-        <v>483000</v>
+        <v>-1.982111239891555</v>
       </c>
       <c r="BE8" t="n">
-        <v>131000000</v>
+        <v>41028693.18181819</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>-0.8484138387155582</v>
-      </c>
+        <v>124238.7065095398</v>
+      </c>
+      <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="n">
-        <v>8.737499999999997</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0.6543356180856392</v>
-      </c>
+        <v>10.11621773288439</v>
+      </c>
+      <c r="BI8" t="inlineStr"/>
       <c r="BJ8" t="n">
-        <v>6.688527226285842</v>
+        <v>-0.550855780022431</v>
       </c>
       <c r="BK8" t="n">
-        <v>250</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.633140933140933</v>
-      </c>
+        <v>-0.4149971941638633</v>
+      </c>
+      <c r="BL8" t="inlineStr"/>
       <c r="BM8" t="n">
-        <v>3</v>
+        <v>9.541540404040404</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.155681818181804</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>58255.34839362426</v>
-      </c>
+        <v>97676.05492192641</v>
+      </c>
+      <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="n">
-        <v>14315550.23500605</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>30175170.45454545</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>246</v>
-      </c>
+        <v>0.803249890206412</v>
+      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="n">
-        <v>10</v>
+        <v>8.839029011006502</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0.9681818181818223</v>
+        <v>7.673757410837865</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.5</v>
+        <v>26125922.04302111</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.345239878257118</v>
+        <v>1.756439393939394</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45570.65625</v>
+        <v>45584.41666666666</v>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
@@ -2390,213 +2290,193 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>243</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7666666666666671</v>
+        <v>-0.5099999999999998</v>
       </c>
       <c r="P9" t="n">
-        <v>1.220384615384616</v>
+        <v>-0.2389999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.685714285714285</v>
+        <v>0.2500000000000001</v>
       </c>
       <c r="S9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.6666666666666643</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.212121212121213</v>
+      </c>
+      <c r="W9" t="n">
         <v>0.5</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.195238095238095</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4.666666666666666</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7.890476190476191</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
+        <v>-0.4242424242424241</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.25</v>
       </c>
-      <c r="X9" t="n">
-        <v>0.9333333333333336</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.6714285714285715</v>
-      </c>
       <c r="AA9" t="n">
-        <v>-9.567467948717947</v>
+        <v>0.9728835978835981</v>
       </c>
       <c r="AB9" t="n">
-        <v>-7.192705891173383</v>
+        <v>-7.054358178048054</v>
       </c>
       <c r="AC9" t="n">
-        <v>-386.0153391171759</v>
+        <v>-195.3247173822023</v>
       </c>
       <c r="AD9" t="n">
-        <v>-197.6487817227506</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>44</v>
-      </c>
+        <v>-321.7459054423148</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>18.33974358974359</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>40.5</v>
-      </c>
+        <v>29.1111111111111</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>25.66666666666666</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.5</v>
+        <v>-2.333333333333332</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.295238095238094</v>
+        <v>-3.249999999999993</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.166666666666671</v>
+        <v>-8.333333333333329</v>
       </c>
       <c r="AL9" t="n">
-        <v>20.18095238095238</v>
+        <v>12.40909090909091</v>
       </c>
       <c r="AM9" t="n">
-        <v>12.58333333333337</v>
+        <v>-78.49999999999994</v>
       </c>
       <c r="AN9" t="n">
-        <v>181.9619047619047</v>
+        <v>94.42424242424238</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.75</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.03571428571428559</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
+        <v>0.8030303030303028</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1</v>
+      </c>
       <c r="AR9" t="n">
-        <v>-1</v>
+        <v>-0.2000000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.833333333333334</v>
+        <v>1</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.2095238095238088</v>
+        <v>4.416666666666668</v>
       </c>
       <c r="AU9" t="n">
-        <v>-9.159718723305684</v>
+        <v>-2.785799168152117</v>
       </c>
       <c r="AV9" t="n">
-        <v>-15.03837060956502</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.03300639077234822</v>
-      </c>
+        <v>-17.34012176401196</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>0.01299190190945802</v>
+        <v>0.0413411382805357</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.143560606060606</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>-3.309974747474712</v>
-      </c>
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>73476.01010101009</v>
+        <v>0.2968653330897553</v>
       </c>
       <c r="BD9" t="n">
-        <v>147000</v>
+        <v>4.567386112547791</v>
       </c>
       <c r="BE9" t="n">
-        <v>64600000</v>
+        <v>330248.0158730149</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.159012021540622</v>
-      </c>
+        <v>-2154.232804232804</v>
+      </c>
+      <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="n">
-        <v>7.205366161616169</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>-0.748725900656666</v>
-      </c>
+        <v>1.619179894179908</v>
+      </c>
+      <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="n">
-        <v>9.838959068836076</v>
+        <v>-3.869312169312195</v>
       </c>
       <c r="BK9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1.303501389914433</v>
-      </c>
+        <v>4.346031746031748</v>
+      </c>
+      <c r="BL9" t="inlineStr"/>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>-1.640211640211632</v>
       </c>
       <c r="BN9" t="n">
-        <v>9.03832070707071</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>57922.75565776712</v>
-      </c>
+        <v>1287.975806923558</v>
+      </c>
+      <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="n">
-        <v>21524176.98438258</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>31817477.90404041</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2442676675413251</v>
+      </c>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="n">
-        <v>3</v>
+        <v>-1.090956054358472</v>
       </c>
       <c r="BT9" t="n">
-        <v>2.107638888888882</v>
+        <v>3.579599663976254</v>
       </c>
       <c r="BU9" t="n">
-        <v>-5.5</v>
+        <v>1588208.846582111</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.673726443592017</v>
+        <v>0.4629629629629626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45570.54166666666</v>
+        <v>45584.41666666666</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
@@ -2618,215 +2498,193 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>227</v>
+        <v>63</v>
       </c>
       <c r="M10" t="n">
-        <v>157</v>
+        <v>64</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.363333333333333</v>
+        <v>-1.663333333333333</v>
       </c>
       <c r="P10" t="n">
-        <v>1.317211538461539</v>
+        <v>-0.7850000000000003</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>-1.25</v>
       </c>
       <c r="R10" t="n">
-        <v>2.125</v>
+        <v>-1.054945054945055</v>
       </c>
       <c r="S10" t="n">
-        <v>2.333333333333334</v>
+        <v>-3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0125</v>
+        <v>-0.702380952380953</v>
       </c>
       <c r="U10" t="n">
-        <v>5.75</v>
+        <v>-2</v>
       </c>
       <c r="V10" t="n">
-        <v>7.758333333333333</v>
+        <v>-3.142857142857144</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>-3</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7583333333333333</v>
+        <v>-0.3571428571428572</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>-4</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.95</v>
+        <v>-0.445054945054945</v>
       </c>
       <c r="AA10" t="n">
-        <v>-6.532771395271395</v>
+        <v>-3.082846320346321</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6.143293212653217</v>
+        <v>5.583207146341544</v>
       </c>
       <c r="AC10" t="n">
-        <v>-209.4280720297686</v>
+        <v>127.4967964587143</v>
       </c>
       <c r="AD10" t="n">
-        <v>-177.2270605258939</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>16</v>
-      </c>
+        <v>292.4236629888547</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>27.49450549450549</v>
-      </c>
-      <c r="AG10" t="n">
+        <v>-16.13636363636364</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>-18.33636363636363</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-1.416666666666668</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-8.758241758241752</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-164.75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-257.6025641025641</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.5897435897435896</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.247252747252748</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.383256856447648</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13.61442625895016</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-0.04255568837141895</v>
+      </c>
+      <c r="AY10" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AH10" t="n">
-        <v>39.63736263736264</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>5.395833333333336</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>23.03333333333333</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>281.75</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>207.3482142857143</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.9333333333333331</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.366666666666667</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-8.819945013491843</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-21.69867521532811</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-0.02834973489043257</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.05258030371278707</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>0.1916666666666667</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.5291666666666666</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.775757575757581</v>
-      </c>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>21431.43939393939</v>
+        <v>-0.8602017254858652</v>
       </c>
       <c r="BD10" t="n">
-        <v>25000</v>
+        <v>1.479629104333529</v>
       </c>
       <c r="BE10" t="n">
-        <v>44300000</v>
+        <v>-6356994.949494952</v>
       </c>
       <c r="BF10" t="n">
-        <v>-9</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>-1.129971238172331</v>
-      </c>
+        <v>-15672.72727272727</v>
+      </c>
+      <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="n">
-        <v>5.453030303030289</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.281244759841428</v>
-      </c>
+        <v>-3.416161616161617</v>
+      </c>
+      <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="n">
-        <v>2.282448968154071</v>
+        <v>-1.541414141414151</v>
       </c>
       <c r="BK10" t="n">
-        <v>74</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.3017876093718657</v>
-      </c>
+        <v>0.6207070707070699</v>
+      </c>
+      <c r="BL10" t="inlineStr"/>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>-3.262457912457918</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.818939393939374</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>8063.396735538256</v>
-      </c>
+        <v>-8979.563649193704</v>
+      </c>
+      <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="n">
-        <v>7958626.980965776</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>12865473.48484848</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>95</v>
-      </c>
+        <v>9.9906520577564e-05</v>
+      </c>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
       <c r="BS10" t="n">
-        <v>1</v>
+        <v>-4.914412049021124</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0.7765151515151452</v>
+        <v>-4.094311917141823</v>
       </c>
       <c r="BU10" t="n">
-        <v>12.33333333333334</v>
+        <v>-4197596.926624101</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.023249968728464</v>
+        <v>-0.4186868686868683</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45570.41666666666</v>
+        <v>45571.65625</v>
       </c>
       <c r="C11" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
@@ -2848,7 +2706,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>243</v>
+        <v>97</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -2857,206 +2715,204 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4166666666666664</v>
+        <v>-1.213333333333333</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4262087912087913</v>
+        <v>-0.708461538461538</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.75</v>
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.5625</v>
+        <v>-0.9846153846153847</v>
       </c>
       <c r="S11" t="n">
-        <v>-2</v>
+        <v>-4.666666666666666</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.058333333333333</v>
+        <v>-0.09230769230769287</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.25</v>
+        <v>-3</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.408333333333333</v>
+        <v>-2.887179487179488</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>-2.666666666666667</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9125</v>
+        <v>-0.2820512820512817</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>-3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.7750000000000001</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.041071428571429</v>
+        <v>-3.915964590964592</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.213216096213872</v>
+        <v>0.3285462278556897</v>
       </c>
       <c r="AC11" t="n">
-        <v>43.99511819649155</v>
+        <v>-289.3481671119148</v>
       </c>
       <c r="AD11" t="n">
-        <v>26.92040194178676</v>
+        <v>-63.9349350936032</v>
       </c>
       <c r="AE11" t="n">
-        <v>-23.5</v>
+        <v>-41</v>
       </c>
       <c r="AF11" t="n">
-        <v>-15.23076923076924</v>
+        <v>-1.426573426573412</v>
       </c>
       <c r="AG11" t="n">
-        <v>-14.5</v>
+        <v>-20</v>
       </c>
       <c r="AH11" t="n">
-        <v>-13.46153846153846</v>
+        <v>-10.3986013986014</v>
       </c>
       <c r="AI11" t="n">
-        <v>-8.5</v>
+        <v>1.333333333333339</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-8.420833333333334</v>
+        <v>3.538461538461537</v>
       </c>
       <c r="AK11" t="n">
-        <v>-2.5</v>
+        <v>-3.333333333333343</v>
       </c>
       <c r="AL11" t="n">
-        <v>-13.34166666666667</v>
+        <v>-0.8820512820512789</v>
       </c>
       <c r="AM11" t="n">
-        <v>-66.5</v>
+        <v>-30</v>
       </c>
       <c r="AN11" t="n">
-        <v>-129.7333333333333</v>
+        <v>-17.21538461538461</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.25</v>
+        <v>2</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-0.5</v>
-      </c>
+        <v>0.4615384615384617</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>-0.3500000000000001</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.25</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.9125000000000014</v>
+        <v>-2.194871794871796</v>
       </c>
       <c r="AU11" t="n">
-        <v>-4.561921389369154</v>
+        <v>-10.37007832209071</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.065636284008342</v>
+        <v>1.944892738274053</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.060150288541246</v>
+        <v>0.09223614936717688</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.05272679833758461</v>
+        <v>-0.03321989428002949</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.25</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.325</v>
+        <v>-0.08717948717948718</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>-326000</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.62838804713806</v>
+        <v>-242</v>
       </c>
       <c r="BC11" t="n">
-        <v>3760.753367003368</v>
+        <v>-1.229997977486534</v>
       </c>
       <c r="BD11" t="n">
-        <v>45000</v>
+        <v>0.209417707260954</v>
       </c>
       <c r="BE11" t="n">
-        <v>21400000</v>
+        <v>-32208851.01010101</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.333333333333332</v>
+        <v>-100191.3720538721</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.173755868931021</v>
+        <v>-3</v>
       </c>
       <c r="BH11" t="n">
-        <v>-2.450052609427615</v>
+        <v>-5.931060606060598</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.398046468387975</v>
+        <v>-58975000</v>
       </c>
       <c r="BJ11" t="n">
-        <v>2.151111635799168</v>
+        <v>-1.519234006734052</v>
       </c>
       <c r="BK11" t="n">
-        <v>152</v>
+        <v>0.4005471380471413</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>-225</v>
       </c>
       <c r="BM11" t="n">
-        <v>2</v>
+        <v>-4.719065656565661</v>
       </c>
       <c r="BN11" t="n">
-        <v>-0.7638573232323154</v>
+        <v>-71110.30187013597</v>
       </c>
       <c r="BO11" t="n">
-        <v>4380.408465653787</v>
+        <v>1.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>-283107.1821768801</v>
+        <v>-0.4153643457991283</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-2481419.66540404</v>
+        <v>-6</v>
       </c>
       <c r="BR11" t="n">
-        <v>158</v>
+        <v>-1.25</v>
       </c>
       <c r="BS11" t="n">
-        <v>4</v>
+        <v>-3.133950151043962</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.9582702020202021</v>
+        <v>-3.122621012981412</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.6666666666666572</v>
+        <v>-17696851.68742076</v>
       </c>
       <c r="BV11" t="n">
-        <v>-0.4441037786985618</v>
+        <v>-1.219402356902357</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.54166666666</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="G12" t="n">
         <v>77</v>
@@ -3078,7 +2934,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
         <v>204</v>
@@ -3087,206 +2943,204 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.253333333333333</v>
+        <v>-1.746666666666667</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1631249999999997</v>
+        <v>-0.6284615384615385</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2</v>
+        <v>-3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.03781512605042003</v>
+        <v>-0.7692307692307692</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.333333333333333</v>
+        <v>-0.9166666666666661</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6974789915966393</v>
+        <v>-1.266666666666667</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.666666666666666</v>
+        <v>-7.333333333333334</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.802521008403362</v>
+        <v>-3.76923076923077</v>
       </c>
       <c r="W12" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-1.583333333333333</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04621848739495804</v>
+        <v>-0.476923076923077</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2</v>
+        <v>-2.75</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.6050420168067225</v>
+        <v>-1</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.765692640692641</v>
+        <v>4.988995215311006</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.469901029450585</v>
+        <v>3.583296571122243</v>
       </c>
       <c r="AC12" t="n">
-        <v>88.99430926835063</v>
+        <v>197.8395530850846</v>
       </c>
       <c r="AD12" t="n">
-        <v>181.7663534887795</v>
+        <v>125.7491661002368</v>
       </c>
       <c r="AE12" t="n">
-        <v>-15</v>
+        <v>-41</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.700000000000003</v>
+        <v>-22.23333333333333</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>-26</v>
       </c>
       <c r="AH12" t="n">
-        <v>14.48333333333333</v>
+        <v>-12.46666666666666</v>
       </c>
       <c r="AI12" t="n">
-        <v>-9.333333333333332</v>
+        <v>-9.916666666666664</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-5.445378151260506</v>
+        <v>-9.676923076923075</v>
       </c>
       <c r="AK12" t="n">
-        <v>-9.333333333333336</v>
+        <v>-26.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>-9.579831932773118</v>
+        <v>-10.71794871794872</v>
       </c>
       <c r="AM12" t="n">
-        <v>-90.33333333333337</v>
+        <v>-248.4166666666667</v>
       </c>
       <c r="AN12" t="n">
-        <v>-94.99159663865544</v>
+        <v>-94.20512820512812</v>
       </c>
       <c r="AO12" t="n">
+        <v>-0.5833333333333333</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.4512820512820515</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.8923076923076909</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>27.76717223311903</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.498230486467072</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-0.03772005772005772</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.01394933868064398</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.5833333333333333</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.3538461538461539</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>220</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.916865928614385</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.43176600922596</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-15392946.12794613</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-17185.43771043771</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-5.59608585858588</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.097685185185156</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0.150841750841753</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>206</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-4.213468013467988</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-6045.139804523387</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.6154290789831407</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR12" t="n">
         <v>1</v>
       </c>
-      <c r="AP12" t="n">
-        <v>1.323529411764706</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-0.3333333333333321</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4.315126050420165</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9.646370564133719</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.01629717857402113</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-0.06770882851257298</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.01953983589760783</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-0.04621848739495801</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-0.05256132756132748</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0.4090548340548708</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2701.551226551228</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>54000</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-1.899999999999999</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0.3826103230974134</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.720274170274166</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>-0.2553057309186499</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>2.45662443328348</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>224</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>-0.008544087491455965</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>2.752344877344882</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>-2625.906404445144</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1320249.08756929</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>2363344.155844157</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>236</v>
-      </c>
       <c r="BS12" t="n">
-        <v>3</v>
+        <v>-5.357223057368941</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0.7635642135642122</v>
+        <v>-4.842559271339312</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.800000000000011</v>
+        <v>-13804033.22585463</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.476510422489497</v>
+        <v>-1.121170033670034</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45569.5625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>187</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
         <v>77</v>
@@ -3308,189 +3162,645 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>227</v>
       </c>
       <c r="M13" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4699999999999999</v>
+        <v>-0.09666666666666701</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.01807692307692332</v>
+        <v>-0.2601923076923078</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.2307692307692308</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-1.000000000000001</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1538461538461542</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1538461538461533</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.2307692307692306</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4615384615384617</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1.144444444444446</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-2.697045023205501</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-264.3489091792463</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-187.9378911759189</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>23.00000000000001</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-12.00000000000001</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.6153846153846132</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-13.33333333333333</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-121.3333333333334</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>122.2307692307692</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1.076923076923077</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.333333333333336</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.1538461538461533</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-1.859528202562259</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-10.4275186766583</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.03668406756642052</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.02759736259354513</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.1538461538461539</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>230000</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>306</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.861118953510243</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.5671142211825426</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5565569.985569988</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>21651.40692640692</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.777092352092353</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>41025000</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.052741702741713</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>2.384163059163065</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>301</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.351202501202508</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>16855.48923126563</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.1669151138716358</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>3.51684520448498</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>4.231546207415775</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4096092.633298379</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.5308080808080806</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>66</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>771</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>38</v>
+      </c>
+      <c r="M14" t="n">
+        <v>23</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8130219780219783</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.085714285714286</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.642857142857142</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.4476190476190477</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.6857142857142855</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-11.43392857142857</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.551064790370408</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-240.0895625417212</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-59.39450681130606</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>86</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>46.96153846153847</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28.47435897435898</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>14.58333333333334</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>13.75714285714285</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>33.24761904761904</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>208.9166666666666</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>298.9857142857142</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.833333333333332</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.033333333333337</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-29.97985618659246</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-29.25161916733127</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.02999945337076275</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.02336219197240378</v>
+      </c>
+      <c r="AY14" t="n">
         <v>-0.25</v>
       </c>
-      <c r="R13" t="n">
-        <v>0.1076923076923078</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-1.083333333333333</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.6307692307692307</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-6.249999999999998</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.564102564102562</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.083333333333333</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.5128205128205128</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.1384615384615384</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-1.46678841991342</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>4.693858265322007</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-71.52411109339667</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>193.1163085169841</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>9.409090909090907</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>35</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>15.87121212121212</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.666666666666664</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>5.75897435897436</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>-5.666666666666671</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.200000000000003</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-44.66666666666669</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>24.18461538461537</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-0.6666666666666679</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.7589743589743598</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-1.103590253915325</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-9.862889138602412</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-0.0303281599721228</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0.02228733192795993</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.2871794871794872</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0.5285143097643101</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.674579124579139</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>77906.74452861951</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>169000</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="n">
-        <v>-1.286614593136331</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>4.835963804713799</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>-0.447870099126618</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>3.860733470759868</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>160</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.4875114431477463</v>
-      </c>
-      <c r="BM13" t="n">
+      <c r="AZ14" t="n">
+        <v>0.280952380952381</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-43000</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-153</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.7264297437667153</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.229290324543943</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>18784913.41991342</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>27338.74458874459</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.19567099567098</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-9800000</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-2.980952380952431</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.991991341991344</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-148</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>7.1943722943723</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>17808.32649713602</v>
+      </c>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="n">
+        <v>0.5582940516273851</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="n">
+        <v>5.753129117259562</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>6.899997430776423</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>8366066.948098199</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45571.3125</v>
+      </c>
+      <c r="C15" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>32</v>
+      </c>
+      <c r="F15" t="n">
+        <v>97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>771</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>223</v>
+      </c>
+      <c r="M15" t="n">
+        <v>105</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.7004615384615386</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6666666666666661</v>
+      </c>
+      <c r="W15" t="n">
         <v>2</v>
       </c>
-      <c r="BN13" t="n">
-        <v>5.313057659932653</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>59513.87228392674</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>9837471.311049946</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>18304892.67676768</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>162</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>-0.6921401515151508</v>
-      </c>
-      <c r="BU13" t="inlineStr"/>
-      <c r="BV13" t="n">
-        <v>4.744935818530308</v>
+      <c r="X15" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-6.826573310948311</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-2.463831937526984</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-528.1166342978481</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-252.0173884908619</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22.15384615384615</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.076923076923073</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-4.133333333333333</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>30.83333333333334</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>357.6666666666667</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-1.600000000000001</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-22.68617350124063</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-9.496146541729455</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.001117935212362454</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.02458534075445749</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>543000</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>327</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.6543356180856392</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.8484138387155582</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>30175170.45454545</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>83912.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>8.155681818181804</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>156000000</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.4568181818181642</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-0.9681818181818223</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>330</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.737499999999997</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>58255.34839362426</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>7.399999999999999</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.633140933140933</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.1999999999999886</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>6.345239878257118</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6.688527226285842</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>14315550.23500605</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1.068181818181818</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -885,112 +885,112 @@
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -1270,55 +1270,55 @@
       <c r="CM2" t="n">
         <v>-1.965376542030967</v>
       </c>
-      <c r="CN2" t="n">
-        <v>-1.865435606060611</v>
-      </c>
+      <c r="CN2" t="inlineStr"/>
       <c r="CO2" t="n">
-        <v>-3.129125349605903</v>
+        <v>13278938.39904415</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.1612342903568447</v>
+        <v>1.282589894135228</v>
       </c>
       <c r="CQ2" t="inlineStr"/>
       <c r="CR2" t="n">
+        <v>4.603721797049886</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-1.865435606060611</v>
+      </c>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="n">
+        <v>24911.45645965084</v>
+      </c>
+      <c r="CX2" t="n">
         <v>0.82362012987013</v>
       </c>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="n">
+      <c r="CY2" t="n">
         <v>2.697307900432904</v>
       </c>
-      <c r="CV2" t="n">
-        <v>13278938.39904415</v>
-      </c>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="n">
-        <v>4.603721797049886</v>
-      </c>
-      <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="n">
-        <v>1.282589894135228</v>
-      </c>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="n">
+        <v>21252408.00865801</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-3.129125349605903</v>
+      </c>
       <c r="DC2" t="n">
-        <v>2.528733766233785</v>
+        <v>38438.16287878789</v>
       </c>
       <c r="DD2" t="inlineStr"/>
       <c r="DE2" t="n">
-        <v>38438.16287878789</v>
+        <v>-0.02058597350716918</v>
       </c>
       <c r="DF2" t="n">
+        <v>2.528733766233785</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.1612342903568447</v>
+      </c>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="n">
         <v>3.810146103896088</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.02058597350716918</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>24911.45645965084</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>21252408.00865801</v>
       </c>
     </row>
     <row r="3">
@@ -1601,55 +1601,55 @@
       <c r="CM3" t="n">
         <v>-1.614359763043964</v>
       </c>
-      <c r="CN3" t="n">
-        <v>-0.1418650793650755</v>
-      </c>
+      <c r="CN3" t="inlineStr"/>
       <c r="CO3" t="n">
-        <v>-1.179910389195552</v>
+        <v>-598123.9104842497</v>
       </c>
       <c r="CP3" t="n">
-        <v>-1.393934388946974</v>
+        <v>-2.029052104294664</v>
       </c>
       <c r="CQ3" t="inlineStr"/>
       <c r="CR3" t="n">
+        <v>-0.7373804665406851</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>-0.1418650793650755</v>
+      </c>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="n">
+        <v>-222.7970524334141</v>
+      </c>
+      <c r="CX3" t="n">
         <v>-0.01785714285714279</v>
       </c>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="n">
+      <c r="CY3" t="n">
         <v>0.04563492063492447</v>
       </c>
-      <c r="CV3" t="n">
-        <v>-598123.9104842497</v>
-      </c>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="n">
-        <v>-0.7373804665406851</v>
-      </c>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="n">
-        <v>-2.029052104294664</v>
-      </c>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="n">
+        <v>1300793.65079365</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>-1.179910389195552</v>
+      </c>
       <c r="DC3" t="n">
-        <v>-0.5291005291005604</v>
+        <v>-713.9550264550271</v>
       </c>
       <c r="DD3" t="inlineStr"/>
       <c r="DE3" t="n">
-        <v>-713.9550264550271</v>
+        <v>-0.006493506493506329</v>
       </c>
       <c r="DF3" t="n">
+        <v>-0.5291005291005604</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>-1.393934388946974</v>
+      </c>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="n">
         <v>0.7734788359788354</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>-0.006493506493506329</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>-222.7970524334141</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>1300793.65079365</v>
       </c>
     </row>
     <row r="4">
@@ -1924,55 +1924,55 @@
       <c r="CM4" t="n">
         <v>-1.060660964279393</v>
       </c>
-      <c r="CN4" t="n">
-        <v>-0.254761904761903</v>
-      </c>
+      <c r="CN4" t="inlineStr"/>
       <c r="CO4" t="n">
-        <v>2.571573078256794</v>
+        <v>-4547436.034736576</v>
       </c>
       <c r="CP4" t="n">
-        <v>-1.748192875964634</v>
+        <v>-2.73735515359202</v>
       </c>
       <c r="CQ4" t="inlineStr"/>
       <c r="CR4" t="n">
+        <v>-4.07335393064136</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>-0.254761904761903</v>
+      </c>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="n">
+        <v>-20843.6084416048</v>
+      </c>
+      <c r="CX4" t="n">
         <v>-0.4387445887445887</v>
       </c>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="n">
+      <c r="CY4" t="n">
         <v>-4.023755411255394</v>
       </c>
-      <c r="CV4" t="n">
-        <v>-4547436.034736576</v>
-      </c>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="n">
-        <v>-4.07335393064136</v>
-      </c>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="n">
-        <v>-2.73735515359202</v>
-      </c>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="n">
+        <v>-6428241.341991343</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>2.571573078256794</v>
+      </c>
       <c r="DC4" t="n">
-        <v>-0.8023809523809575</v>
+        <v>-28980.46536796536</v>
       </c>
       <c r="DD4" t="inlineStr"/>
       <c r="DE4" t="n">
-        <v>-28980.46536796536</v>
+        <v>-0.1641739937081554</v>
       </c>
       <c r="DF4" t="n">
+        <v>-0.8023809523809575</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>-1.748192875964634</v>
+      </c>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="n">
         <v>-3.435191197691196</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>-0.1641739937081554</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>-20843.6084416048</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>-6428241.341991343</v>
       </c>
     </row>
     <row r="5">
@@ -2251,55 +2251,55 @@
       <c r="CM5" t="n">
         <v>0.2806727562708318</v>
       </c>
-      <c r="CN5" t="n">
-        <v>-0.5130952380952394</v>
-      </c>
+      <c r="CN5" t="inlineStr"/>
       <c r="CO5" t="n">
-        <v>-0.5856555527215903</v>
+        <v>-7653799.362287303</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.318417394417736</v>
+        <v>-1.1394521600226</v>
       </c>
       <c r="CQ5" t="inlineStr"/>
       <c r="CR5" t="n">
+        <v>-0.9870964519117393</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.5130952380952394</v>
+      </c>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="n">
+        <v>5213.506558640584</v>
+      </c>
+      <c r="CX5" t="n">
         <v>-0.8134920634920637</v>
       </c>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="n">
+      <c r="CY5" t="n">
         <v>-2.176587301587318</v>
       </c>
-      <c r="CV5" t="n">
-        <v>-7653799.362287303</v>
-      </c>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="n">
-        <v>-0.9870964519117393</v>
-      </c>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="n">
-        <v>-1.1394521600226</v>
-      </c>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="n">
+        <v>-8239603.174603174</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0.5856555527215903</v>
+      </c>
       <c r="DC5" t="n">
-        <v>1.580952380952368</v>
+        <v>-321.8253968253921</v>
       </c>
       <c r="DD5" t="inlineStr"/>
       <c r="DE5" t="n">
-        <v>-321.8253968253921</v>
+        <v>-0.438442059919667</v>
       </c>
       <c r="DF5" t="n">
+        <v>1.580952380952368</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>2.318417394417736</v>
+      </c>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="n">
         <v>-0.7190476190476147</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>-0.438442059919667</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>5213.506558640584</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-8239603.174603174</v>
       </c>
     </row>
     <row r="6">
@@ -2578,55 +2578,55 @@
       <c r="CM6" t="n">
         <v>0.06358320042531318</v>
       </c>
-      <c r="CN6" t="n">
-        <v>4.027272727272731</v>
-      </c>
+      <c r="CN6" t="inlineStr"/>
       <c r="CO6" t="n">
-        <v>1.890096497705194</v>
+        <v>9312123.492449582</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.476610346175562</v>
+        <v>2.683907034994007</v>
       </c>
       <c r="CQ6" t="inlineStr"/>
       <c r="CR6" t="n">
+        <v>0.735371512545413</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>4.027272727272731</v>
+      </c>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="n">
+        <v>10515.76756576756</v>
+      </c>
+      <c r="CX6" t="n">
         <v>1.20487012987013</v>
       </c>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="n">
+      <c r="CY6" t="n">
         <v>3.864610389610377</v>
       </c>
-      <c r="CV6" t="n">
-        <v>9312123.492449582</v>
-      </c>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="n">
-        <v>0.735371512545413</v>
-      </c>
-      <c r="CY6" t="inlineStr"/>
-      <c r="CZ6" t="n">
-        <v>2.683907034994007</v>
-      </c>
-      <c r="DA6" t="inlineStr"/>
-      <c r="DB6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="n">
+        <v>7738311.688311689</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>1.890096497705194</v>
+      </c>
       <c r="DC6" t="n">
-        <v>-2.843506493506453</v>
+        <v>10786.36363636363</v>
       </c>
       <c r="DD6" t="inlineStr"/>
       <c r="DE6" t="n">
-        <v>10786.36363636363</v>
+        <v>0.7185835903227207</v>
       </c>
       <c r="DF6" t="n">
+        <v>-2.843506493506453</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.476610346175562</v>
+      </c>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="n">
         <v>0.8298701298701303</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>0.7185835903227207</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>10515.76756576756</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>7738311.688311689</v>
       </c>
     </row>
     <row r="7">
@@ -2905,55 +2905,55 @@
       <c r="CM7" t="n">
         <v>5.621612718090006</v>
       </c>
-      <c r="CN7" t="n">
-        <v>-0.04705988455988575</v>
-      </c>
+      <c r="CN7" t="inlineStr"/>
       <c r="CO7" t="n">
-        <v>1.294971310346483</v>
+        <v>4105364.686821525</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.6506639232126474</v>
+        <v>3.709093135919531</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
+        <v>2.297599003438847</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0.04705988455988575</v>
+      </c>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="n">
+        <v>19730.2704016736</v>
+      </c>
+      <c r="CX7" t="n">
         <v>0.1575757575757577</v>
       </c>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="n">
+      <c r="CY7" t="n">
         <v>1.959938672438668</v>
       </c>
-      <c r="CV7" t="n">
-        <v>4105364.686821525</v>
-      </c>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="n">
-        <v>2.297599003438847</v>
-      </c>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="n">
-        <v>3.709093135919531</v>
-      </c>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="n">
+        <v>2920128.066378065</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.294971310346483</v>
+      </c>
       <c r="DC7" t="n">
-        <v>0.2936327561327516</v>
+        <v>12942.27994227995</v>
       </c>
       <c r="DD7" t="inlineStr"/>
       <c r="DE7" t="n">
-        <v>12942.27994227995</v>
+        <v>0.2805710520634299</v>
       </c>
       <c r="DF7" t="n">
+        <v>0.2936327561327516</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-0.6506639232126474</v>
+      </c>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="n">
         <v>2.019931457431483</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0.2805710520634299</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>19730.2704016736</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>2920128.066378065</v>
       </c>
     </row>
     <row r="8">
@@ -3220,55 +3220,55 @@
       <c r="CM8" t="n">
         <v>-0.2998436748436717</v>
       </c>
-      <c r="CN8" t="n">
-        <v>-0.1668831168831133</v>
-      </c>
+      <c r="CN8" t="inlineStr"/>
       <c r="CO8" t="n">
-        <v>1.044096385676969</v>
+        <v>8067503.675758337</v>
       </c>
       <c r="CP8" t="n">
-        <v>-1.66740581664169</v>
+        <v>6.602293149382078</v>
       </c>
       <c r="CQ8" t="inlineStr"/>
       <c r="CR8" t="n">
+        <v>6.076603140330661</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0.1668831168831133</v>
+      </c>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="n">
+        <v>9377.121888378835</v>
+      </c>
+      <c r="CX8" t="n">
         <v>0.8738636363636363</v>
       </c>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="n">
+      <c r="CY8" t="n">
         <v>6.33051948051947</v>
       </c>
-      <c r="CV8" t="n">
-        <v>8067503.675758337</v>
-      </c>
-      <c r="CW8" t="inlineStr"/>
-      <c r="CX8" t="n">
-        <v>6.076603140330661</v>
-      </c>
-      <c r="CY8" t="inlineStr"/>
-      <c r="CZ8" t="n">
-        <v>6.602293149382078</v>
-      </c>
-      <c r="DA8" t="inlineStr"/>
-      <c r="DB8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="n">
+        <v>17686404.22077922</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.044096385676969</v>
+      </c>
       <c r="DC8" t="n">
-        <v>-2.550324675324646</v>
+        <v>17724.83766233766</v>
       </c>
       <c r="DD8" t="inlineStr"/>
       <c r="DE8" t="n">
-        <v>17724.83766233766</v>
+        <v>0.4641658738389698</v>
       </c>
       <c r="DF8" t="n">
+        <v>-2.550324675324646</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-1.66740581664169</v>
+      </c>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="n">
         <v>6.009415584415578</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>0.4641658738389698</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>9377.121888378835</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>17686404.22077922</v>
       </c>
     </row>
     <row r="9">
@@ -3547,55 +3547,55 @@
       <c r="CM9" t="n">
         <v>-6.443075196408529</v>
       </c>
-      <c r="CN9" t="n">
-        <v>-1.201984126984129</v>
-      </c>
+      <c r="CN9" t="inlineStr"/>
       <c r="CO9" t="n">
-        <v>-0.475410217801528</v>
+        <v>38302.91673905822</v>
       </c>
       <c r="CP9" t="n">
-        <v>-1.389371009425361</v>
+        <v>-0.153864462831848</v>
       </c>
       <c r="CQ9" t="inlineStr"/>
       <c r="CR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS9" t="inlineStr"/>
+        <v>0.6141789008093212</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-1.201984126984129</v>
+      </c>
       <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="n">
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="n">
+        <v>259.8871569252042</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
         <v>2.622186147186142</v>
       </c>
-      <c r="CV9" t="n">
-        <v>38302.91673905822</v>
-      </c>
-      <c r="CW9" t="inlineStr"/>
-      <c r="CX9" t="n">
-        <v>0.6141789008093212</v>
-      </c>
-      <c r="CY9" t="inlineStr"/>
-      <c r="CZ9" t="n">
-        <v>-0.153864462831848</v>
-      </c>
-      <c r="DA9" t="inlineStr"/>
-      <c r="DB9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="n">
+        <v>2556709.956709957</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0.475410217801528</v>
+      </c>
       <c r="DC9" t="n">
-        <v>-0.301370851370848</v>
+        <v>4335.028860028862</v>
       </c>
       <c r="DD9" t="inlineStr"/>
       <c r="DE9" t="n">
-        <v>4335.028860028862</v>
+        <v>-0.04624662776836708</v>
       </c>
       <c r="DF9" t="n">
+        <v>-0.301370851370848</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-1.389371009425361</v>
+      </c>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="n">
         <v>3.680952380952391</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>-0.04624662776836708</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>259.8871569252042</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>2556709.956709957</v>
       </c>
     </row>
     <row r="10">
@@ -3874,55 +3874,55 @@
       <c r="CM10" t="n">
         <v>-0.4446969696969774</v>
       </c>
-      <c r="CN10" t="n">
-        <v>0.970670995671</v>
-      </c>
+      <c r="CN10" t="inlineStr"/>
       <c r="CO10" t="n">
-        <v>-0.8252917176642747</v>
+        <v>7759156.666905239</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.811113771438158</v>
+        <v>1.241718653291073</v>
       </c>
       <c r="CQ10" t="inlineStr"/>
       <c r="CR10" t="n">
+        <v>2.670089550598362</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.970670995671</v>
+      </c>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="n">
+        <v>28199.3944313522</v>
+      </c>
+      <c r="CX10" t="n">
         <v>0.6639610389610389</v>
       </c>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="n">
+      <c r="CY10" t="n">
         <v>4.999278499278503</v>
       </c>
-      <c r="CV10" t="n">
-        <v>7759156.666905239</v>
-      </c>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="n">
-        <v>2.670089550598362</v>
-      </c>
-      <c r="CY10" t="inlineStr"/>
-      <c r="CZ10" t="n">
-        <v>1.241718653291073</v>
-      </c>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="n">
+        <v>12971222.94372294</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0.8252917176642747</v>
+      </c>
       <c r="DC10" t="n">
-        <v>2.918975468975418</v>
+        <v>41497.65512265512</v>
       </c>
       <c r="DD10" t="inlineStr"/>
       <c r="DE10" t="n">
-        <v>41497.65512265512</v>
+        <v>0.465863364436524</v>
       </c>
       <c r="DF10" t="n">
+        <v>2.918975468975418</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>1.811113771438158</v>
+      </c>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="n">
         <v>4.398412698412699</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>0.465863364436524</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>28199.3944313522</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>12971222.94372294</v>
       </c>
     </row>
     <row r="11">
@@ -4205,55 +4205,55 @@
       <c r="CM11" t="n">
         <v>-0.3022908826830388</v>
       </c>
-      <c r="CN11" t="n">
-        <v>0.5267316017316048</v>
-      </c>
+      <c r="CN11" t="inlineStr"/>
       <c r="CO11" t="n">
-        <v>0.2578768844754435</v>
+        <v>-21191934.09657793</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.297571410283098</v>
+        <v>-4.586073625078214</v>
       </c>
       <c r="CQ11" t="inlineStr"/>
       <c r="CR11" t="n">
+        <v>-4.594511364194275</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.5267316017316048</v>
+      </c>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="n">
+        <v>-71440.85529214167</v>
+      </c>
+      <c r="CX11" t="n">
         <v>-1.284307359307359</v>
       </c>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="n">
+      <c r="CY11" t="n">
         <v>-6.05735930735932</v>
       </c>
-      <c r="CV11" t="n">
-        <v>-21191934.09657793</v>
-      </c>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="n">
-        <v>-4.594511364194275</v>
-      </c>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="n">
-        <v>-4.586073625078214</v>
-      </c>
-      <c r="DA11" t="inlineStr"/>
-      <c r="DB11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="n">
+        <v>-34642803.03030303</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.2578768844754435</v>
+      </c>
       <c r="DC11" t="n">
-        <v>0.5702380952380963</v>
+        <v>-93494.91341991341</v>
       </c>
       <c r="DD11" t="inlineStr"/>
       <c r="DE11" t="n">
-        <v>-93494.91341991341</v>
+        <v>-0.5587081965653393</v>
       </c>
       <c r="DF11" t="n">
+        <v>0.5702380952380963</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.297571410283098</v>
+      </c>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="n">
         <v>-5.858477633477619</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>-0.5587081965653393</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>-71440.85529214167</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>-34642803.03030303</v>
       </c>
     </row>
     <row r="12">
@@ -4536,55 +4536,55 @@
       <c r="CM12" t="n">
         <v>-2.126608791261887</v>
       </c>
-      <c r="CN12" t="n">
-        <v>2.218339646464646</v>
-      </c>
+      <c r="CN12" t="inlineStr"/>
       <c r="CO12" t="n">
-        <v>2.816356482784503</v>
+        <v>12301122.87493745</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.2480131227131892</v>
+        <v>8.035446082340428</v>
       </c>
       <c r="CQ12" t="inlineStr"/>
       <c r="CR12" t="n">
+        <v>4.050200632485854</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.218339646464646</v>
+      </c>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="n">
+        <v>75599.59081918253</v>
+      </c>
+      <c r="CX12" t="n">
         <v>0.9676136363636363</v>
       </c>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="n">
+      <c r="CY12" t="n">
         <v>6.539236111111109</v>
       </c>
-      <c r="CV12" t="n">
-        <v>12301122.87493745</v>
-      </c>
-      <c r="CW12" t="inlineStr"/>
-      <c r="CX12" t="n">
-        <v>4.050200632485854</v>
-      </c>
-      <c r="CY12" t="inlineStr"/>
-      <c r="CZ12" t="n">
-        <v>8.035446082340428</v>
-      </c>
-      <c r="DA12" t="inlineStr"/>
-      <c r="DB12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="n">
+        <v>17842361.11111111</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>2.816356482784503</v>
+      </c>
       <c r="DC12" t="n">
-        <v>-0.4140993265993416</v>
+        <v>90125.93644781144</v>
       </c>
       <c r="DD12" t="inlineStr"/>
       <c r="DE12" t="n">
-        <v>90125.93644781144</v>
+        <v>0.7640309343434344</v>
       </c>
       <c r="DF12" t="n">
+        <v>-0.4140993265993416</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.2480131227131892</v>
+      </c>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="n">
         <v>3.393034511784521</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>0.7640309343434344</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>75599.59081918253</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>17842361.11111111</v>
       </c>
     </row>
     <row r="13">
@@ -4863,55 +4863,55 @@
       <c r="CM13" t="n">
         <v>5.358535353535359</v>
       </c>
-      <c r="CN13" t="n">
-        <v>-1.43472222222222</v>
-      </c>
+      <c r="CN13" t="inlineStr"/>
       <c r="CO13" t="n">
-        <v>-3.46343208464036</v>
+        <v>873005.5327917216</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.708352862315991</v>
+        <v>-2.387432921993422</v>
       </c>
       <c r="CQ13" t="inlineStr"/>
       <c r="CR13" t="n">
+        <v>2.016628701455758</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-1.43472222222222</v>
+      </c>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="n">
+        <v>6268.103092999849</v>
+      </c>
+      <c r="CX13" t="n">
         <v>-0.2423611111111106</v>
       </c>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="n">
+      <c r="CY13" t="n">
         <v>0.9451388888888772</v>
       </c>
-      <c r="CV13" t="n">
-        <v>873005.5327917216</v>
-      </c>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="n">
-        <v>2.016628701455758</v>
-      </c>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="n">
-        <v>-2.387432921993422</v>
-      </c>
-      <c r="DA13" t="inlineStr"/>
-      <c r="DB13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="n">
+        <v>4776527.777777778</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-3.46343208464036</v>
+      </c>
       <c r="DC13" t="n">
-        <v>4.608680555555566</v>
+        <v>15386.80555555555</v>
       </c>
       <c r="DD13" t="inlineStr"/>
       <c r="DE13" t="n">
-        <v>15386.80555555555</v>
+        <v>-0.1929076373632461</v>
       </c>
       <c r="DF13" t="n">
+        <v>4.608680555555566</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>2.708352862315991</v>
+      </c>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="n">
         <v>1.87395833333332</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>-0.1929076373632461</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>6268.103092999849</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>4776527.777777778</v>
       </c>
     </row>
     <row r="14">
@@ -5194,55 +5194,55 @@
       <c r="CM14" t="n">
         <v>0.8992446393762208</v>
       </c>
-      <c r="CN14" t="n">
-        <v>0.06398358585858688</v>
-      </c>
+      <c r="CN14" t="inlineStr"/>
       <c r="CO14" t="n">
-        <v>-0.6618646209192072</v>
+        <v>-293018.6531267995</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.077299308878253</v>
+        <v>-0.2765763700870565</v>
       </c>
       <c r="CQ14" t="inlineStr"/>
       <c r="CR14" t="n">
+        <v>-0.3857164689542287</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.06398358585858688</v>
+      </c>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="n">
+        <v>-4021.427604685639</v>
+      </c>
+      <c r="CX14" t="n">
         <v>-0.06818181818181834</v>
       </c>
-      <c r="CS14" t="inlineStr"/>
-      <c r="CT14" t="inlineStr"/>
-      <c r="CU14" t="n">
+      <c r="CY14" t="n">
         <v>-0.2403093434343333</v>
       </c>
-      <c r="CV14" t="n">
-        <v>-293018.6531267995</v>
-      </c>
-      <c r="CW14" t="inlineStr"/>
-      <c r="CX14" t="n">
-        <v>-0.3857164689542287</v>
-      </c>
-      <c r="CY14" t="inlineStr"/>
-      <c r="CZ14" t="n">
-        <v>-0.2765763700870565</v>
-      </c>
-      <c r="DA14" t="inlineStr"/>
-      <c r="DB14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="n">
+        <v>-614803.5037878794</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0.6618646209192072</v>
+      </c>
       <c r="DC14" t="n">
-        <v>0.6644570707071011</v>
+        <v>-2601.167929292933</v>
       </c>
       <c r="DD14" t="inlineStr"/>
       <c r="DE14" t="n">
-        <v>-2601.167929292933</v>
+        <v>-0.02056277056277045</v>
       </c>
       <c r="DF14" t="n">
+        <v>0.6644570707071011</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>1.077299308878253</v>
+      </c>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="n">
         <v>-0.3349431818181898</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>-0.02056277056277045</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>-4021.427604685639</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>-614803.5037878794</v>
       </c>
     </row>
     <row r="15">
@@ -5521,55 +5521,55 @@
       <c r="CM15" t="n">
         <v>0.09353980986332999</v>
       </c>
-      <c r="CN15" t="n">
-        <v>-0.4573773448773473</v>
-      </c>
+      <c r="CN15" t="inlineStr"/>
       <c r="CO15" t="n">
-        <v>-1.340424652906719</v>
+        <v>-2703621.06746823</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.9339432914054271</v>
+        <v>-1.370386874689558</v>
       </c>
       <c r="CQ15" t="inlineStr"/>
       <c r="CR15" t="n">
+        <v>-0.7202732308858657</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0.4573773448773473</v>
+      </c>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="n">
+        <v>-22829.41672409551</v>
+      </c>
+      <c r="CX15" t="n">
         <v>-0.1942640692640694</v>
       </c>
-      <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="inlineStr"/>
-      <c r="CU15" t="n">
+      <c r="CY15" t="n">
         <v>0.4888347763347696</v>
       </c>
-      <c r="CV15" t="n">
-        <v>-2703621.06746823</v>
-      </c>
-      <c r="CW15" t="inlineStr"/>
-      <c r="CX15" t="n">
-        <v>-0.7202732308858657</v>
-      </c>
-      <c r="CY15" t="inlineStr"/>
-      <c r="CZ15" t="n">
-        <v>-1.370386874689558</v>
-      </c>
-      <c r="DA15" t="inlineStr"/>
-      <c r="DB15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="n">
+        <v>-898331.5295815291</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>-1.340424652906719</v>
+      </c>
       <c r="DC15" t="n">
-        <v>-0.07624458874454376</v>
+        <v>-10625.64935064935</v>
       </c>
       <c r="DD15" t="inlineStr"/>
       <c r="DE15" t="n">
-        <v>-10625.64935064935</v>
+        <v>-0.2815963425624048</v>
       </c>
       <c r="DF15" t="n">
+        <v>-0.07624458874454376</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.9339432914054271</v>
+      </c>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="n">
         <v>0.1725649350649121</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>-0.2815963425624048</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>-22829.41672409551</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>-898331.5295815291</v>
       </c>
     </row>
     <row r="16">
@@ -5848,55 +5848,55 @@
       <c r="CM16" t="n">
         <v>-0.5229871817591061</v>
       </c>
-      <c r="CN16" t="n">
-        <v>-2.817352092352095</v>
-      </c>
+      <c r="CN16" t="inlineStr"/>
       <c r="CO16" t="n">
-        <v>-2.636496860083</v>
+        <v>-7816603.428762227</v>
       </c>
       <c r="CP16" t="n">
-        <v>-4.957350345524588</v>
+        <v>-3.67042202376463</v>
       </c>
       <c r="CQ16" t="inlineStr"/>
       <c r="CR16" t="n">
+        <v>-0.7512344925061427</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-2.817352092352095</v>
+      </c>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="n">
+        <v>-51910.14853984778</v>
+      </c>
+      <c r="CX16" t="n">
         <v>-0.9925685425685429</v>
       </c>
-      <c r="CS16" t="inlineStr"/>
-      <c r="CT16" t="inlineStr"/>
-      <c r="CU16" t="n">
+      <c r="CY16" t="n">
         <v>-5.862229437229416</v>
       </c>
-      <c r="CV16" t="n">
-        <v>-7816603.428762227</v>
-      </c>
-      <c r="CW16" t="inlineStr"/>
-      <c r="CX16" t="n">
-        <v>-0.7512344925061427</v>
-      </c>
-      <c r="CY16" t="inlineStr"/>
-      <c r="CZ16" t="n">
-        <v>-3.67042202376463</v>
-      </c>
-      <c r="DA16" t="inlineStr"/>
-      <c r="DB16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="n">
+        <v>-21176803.75180375</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>-2.636496860083</v>
+      </c>
       <c r="DC16" t="n">
-        <v>-0.8128427128427234</v>
+        <v>-72366.91919191918</v>
       </c>
       <c r="DD16" t="inlineStr"/>
       <c r="DE16" t="n">
-        <v>-72366.91919191918</v>
+        <v>-0.5658500248072</v>
       </c>
       <c r="DF16" t="n">
+        <v>-0.8128427128427234</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>-4.957350345524588</v>
+      </c>
+      <c r="DH16" t="inlineStr"/>
+      <c r="DI16" t="n">
         <v>-4.113997113997115</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>-0.5658500248072</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>-51910.14853984778</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>-21176803.75180375</v>
       </c>
     </row>
     <row r="17">
@@ -6175,55 +6175,55 @@
       <c r="CM17" t="n">
         <v>-1.110107339054721</v>
       </c>
-      <c r="CN17" t="n">
-        <v>-0.9334595959595973</v>
-      </c>
+      <c r="CN17" t="inlineStr"/>
       <c r="CO17" t="n">
-        <v>2.041007650848847</v>
+        <v>-2977165.143915372</v>
       </c>
       <c r="CP17" t="n">
-        <v>-1.918504521794034</v>
+        <v>0.1557025400491767</v>
       </c>
       <c r="CQ17" t="inlineStr"/>
       <c r="CR17" t="n">
+        <v>-1.55781881004657</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>-0.9334595959595973</v>
+      </c>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="n">
+        <v>-11711.26692197699</v>
+      </c>
+      <c r="CX17" t="n">
         <v>-0.133901515151515</v>
       </c>
-      <c r="CS17" t="inlineStr"/>
-      <c r="CT17" t="inlineStr"/>
-      <c r="CU17" t="n">
+      <c r="CY17" t="n">
         <v>-2.83137626262625</v>
       </c>
-      <c r="CV17" t="n">
-        <v>-2977165.143915372</v>
-      </c>
-      <c r="CW17" t="inlineStr"/>
-      <c r="CX17" t="n">
-        <v>-1.55781881004657</v>
-      </c>
-      <c r="CY17" t="inlineStr"/>
-      <c r="CZ17" t="n">
-        <v>0.1557025400491767</v>
-      </c>
-      <c r="DA17" t="inlineStr"/>
-      <c r="DB17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="n">
+        <v>-6043080.808080807</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>2.041007650848847</v>
+      </c>
       <c r="DC17" t="n">
-        <v>-0.7354482323232219</v>
+        <v>-20879.10353535353</v>
       </c>
       <c r="DD17" t="inlineStr"/>
       <c r="DE17" t="n">
-        <v>-20879.10353535353</v>
+        <v>-0.0527056277056277</v>
       </c>
       <c r="DF17" t="n">
+        <v>-0.7354482323232219</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-1.918504521794034</v>
+      </c>
+      <c r="DH17" t="inlineStr"/>
+      <c r="DI17" t="n">
         <v>-2.286205808080794</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>-0.0527056277056277</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>-11711.26692197699</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>-6043080.808080807</v>
       </c>
     </row>
     <row r="18">
@@ -6502,55 +6502,55 @@
       <c r="CM18" t="n">
         <v>-8.541791526374865</v>
       </c>
-      <c r="CN18" t="n">
-        <v>-0.466233766233767</v>
-      </c>
+      <c r="CN18" t="inlineStr"/>
       <c r="CO18" t="n">
-        <v>0.870745060224511</v>
+        <v>-9160900.286258535</v>
       </c>
       <c r="CP18" t="n">
-        <v>-2.094393139630938</v>
+        <v>-3.580424914521046</v>
       </c>
       <c r="CQ18" t="inlineStr"/>
       <c r="CR18" t="n">
+        <v>-4.247415323151344</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0.466233766233767</v>
+      </c>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="n">
+        <v>-25100.2481089303</v>
+      </c>
+      <c r="CX18" t="n">
         <v>-0.6272727272727272</v>
       </c>
-      <c r="CS18" t="inlineStr"/>
-      <c r="CT18" t="inlineStr"/>
-      <c r="CU18" t="n">
+      <c r="CY18" t="n">
         <v>-7.44805194805194</v>
       </c>
-      <c r="CV18" t="n">
-        <v>-9160900.286258535</v>
-      </c>
-      <c r="CW18" t="inlineStr"/>
-      <c r="CX18" t="n">
-        <v>-4.247415323151344</v>
-      </c>
-      <c r="CY18" t="inlineStr"/>
-      <c r="CZ18" t="n">
-        <v>-3.580424914521046</v>
-      </c>
-      <c r="DA18" t="inlineStr"/>
-      <c r="DB18" t="inlineStr"/>
+      <c r="CZ18" t="inlineStr"/>
+      <c r="DA18" t="n">
+        <v>-14993019.48051948</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0.870745060224511</v>
+      </c>
       <c r="DC18" t="n">
-        <v>-3.136363636363626</v>
+        <v>-43814.28571428572</v>
       </c>
       <c r="DD18" t="inlineStr"/>
       <c r="DE18" t="n">
-        <v>-43814.28571428572</v>
+        <v>-0.4648380739375491</v>
       </c>
       <c r="DF18" t="n">
+        <v>-3.136363636363626</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>-2.094393139630938</v>
+      </c>
+      <c r="DH18" t="inlineStr"/>
+      <c r="DI18" t="n">
         <v>-6.590909090909093</v>
-      </c>
-      <c r="DG18" t="n">
-        <v>-0.4648380739375491</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>-25100.2481089303</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>-14993019.48051948</v>
       </c>
     </row>
     <row r="19">
@@ -6829,55 +6829,55 @@
       <c r="CM19" t="n">
         <v>-2.108394471026045</v>
       </c>
-      <c r="CN19" t="n">
-        <v>-0.4898809523809504</v>
-      </c>
+      <c r="CN19" t="inlineStr"/>
       <c r="CO19" t="n">
-        <v>-0.2167320251165634</v>
+        <v>-8114064.772675888</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.3219596445557613</v>
+        <v>-6.4997454378762</v>
       </c>
       <c r="CQ19" t="inlineStr"/>
       <c r="CR19" t="n">
+        <v>-5.444053069300253</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>-0.4898809523809504</v>
+      </c>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="n">
+        <v>-30861.55776377176</v>
+      </c>
+      <c r="CX19" t="n">
         <v>-0.5238095238095237</v>
       </c>
-      <c r="CS19" t="inlineStr"/>
-      <c r="CT19" t="inlineStr"/>
-      <c r="CU19" t="n">
+      <c r="CY19" t="n">
         <v>-3.136904761904759</v>
       </c>
-      <c r="CV19" t="n">
-        <v>-8114064.772675888</v>
-      </c>
-      <c r="CW19" t="inlineStr"/>
-      <c r="CX19" t="n">
-        <v>-5.444053069300253</v>
-      </c>
-      <c r="CY19" t="inlineStr"/>
-      <c r="CZ19" t="n">
-        <v>-6.4997454378762</v>
-      </c>
-      <c r="DA19" t="inlineStr"/>
-      <c r="DB19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="n">
+        <v>-6520515.873015875</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>-0.2167320251165634</v>
+      </c>
       <c r="DC19" t="n">
-        <v>-0.1616402116402185</v>
+        <v>-27939.74867724868</v>
       </c>
       <c r="DD19" t="inlineStr"/>
       <c r="DE19" t="n">
-        <v>-27939.74867724868</v>
+        <v>-0.3824733237776716</v>
       </c>
       <c r="DF19" t="n">
+        <v>-0.1616402116402185</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0.3219596445557613</v>
+      </c>
+      <c r="DH19" t="inlineStr"/>
+      <c r="DI19" t="n">
         <v>-2.50747354497355</v>
-      </c>
-      <c r="DG19" t="n">
-        <v>-0.3824733237776716</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>-30861.55776377176</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>-6520515.873015875</v>
       </c>
     </row>
     <row r="20">
@@ -7156,55 +7156,55 @@
       <c r="CM20" t="n">
         <v>-1.366230936819164</v>
       </c>
-      <c r="CN20" t="n">
-        <v>-2.739569805194805</v>
-      </c>
+      <c r="CN20" t="inlineStr"/>
       <c r="CO20" t="n">
-        <v>-2.884901595988552</v>
+        <v>-12282770.03208898</v>
       </c>
       <c r="CP20" t="n">
-        <v>1.174396359980591</v>
+        <v>-7.680538710987079</v>
       </c>
       <c r="CQ20" t="inlineStr"/>
       <c r="CR20" t="n">
+        <v>-4.492033887006713</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>-2.739569805194805</v>
+      </c>
+      <c r="CT20" t="inlineStr"/>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="inlineStr"/>
+      <c r="CW20" t="n">
+        <v>-63940.42430244875</v>
+      </c>
+      <c r="CX20" t="n">
         <v>-0.9676136363636363</v>
       </c>
-      <c r="CS20" t="inlineStr"/>
-      <c r="CT20" t="inlineStr"/>
-      <c r="CU20" t="n">
+      <c r="CY20" t="n">
         <v>-9.433644480519476</v>
       </c>
-      <c r="CV20" t="n">
-        <v>-12282770.03208898</v>
-      </c>
-      <c r="CW20" t="inlineStr"/>
-      <c r="CX20" t="n">
-        <v>-4.492033887006713</v>
-      </c>
-      <c r="CY20" t="inlineStr"/>
-      <c r="CZ20" t="n">
-        <v>-7.680538710987079</v>
-      </c>
-      <c r="DA20" t="inlineStr"/>
-      <c r="DB20" t="inlineStr"/>
+      <c r="CZ20" t="inlineStr"/>
+      <c r="DA20" t="n">
+        <v>-20920340.90909091</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>-2.884901595988552</v>
+      </c>
       <c r="DC20" t="n">
-        <v>2.184253246753286</v>
+        <v>-80349.39123376622</v>
       </c>
       <c r="DD20" t="inlineStr"/>
       <c r="DE20" t="n">
-        <v>-80349.39123376622</v>
+        <v>-0.7177843065750673</v>
       </c>
       <c r="DF20" t="n">
+        <v>2.184253246753286</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>1.174396359980591</v>
+      </c>
+      <c r="DH20" t="inlineStr"/>
+      <c r="DI20" t="n">
         <v>-6.482386363636365</v>
-      </c>
-      <c r="DG20" t="n">
-        <v>-0.7177843065750673</v>
-      </c>
-      <c r="DH20" t="n">
-        <v>-63940.42430244875</v>
-      </c>
-      <c r="DI20" t="n">
-        <v>-20920340.90909091</v>
       </c>
     </row>
     <row r="21">
@@ -7487,55 +7487,55 @@
       <c r="CM21" t="n">
         <v>-0.6470319220917276</v>
       </c>
-      <c r="CN21" t="n">
-        <v>-1.528571428571428</v>
-      </c>
+      <c r="CN21" t="inlineStr"/>
       <c r="CO21" t="n">
-        <v>-0.8505686560966055</v>
+        <v>6271826.119446456</v>
       </c>
       <c r="CP21" t="n">
-        <v>1.31402821471147</v>
+        <v>1.655852506131993</v>
       </c>
       <c r="CQ21" t="inlineStr"/>
       <c r="CR21" t="n">
+        <v>1.574473662982982</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>-1.528571428571428</v>
+      </c>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr"/>
+      <c r="CW21" t="n">
+        <v>38429.55771856393</v>
+      </c>
+      <c r="CX21" t="n">
         <v>0.125</v>
       </c>
-      <c r="CS21" t="inlineStr"/>
-      <c r="CT21" t="inlineStr"/>
-      <c r="CU21" t="n">
+      <c r="CY21" t="n">
         <v>0.9535714285714505</v>
       </c>
-      <c r="CV21" t="n">
-        <v>6271826.119446456</v>
-      </c>
-      <c r="CW21" t="inlineStr"/>
-      <c r="CX21" t="n">
-        <v>1.574473662982982</v>
-      </c>
-      <c r="CY21" t="inlineStr"/>
-      <c r="CZ21" t="n">
-        <v>1.655852506131993</v>
-      </c>
-      <c r="DA21" t="inlineStr"/>
-      <c r="DB21" t="inlineStr"/>
+      <c r="CZ21" t="inlineStr"/>
+      <c r="DA21" t="n">
+        <v>12102857.14285714</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>-0.8505686560966055</v>
+      </c>
       <c r="DC21" t="n">
-        <v>3.607142857142833</v>
+        <v>52178.57142857143</v>
       </c>
       <c r="DD21" t="inlineStr"/>
       <c r="DE21" t="n">
-        <v>52178.57142857143</v>
+        <v>0.07081154640160814</v>
       </c>
       <c r="DF21" t="n">
+        <v>3.607142857142833</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>1.31402821471147</v>
+      </c>
+      <c r="DH21" t="inlineStr"/>
+      <c r="DI21" t="n">
         <v>2.142857142857139</v>
-      </c>
-      <c r="DG21" t="n">
-        <v>0.07081154640160814</v>
-      </c>
-      <c r="DH21" t="n">
-        <v>38429.55771856393</v>
-      </c>
-      <c r="DI21" t="n">
-        <v>12102857.14285714</v>
       </c>
     </row>
     <row r="22">
@@ -7818,55 +7818,55 @@
       <c r="CM22" t="n">
         <v>-1.623114478114459</v>
       </c>
-      <c r="CN22" t="n">
-        <v>-0.3359532828282887</v>
-      </c>
+      <c r="CN22" t="inlineStr"/>
       <c r="CO22" t="n">
-        <v>-2.16758534181303</v>
+        <v>26032388.78444131</v>
       </c>
       <c r="CP22" t="n">
-        <v>-1.626677843196717</v>
+        <v>7.60000514875729</v>
       </c>
       <c r="CQ22" t="inlineStr"/>
       <c r="CR22" t="n">
+        <v>9.053581763789865</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>-0.3359532828282887</v>
+      </c>
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="inlineStr"/>
+      <c r="CV22" t="inlineStr"/>
+      <c r="CW22" t="n">
+        <v>96305.89133843211</v>
+      </c>
+      <c r="CX22" t="n">
         <v>1.791233766233766</v>
       </c>
-      <c r="CS22" t="inlineStr"/>
-      <c r="CT22" t="inlineStr"/>
-      <c r="CU22" t="n">
+      <c r="CY22" t="n">
         <v>10.32142406204905</v>
       </c>
-      <c r="CV22" t="n">
-        <v>26032388.78444131</v>
-      </c>
-      <c r="CW22" t="inlineStr"/>
-      <c r="CX22" t="n">
-        <v>9.053581763789865</v>
-      </c>
-      <c r="CY22" t="inlineStr"/>
-      <c r="CZ22" t="n">
-        <v>7.60000514875729</v>
-      </c>
-      <c r="DA22" t="inlineStr"/>
-      <c r="DB22" t="inlineStr"/>
+      <c r="CZ22" t="inlineStr"/>
+      <c r="DA22" t="n">
+        <v>41685847.87608226</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>-2.16758534181303</v>
+      </c>
       <c r="DC22" t="n">
-        <v>-0.4323142135642399</v>
+        <v>125076.5467171717</v>
       </c>
       <c r="DD22" t="inlineStr"/>
       <c r="DE22" t="n">
-        <v>125076.5467171717</v>
+        <v>0.7434449608362652</v>
       </c>
       <c r="DF22" t="n">
+        <v>-0.4323142135642399</v>
+      </c>
+      <c r="DG22" t="n">
+        <v>-1.626677843196717</v>
+      </c>
+      <c r="DH22" t="inlineStr"/>
+      <c r="DI22" t="n">
         <v>9.628612012987006</v>
-      </c>
-      <c r="DG22" t="n">
-        <v>0.7434449608362652</v>
-      </c>
-      <c r="DH22" t="n">
-        <v>96305.89133843211</v>
-      </c>
-      <c r="DI22" t="n">
-        <v>41685847.87608226</v>
       </c>
     </row>
     <row r="23">
@@ -8149,55 +8149,55 @@
       <c r="CM23" t="n">
         <v>-0.7438799762329324</v>
       </c>
-      <c r="CN23" t="n">
-        <v>4.716269841269842</v>
-      </c>
+      <c r="CN23" t="inlineStr"/>
       <c r="CO23" t="n">
-        <v>4.483060860707926</v>
+        <v>1888194.994203214</v>
       </c>
       <c r="CP23" t="n">
-        <v>0.135739133598122</v>
+        <v>4.025294671228167</v>
       </c>
       <c r="CQ23" t="inlineStr"/>
       <c r="CR23" t="n">
+        <v>-0.6450984029975473</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>4.716269841269842</v>
+      </c>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
+      <c r="CV23" t="inlineStr"/>
+      <c r="CW23" t="n">
+        <v>1750.693700405063</v>
+      </c>
+      <c r="CX23" t="n">
         <v>0.444444444444444</v>
       </c>
-      <c r="CS23" t="inlineStr"/>
-      <c r="CT23" t="inlineStr"/>
-      <c r="CU23" t="n">
+      <c r="CY23" t="n">
         <v>1.313888888888897</v>
       </c>
-      <c r="CV23" t="n">
-        <v>1888194.994203214</v>
-      </c>
-      <c r="CW23" t="inlineStr"/>
-      <c r="CX23" t="n">
-        <v>-0.6450984029975473</v>
-      </c>
-      <c r="CY23" t="inlineStr"/>
-      <c r="CZ23" t="n">
-        <v>4.025294671228167</v>
-      </c>
-      <c r="DA23" t="inlineStr"/>
-      <c r="DB23" t="inlineStr"/>
+      <c r="CZ23" t="inlineStr"/>
+      <c r="DA23" t="n">
+        <v>-188452.3809523815</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>4.483060860707926</v>
+      </c>
       <c r="DC23" t="n">
-        <v>-3.459523809523859</v>
+        <v>-2530.555555555555</v>
       </c>
       <c r="DD23" t="inlineStr"/>
       <c r="DE23" t="n">
-        <v>-2530.555555555555</v>
+        <v>0.2661760356316443</v>
       </c>
       <c r="DF23" t="n">
+        <v>-3.459523809523859</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>0.135739133598122</v>
+      </c>
+      <c r="DH23" t="inlineStr"/>
+      <c r="DI23" t="n">
         <v>-2.26984126984128</v>
-      </c>
-      <c r="DG23" t="n">
-        <v>0.2661760356316443</v>
-      </c>
-      <c r="DH23" t="n">
-        <v>1750.693700405063</v>
-      </c>
-      <c r="DI23" t="n">
-        <v>-188452.3809523815</v>
       </c>
     </row>
     <row r="24">
@@ -8472,55 +8472,55 @@
       <c r="CM24" t="n">
         <v>-1.934733297891199</v>
       </c>
-      <c r="CN24" t="n">
-        <v>0.6088744588744568</v>
-      </c>
+      <c r="CN24" t="inlineStr"/>
       <c r="CO24" t="n">
-        <v>1.410152192981553</v>
+        <v>-4455112.901332623</v>
       </c>
       <c r="CP24" t="n">
-        <v>-0.513078261047383</v>
+        <v>-4.36439542024209</v>
       </c>
       <c r="CQ24" t="inlineStr"/>
       <c r="CR24" t="n">
+        <v>-5.263475367482386</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>0.6088744588744568</v>
+      </c>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="n">
+        <v>-9834.439414423065</v>
+      </c>
+      <c r="CX24" t="n">
         <v>-0.3807900432900433</v>
       </c>
-      <c r="CS24" t="inlineStr"/>
-      <c r="CT24" t="inlineStr"/>
-      <c r="CU24" t="n">
+      <c r="CY24" t="n">
         <v>-3.152164502164496</v>
       </c>
-      <c r="CV24" t="n">
-        <v>-4455112.901332623</v>
-      </c>
-      <c r="CW24" t="inlineStr"/>
-      <c r="CX24" t="n">
-        <v>-5.263475367482386</v>
-      </c>
-      <c r="CY24" t="inlineStr"/>
-      <c r="CZ24" t="n">
-        <v>-4.36439542024209</v>
-      </c>
-      <c r="DA24" t="inlineStr"/>
-      <c r="DB24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="n">
+        <v>-6042616.341991343</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>1.410152192981553</v>
+      </c>
       <c r="DC24" t="n">
-        <v>-1.5046536796537</v>
+        <v>-15130.46536796536</v>
       </c>
       <c r="DD24" t="inlineStr"/>
       <c r="DE24" t="n">
-        <v>-15130.46536796536</v>
+        <v>-0.05153236632968583</v>
       </c>
       <c r="DF24" t="n">
+        <v>-1.5046536796537</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>-0.513078261047383</v>
+      </c>
+      <c r="DH24" t="inlineStr"/>
+      <c r="DI24" t="n">
         <v>-2.986327561327556</v>
-      </c>
-      <c r="DG24" t="n">
-        <v>-0.05153236632968583</v>
-      </c>
-      <c r="DH24" t="n">
-        <v>-9834.439414423065</v>
-      </c>
-      <c r="DI24" t="n">
-        <v>-6042616.341991343</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -885,112 +885,112 @@
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rep_player_start</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
     </row>
@@ -1275,70 +1275,70 @@
         <v>0.379877157474553</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.5512987012986983</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.9061688311688312</v>
+        <v>30621.91558441558</v>
       </c>
       <c r="CP2" t="n">
         <v>-0.06453721039794402</v>
       </c>
       <c r="CQ2" t="n">
+        <v>0.5512987012986983</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>7823681.440340288</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-50.66666666666666</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>18318457.79220779</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.5705907911963812</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>-3.218506493506453</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>4.778327726567696</v>
+      </c>
+      <c r="CX2" t="n">
         <v>20179.01489850194</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0.5705907911963812</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>6.575487012987011</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>30621.91558441558</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>15337500</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>-3.218506493506453</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>-0.8333333333333335</v>
       </c>
       <c r="CY2" t="n">
         <v>7.190746753246728</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.778327726567696</v>
+        <v>6.575487012987011</v>
       </c>
       <c r="DA2" t="n">
+        <v>-51.33333333333334</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>15337500</v>
+      </c>
+      <c r="DC2" t="n">
         <v>47500</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.08333333333333348</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.08333333333333215</v>
       </c>
       <c r="DD2" t="n">
         <v>4.714539515243089</v>
       </c>
       <c r="DE2" t="n">
-        <v>-51.33333333333334</v>
+        <v>-0.08333333333333215</v>
       </c>
       <c r="DF2" t="n">
-        <v>18318457.79220779</v>
+        <v>0.9061688311688312</v>
       </c>
       <c r="DG2" t="n">
-        <v>-50.66666666666666</v>
+        <v>-4.5</v>
       </c>
       <c r="DH2" t="n">
         <v>-0.08433903312007374</v>
       </c>
       <c r="DI2" t="n">
-        <v>7823681.440340288</v>
+        <v>-0.08333333333333348</v>
       </c>
     </row>
     <row r="3">
@@ -1622,70 +1622,70 @@
         <v>-3.573409289408104</v>
       </c>
       <c r="CN3" t="n">
-        <v>-2.922619047619047</v>
+        <v>-0.5714285714285716</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.09204545454545476</v>
+        <v>-4918.885281385279</v>
       </c>
       <c r="CP3" t="n">
         <v>-1.444190524387892</v>
       </c>
       <c r="CQ3" t="n">
+        <v>-2.922619047619047</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>155628.0906593408</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>-39.71428571428572</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>1280696.248196248</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>-0.1255655090523513</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>-0.02254689754687433</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>0.3331438517622871</v>
+      </c>
+      <c r="CX3" t="n">
         <v>-7088.545862032704</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>-0.1255655090523513</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>2.14557823129249</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>2.533946608946621</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>-4918.885281385279</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>-2964285.714285715</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>-0.02254689754687433</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>-0.5714285714285716</v>
       </c>
       <c r="CY3" t="n">
         <v>0.004834054834049084</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.3331438517622871</v>
+        <v>2.533946608946621</v>
       </c>
       <c r="DA3" t="n">
+        <v>-37.85714285714289</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>-2964285.714285715</v>
+      </c>
+      <c r="DC3" t="n">
         <v>-62142.85714285714</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>-1.571428571428572</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>-1.087414965986387</v>
       </c>
       <c r="DD3" t="n">
         <v>1.41613993462677</v>
       </c>
       <c r="DE3" t="n">
-        <v>-37.85714285714289</v>
+        <v>-1.087414965986387</v>
       </c>
       <c r="DF3" t="n">
-        <v>1280696.248196248</v>
+        <v>-0.09204545454545476</v>
       </c>
       <c r="DG3" t="n">
-        <v>-39.71428571428572</v>
+        <v>2.14557823129249</v>
       </c>
       <c r="DH3" t="n">
         <v>-1.83128524983789</v>
       </c>
       <c r="DI3" t="n">
-        <v>155628.0906593408</v>
+        <v>-1.571428571428572</v>
       </c>
     </row>
     <row r="4">
@@ -1965,70 +1965,70 @@
         <v>4.71625036271098</v>
       </c>
       <c r="CN4" t="n">
-        <v>-3.061038961038964</v>
+        <v>3.952380952380953</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0.444444444444444</v>
+        <v>-2288.167388167389</v>
       </c>
       <c r="CP4" t="n">
         <v>-4.055040752796504</v>
       </c>
       <c r="CQ4" t="n">
+        <v>-3.061038961038964</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-1947517.82852469</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>299.7619047619048</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-2777005.772005772</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0.2282627411966105</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>3.11630591630589</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-4.066805666271776</v>
+      </c>
+      <c r="CX4" t="n">
         <v>-1412.549721799125</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>-0.2282627411966105</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>0.8547619047618866</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>-2.192063492063482</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>-2288.167388167389</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>13252380.95238095</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>3.11630591630589</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>3.952380952380953</v>
       </c>
       <c r="CY4" t="n">
         <v>-4.511976911976916</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-4.066805666271776</v>
+        <v>-2.192063492063482</v>
       </c>
       <c r="DA4" t="n">
+        <v>281.5</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>13252380.95238095</v>
+      </c>
+      <c r="DC4" t="n">
         <v>35357.14285714286</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>4.095238095238096</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>-4.5</v>
       </c>
       <c r="DD4" t="n">
         <v>-0.3220566882879581</v>
       </c>
       <c r="DE4" t="n">
-        <v>281.5</v>
+        <v>-4.5</v>
       </c>
       <c r="DF4" t="n">
-        <v>-2777005.772005772</v>
+        <v>-0.444444444444444</v>
       </c>
       <c r="DG4" t="n">
-        <v>299.7619047619048</v>
+        <v>0.8547619047618866</v>
       </c>
       <c r="DH4" t="n">
         <v>1.830600740296148</v>
       </c>
       <c r="DI4" t="n">
-        <v>-1947517.82852469</v>
+        <v>4.095238095238096</v>
       </c>
     </row>
     <row r="5">
@@ -2312,70 +2312,70 @@
         <v>3.968468511647075</v>
       </c>
       <c r="CN5" t="n">
-        <v>3.496103896103893</v>
+        <v>-0.4285714285714284</v>
       </c>
       <c r="CO5" t="n">
-        <v>2.301298701298701</v>
+        <v>102836.3636363636</v>
       </c>
       <c r="CP5" t="n">
         <v>2.195678351832324</v>
       </c>
       <c r="CQ5" t="n">
+        <v>3.496103896103893</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>24483742.92181067</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-19.42857142857142</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>39351753.24675325</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.401503340290526</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-1.090909090909065</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>11.4281764701101</v>
+      </c>
+      <c r="CX5" t="n">
         <v>74842.63022401303</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.401503340290526</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>0.7380952380952408</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>10.09350649350647</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>102836.3636363636</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>48610714.28571428</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>-1.090909090909065</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>-0.4285714285714284</v>
       </c>
       <c r="CY5" t="n">
         <v>13.74675324675326</v>
       </c>
       <c r="CZ5" t="n">
-        <v>11.4281764701101</v>
+        <v>10.09350649350647</v>
       </c>
       <c r="DA5" t="n">
+        <v>-11.57142857142856</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>48610714.28571428</v>
+      </c>
+      <c r="DC5" t="n">
         <v>142714.2857142857</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>0.5476190476190474</v>
       </c>
       <c r="DD5" t="n">
         <v>7.798778595092742</v>
       </c>
       <c r="DE5" t="n">
-        <v>-11.57142857142856</v>
+        <v>0.5476190476190474</v>
       </c>
       <c r="DF5" t="n">
-        <v>39351753.24675325</v>
+        <v>2.301298701298701</v>
       </c>
       <c r="DG5" t="n">
-        <v>-19.42857142857142</v>
+        <v>0.7380952380952408</v>
       </c>
       <c r="DH5" t="n">
         <v>2.023687407358523</v>
       </c>
       <c r="DI5" t="n">
-        <v>24483742.92181067</v>
+        <v>1.285714285714286</v>
       </c>
     </row>
     <row r="6">
@@ -2655,70 +2655,70 @@
         <v>0.3128493695458019</v>
       </c>
       <c r="CN6" t="n">
-        <v>-1.242063492063494</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="CO6" t="n">
-        <v>-1.390873015873016</v>
+        <v>-28682.53968253968</v>
       </c>
       <c r="CP6" t="n">
         <v>1.028810120539443</v>
       </c>
       <c r="CQ6" t="n">
+        <v>-1.242063492063494</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-14279850.7280105</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-17108531.74603175</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0.7336973385845569</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1.464285714285722</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-5.105656999641951</v>
+      </c>
+      <c r="CX6" t="n">
         <v>-23974.01241198234</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>-0.7336973385845569</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>4.898809523809547</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-3.946428571428569</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>-28682.53968253968</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>-22003571.42857143</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.464285714285722</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.785714285714286</v>
       </c>
       <c r="CY6" t="n">
         <v>-5.759920634920661</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-5.105656999641951</v>
+        <v>-3.946428571428569</v>
       </c>
       <c r="DA6" t="n">
+        <v>117.2142857142857</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-22003571.42857143</v>
+      </c>
+      <c r="DC6" t="n">
         <v>-79928.57142857142</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1.392857142857143</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-0.5845238095238088</v>
       </c>
       <c r="DD6" t="n">
         <v>-5.866678601265065</v>
       </c>
       <c r="DE6" t="n">
-        <v>117.2142857142857</v>
+        <v>-0.5845238095238088</v>
       </c>
       <c r="DF6" t="n">
-        <v>-17108531.74603175</v>
+        <v>-1.390873015873016</v>
       </c>
       <c r="DG6" t="n">
-        <v>125.5</v>
+        <v>4.898809523809547</v>
       </c>
       <c r="DH6" t="n">
         <v>4.689563193698547</v>
       </c>
       <c r="DI6" t="n">
-        <v>-14279850.7280105</v>
+        <v>1.392857142857143</v>
       </c>
     </row>
     <row r="7">
@@ -3002,70 +3002,70 @@
         <v>0.4838682596446517</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.306894841269841</v>
+        <v>1.071428571428572</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.3530753968253966</v>
+        <v>-1930.158730158735</v>
       </c>
       <c r="CP7" t="n">
         <v>-0.1121869444438097</v>
       </c>
       <c r="CQ7" t="n">
+        <v>1.306894841269841</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-6172195.028536489</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>90.04761904761905</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>-3184538.690476192</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0.3131593768550291</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>2.931498015873018</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-5.486668937469844</v>
+      </c>
+      <c r="CX7" t="n">
         <v>-12898.11723459607</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>-0.3131593768550291</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>0.4880952380952408</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>-2.608134920634924</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>-1930.158730158735</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>12695238.0952381</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>2.931498015873018</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>1.071428571428572</v>
       </c>
       <c r="CY7" t="n">
         <v>-1.289335317460328</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-5.486668937469844</v>
+        <v>-2.608134920634924</v>
       </c>
       <c r="DA7" t="n">
+        <v>69.47619047619047</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>12695238.0952381</v>
+      </c>
+      <c r="DC7" t="n">
         <v>17547.61904761904</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>1.023809523809524</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>-3.964285714285715</v>
       </c>
       <c r="DD7" t="n">
         <v>-4.191616047948997</v>
       </c>
       <c r="DE7" t="n">
-        <v>69.47619047619047</v>
+        <v>-3.964285714285715</v>
       </c>
       <c r="DF7" t="n">
-        <v>-3184538.690476192</v>
+        <v>-0.3530753968253966</v>
       </c>
       <c r="DG7" t="n">
-        <v>90.04761904761905</v>
+        <v>0.4880952380952408</v>
       </c>
       <c r="DH7" t="n">
         <v>2.832454502972212</v>
       </c>
       <c r="DI7" t="n">
-        <v>-6172195.028536489</v>
+        <v>1.023809523809524</v>
       </c>
     </row>
     <row r="8">
@@ -3349,70 +3349,70 @@
         <v>-0.5935261351516345</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.9757530663780649</v>
+        <v>-1.628571428571428</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.2224837662337664</v>
+        <v>47352.27723665223</v>
       </c>
       <c r="CP8" t="n">
         <v>2.465222458700723</v>
       </c>
       <c r="CQ8" t="n">
+        <v>0.9757530663780649</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>3320895.912255412</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-139.5142857142857</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>5903786.075036079</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0.2790751642045981</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>-3.291829004329031</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>4.027035771325671</v>
+      </c>
+      <c r="CX8" t="n">
         <v>48091.75881922234</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0.2790751642045981</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>-16.19047619047623</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>-0.08543470418469212</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>47352.27723665223</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>-40800000</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>-3.291829004329031</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>-1.628571428571428</v>
       </c>
       <c r="CY8" t="n">
         <v>1.457526154401165</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.027035771325671</v>
+        <v>-0.08543470418469212</v>
       </c>
       <c r="DA8" t="n">
+        <v>-121.5714285714286</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>-40800000</v>
+      </c>
+      <c r="DC8" t="n">
         <v>-8314.28571428571</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>7.152380952380955</v>
       </c>
       <c r="DD8" t="n">
         <v>-0.1101419850490117</v>
       </c>
       <c r="DE8" t="n">
-        <v>-121.5714285714286</v>
+        <v>7.152380952380955</v>
       </c>
       <c r="DF8" t="n">
-        <v>5903786.075036079</v>
+        <v>0.2224837662337664</v>
       </c>
       <c r="DG8" t="n">
-        <v>-139.5142857142857</v>
+        <v>-16.19047619047623</v>
       </c>
       <c r="DH8" t="n">
         <v>-2.909235056435449</v>
       </c>
       <c r="DI8" t="n">
-        <v>3320895.912255412</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="9">
@@ -3692,70 +3692,70 @@
         <v>-0.6965341357227857</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.3710137085137077</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="CO9" t="n">
-        <v>-1.542748917748918</v>
+        <v>-114939.5923520924</v>
       </c>
       <c r="CP9" t="n">
         <v>2.797267869962635</v>
       </c>
       <c r="CQ9" t="n">
+        <v>0.3710137085137077</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-20843959.55901613</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-1.857142857142833</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-38449796.17604619</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0.425674375849618</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>-1.704419191919243</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-5.775063447707907</v>
+      </c>
+      <c r="CX9" t="n">
         <v>-71886.76910836504</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>-0.425674375849618</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>-4.023809523809547</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>-8.089646464646449</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>-114939.5923520924</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>-74582142.85714285</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>-1.704419191919243</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>0.2857142857142856</v>
       </c>
       <c r="CY9" t="n">
         <v>-9.294552669552672</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-5.775063447707907</v>
+        <v>-8.089646464646449</v>
       </c>
       <c r="DA9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-74582142.85714285</v>
+      </c>
+      <c r="DC9" t="n">
         <v>-341571.4285714286</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>-3.857142857142858</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>-0.0238095238095255</v>
       </c>
       <c r="DD9" t="n">
         <v>-6.96388236847281</v>
       </c>
       <c r="DE9" t="n">
-        <v>-3</v>
+        <v>-0.0238095238095255</v>
       </c>
       <c r="DF9" t="n">
-        <v>-38449796.17604619</v>
+        <v>-1.542748917748918</v>
       </c>
       <c r="DG9" t="n">
-        <v>-1.857142857142833</v>
+        <v>-4.023809523809547</v>
       </c>
       <c r="DH9" t="n">
         <v>-0.5826978739700337</v>
       </c>
       <c r="DI9" t="n">
-        <v>-20843959.55901613</v>
+        <v>-3.857142857142858</v>
       </c>
     </row>
     <row r="10">
@@ -4039,70 +4039,70 @@
         <v>-0.5124838950731743</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.7909722222222229</v>
+        <v>-1.428571428571429</v>
       </c>
       <c r="CO10" t="n">
-        <v>-1.1875</v>
+        <v>-87748.61111111111</v>
       </c>
       <c r="CP10" t="n">
         <v>0.3055821062042448</v>
       </c>
       <c r="CQ10" t="n">
+        <v>0.7909722222222229</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-14404241.89423555</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-127.4285714285714</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-31577473.95833333</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0.6396103896103895</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.7045138888889255</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-6.719735330379635</v>
+      </c>
+      <c r="CX10" t="n">
         <v>-62280.356595953</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>-0.6396103896103895</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>-6.588095238095264</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>-9.090625000000003</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>-87748.61111111111</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>-84571428.57142857</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>0.7045138888889255</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>-1.428571428571429</v>
       </c>
       <c r="CY10" t="n">
         <v>-8.720138888888883</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-6.719735330379635</v>
+        <v>-9.090625000000003</v>
       </c>
       <c r="DA10" t="n">
+        <v>-128</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-84571428.57142857</v>
+      </c>
+      <c r="DC10" t="n">
         <v>-383428.5714285715</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>-6.571428571428572</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>-0.6285714285714299</v>
       </c>
       <c r="DD10" t="n">
         <v>-6.727698621141116</v>
       </c>
       <c r="DE10" t="n">
-        <v>-128</v>
+        <v>-0.6285714285714299</v>
       </c>
       <c r="DF10" t="n">
-        <v>-31577473.95833333</v>
+        <v>-1.1875</v>
       </c>
       <c r="DG10" t="n">
-        <v>-127.4285714285714</v>
+        <v>-6.588095238095264</v>
       </c>
       <c r="DH10" t="n">
         <v>0.1027051530340657</v>
       </c>
       <c r="DI10" t="n">
-        <v>-14404241.89423555</v>
+        <v>-6.571428571428572</v>
       </c>
     </row>
     <row r="11">
@@ -4386,70 +4386,70 @@
         <v>0.282054316456481</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.6055555555555543</v>
+        <v>0.4285714285714279</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.5083694083694084</v>
+        <v>34882.31721981723</v>
       </c>
       <c r="CP11" t="n">
         <v>-0.2622228094136219</v>
       </c>
       <c r="CQ11" t="n">
+        <v>0.6055555555555543</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>4520034.519287788</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>41.28571428571428</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>4568533.549783551</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.2061653356994972</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>2.45444324194321</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>4.566482475236469</v>
+      </c>
+      <c r="CX11" t="n">
         <v>29120.55686948693</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>0.2061653356994972</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>1.039795918367361</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>1.460413660413678</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>34882.31721981723</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>32803571.42857143</v>
-      </c>
-      <c r="CW11" t="n">
-        <v>2.45444324194321</v>
-      </c>
-      <c r="CX11" t="n">
-        <v>0.4285714285714279</v>
       </c>
       <c r="CY11" t="n">
         <v>3.010263347763356</v>
       </c>
       <c r="CZ11" t="n">
-        <v>4.566482475236469</v>
+        <v>1.460413660413678</v>
       </c>
       <c r="DA11" t="n">
+        <v>53.42857142857144</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>32803571.42857143</v>
+      </c>
+      <c r="DC11" t="n">
         <v>162285.7142857143</v>
-      </c>
-      <c r="DB11" t="n">
-        <v>0.4285714285714279</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>-0.4312925170068027</v>
       </c>
       <c r="DD11" t="n">
         <v>4.233968783165437</v>
       </c>
       <c r="DE11" t="n">
-        <v>53.42857142857144</v>
+        <v>-0.4312925170068027</v>
       </c>
       <c r="DF11" t="n">
-        <v>4568533.549783551</v>
+        <v>0.5083694083694084</v>
       </c>
       <c r="DG11" t="n">
-        <v>41.28571428571428</v>
+        <v>1.039795918367361</v>
       </c>
       <c r="DH11" t="n">
         <v>3.167975391243431</v>
       </c>
       <c r="DI11" t="n">
-        <v>4520034.519287788</v>
+        <v>0.4285714285714279</v>
       </c>
     </row>
     <row r="12">
@@ -4733,70 +4733,70 @@
         <v>-3.764990455146702</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.271428571428572</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0.5412698412698418</v>
+        <v>-24979.36507936507</v>
       </c>
       <c r="CP12" t="n">
         <v>1.405230874958679</v>
       </c>
       <c r="CQ12" t="n">
+        <v>1.271428571428572</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>-5826478.10211041</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-28.83333333333333</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-16654682.53968254</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0.3095471231971048</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.0460317460317583</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-2.625947161473277</v>
+      </c>
+      <c r="CX12" t="n">
         <v>-15301.14410981784</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>-0.3095471231971048</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>8.333333333333343</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>-5.50793650793652</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>-24979.36507936507</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>-18991666.66666667</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>0.0460317460317583</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>-0.1666666666666667</v>
       </c>
       <c r="CY12" t="n">
         <v>-4.926984126984109</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-2.625947161473277</v>
+        <v>-5.50793650793652</v>
       </c>
       <c r="DA12" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>-18991666.66666667</v>
+      </c>
+      <c r="DC12" t="n">
         <v>-50000</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>-0.9166666666666667</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>4.083333333333332</v>
       </c>
       <c r="DD12" t="n">
         <v>-4.993221201524079</v>
       </c>
       <c r="DE12" t="n">
-        <v>-21.5</v>
+        <v>4.083333333333332</v>
       </c>
       <c r="DF12" t="n">
-        <v>-16654682.53968254</v>
+        <v>-0.5412698412698418</v>
       </c>
       <c r="DG12" t="n">
-        <v>-28.83333333333333</v>
+        <v>8.333333333333343</v>
       </c>
       <c r="DH12" t="n">
         <v>-0.9649415418341789</v>
       </c>
       <c r="DI12" t="n">
-        <v>-5826478.10211041</v>
+        <v>-0.9166666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -5076,70 +5076,70 @@
         <v>-0.9657305194805019</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.3727678571428577</v>
+        <v>-1.071428571428572</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.213789682539682</v>
+        <v>3107.142857142855</v>
       </c>
       <c r="CP13" t="n">
         <v>0.1349221528262881</v>
       </c>
       <c r="CQ13" t="n">
+        <v>-0.3727678571428577</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>12602545.44236569</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-87.21428571428572</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>12136483.13492063</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.6948900931983641</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-3.981894841269821</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>5.942084920092427</v>
+      </c>
+      <c r="CX13" t="n">
         <v>5152.807254358013</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>0.6948900931983641</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>-6.196428571428584</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>3.241071428571431</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>3107.142857142855</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>7846428.571428571</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>-3.981894841269821</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>-1.071428571428572</v>
       </c>
       <c r="CY13" t="n">
         <v>3.733382936507951</v>
       </c>
       <c r="CZ13" t="n">
-        <v>5.942084920092427</v>
+        <v>3.241071428571431</v>
       </c>
       <c r="DA13" t="n">
+        <v>-65.64285714285714</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>7846428.571428571</v>
+      </c>
+      <c r="DC13" t="n">
         <v>42785.71428571429</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>-0.1071428571428572</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>3.755952380952383</v>
       </c>
       <c r="DD13" t="n">
         <v>5.151496634109421</v>
       </c>
       <c r="DE13" t="n">
-        <v>-65.64285714285714</v>
+        <v>3.755952380952383</v>
       </c>
       <c r="DF13" t="n">
-        <v>12136483.13492063</v>
+        <v>1.213789682539682</v>
       </c>
       <c r="DG13" t="n">
-        <v>-87.21428571428572</v>
+        <v>-6.196428571428584</v>
       </c>
       <c r="DH13" t="n">
         <v>-5.88837216981014</v>
       </c>
       <c r="DI13" t="n">
-        <v>12602545.44236569</v>
+        <v>-0.1071428571428572</v>
       </c>
     </row>
     <row r="14">
@@ -5423,70 +5423,70 @@
         <v>-0.8912163533916839</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.9634920634920618</v>
+        <v>2.642857142857143</v>
       </c>
       <c r="CO14" t="n">
-        <v>-0.4381132756132753</v>
+        <v>-9071.194083694088</v>
       </c>
       <c r="CP14" t="n">
         <v>0.5079752179551917</v>
       </c>
       <c r="CQ14" t="n">
+        <v>0.9634920634920618</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-8630035.550952669</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>193.9047619047619</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-8541966.089466091</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0.2489575041663141</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>1.531277056277048</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-6.935883648197716</v>
+      </c>
+      <c r="CX14" t="n">
         <v>-12733.64766907387</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>-0.2489575041663141</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>-0.5670068027210959</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>-4.535533910533914</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>-9071.194083694088</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>-3097619.047619047</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>1.531277056277048</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>2.642857142857143</v>
       </c>
       <c r="CY14" t="n">
         <v>-3.418722943722955</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-6.935883648197716</v>
+        <v>-4.535533910533914</v>
       </c>
       <c r="DA14" t="n">
+        <v>179.7619047619048</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-3097619.047619047</v>
+      </c>
+      <c r="DC14" t="n">
         <v>83404.76190476191</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>3.30952380952381</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>-0.4459183673469411</v>
       </c>
       <c r="DD14" t="n">
         <v>-6.815052326582631</v>
       </c>
       <c r="DE14" t="n">
-        <v>179.7619047619048</v>
+        <v>-0.4459183673469411</v>
       </c>
       <c r="DF14" t="n">
-        <v>-8541966.089466091</v>
+        <v>-0.4381132756132753</v>
       </c>
       <c r="DG14" t="n">
-        <v>193.9047619047619</v>
+        <v>-0.5670068027210959</v>
       </c>
       <c r="DH14" t="n">
         <v>2.483985231016106</v>
       </c>
       <c r="DI14" t="n">
-        <v>-8630035.550952669</v>
+        <v>3.30952380952381</v>
       </c>
     </row>
     <row r="15">
@@ -5766,70 +5766,70 @@
         <v>0.6268890200708341</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.4746572871572887</v>
+        <v>-0.5714285714285716</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.519372294372294</v>
+        <v>31952.36291486291</v>
       </c>
       <c r="CP15" t="n">
         <v>-1.903027772404457</v>
       </c>
       <c r="CQ15" t="n">
+        <v>0.4746572871572887</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>5754722.598100111</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-18.28571428571428</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>12630001.8037518</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.1956863623375771</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>2.64662698412701</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.8381878392075777</v>
+      </c>
+      <c r="CX15" t="n">
         <v>5335.461059688569</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>0.1956863623375771</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>11.83095238095243</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>4.660750360750342</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>31952.36291486291</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>47171428.57142857</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>2.64662698412701</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>-0.5714285714285716</v>
       </c>
       <c r="CY15" t="n">
         <v>5.456457431457423</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.8381878392075777</v>
+        <v>4.660750360750342</v>
       </c>
       <c r="DA15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>47171428.57142857</v>
+      </c>
+      <c r="DC15" t="n">
         <v>84142.85714285714</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>1.571428571428571</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>-3.676190476190474</v>
       </c>
       <c r="DD15" t="n">
         <v>2.576177091293857</v>
       </c>
       <c r="DE15" t="n">
-        <v>-27</v>
+        <v>-3.676190476190474</v>
       </c>
       <c r="DF15" t="n">
-        <v>12630001.8037518</v>
+        <v>0.519372294372294</v>
       </c>
       <c r="DG15" t="n">
-        <v>-18.28571428571428</v>
+        <v>11.83095238095243</v>
       </c>
       <c r="DH15" t="n">
         <v>2.696260271399751</v>
       </c>
       <c r="DI15" t="n">
-        <v>5754722.598100111</v>
+        <v>1.571428571428571</v>
       </c>
     </row>
     <row r="16">
@@ -6113,70 +6113,70 @@
         <v>5.350501088029688</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.597619047619048</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.1875</v>
+        <v>77052.97619047618</v>
       </c>
       <c r="CP16" t="n">
         <v>1.994761904761905</v>
       </c>
       <c r="CQ16" t="n">
+        <v>1.597619047619048</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>13962295.45454545</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>29415099.20634921</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0.6396103896103895</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0.9106150793650727</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>8.287402597402576</v>
+      </c>
+      <c r="CX16" t="n">
         <v>54657.22943722944</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>0.6396103896103895</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>-0.2999999999999829</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>6.042757936507925</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>77052.97619047618</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>92157142.85714287</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>0.9106150793650727</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>0.1428571428571428</v>
       </c>
       <c r="CY16" t="n">
         <v>7.883234126984135</v>
       </c>
       <c r="CZ16" t="n">
-        <v>8.287402597402576</v>
+        <v>6.042757936507925</v>
       </c>
       <c r="DA16" t="n">
+        <v>41.85714285714289</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>92157142.85714287</v>
+      </c>
+      <c r="DC16" t="n">
         <v>337285.7142857143</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>7.285714285714286</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>3.483333333333327</v>
       </c>
       <c r="DD16" t="n">
         <v>6.236623376623371</v>
       </c>
       <c r="DE16" t="n">
-        <v>41.85714285714289</v>
+        <v>3.483333333333327</v>
       </c>
       <c r="DF16" t="n">
-        <v>29415099.20634921</v>
+        <v>1.1875</v>
       </c>
       <c r="DG16" t="n">
-        <v>31</v>
+        <v>-0.2999999999999829</v>
       </c>
       <c r="DH16" t="n">
         <v>1.35965367965369</v>
       </c>
       <c r="DI16" t="n">
-        <v>13962295.45454545</v>
+        <v>7.285714285714286</v>
       </c>
     </row>
     <row r="17">
@@ -6456,70 +6456,70 @@
         <v>0.6945748065066226</v>
       </c>
       <c r="CN17" t="n">
-        <v>-4.453246753246756</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="CO17" t="n">
-        <v>-2.355844155844156</v>
+        <v>-91751.94805194803</v>
       </c>
       <c r="CP17" t="n">
         <v>-3.704664381512206</v>
       </c>
       <c r="CQ17" t="n">
+        <v>-4.453246753246756</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>-23805530.08359394</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>244.7142857142857</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>-39239740.25974026</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-1.356823128562259</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>2.528571428571411</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-11.104228494935</v>
+      </c>
+      <c r="CX17" t="n">
         <v>-66040.02900782792</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>-1.356823128562259</v>
-      </c>
-      <c r="CS17" t="n">
-        <v>6.985714285714266</v>
-      </c>
-      <c r="CT17" t="n">
-        <v>-10.53116883116881</v>
-      </c>
-      <c r="CU17" t="n">
-        <v>-91751.94805194803</v>
-      </c>
-      <c r="CV17" t="n">
-        <v>-38971428.57142857</v>
-      </c>
-      <c r="CW17" t="n">
-        <v>2.528571428571411</v>
-      </c>
-      <c r="CX17" t="n">
-        <v>3.428571428571428</v>
       </c>
       <c r="CY17" t="n">
         <v>-14.34805194805196</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-11.104228494935</v>
+        <v>-10.53116883116881</v>
       </c>
       <c r="DA17" t="n">
+        <v>229.2857142857143</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-38971428.57142857</v>
+      </c>
+      <c r="DC17" t="n">
         <v>-100571.4285714286</v>
-      </c>
-      <c r="DB17" t="n">
-        <v>1.571428571428572</v>
-      </c>
-      <c r="DC17" t="n">
-        <v>-0.4285714285714306</v>
       </c>
       <c r="DD17" t="n">
         <v>-7.770309400744168</v>
       </c>
       <c r="DE17" t="n">
-        <v>229.2857142857143</v>
+        <v>-0.4285714285714306</v>
       </c>
       <c r="DF17" t="n">
-        <v>-39239740.25974026</v>
+        <v>-2.355844155844156</v>
       </c>
       <c r="DG17" t="n">
-        <v>244.7142857142857</v>
+        <v>6.985714285714266</v>
       </c>
       <c r="DH17" t="n">
         <v>-1.403671563943306</v>
       </c>
       <c r="DI17" t="n">
-        <v>-23805530.08359394</v>
+        <v>1.571428571428572</v>
       </c>
     </row>
     <row r="18">
@@ -6803,70 +6803,70 @@
         <v>-4.508611111111108</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.2698683261183241</v>
+        <v>0</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.05454545454545467</v>
+        <v>-4783.694083694083</v>
       </c>
       <c r="CP18" t="n">
         <v>-0.3791763826916217</v>
       </c>
       <c r="CQ18" t="n">
+        <v>-0.2698683261183241</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-281839.2328481129</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-8.285714285714278</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>-566405.9117965363</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0.007518796992481258</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-2.418231421356467</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>-1.834679032272717</v>
+      </c>
+      <c r="CX18" t="n">
         <v>-1007.479147178597</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>0.007518796992481258</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>0.4404761904762324</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>-0.2922483766233626</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>-4783.694083694083</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>-15610714.28571429</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>-2.418231421356467</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>-1.277344877344888</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-1.834679032272717</v>
+        <v>-0.2922483766233626</v>
       </c>
       <c r="DA18" t="n">
+        <v>-14.14285714285714</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>-15610714.28571429</v>
+      </c>
+      <c r="DC18" t="n">
         <v>-23571.42857142857</v>
-      </c>
-      <c r="DB18" t="n">
-        <v>-1.714285714285714</v>
-      </c>
-      <c r="DC18" t="n">
-        <v>-2.690476190476186</v>
       </c>
       <c r="DD18" t="n">
         <v>-0.2961639479486422</v>
       </c>
       <c r="DE18" t="n">
-        <v>-14.14285714285714</v>
+        <v>-2.690476190476186</v>
       </c>
       <c r="DF18" t="n">
-        <v>-566405.9117965363</v>
+        <v>0.05454545454545467</v>
       </c>
       <c r="DG18" t="n">
-        <v>-8.285714285714278</v>
+        <v>0.4404761904762324</v>
       </c>
       <c r="DH18" t="n">
         <v>-1.152991323947873</v>
       </c>
       <c r="DI18" t="n">
-        <v>-281839.2328481129</v>
+        <v>-1.714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -7150,70 +7150,70 @@
         <v>0.8526797192706255</v>
       </c>
       <c r="CN19" t="n">
-        <v>-1.821424062049061</v>
+        <v>1.914285714285714</v>
       </c>
       <c r="CO19" t="n">
-        <v>0.8008928571428573</v>
+        <v>35634.9522005772</v>
       </c>
       <c r="CP19" t="n">
         <v>-3.359462556258901</v>
       </c>
       <c r="CQ19" t="n">
+        <v>-1.821424062049061</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>11768341.04866061</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>159.6571428571428</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>19916008.2972583</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>-0.0490871506925572</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>2.349621212121264</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>0.9098398371746583</v>
+      </c>
+      <c r="CX19" t="n">
         <v>18459.54922945413</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>-0.0490871506925572</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>8.383333333333354</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>3.5143308080808</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>35634.9522005772</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>68210714.28571428</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>2.349621212121264</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>1.914285714285714</v>
       </c>
       <c r="CY19" t="n">
         <v>2.380569083694084</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.9098398371746583</v>
+        <v>3.5143308080808</v>
       </c>
       <c r="DA19" t="n">
+        <v>151.5714285714286</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>68210714.28571428</v>
+      </c>
+      <c r="DC19" t="n">
         <v>265742.8571428572</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>3.885714285714286</v>
-      </c>
-      <c r="DC19" t="n">
-        <v>-3.452380952380956</v>
       </c>
       <c r="DD19" t="n">
         <v>4.497847262227964</v>
       </c>
       <c r="DE19" t="n">
-        <v>151.5714285714286</v>
+        <v>-3.452380952380956</v>
       </c>
       <c r="DF19" t="n">
-        <v>19916008.2972583</v>
+        <v>0.8008928571428573</v>
       </c>
       <c r="DG19" t="n">
-        <v>159.6571428571428</v>
+        <v>8.383333333333354</v>
       </c>
       <c r="DH19" t="n">
         <v>0.7956726590057315</v>
       </c>
       <c r="DI19" t="n">
-        <v>11768341.04866061</v>
+        <v>3.885714285714286</v>
       </c>
     </row>
     <row r="20">
@@ -7497,70 +7497,70 @@
         <v>-0.5642843614718487</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.2658730158730194</v>
+        <v>0.8571428571428577</v>
       </c>
       <c r="CO20" t="n">
-        <v>0</v>
+        <v>-394.5105820105819</v>
       </c>
       <c r="CP20" t="n">
         <v>-1.330884415169578</v>
       </c>
       <c r="CQ20" t="n">
+        <v>0.2658730158730194</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>-628291.6761551113</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>73</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>1403472.222222221</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>-0.02255639097744355</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>0.2080026455026314</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>-1.946757463950505</v>
+      </c>
+      <c r="CX20" t="n">
         <v>-52.72447794907748</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>-0.02255639097744355</v>
-      </c>
-      <c r="CS20" t="n">
-        <v>-2.523809523809547</v>
-      </c>
-      <c r="CT20" t="n">
-        <v>0.6335978835978722</v>
-      </c>
-      <c r="CU20" t="n">
-        <v>-394.5105820105837</v>
-      </c>
-      <c r="CV20" t="n">
-        <v>-6089285.714285715</v>
-      </c>
-      <c r="CW20" t="n">
-        <v>0.2080026455026314</v>
-      </c>
-      <c r="CX20" t="n">
-        <v>0.8571428571428577</v>
       </c>
       <c r="CY20" t="n">
         <v>0.4136904761904816</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-1.946757463950505</v>
+        <v>0.6335978835978722</v>
       </c>
       <c r="DA20" t="n">
+        <v>49.85714285714283</v>
+      </c>
+      <c r="DB20" t="n">
+        <v>-6089285.714285715</v>
+      </c>
+      <c r="DC20" t="n">
         <v>-9142.857142857145</v>
-      </c>
-      <c r="DB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC20" t="n">
-        <v>-1.709523809523812</v>
       </c>
       <c r="DD20" t="n">
         <v>-0.6806326477959601</v>
       </c>
       <c r="DE20" t="n">
-        <v>49.85714285714283</v>
+        <v>-1.709523809523812</v>
       </c>
       <c r="DF20" t="n">
-        <v>1403472.222222221</v>
+        <v>0</v>
       </c>
       <c r="DG20" t="n">
-        <v>73</v>
+        <v>-2.523809523809547</v>
       </c>
       <c r="DH20" t="n">
         <v>-1.812097108580247</v>
       </c>
       <c r="DI20" t="n">
-        <v>-628291.6761551113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -7844,70 +7844,70 @@
         <v>-0.950694286220596</v>
       </c>
       <c r="CN21" t="n">
-        <v>-0.1227272727272712</v>
+        <v>-2.238095238095238</v>
       </c>
       <c r="CO21" t="n">
-        <v>-0.4288239538239538</v>
+        <v>-28721.62698412699</v>
       </c>
       <c r="CP21" t="n">
         <v>2.731875276058993</v>
       </c>
       <c r="CQ21" t="n">
+        <v>-0.1227272727272712</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>-4611908.333271373</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>-188.1190476190476</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>-6580225.468975469</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>-0.1867472537814152</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>-0.8768759018759056</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>-2.600862479599343</v>
+      </c>
+      <c r="CX21" t="n">
         <v>-20464.02968702605</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>-0.1867472537814152</v>
-      </c>
-      <c r="CS21" t="n">
-        <v>0.4602040816326394</v>
-      </c>
-      <c r="CT21" t="n">
-        <v>-3.435371572871574</v>
-      </c>
-      <c r="CU21" t="n">
-        <v>-28721.62698412699</v>
-      </c>
-      <c r="CV21" t="n">
-        <v>-39298214.28571428</v>
-      </c>
-      <c r="CW21" t="n">
-        <v>-0.8768759018759056</v>
-      </c>
-      <c r="CX21" t="n">
-        <v>-2.238095238095238</v>
       </c>
       <c r="CY21" t="n">
         <v>-3.989303751803746</v>
       </c>
       <c r="CZ21" t="n">
-        <v>-2.600862479599343</v>
+        <v>-3.435371572871574</v>
       </c>
       <c r="DA21" t="n">
+        <v>-173.6666666666667</v>
+      </c>
+      <c r="DB21" t="n">
+        <v>-39298214.28571428</v>
+      </c>
+      <c r="DC21" t="n">
         <v>-172714.2857142857</v>
-      </c>
-      <c r="DB21" t="n">
-        <v>-2.238095238095238</v>
-      </c>
-      <c r="DC21" t="n">
-        <v>2.183673469387756</v>
       </c>
       <c r="DD21" t="n">
         <v>-4.203482135769562</v>
       </c>
       <c r="DE21" t="n">
-        <v>-173.6666666666667</v>
+        <v>2.183673469387756</v>
       </c>
       <c r="DF21" t="n">
-        <v>-6580225.468975469</v>
+        <v>-0.4288239538239538</v>
       </c>
       <c r="DG21" t="n">
-        <v>-188.1190476190476</v>
+        <v>0.4602040816326394</v>
       </c>
       <c r="DH21" t="n">
         <v>-2.188760641532383</v>
       </c>
       <c r="DI21" t="n">
-        <v>-4611908.333271373</v>
+        <v>-2.238095238095238</v>
       </c>
     </row>
     <row r="22">
@@ -8187,70 +8187,70 @@
         <v>0.7480785123966882</v>
       </c>
       <c r="CN22" t="n">
-        <v>-0.9341269841269835</v>
+        <v>0</v>
       </c>
       <c r="CO22" t="n">
-        <v>-0.8607142857142858</v>
+        <v>-1176.98412698412</v>
       </c>
       <c r="CP22" t="n">
         <v>-0.02273520838247833</v>
       </c>
       <c r="CQ22" t="n">
+        <v>-0.9341269841269835</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>-6430350.413829204</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>-2.833333333333329</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>-8951944.444444442</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>-0.381730716343335</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>1.050396825396803</v>
+      </c>
+      <c r="CW22" t="n">
+        <v>-0.4554159826225828</v>
+      </c>
+      <c r="CX22" t="n">
         <v>7745.30998023806</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>-0.381730716343335</v>
-      </c>
-      <c r="CS22" t="n">
-        <v>5.708333333333343</v>
-      </c>
-      <c r="CT22" t="n">
-        <v>-0.6329365079365061</v>
-      </c>
-      <c r="CU22" t="n">
-        <v>-1176.98412698412</v>
-      </c>
-      <c r="CV22" t="n">
-        <v>-20541666.66666667</v>
-      </c>
-      <c r="CW22" t="n">
-        <v>1.050396825396803</v>
-      </c>
-      <c r="CX22" t="n">
-        <v>0</v>
       </c>
       <c r="CY22" t="n">
         <v>-2.444047619047623</v>
       </c>
       <c r="CZ22" t="n">
-        <v>-0.4554159826225828</v>
+        <v>-0.6329365079365061</v>
       </c>
       <c r="DA22" t="n">
+        <v>-3.833333333333329</v>
+      </c>
+      <c r="DB22" t="n">
+        <v>-20541666.66666667</v>
+      </c>
+      <c r="DC22" t="n">
         <v>-60333.33333333333</v>
-      </c>
-      <c r="DB22" t="n">
-        <v>-0.9166666666666667</v>
-      </c>
-      <c r="DC22" t="n">
-        <v>0.2083333333333321</v>
       </c>
       <c r="DD22" t="n">
         <v>-0.9598805861604234</v>
       </c>
       <c r="DE22" t="n">
-        <v>-3.833333333333329</v>
+        <v>0.2083333333333321</v>
       </c>
       <c r="DF22" t="n">
-        <v>-8951944.444444442</v>
+        <v>-0.8607142857142858</v>
       </c>
       <c r="DG22" t="n">
-        <v>-2.833333333333329</v>
+        <v>5.708333333333343</v>
       </c>
       <c r="DH22" t="n">
         <v>3.055917666837928</v>
       </c>
       <c r="DI22" t="n">
-        <v>-6430350.413829204</v>
+        <v>-0.9166666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -8534,70 +8534,70 @@
         <v>-0.8471909310496386</v>
       </c>
       <c r="CN23" t="n">
-        <v>4.017207792207792</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="CO23" t="n">
-        <v>1.168344155844156</v>
+        <v>10304.05844155842</v>
       </c>
       <c r="CP23" t="n">
         <v>2.122084075344947</v>
       </c>
       <c r="CQ23" t="n">
+        <v>4.017207792207792</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>9797661.794727013</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>-155.1428571428571</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>7207873.376623377</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>0.7694117476726174</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>-2.804626623376606</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>2.87376210745775</v>
+      </c>
+      <c r="CX23" t="n">
         <v>11554.79448088144</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>0.7694117476726174</v>
-      </c>
-      <c r="CS23" t="n">
-        <v>-5.40952380952379</v>
-      </c>
-      <c r="CT23" t="n">
-        <v>0.7106331168831019</v>
-      </c>
-      <c r="CU23" t="n">
-        <v>10304.05844155842</v>
-      </c>
-      <c r="CV23" t="n">
-        <v>-51571428.57142857</v>
-      </c>
-      <c r="CW23" t="n">
-        <v>-2.804626623376606</v>
-      </c>
-      <c r="CX23" t="n">
-        <v>-1.857142857142857</v>
       </c>
       <c r="CY23" t="n">
         <v>3.749269480519487</v>
       </c>
       <c r="CZ23" t="n">
-        <v>2.87376210745775</v>
+        <v>0.7106331168831019</v>
       </c>
       <c r="DA23" t="n">
+        <v>-153.7142857142857</v>
+      </c>
+      <c r="DB23" t="n">
+        <v>-51571428.57142857</v>
+      </c>
+      <c r="DC23" t="n">
         <v>-264285.7142857143</v>
-      </c>
-      <c r="DB23" t="n">
-        <v>-7</v>
-      </c>
-      <c r="DC23" t="n">
-        <v>-2.771428571428569</v>
       </c>
       <c r="DD23" t="n">
         <v>0.7749160260029839</v>
       </c>
       <c r="DE23" t="n">
-        <v>-153.7142857142857</v>
+        <v>-2.771428571428569</v>
       </c>
       <c r="DF23" t="n">
-        <v>7207873.376623377</v>
+        <v>1.168344155844156</v>
       </c>
       <c r="DG23" t="n">
-        <v>-155.1428571428571</v>
+        <v>-5.40952380952379</v>
       </c>
       <c r="DH23" t="n">
         <v>0.9734012364447153</v>
       </c>
       <c r="DI23" t="n">
-        <v>9797661.794727013</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="24">
@@ -8877,70 +8877,70 @@
         <v>3.979966329966331</v>
       </c>
       <c r="CN24" t="n">
-        <v>0.2487193362193345</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="CO24" t="n">
-        <v>0.1598484848484847</v>
+        <v>12895.68903318903</v>
       </c>
       <c r="CP24" t="n">
         <v>1.044694949802263</v>
       </c>
       <c r="CQ24" t="n">
+        <v>0.2487193362193345</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>3881348.511033027</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>134.8571428571429</v>
+      </c>
+      <c r="CT24" t="n">
+        <v>3074738.455988455</v>
+      </c>
+      <c r="CU24" t="n">
+        <v>0.2985634763058542</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>0.278048340548338</v>
+      </c>
+      <c r="CW24" t="n">
+        <v>3.212583395659777</v>
+      </c>
+      <c r="CX24" t="n">
         <v>20635.26614997293</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>0.2985634763058542</v>
-      </c>
-      <c r="CS24" t="n">
-        <v>0.01190476190473078</v>
-      </c>
-      <c r="CT24" t="n">
-        <v>1.911976911976907</v>
-      </c>
-      <c r="CU24" t="n">
-        <v>12895.68903318903</v>
-      </c>
-      <c r="CV24" t="n">
-        <v>16882142.85714286</v>
-      </c>
-      <c r="CW24" t="n">
-        <v>0.278048340548338</v>
-      </c>
-      <c r="CX24" t="n">
-        <v>1.714285714285714</v>
       </c>
       <c r="CY24" t="n">
         <v>2.224062049062056</v>
       </c>
       <c r="CZ24" t="n">
-        <v>3.212583395659777</v>
+        <v>1.911976911976907</v>
       </c>
       <c r="DA24" t="n">
+        <v>135.2857142857143</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>16882142.85714286</v>
+      </c>
+      <c r="DC24" t="n">
         <v>68857.14285714286</v>
-      </c>
-      <c r="DB24" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="DC24" t="n">
-        <v>2.44285714285714</v>
       </c>
       <c r="DD24" t="n">
         <v>1.997084934174765</v>
       </c>
       <c r="DE24" t="n">
-        <v>135.2857142857143</v>
+        <v>2.44285714285714</v>
       </c>
       <c r="DF24" t="n">
-        <v>3074738.455988455</v>
+        <v>0.1598484848484847</v>
       </c>
       <c r="DG24" t="n">
-        <v>134.8571428571429</v>
+        <v>0.01190476190473078</v>
       </c>
       <c r="DH24" t="n">
         <v>-0.4820337438682145</v>
       </c>
       <c r="DI24" t="n">
-        <v>3881348.511033027</v>
+        <v>1.857142857142857</v>
       </c>
     </row>
     <row r="25">
@@ -9224,70 +9224,70 @@
         <v>0.2381072631072669</v>
       </c>
       <c r="CN25" t="n">
-        <v>0.02857142857142847</v>
+        <v>-2.642857142857143</v>
       </c>
       <c r="CO25" t="n">
-        <v>0.893668831168831</v>
+        <v>17953.73376623376</v>
       </c>
       <c r="CP25" t="n">
         <v>1.617800952044579</v>
       </c>
       <c r="CQ25" t="n">
+        <v>0.02857142857142847</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>7884051.186972965</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>-190.0714285714286</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>18095616.88311688</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>0.464443364062112</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>-2.550324675324646</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>7.082832889432666</v>
+      </c>
+      <c r="CX25" t="n">
         <v>9797.142879867213</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>0.464443364062112</v>
-      </c>
-      <c r="CS25" t="n">
-        <v>-5.766326530612247</v>
-      </c>
-      <c r="CT25" t="n">
-        <v>6.456168831168839</v>
-      </c>
-      <c r="CU25" t="n">
-        <v>17953.73376623376</v>
-      </c>
-      <c r="CV25" t="n">
-        <v>4389285.714285715</v>
-      </c>
-      <c r="CW25" t="n">
-        <v>-2.550324675324646</v>
-      </c>
-      <c r="CX25" t="n">
-        <v>-2.642857142857143</v>
       </c>
       <c r="CY25" t="n">
         <v>6.728246753246736</v>
       </c>
       <c r="CZ25" t="n">
-        <v>7.082832889432666</v>
+        <v>6.456168831168839</v>
       </c>
       <c r="DA25" t="n">
+        <v>-180.4285714285714</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>4389285.714285715</v>
+      </c>
+      <c r="DC25" t="n">
         <v>-75071.42857142858</v>
-      </c>
-      <c r="DB25" t="n">
-        <v>-2.892857142857143</v>
-      </c>
-      <c r="DC25" t="n">
-        <v>-0.387414965986391</v>
       </c>
       <c r="DD25" t="n">
         <v>5.972647826320994</v>
       </c>
       <c r="DE25" t="n">
-        <v>-180.4285714285714</v>
+        <v>-0.387414965986391</v>
       </c>
       <c r="DF25" t="n">
-        <v>18095616.88311688</v>
+        <v>0.893668831168831</v>
       </c>
       <c r="DG25" t="n">
-        <v>-190.0714285714286</v>
+        <v>-5.766326530612247</v>
       </c>
       <c r="DH25" t="n">
         <v>-1.76756109614476</v>
       </c>
       <c r="DI25" t="n">
-        <v>7884051.186972965</v>
+        <v>-2.892857142857143</v>
       </c>
     </row>
     <row r="26">
@@ -9567,70 +9567,70 @@
         <v>-5.545939055628068</v>
       </c>
       <c r="CN26" t="n">
-        <v>-1.161580086580084</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="CO26" t="n">
-        <v>0</v>
+        <v>4394.913419913421</v>
       </c>
       <c r="CP26" t="n">
         <v>-0.4121815985946462</v>
       </c>
       <c r="CQ26" t="n">
+        <v>-1.161580086580084</v>
+      </c>
+      <c r="CR26" t="n">
+        <v>45572.83432147559</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>-120.5714285714286</v>
+      </c>
+      <c r="CT26" t="n">
+        <v>2616767.676767677</v>
+      </c>
+      <c r="CU26" t="n">
+        <v>-0.05219900872074801</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>-0.6345598845598772</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>-0.05693620992532544</v>
+      </c>
+      <c r="CX26" t="n">
         <v>-171.994910282956</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>-0.05219900872074801</v>
-      </c>
-      <c r="CS26" t="n">
-        <v>-1.276190476190493</v>
-      </c>
-      <c r="CT26" t="n">
-        <v>3.777777777777786</v>
-      </c>
-      <c r="CU26" t="n">
-        <v>4394.913419913421</v>
-      </c>
-      <c r="CV26" t="n">
-        <v>-1614285.714285715</v>
-      </c>
-      <c r="CW26" t="n">
-        <v>-0.6345598845598772</v>
-      </c>
-      <c r="CX26" t="n">
-        <v>-1.714285714285714</v>
       </c>
       <c r="CY26" t="n">
         <v>2.715548340548338</v>
       </c>
       <c r="CZ26" t="n">
-        <v>-0.05693620992532544</v>
+        <v>3.777777777777786</v>
       </c>
       <c r="DA26" t="n">
+        <v>-117.4285714285714</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>-1614285.714285715</v>
+      </c>
+      <c r="DC26" t="n">
         <v>27571.42857142858</v>
-      </c>
-      <c r="DB26" t="n">
-        <v>-1.857142857142857</v>
-      </c>
-      <c r="DC26" t="n">
-        <v>-0.2833333333333279</v>
       </c>
       <c r="DD26" t="n">
         <v>0.7587699981178133</v>
       </c>
       <c r="DE26" t="n">
-        <v>-117.4285714285714</v>
+        <v>-0.2833333333333279</v>
       </c>
       <c r="DF26" t="n">
-        <v>2616767.676767677</v>
+        <v>0</v>
       </c>
       <c r="DG26" t="n">
-        <v>-120.5714285714286</v>
+        <v>-1.276190476190493</v>
       </c>
       <c r="DH26" t="n">
         <v>-0.9293833521550994</v>
       </c>
       <c r="DI26" t="n">
-        <v>45572.83432147559</v>
+        <v>-1.857142857142857</v>
       </c>
     </row>
     <row r="27">
@@ -9914,70 +9914,70 @@
         <v>-0.04623966942149593</v>
       </c>
       <c r="CN27" t="n">
-        <v>1.190909090909095</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CO27" t="n">
-        <v>0.7337662337662334</v>
+        <v>42884.19913419913</v>
       </c>
       <c r="CP27" t="n">
         <v>-0.9249258296822873</v>
       </c>
       <c r="CQ27" t="n">
+        <v>1.190909090909095</v>
+      </c>
+      <c r="CR27" t="n">
+        <v>8287378.290482899</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>37.71428571428572</v>
+      </c>
+      <c r="CT27" t="n">
+        <v>13871277.05627705</v>
+      </c>
+      <c r="CU27" t="n">
+        <v>0.479212244658469</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>3.216414141414134</v>
+      </c>
+      <c r="CW27" t="n">
+        <v>1.831260690201518</v>
+      </c>
+      <c r="CX27" t="n">
         <v>29237.24976487317</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>0.479212244658469</v>
-      </c>
-      <c r="CS27" t="n">
-        <v>7.783333333333331</v>
-      </c>
-      <c r="CT27" t="n">
-        <v>4.54451659451658</v>
-      </c>
-      <c r="CU27" t="n">
-        <v>42884.19913419913</v>
-      </c>
-      <c r="CV27" t="n">
-        <v>51428571.42857143</v>
-      </c>
-      <c r="CW27" t="n">
-        <v>3.216414141414134</v>
-      </c>
-      <c r="CX27" t="n">
-        <v>0.1428571428571428</v>
       </c>
       <c r="CY27" t="n">
         <v>5.468253968253975</v>
       </c>
       <c r="CZ27" t="n">
-        <v>1.831260690201518</v>
+        <v>4.54451659451658</v>
       </c>
       <c r="DA27" t="n">
+        <v>28.85714285714283</v>
+      </c>
+      <c r="DB27" t="n">
+        <v>51428571.42857143</v>
+      </c>
+      <c r="DC27" t="n">
         <v>124142.8571428571</v>
-      </c>
-      <c r="DB27" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="DC27" t="n">
-        <v>-1.80952380952381</v>
       </c>
       <c r="DD27" t="n">
         <v>3.293908456151016</v>
       </c>
       <c r="DE27" t="n">
-        <v>28.85714285714283</v>
+        <v>-1.80952380952381</v>
       </c>
       <c r="DF27" t="n">
-        <v>13871277.05627705</v>
+        <v>0.7337662337662334</v>
       </c>
       <c r="DG27" t="n">
-        <v>37.71428571428572</v>
+        <v>7.783333333333331</v>
       </c>
       <c r="DH27" t="n">
         <v>1.542648490589016</v>
       </c>
       <c r="DI27" t="n">
-        <v>8287378.290482899</v>
+        <v>1.857142857142857</v>
       </c>
     </row>
     <row r="28">
@@ -10261,70 +10261,70 @@
         <v>-0.1825192716639918</v>
       </c>
       <c r="CN28" t="n">
-        <v>0.5261904761904752</v>
+        <v>0.8571428571428568</v>
       </c>
       <c r="CO28" t="n">
-        <v>-1.248773448773449</v>
+        <v>-91383.62193362192</v>
       </c>
       <c r="CP28" t="n">
         <v>0.2260587026572658</v>
       </c>
       <c r="CQ28" t="n">
+        <v>0.5261904761904752</v>
+      </c>
+      <c r="CR28" t="n">
+        <v>-19484872.40826625</v>
+      </c>
+      <c r="CS28" t="n">
+        <v>56.42857142857144</v>
+      </c>
+      <c r="CT28" t="n">
+        <v>-33719065.65656567</v>
+      </c>
+      <c r="CU28" t="n">
+        <v>-0.5255913134484562</v>
+      </c>
+      <c r="CV28" t="n">
+        <v>0.3882395382394748</v>
+      </c>
+      <c r="CW28" t="n">
+        <v>-4.148411287415882</v>
+      </c>
+      <c r="CX28" t="n">
         <v>-66720.72542201179</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>-0.5255913134484562</v>
-      </c>
-      <c r="CS28" t="n">
-        <v>-1.460204081632639</v>
-      </c>
-      <c r="CT28" t="n">
-        <v>-5.879401154401137</v>
-      </c>
-      <c r="CU28" t="n">
-        <v>-91383.62193362192</v>
-      </c>
-      <c r="CV28" t="n">
-        <v>-52125000</v>
-      </c>
-      <c r="CW28" t="n">
-        <v>0.3882395382394748</v>
-      </c>
-      <c r="CX28" t="n">
-        <v>0.8571428571428568</v>
       </c>
       <c r="CY28" t="n">
         <v>-5.882395382395387</v>
       </c>
       <c r="CZ28" t="n">
-        <v>-4.148411287415882</v>
+        <v>-5.879401154401137</v>
       </c>
       <c r="DA28" t="n">
+        <v>44.42857142857144</v>
+      </c>
+      <c r="DB28" t="n">
+        <v>-52125000</v>
+      </c>
+      <c r="DC28" t="n">
         <v>-228428.5714285714</v>
-      </c>
-      <c r="DB28" t="n">
-        <v>-3.714285714285715</v>
-      </c>
-      <c r="DC28" t="n">
-        <v>-4.031292517006804</v>
       </c>
       <c r="DD28" t="n">
         <v>-4.128277597960491</v>
       </c>
       <c r="DE28" t="n">
-        <v>44.42857142857144</v>
+        <v>-4.031292517006804</v>
       </c>
       <c r="DF28" t="n">
-        <v>-33719065.65656567</v>
+        <v>-1.248773448773449</v>
       </c>
       <c r="DG28" t="n">
-        <v>56.42857142857144</v>
+        <v>-1.460204081632639</v>
       </c>
       <c r="DH28" t="n">
         <v>1.926792189503885</v>
       </c>
       <c r="DI28" t="n">
-        <v>-19484872.40826625</v>
+        <v>-3.714285714285715</v>
       </c>
     </row>
     <row r="29">
@@ -10608,70 +10608,70 @@
         <v>-0.1285943854125833</v>
       </c>
       <c r="CN29" t="n">
-        <v>1.90078914141414</v>
+        <v>-2.342857142857143</v>
       </c>
       <c r="CO29" t="n">
-        <v>0.9562499999999998</v>
+        <v>90630.98695286195</v>
       </c>
       <c r="CP29" t="n">
         <v>2.871181044188013</v>
       </c>
       <c r="CQ29" t="n">
+        <v>1.90078914141414</v>
+      </c>
+      <c r="CR29" t="n">
+        <v>12236565.87889342</v>
+      </c>
+      <c r="CS29" t="n">
+        <v>-174.8</v>
+      </c>
+      <c r="CT29" t="n">
+        <v>18371590.90909091</v>
+      </c>
+      <c r="CU29" t="n">
+        <v>0.7808437998405107</v>
+      </c>
+      <c r="CV29" t="n">
+        <v>-0.2834175084175286</v>
+      </c>
+      <c r="CW29" t="n">
+        <v>7.805053925477694</v>
+      </c>
+      <c r="CX29" t="n">
         <v>77381.73306204459</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>0.7808437998405107</v>
-      </c>
-      <c r="CS29" t="n">
-        <v>-5.883333333333354</v>
-      </c>
-      <c r="CT29" t="n">
-        <v>3.825484006734015</v>
-      </c>
-      <c r="CU29" t="n">
-        <v>90630.98695286195</v>
-      </c>
-      <c r="CV29" t="n">
-        <v>16717857.14285714</v>
-      </c>
-      <c r="CW29" t="n">
-        <v>-0.2834175084175286</v>
-      </c>
-      <c r="CX29" t="n">
-        <v>-2.342857142857143</v>
       </c>
       <c r="CY29" t="n">
         <v>6.512089646464659</v>
       </c>
       <c r="CZ29" t="n">
-        <v>7.805053925477694</v>
+        <v>3.825484006734015</v>
       </c>
       <c r="DA29" t="n">
+        <v>-142.5714285714286</v>
+      </c>
+      <c r="DB29" t="n">
+        <v>16717857.14285714</v>
+      </c>
+      <c r="DC29" t="n">
         <v>124971.4285714286</v>
-      </c>
-      <c r="DB29" t="n">
-        <v>0.2571428571428571</v>
-      </c>
-      <c r="DC29" t="n">
-        <v>7.052380952380958</v>
       </c>
       <c r="DD29" t="n">
         <v>3.864399118897964</v>
       </c>
       <c r="DE29" t="n">
-        <v>-142.5714285714286</v>
+        <v>7.052380952380958</v>
       </c>
       <c r="DF29" t="n">
-        <v>18371590.90909091</v>
+        <v>0.9562499999999998</v>
       </c>
       <c r="DG29" t="n">
-        <v>-174.8</v>
+        <v>-5.883333333333354</v>
       </c>
       <c r="DH29" t="n">
         <v>0.445510542733814</v>
       </c>
       <c r="DI29" t="n">
-        <v>12236565.87889342</v>
+        <v>0.2571428571428571</v>
       </c>
     </row>
     <row r="30">
@@ -10955,70 +10955,70 @@
         <v>5.297020202020192</v>
       </c>
       <c r="CN30" t="n">
-        <v>-0.9565972222222214</v>
+        <v>1.238095238095238</v>
       </c>
       <c r="CO30" t="n">
-        <v>-0.2673611111111105</v>
+        <v>14166.66666666666</v>
       </c>
       <c r="CP30" t="n">
         <v>-3.64319398940226</v>
       </c>
       <c r="CQ30" t="n">
+        <v>-0.9565972222222214</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>400267.4375536256</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>115.0476190476191</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>3916493.055555555</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>-0.2190981135537222</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>3.904513888888857</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>-3.007671017231516</v>
+      </c>
+      <c r="CX30" t="n">
         <v>5339.531664428421</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>-0.2190981135537222</v>
-      </c>
-      <c r="CS30" t="n">
-        <v>-1.511904761904759</v>
-      </c>
-      <c r="CT30" t="n">
-        <v>0.9791666666666714</v>
-      </c>
-      <c r="CU30" t="n">
-        <v>14166.66666666666</v>
-      </c>
-      <c r="CV30" t="n">
-        <v>30395238.0952381</v>
-      </c>
-      <c r="CW30" t="n">
-        <v>3.904513888888857</v>
-      </c>
-      <c r="CX30" t="n">
-        <v>1.238095238095238</v>
       </c>
       <c r="CY30" t="n">
         <v>0.328125</v>
       </c>
       <c r="CZ30" t="n">
-        <v>-3.007671017231516</v>
+        <v>0.9791666666666714</v>
       </c>
       <c r="DA30" t="n">
+        <v>91.64285714285714</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>30395238.0952381</v>
+      </c>
+      <c r="DC30" t="n">
         <v>59214.28571428571</v>
-      </c>
-      <c r="DB30" t="n">
-        <v>1.523809523809524</v>
-      </c>
-      <c r="DC30" t="n">
-        <v>-7.214285714285715</v>
       </c>
       <c r="DD30" t="n">
         <v>1.644009653836719</v>
       </c>
       <c r="DE30" t="n">
-        <v>91.64285714285714</v>
+        <v>-7.214285714285715</v>
       </c>
       <c r="DF30" t="n">
-        <v>3916493.055555555</v>
+        <v>-0.2673611111111105</v>
       </c>
       <c r="DG30" t="n">
-        <v>115.0476190476191</v>
+        <v>-1.511904761904759</v>
       </c>
       <c r="DH30" t="n">
         <v>3.080971909935045</v>
       </c>
       <c r="DI30" t="n">
-        <v>400267.4375536256</v>
+        <v>1.523809523809524</v>
       </c>
     </row>
     <row r="31">
@@ -11302,70 +11302,70 @@
         <v>1.220434102934092</v>
       </c>
       <c r="CN31" t="n">
-        <v>-0.01130050505050662</v>
+        <v>-0.04761904761904789</v>
       </c>
       <c r="CO31" t="n">
-        <v>-0.07954545454545459</v>
+        <v>-2946.338383838385</v>
       </c>
       <c r="CP31" t="n">
         <v>-0.8261846758642655</v>
       </c>
       <c r="CQ31" t="n">
+        <v>-0.01130050505050662</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>-346688.0956634302</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>3.261904761904759</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>-658837.5946969697</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>-0.01941808191808203</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>0.9244002525253165</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>-0.4036940440797423</v>
+      </c>
+      <c r="CX31" t="n">
         <v>-4329.801002121534</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>-0.01941808191808203</v>
-      </c>
-      <c r="CS31" t="n">
-        <v>-3.47619047619051</v>
-      </c>
-      <c r="CT31" t="n">
-        <v>-0.3946022727272833</v>
-      </c>
-      <c r="CU31" t="n">
-        <v>-2946.338383838385</v>
-      </c>
-      <c r="CV31" t="n">
-        <v>15569642.85714286</v>
-      </c>
-      <c r="CW31" t="n">
-        <v>0.9244002525253165</v>
-      </c>
-      <c r="CX31" t="n">
-        <v>-0.04761904761904789</v>
       </c>
       <c r="CY31" t="n">
         <v>-0.3695707070707073</v>
       </c>
       <c r="CZ31" t="n">
-        <v>-0.4036940440797423</v>
+        <v>-0.3946022727272833</v>
       </c>
       <c r="DA31" t="n">
+        <v>5.095238095238074</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>15569642.85714286</v>
+      </c>
+      <c r="DC31" t="n">
         <v>14285.71428571428</v>
-      </c>
-      <c r="DB31" t="n">
-        <v>1.952380952380952</v>
-      </c>
-      <c r="DC31" t="n">
-        <v>2.071428571428569</v>
       </c>
       <c r="DD31" t="n">
         <v>-0.3330436209688798</v>
       </c>
       <c r="DE31" t="n">
-        <v>5.095238095238074</v>
+        <v>2.071428571428569</v>
       </c>
       <c r="DF31" t="n">
-        <v>-658837.5946969697</v>
+        <v>-0.07954545454545459</v>
       </c>
       <c r="DG31" t="n">
-        <v>3.261904761904759</v>
+        <v>-3.47619047619051</v>
       </c>
       <c r="DH31" t="n">
         <v>1.314295645874552</v>
       </c>
       <c r="DI31" t="n">
-        <v>-346688.0956634302</v>
+        <v>1.952380952380952</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -690,135 +690,135 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45600.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D2" t="n">
         <v>41</v>
       </c>
-      <c r="D2" t="n">
-        <v>55</v>
-      </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -840,207 +840,207 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="M2" t="n">
-        <v>239</v>
+        <v>64</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.343333333333333</v>
+        <v>0.1149999999999998</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64377990430622</v>
+        <v>1.082</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.923444976076555</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>7.333333333333334</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>4.150717703349283</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>18.66666666666666</v>
+        <v>12.75</v>
       </c>
       <c r="V2" t="n">
-        <v>7.598086124401913</v>
+        <v>8.083333333333332</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>-1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1.832535885167464</v>
+        <v>1.277777777777778</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>-1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.784688995215311</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.03889397639398</v>
+        <v>14.00274956126249</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.99564727439587</v>
+        <v>17.40871921131234</v>
       </c>
       <c r="AC2" t="n">
-        <v>646.730344778417</v>
+        <v>716.567779888348</v>
       </c>
       <c r="AD2" t="n">
-        <v>751.996360718117</v>
+        <v>869.4719324376954</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>38.77499999999999</v>
+        <v>-0.6749999999999972</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>18.975</v>
+        <v>12.325</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.333333333333336</v>
+        <v>8.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1.557416267942578</v>
+        <v>3.283333333333324</v>
       </c>
       <c r="AK2" t="n">
-        <v>49.33333333333334</v>
+        <v>33.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>26.6555023923445</v>
+        <v>7.888888888888886</v>
       </c>
       <c r="AM2" t="n">
-        <v>455.3333333333333</v>
+        <v>314.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>251.6483253588517</v>
+        <v>78.51666666666665</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.3995215311004783</v>
+        <v>-0.4046052631578949</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>0.2</v>
+        <v>-2.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.999999999999998</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.5789473684210531</v>
+        <v>1.161111111111113</v>
       </c>
       <c r="AU2" t="n">
-        <v>-46.65812114635138</v>
+        <v>-38.99460410678287</v>
       </c>
       <c r="AV2" t="n">
-        <v>-15.78213819167517</v>
+        <v>-1.99105134364158</v>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-0.02063057624427692</v>
+        <v>-0.04183045572618022</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.6666666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.5358851674641147</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>-66.75</v>
+        <v>-4.604166666666671</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.8175324675324673</v>
+        <v>1.387373737373737</v>
       </c>
       <c r="BC2" t="n">
-        <v>17188620.12987013</v>
+        <v>18900659.37149271</v>
       </c>
       <c r="BD2" t="n">
-        <v>20399.44970976804</v>
+        <v>1.289225589225591</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.5760722145349473</v>
+        <v>3.32362454205753</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.2910846055256009</v>
+        <v>-1.941722783389423</v>
       </c>
       <c r="BG2" t="n">
-        <v>27151.78571428572</v>
+        <v>9887342.949404109</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.475811688311694</v>
+        <v>-2500</v>
       </c>
       <c r="BI2" t="n">
-        <v>-62.17857142857142</v>
+        <v>3.338816331350671</v>
       </c>
       <c r="BJ2" t="n">
-        <v>31957142.85714286</v>
+        <v>22</v>
       </c>
       <c r="BK2" t="n">
-        <v>-1.071428571428572</v>
+        <v>3.395679012345667</v>
       </c>
       <c r="BL2" t="n">
-        <v>59714.28571428572</v>
+        <v>0.25</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.9047619047619015</v>
+        <v>18.625</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.7843476637809204</v>
+        <v>4.286812570145898</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9285714285714284</v>
+        <v>0.7089929165849265</v>
       </c>
       <c r="BP2" t="n">
-        <v>-7.50595238095238</v>
+        <v>-0.25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.659560251113064</v>
+        <v>7.895833333333371</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.4029220779220815</v>
+        <v>9722.558922558936</v>
       </c>
       <c r="BS2" t="n">
-        <v>-2.762337662337643</v>
+        <v>1.152892707643371</v>
       </c>
       <c r="BT2" t="n">
-        <v>7436023.687521359</v>
+        <v>22437500</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.568575367868831</v>
+        <v>2.93603674123078</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.819318181818176</v>
+        <v>763.3904662341956</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -1062,193 +1062,209 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2916666666666667</v>
+        <v>-0.7030000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6762865497076026</v>
+        <v>-0.4636842105263159</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.7815789473684209</v>
+        <v>-0.6928571428571428</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.666666666666667</v>
+        <v>-2</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.568421052631579</v>
+        <v>-0.04285714285714359</v>
       </c>
       <c r="U3" t="n">
-        <v>-11.41666666666667</v>
+        <v>-2.416666666666668</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.307894736842103</v>
+        <v>1.511904761904761</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.75</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.05789473684210533</v>
+        <v>-0.430952380952381</v>
       </c>
       <c r="Y3" t="n">
         <v>-0.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.3157894736842104</v>
+        <v>-0.4214285714285715</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.15004208754209</v>
+        <v>21.00380719426772</v>
       </c>
       <c r="AB3" t="n">
-        <v>23.12103412497375</v>
+        <v>20.06744734706117</v>
       </c>
       <c r="AC3" t="n">
-        <v>1141.718873145156</v>
+        <v>860.2254382590581</v>
       </c>
       <c r="AD3" t="n">
-        <v>943.4428589925094</v>
+        <v>863.4369109923971</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-30.30882352941177</v>
+        <v>-3.3125</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-18.33088235294118</v>
+        <v>3.1875</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2.000000000000004</v>
+        <v>0.0833333333333357</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-4.455263157894734</v>
+        <v>1.673809523809517</v>
       </c>
       <c r="AK3" t="n">
-        <v>-41.16666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-26.22105263157894</v>
+        <v>4.961904761904762</v>
       </c>
       <c r="AM3" t="n">
-        <v>-413.3333333333333</v>
+        <v>-11.91666666666669</v>
       </c>
       <c r="AN3" t="n">
-        <v>-244.3</v>
+        <v>44.01666666666659</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1.166666666666667</v>
+        <v>-0.2500000000000002</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.6078947368421055</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>-0.638095238095238</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AR3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.9166666666666679</v>
+        <v>-4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>-2.981578947368423</v>
+        <v>-3.866666666666665</v>
       </c>
       <c r="AU3" t="n">
-        <v>29.80876830853682</v>
+        <v>9.343786731743993</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.61165525794645</v>
+        <v>6.134244869950436</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-0.04927060389812535</v>
+        <v>0.009899025146038236</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.08333333333333334</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.1605263157894737</v>
+        <v>0.05000000000000002</v>
       </c>
       <c r="BA3" t="n">
-        <v>309.5</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
+        <v>-0.01458333333333428</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-0.6440235690235692</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-15123539.21156004</v>
+      </c>
       <c r="BD3" t="n">
-        <v>-630.439006699693</v>
+        <v>-0.43124298540965</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.253687673928874</v>
+        <v>-0.5405410588119537</v>
       </c>
       <c r="BF3" t="n">
-        <v>-3.708331508093845</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+        <v>1.595187991021305</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-4414738.05619707</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>10875</v>
+      </c>
       <c r="BI3" t="n">
-        <v>289.0714285714286</v>
+        <v>-3.793188136816582</v>
       </c>
       <c r="BJ3" t="n">
-        <v>15275000</v>
+        <v>227.375</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.035714285714286</v>
+        <v>-5.384862514029194</v>
       </c>
       <c r="BL3" t="n">
-        <v>42142.85714285714</v>
+        <v>3.125</v>
       </c>
       <c r="BM3" t="n">
-        <v>-4.488095238095241</v>
+        <v>218.25</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.927275435692621</v>
+        <v>-6.307687991021339</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.035714285714286</v>
+        <v>-0.3505211916031004</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.2083333333333428</v>
+        <v>1.875</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-4.200827368254011</v>
-      </c>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
+        <v>3.564583333333303</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>-22794.41638608306</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.3713890961176141</v>
+      </c>
       <c r="BT3" t="n">
-        <v>-2060309.595550479</v>
+        <v>-13050000</v>
       </c>
       <c r="BU3" t="n">
-        <v>-1.008737710377815</v>
-      </c>
-      <c r="BV3" t="inlineStr"/>
+        <v>-3.216018783695205</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-4664.495765946158</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1270,207 +1286,205 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="M4" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.243333333333334</v>
+        <v>0.1125</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9843464052287583</v>
+        <v>0.6646315789473687</v>
       </c>
       <c r="Q4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9394736842105263</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2315789473684209</v>
+      </c>
+      <c r="U4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.277777777777778</v>
-      </c>
-      <c r="U4" t="n">
-        <v>12.66666666666667</v>
-      </c>
       <c r="V4" t="n">
-        <v>11.72222222222222</v>
+        <v>4.592105263157896</v>
       </c>
       <c r="W4" t="n">
-        <v>2.333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9444444444444446</v>
+        <v>0.5842105263157893</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.166666666666667</v>
+        <v>0.6631578947368424</v>
       </c>
       <c r="AA4" t="n">
-        <v>15.12086551792434</v>
+        <v>19.39420995670996</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.57437441979022</v>
+        <v>18.57130313328832</v>
       </c>
       <c r="AC4" t="n">
-        <v>748.3987585549495</v>
+        <v>829.3144892915774</v>
       </c>
       <c r="AD4" t="n">
-        <v>749.0132435952353</v>
+        <v>926.957930921918</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>69.62083333333332</v>
+        <v>-1.670588235294119</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>44.27083333333334</v>
+        <v>7.686274509803923</v>
       </c>
       <c r="AI4" t="n">
-        <v>18.66666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.66666666666667</v>
+        <v>6.292105263157897</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AL4" t="n">
-        <v>26.1111111111111</v>
+        <v>-4.215789473684211</v>
       </c>
       <c r="AM4" t="n">
-        <v>260.6666666666667</v>
+        <v>56</v>
       </c>
       <c r="AN4" t="n">
-        <v>236.2777777777778</v>
+        <v>-47.4131578947368</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.5882352941176472</v>
+        <v>0.7526315789473683</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-3.333333333333332</v>
+        <v>4.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>-4.500000000000004</v>
+        <v>1.144736842105264</v>
       </c>
       <c r="AU4" t="n">
-        <v>-9.056202963466383</v>
+        <v>-8.782858980104226</v>
       </c>
       <c r="AV4" t="n">
-        <v>-4.552337932291376</v>
+        <v>2.915384080070243</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>0.05455242521376386</v>
+        <v>-0.01778969254522732</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3657894736842105</v>
       </c>
       <c r="BA4" t="n">
-        <v>-168.1428571428571</v>
+        <v>1.97891156462585</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.06931818181818183</v>
+        <v>0.9239177489177492</v>
       </c>
       <c r="BC4" t="n">
-        <v>1641573.773448773</v>
+        <v>11862673.16017316</v>
       </c>
       <c r="BD4" t="n">
-        <v>-6576.662888556475</v>
+        <v>0.1168831168831161</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.08861528822055131</v>
+        <v>-6.14971809051616</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.9900547055495572</v>
+        <v>-4.439826839826821</v>
       </c>
       <c r="BG4" t="n">
-        <v>-4264.844877344873</v>
+        <v>11494271.64248613</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.808044733044724</v>
+        <v>-83857.14285714286</v>
       </c>
       <c r="BI4" t="n">
-        <v>-168.2857142857143</v>
+        <v>3.032553303548738</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-12385714.28571429</v>
+        <v>-253</v>
       </c>
       <c r="BK4" t="n">
+        <v>2.005122655122676</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-3.285714285714286</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-235.5714285714286</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>2.377994227994222</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.7183114813431091</v>
+      </c>
+      <c r="BP4" t="n">
         <v>-2.285714285714286</v>
       </c>
-      <c r="BL4" t="n">
-        <v>-125285.7142857143</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>-4.209353741496596</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>-1.974382617446111</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-4.142857142857143</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>3.243537414965999</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>0.7557469830152996</v>
+        <v>-3.975510204081644</v>
       </c>
       <c r="BR4" t="n">
-        <v>-2.511922799422802</v>
+        <v>-6027.849927849937</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0.42700216450217</v>
+        <v>1.34412972130119</v>
       </c>
       <c r="BT4" t="n">
-        <v>326242.9326913026</v>
+        <v>-5842857.142857142</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.474029222430261</v>
+        <v>1.926641934805957</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.4076118326118348</v>
+        <v>-4522.525224811514</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C5" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D5" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1492,209 +1506,209 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>255</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8850000000000002</v>
+        <v>2.5625</v>
       </c>
       <c r="P5" t="n">
-        <v>1.516857142857142</v>
+        <v>1.170446428571428</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.75</v>
+        <v>4.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.222727272727273</v>
+        <v>1.352941176470588</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="T5" t="n">
-        <v>3.759090909090909</v>
+        <v>3.145658263305322</v>
       </c>
       <c r="U5" t="n">
-        <v>14.75</v>
+        <v>10.75</v>
       </c>
       <c r="V5" t="n">
-        <v>10.09545454545455</v>
+        <v>8.862745098039214</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="X5" t="n">
-        <v>1.777272727272727</v>
+        <v>1.694677871148459</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.481818181818181</v>
+        <v>2.80672268907563</v>
       </c>
       <c r="AA5" t="n">
-        <v>16.75663487215211</v>
+        <v>19.13972431077694</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.37368921077444</v>
+        <v>17.61527740125752</v>
       </c>
       <c r="AC5" t="n">
-        <v>664.0796357865829</v>
+        <v>785.7485545983095</v>
       </c>
       <c r="AD5" t="n">
-        <v>782.9336311982311</v>
+        <v>698.5024096746274</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>14.86068111455108</v>
+        <v>51.92063492063491</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>26.19814241486068</v>
+        <v>28.77777777777778</v>
       </c>
       <c r="AI5" t="n">
-        <v>20.91666666666667</v>
+        <v>16.58333333333333</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11.02272727272727</v>
+        <v>19.52100840336134</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>9.166666666666671</v>
       </c>
       <c r="AL5" t="n">
-        <v>21.54545454545455</v>
+        <v>26.25210084033614</v>
       </c>
       <c r="AM5" t="n">
-        <v>318.0833333333334</v>
+        <v>107.4166666666667</v>
       </c>
       <c r="AN5" t="n">
-        <v>204.2636363636364</v>
+        <v>218.3025210084033</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.5</v>
+        <v>-3.166666666666667</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.4473684210526314</v>
+        <v>-1.369747899159664</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.75</v>
+        <v>-2.25</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.833333333333334</v>
+        <v>-13.08333333333333</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.1227272727272748</v>
+        <v>-3.058823529411764</v>
       </c>
       <c r="AU5" t="n">
-        <v>-48.76309381185249</v>
+        <v>10.55747745310245</v>
       </c>
       <c r="AV5" t="n">
-        <v>-16.59923531408338</v>
+        <v>-10.26355733736644</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-0.02165983618467619</v>
+        <v>0.0105024421106325</v>
       </c>
       <c r="AY5" t="n">
         <v>0.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.4590909090909091</v>
+        <v>0.3081232492997199</v>
       </c>
       <c r="BA5" t="n">
-        <v>101</v>
+        <v>0.1011904761904816</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.268831168831169</v>
+        <v>0.4715277777777778</v>
       </c>
       <c r="BC5" t="n">
-        <v>39916883.11688311</v>
+        <v>7966388.888888888</v>
       </c>
       <c r="BD5" t="n">
-        <v>74809.82113759984</v>
+        <v>-0.05451388888888431</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.40959919180743</v>
+        <v>-0.9882385373017541</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.152969230290253</v>
+        <v>-1.594097222222246</v>
       </c>
       <c r="BG5" t="n">
-        <v>101803.8961038961</v>
+        <v>7508226.668306904</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.788311688311694</v>
+        <v>32125</v>
       </c>
       <c r="BI5" t="n">
-        <v>107</v>
+        <v>4.392012837943895</v>
       </c>
       <c r="BJ5" t="n">
-        <v>83100000</v>
+        <v>-139.0357142857143</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>3.429861111111109</v>
       </c>
       <c r="BL5" t="n">
-        <v>262000</v>
+        <v>-2.017857142857143</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.666666666666668</v>
+        <v>-131.4464285714286</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.737254446726496</v>
+        <v>3.13611111111112</v>
       </c>
       <c r="BO5" t="n">
-        <v>4</v>
+        <v>0.3987567793095539</v>
       </c>
       <c r="BP5" t="n">
-        <v>-1.833333333333343</v>
+        <v>-1.946428571428572</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11.17513544172584</v>
+        <v>0.6443452380952408</v>
       </c>
       <c r="BR5" t="n">
-        <v>3.344155844155836</v>
+        <v>27050</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.4012987012987139</v>
+        <v>-0.6212777580447764</v>
       </c>
       <c r="BT5" t="n">
-        <v>23259581.29158354</v>
+        <v>9985357.142857142</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.547761705803552</v>
+        <v>4.248300806506606</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.5</v>
+        <v>32831.93550228376</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.58333333334</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1716,209 +1730,213 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009999999999999565</v>
+        <v>2.0185</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1977894736842103</v>
+        <v>1.568888888888889</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.313131313131314</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>10.95454545454545</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.146464646464646</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>18.05365701549912</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>17.69606419501039</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>775.8598167929163</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>711.5179669833035</v>
+      </c>
+      <c r="AE6" t="n">
         <v>-1</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.9999999999999982</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.1500000000000001</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23.54662698412698</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>20.39891608994434</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>998.7511799695037</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>952.3818777455485</v>
-      </c>
-      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>-1.764705882352956</v>
-      </c>
-      <c r="AG6" t="inlineStr"/>
+        <v>59.92222222222223</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-9</v>
+      </c>
       <c r="AH6" t="n">
-        <v>1.529411764705884</v>
+        <v>53.33333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.3333333333333393</v>
+        <v>14.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-4.350000000000001</v>
+        <v>14.52020202020202</v>
       </c>
       <c r="AK6" t="n">
-        <v>-26</v>
+        <v>24.59999999999999</v>
       </c>
       <c r="AL6" t="n">
-        <v>-23.39999999999999</v>
+        <v>35.22222222222223</v>
       </c>
       <c r="AM6" t="n">
-        <v>-290.6666666666667</v>
+        <v>247.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>-232.9499999999999</v>
+        <v>298.9242424242425</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.8421052631578949</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.916666666666667</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>0.2666666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AS6" t="n">
-        <v>-2.000000000000002</v>
+        <v>-6.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.549999999999999</v>
+        <v>-0.4090909090909083</v>
       </c>
       <c r="AU6" t="n">
-        <v>19.33100062247121</v>
+        <v>0.2936373400421459</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.66602512023731</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+        <v>-17.13664205801063</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.02004345783415551</v>
+      </c>
       <c r="AX6" t="n">
-        <v>0.01092315120147441</v>
+        <v>0.02545740079368261</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.15</v>
+        <v>0.4393939393939393</v>
       </c>
       <c r="BA6" t="n">
-        <v>278</v>
+        <v>-3.891666666666666</v>
       </c>
       <c r="BB6" t="n">
-        <v>-1.352777777777778</v>
+        <v>0.7670454545454546</v>
       </c>
       <c r="BC6" t="n">
-        <v>-17392817.46031746</v>
+        <v>16258498.17620651</v>
       </c>
       <c r="BD6" t="n">
-        <v>-24247.12525361021</v>
+        <v>0.4229938271604929</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.8321204797708559</v>
+        <v>1.873100277410003</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.6751596252536132</v>
+        <v>-0.01042368125706616</v>
       </c>
       <c r="BG6" t="n">
-        <v>-28235.71428571428</v>
+        <v>9706274.149888515</v>
       </c>
       <c r="BH6" t="n">
-        <v>-3.963492063492083</v>
+        <v>92875</v>
       </c>
       <c r="BI6" t="n">
-        <v>257</v>
+        <v>3.792933672748703</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-17170000</v>
+        <v>64.25</v>
       </c>
       <c r="BK6" t="n">
-        <v>4</v>
+        <v>6.688482042648701</v>
       </c>
       <c r="BL6" t="n">
-        <v>-71000</v>
+        <v>0.625</v>
       </c>
       <c r="BM6" t="n">
-        <v>-2.166666666666668</v>
+        <v>52.875</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.363226518677664</v>
+        <v>6.74339225589226</v>
       </c>
       <c r="BO6" t="n">
-        <v>2</v>
+        <v>0.5991299890041311</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.833333333333343</v>
+        <v>0.75</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-5.112027091538351</v>
+        <v>9.631249999999994</v>
       </c>
       <c r="BR6" t="n">
-        <v>-1.431746031746034</v>
+        <v>42714.74466891133</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.048809523809496</v>
+        <v>-0.7431934166773999</v>
       </c>
       <c r="BT6" t="n">
-        <v>-14776775.88316028</v>
+        <v>39050000</v>
       </c>
       <c r="BU6" t="n">
-        <v>-5.309590941639826</v>
+        <v>5.12598410185177</v>
       </c>
       <c r="BV6" t="n">
-        <v>-5.773809523809518</v>
+        <v>27045.34410062633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1940,7 +1958,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>243</v>
       </c>
       <c r="M7" t="n">
         <v>23</v>
@@ -1949,204 +1967,200 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9408333333333333</v>
+        <v>1.065</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3749411764705884</v>
+        <v>1.080861244019139</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7657894736842105</v>
+        <v>1.543062200956938</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.25</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7605263157894733</v>
+        <v>3.861244019138756</v>
       </c>
       <c r="U7" t="n">
-        <v>-9.25</v>
+        <v>14.75</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.694736842105264</v>
+        <v>9.45933014354067</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.75</v>
+        <v>0.75</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7315789473684212</v>
+        <v>1.413875598086124</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.397368421052632</v>
+        <v>1.995215311004785</v>
       </c>
       <c r="AA7" t="n">
-        <v>24.13436355311355</v>
+        <v>14.84787561576355</v>
       </c>
       <c r="AB7" t="n">
-        <v>20.95643653474149</v>
+        <v>16.45190579944482</v>
       </c>
       <c r="AC7" t="n">
-        <v>932.5615502279272</v>
+        <v>760.5645416822183</v>
       </c>
       <c r="AD7" t="n">
-        <v>862.1901580581193</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>9</v>
-      </c>
+        <v>877.9109824474808</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>-17.47058823529412</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>7.5</v>
-      </c>
+        <v>6.088888888888889</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>-13.23529411764706</v>
+        <v>16.24444444444444</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.25</v>
+        <v>5.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-5.923684210526311</v>
+        <v>4.516746411483254</v>
       </c>
       <c r="AK7" t="n">
-        <v>-22</v>
+        <v>39</v>
       </c>
       <c r="AL7" t="n">
-        <v>-15.01052631578948</v>
+        <v>3.555023923444978</v>
       </c>
       <c r="AM7" t="n">
-        <v>-197</v>
+        <v>379.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>-116.5394736842105</v>
+        <v>26.49760765550235</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1.026315789473684</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
+        <v>-0.04040404040404066</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
       <c r="AR7" t="n">
-        <v>-0.1333333333333332</v>
+        <v>0.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>-1.5</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.2105263157894743</v>
+        <v>2.12200956937799</v>
       </c>
       <c r="AU7" t="n">
-        <v>10.67537081380802</v>
+        <v>-30.27642179502794</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.038952222718773</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.0003989248422697246</v>
-      </c>
+        <v>-7.323631888893029</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-0.0509782342229597</v>
+        <v>-0.02175734009148228</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3657894736842106</v>
+        <v>0.5215311004784688</v>
       </c>
       <c r="BA7" t="n">
-        <v>165</v>
+        <v>4.629166666666663</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.3948412698412698</v>
+        <v>0.9900793650793651</v>
       </c>
       <c r="BC7" t="n">
-        <v>-4079960.317460317</v>
+        <v>21760515.87301587</v>
       </c>
       <c r="BD7" t="n">
-        <v>-13878.11940452304</v>
+        <v>-1.561011904761905</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.3622379173621411</v>
+        <v>-0.7433702506070858</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1218655511336912</v>
+        <v>-1.023313492063465</v>
       </c>
       <c r="BG7" t="n">
-        <v>-2787.698412698417</v>
+        <v>11473003.2755581</v>
       </c>
       <c r="BH7" t="n">
-        <v>-2.92063492063491</v>
+        <v>340000</v>
       </c>
       <c r="BI7" t="n">
-        <v>146</v>
+        <v>6.738999487354747</v>
       </c>
       <c r="BJ7" t="n">
-        <v>25900000</v>
+        <v>64.875</v>
       </c>
       <c r="BK7" t="n">
-        <v>2</v>
+        <v>6.004960317460316</v>
       </c>
       <c r="BL7" t="n">
-        <v>79000</v>
+        <v>0.75</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.3333333333333321</v>
+        <v>85.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.807917185652968</v>
+        <v>5.504464285714292</v>
       </c>
       <c r="BO7" t="n">
-        <v>3</v>
+        <v>0.4953282828282828</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.2666666666666515</v>
+        <v>7.875</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-5.608334709041642</v>
+        <v>2.345833333333331</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.488095238095237</v>
+        <v>59973.71031746032</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.684523809523796</v>
+        <v>0.6555253429156878</v>
       </c>
       <c r="BT7" t="n">
-        <v>-6523494.159751971</v>
+        <v>86625000</v>
       </c>
       <c r="BU7" t="n">
-        <v>-4.322348018568206</v>
+        <v>5.288964613197066</v>
       </c>
       <c r="BV7" t="n">
-        <v>-1.599206349206355</v>
+        <v>48158.11625427853</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.35416666666</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -2168,209 +2182,207 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="M8" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5150000000000001</v>
+        <v>-1.155</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5691818181818182</v>
+        <v>-0.4602476780185751</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8999999999999999</v>
+        <v>-0.7731092436974787</v>
       </c>
       <c r="S8" t="n">
-        <v>0.75</v>
+        <v>-5.066666666666666</v>
       </c>
       <c r="T8" t="n">
-        <v>2.858333333333333</v>
+        <v>-0.403361344537815</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.25</v>
+        <v>1.666666666666664</v>
       </c>
       <c r="V8" t="n">
-        <v>9.116666666666667</v>
+        <v>0.7450980392156872</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>-1.533333333333333</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2333333333333336</v>
+        <v>-0.3781512605042019</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6000000000000001</v>
+        <v>-0.3865546218487395</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.53554292929293</v>
+        <v>22.0072496947497</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.86883533132916</v>
+        <v>21.12045655313997</v>
       </c>
       <c r="AC8" t="n">
-        <v>940.5579626361576</v>
+        <v>857.4779994033482</v>
       </c>
       <c r="AD8" t="n">
-        <v>797.0776327537845</v>
+        <v>922.6351566888964</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>41.34999999999999</v>
+        <v>-26.00793650793651</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>26.9111111111111</v>
+        <v>-11.95238095238095</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18.575</v>
+        <v>-0.2016806722689068</v>
       </c>
       <c r="AK8" t="n">
-        <v>-12</v>
+        <v>-8.933333333333323</v>
       </c>
       <c r="AL8" t="n">
-        <v>18.76666666666667</v>
+        <v>-29.72549019607844</v>
       </c>
       <c r="AM8" t="n">
-        <v>-104</v>
+        <v>-82.26666666666671</v>
       </c>
       <c r="AN8" t="n">
-        <v>183.7333333333333</v>
+        <v>-256.7619047619048</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.25</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.9826086956521745</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.6442577030812326</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>1</v>
+        <v>0.2000000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.75</v>
+        <v>3.133333333333333</v>
       </c>
       <c r="AT8" t="n">
-        <v>-2.050000000000001</v>
+        <v>1.252100840336134</v>
       </c>
       <c r="AU8" t="n">
-        <v>-4.750629880303205</v>
+        <v>-10.29283998066457</v>
       </c>
       <c r="AV8" t="n">
-        <v>-9.086631677015024</v>
+        <v>12.32906625244443</v>
       </c>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>0.02583481406120761</v>
+        <v>-0.02606482078087154</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.25</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.04999999999999999</v>
+        <v>-0.2717086834733893</v>
       </c>
       <c r="BA8" t="n">
-        <v>-7</v>
+        <v>0.06666666666666998</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.200974025974026</v>
+        <v>-1.548340548340548</v>
       </c>
       <c r="BC8" t="n">
-        <v>4552128.878066376</v>
+        <v>-38347085.13708514</v>
       </c>
       <c r="BD8" t="n">
-        <v>47073.76500787542</v>
+        <v>0.4187590187590189</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.1147327162957272</v>
+        <v>-1.255718273612842</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.425422693520932</v>
+        <v>-1.028968253968316</v>
       </c>
       <c r="BG8" t="n">
-        <v>45393.38023088023</v>
+        <v>-24776728.25297444</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.2390692640692578</v>
+        <v>-434285.7142857143</v>
       </c>
       <c r="BI8" t="n">
-        <v>14</v>
+        <v>-6.802558449443552</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-3300000</v>
+        <v>-140.8571428571428</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>-9.039321789321775</v>
       </c>
       <c r="BL8" t="n">
-        <v>216000</v>
+        <v>-1.428571428571428</v>
       </c>
       <c r="BM8" t="n">
-        <v>8</v>
+        <v>-136.7142857142858</v>
       </c>
       <c r="BN8" t="n">
-        <v>-3.142375967445446</v>
+        <v>-9.465656565656573</v>
       </c>
       <c r="BO8" t="n">
-        <v>3</v>
+        <v>-0.8848258022171065</v>
       </c>
       <c r="BP8" t="n">
-        <v>-17</v>
+        <v>-6.285714285714286</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.708382003380365</v>
+        <v>2.473809523809535</v>
       </c>
       <c r="BR8" t="n">
-        <v>1.056944444444444</v>
+        <v>-114863.5642135642</v>
       </c>
       <c r="BS8" t="n">
-        <v>-1.942555014430042</v>
+        <v>2.400119536123373</v>
       </c>
       <c r="BT8" t="n">
-        <v>4661196.040977068</v>
+        <v>-112025000</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0.3955360710264415</v>
+        <v>-8.101394411621584</v>
       </c>
       <c r="BV8" t="n">
-        <v>1.19415584415583</v>
+        <v>-90515.85861345063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45598.69791666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
@@ -2392,209 +2404,209 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.14</v>
+        <v>1.309166666666667</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.160216718266254</v>
+        <v>0.4315497076023391</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.882352941176471</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.699999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.787114845938376</v>
+        <v>-0.08479532163742665</v>
       </c>
       <c r="U9" t="n">
-        <v>-7.300000000000001</v>
+        <v>2.916666666666666</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.952380952380953</v>
+        <v>0.6432748538011701</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5098039215686274</v>
+        <v>0.4590643274853803</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.7815126050420167</v>
+        <v>0.8596491228070178</v>
       </c>
       <c r="AA9" t="n">
-        <v>24.67018218623482</v>
+        <v>23.828619053948</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.20017909774199</v>
+        <v>23.33048135199737</v>
       </c>
       <c r="AC9" t="n">
-        <v>945.9570629807968</v>
+        <v>763.1555004877468</v>
       </c>
       <c r="AD9" t="n">
-        <v>895.0266095738368</v>
+        <v>816.7093682547279</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>-20.15686274509804</v>
+        <v>9.73333333333332</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>-9.839215686274514</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.700000000000003</v>
+        <v>8.583333333333329</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5210084033613427</v>
+        <v>-1.497076023391813</v>
       </c>
       <c r="AK9" t="n">
-        <v>-15.59999999999999</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="AL9" t="n">
-        <v>-9.966386554621849</v>
+        <v>9.315789473684205</v>
       </c>
       <c r="AM9" t="n">
-        <v>-139.7</v>
+        <v>142.6666666666666</v>
       </c>
       <c r="AN9" t="n">
-        <v>-81.93557422969189</v>
+        <v>83.9736842105263</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.4</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.3445378151260501</v>
+        <v>-0.131578947368421</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1.5</v>
+        <v>1.666666666666668</v>
       </c>
       <c r="AT9" t="n">
-        <v>-1.605042016806722</v>
+        <v>0.6140350877193015</v>
       </c>
       <c r="AU9" t="n">
-        <v>-1.020932474056391</v>
+        <v>-6.035355657414485</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.73147562431831</v>
+        <v>-4.247109940296767</v>
       </c>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>-0.01253768202839931</v>
+        <v>-0.02159095192671039</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.07002801120448181</v>
+        <v>0.06140350877192985</v>
       </c>
       <c r="BA9" t="n">
-        <v>126</v>
+        <v>0.96875</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1.429545454545454</v>
+        <v>0.04886363636363633</v>
       </c>
       <c r="BC9" t="n">
-        <v>-36674318.18181819</v>
+        <v>-2766874.210858585</v>
       </c>
       <c r="BD9" t="n">
-        <v>-72294.10724696176</v>
+        <v>1.900347222222226</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.5442162896947356</v>
+        <v>-0.5349000068708847</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.655043311530974</v>
+        <v>-1.186174242424244</v>
       </c>
       <c r="BG9" t="n">
-        <v>-110447.8535353535</v>
+        <v>-512178.6814933629</v>
       </c>
       <c r="BH9" t="n">
-        <v>-8.06805555555556</v>
+        <v>-54500</v>
       </c>
       <c r="BI9" t="n">
-        <v>125</v>
+        <v>0.2844038111858396</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-74700000</v>
+        <v>-96</v>
       </c>
       <c r="BK9" t="n">
-        <v>2</v>
+        <v>-3.28573232323231</v>
       </c>
       <c r="BL9" t="n">
-        <v>-345000</v>
+        <v>-1.125</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.628571428571426</v>
+        <v>-90.125</v>
       </c>
       <c r="BN9" t="n">
-        <v>-1.034163294514428</v>
+        <v>-2.140751262626253</v>
       </c>
       <c r="BO9" t="n">
-        <v>-1</v>
+        <v>0.02856511337632606</v>
       </c>
       <c r="BP9" t="n">
-        <v>-1.028571428571411</v>
+        <v>-0.875</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-5.287151885585814</v>
+        <v>-5.729166666666657</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.428409090909085</v>
+        <v>-15131.47095959596</v>
       </c>
       <c r="BS9" t="n">
-        <v>-2.423358585858665</v>
+        <v>2.197000838702785</v>
       </c>
       <c r="BT9" t="n">
-        <v>-20456305.0826763</v>
+        <v>-9025000</v>
       </c>
       <c r="BU9" t="n">
-        <v>-6.572838770575686</v>
+        <v>-0.4954443196963325</v>
       </c>
       <c r="BV9" t="n">
-        <v>-9.038131313131316</v>
+        <v>-8876.576005251636</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45598.58333333334</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C10" t="n">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="E10" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
@@ -2616,213 +2628,213 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="M10" t="n">
-        <v>196</v>
+        <v>148</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7566666666666666</v>
+        <v>0.8899999999999998</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6826315789473688</v>
+        <v>0.6546078431372547</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.75</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.030075187969925</v>
+        <v>0.9473684210526319</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2807017543859649</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.166666666666666</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5789473684210531</v>
+        <v>7.94736842105263</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-2.25</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1403508771929824</v>
+        <v>-0.736842105263158</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.3308270676691731</v>
+        <v>0.1578947368421051</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.66969881969882</v>
+        <v>17.27866771708683</v>
       </c>
       <c r="AB10" t="n">
-        <v>20.37929665260521</v>
+        <v>17.65287590391672</v>
       </c>
       <c r="AC10" t="n">
-        <v>1026.144520514626</v>
+        <v>757.5685879164397</v>
       </c>
       <c r="AD10" t="n">
-        <v>922.8276289340251</v>
+        <v>786.8172503290782</v>
       </c>
       <c r="AE10" t="n">
-        <v>-62</v>
+        <v>64</v>
       </c>
       <c r="AF10" t="n">
-        <v>-18.1764705882353</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>-22</v>
+        <v>57</v>
       </c>
       <c r="AH10" t="n">
-        <v>-7.411764705882348</v>
+        <v>24.875</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.666666666666664</v>
+        <v>25.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-2.032581453634087</v>
+        <v>11.10526315789475</v>
       </c>
       <c r="AK10" t="n">
-        <v>-16.33333333333333</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>-14.56641604010025</v>
+        <v>4.842105263157904</v>
       </c>
       <c r="AM10" t="n">
-        <v>-205.9999999999999</v>
+        <v>131.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>-143.0447368421052</v>
+        <v>29.78947368421052</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.08333333333333348</v>
+        <v>-2.25</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.372222222222222</v>
+        <v>-1.789473684210526</v>
       </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>1</v>
+        <v>0.1333333333333332</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.5000000000000018</v>
+        <v>-5.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.4411027568922279</v>
+        <v>-0.4210526315789451</v>
       </c>
       <c r="AU10" t="n">
-        <v>13.35254469262621</v>
+        <v>0.1694931196983092</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.20372464988834</v>
+        <v>-0.6575616268584454</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.06989348370927317</v>
+        <v>0.1210699023199023</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.02665378246553048</v>
+        <v>0.04336511095442891</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.08521303258145363</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-25</v>
+        <v>-1.525595238095242</v>
       </c>
       <c r="BB10" t="n">
-        <v>-1.125</v>
+        <v>-0.01136363636363624</v>
       </c>
       <c r="BC10" t="n">
-        <v>-27229418.40277778</v>
+        <v>2897864.357864358</v>
       </c>
       <c r="BD10" t="n">
-        <v>-63154.22813662943</v>
+        <v>0.6568181818181813</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.5450937950937951</v>
+        <v>-2.541641222438301</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.611377401837931</v>
+        <v>-1.679707792207779</v>
       </c>
       <c r="BG10" t="n">
-        <v>-81442.01388888889</v>
+        <v>249516.1717702746</v>
       </c>
       <c r="BH10" t="n">
-        <v>-8.279513888888886</v>
+        <v>-31875</v>
       </c>
       <c r="BI10" t="n">
-        <v>-35</v>
+        <v>0.7397192144314886</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-129700000</v>
+        <v>-65.875</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>2.936165223665213</v>
       </c>
       <c r="BL10" t="n">
-        <v>-417000</v>
+        <v>-1</v>
       </c>
       <c r="BM10" t="n">
-        <v>-1.5</v>
+        <v>-86.125</v>
       </c>
       <c r="BN10" t="n">
-        <v>-0.7753363047771415</v>
+        <v>2.873701298701292</v>
       </c>
       <c r="BO10" t="n">
-        <v>-7</v>
+        <v>-0.06618026364403184</v>
       </c>
       <c r="BP10" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-6.740051952798666</v>
+        <v>-5.723511904761949</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.9444444444444429</v>
+        <v>-9881.457431457431</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.584027777777806</v>
+        <v>0.6741084627380438</v>
       </c>
       <c r="BT10" t="n">
-        <v>-14439335.6348969</v>
+        <v>-6296875</v>
       </c>
       <c r="BU10" t="n">
-        <v>-7.176352101845524</v>
+        <v>0.7792009476898727</v>
       </c>
       <c r="BV10" t="n">
-        <v>-7.970833333333331</v>
+        <v>-12369.96120216495</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45598.45833333334</v>
+        <v>45603.69791666666</v>
       </c>
       <c r="C11" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
@@ -2844,187 +2856,171 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="M11" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4850000000000001</v>
+        <v>-0.5549999999999997</v>
       </c>
       <c r="P11" t="n">
-        <v>1.041393188854489</v>
+        <v>-0.5047368421052629</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.75</v>
+        <v>-1.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.356037151702786</v>
+        <v>-0.5785714285714284</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="T11" t="n">
-        <v>2.399380804953561</v>
+        <v>-0.6261904761904762</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.75</v>
+        <v>-6.549999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>7.195046439628483</v>
+        <v>-3.726190476190476</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>-0.25</v>
       </c>
       <c r="X11" t="n">
-        <v>1.894736842105263</v>
+        <v>0.1047619047619046</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>-0.3000000000000003</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.656346749226007</v>
+        <v>0.1571428571428573</v>
       </c>
       <c r="AA11" t="n">
-        <v>29.90227732793522</v>
+        <v>23.13213744588744</v>
       </c>
       <c r="AB11" t="n">
-        <v>19.83026101439534</v>
+        <v>22.31460960683705</v>
       </c>
       <c r="AC11" t="n">
-        <v>702.5576777819356</v>
+        <v>1038.220342264347</v>
       </c>
       <c r="AD11" t="n">
-        <v>667.1076837574665</v>
+        <v>878.5164106126172</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>54.37916666666666</v>
+        <v>-11.89583333333333</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>35.38333333333333</v>
+        <v>-8.791666666666671</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.75</v>
+        <v>-4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14.9876160990712</v>
+        <v>-3.338095238095242</v>
       </c>
       <c r="AK11" t="n">
-        <v>22.5</v>
+        <v>-39.2</v>
       </c>
       <c r="AL11" t="n">
-        <v>41.07739938080495</v>
+        <v>-14.49523809523811</v>
       </c>
       <c r="AM11" t="n">
-        <v>201.75</v>
+        <v>-355.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>383.6934984520124</v>
+        <v>-132.5500000000001</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.25</v>
+        <v>-0.04999999999999982</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1.908496732026144</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1</v>
-      </c>
+        <v>-0.9190476190476189</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>0.1333333333333334</v>
+        <v>-2</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.5</v>
+        <v>1.949999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>-1.439628482972136</v>
+        <v>-3.897619047619049</v>
       </c>
       <c r="AU11" t="n">
-        <v>-5.818180074991556</v>
+        <v>23.32209273209233</v>
       </c>
       <c r="AV11" t="n">
-        <v>-21.90047792883748</v>
+        <v>14.70635463554281</v>
       </c>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>-0.007111520590148468</v>
+        <v>-0.01960614388159125</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.75</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.7739938080495355</v>
+        <v>0.15</v>
       </c>
       <c r="BA11" t="n">
-        <v>86</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.4688552188552191</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4390677.609427609</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>29347.70135590468</v>
-      </c>
+        <v>-1.375</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="n">
-        <v>0.2138595583160801</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-0.9418695576056564</v>
-      </c>
+        <v>3.750050402265714</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
-        <v>34313.97306397306</v>
+        <v>-2412054.686712421</v>
       </c>
       <c r="BH11" t="n">
-        <v>1.58522727272728</v>
+        <v>235000</v>
       </c>
       <c r="BI11" t="n">
-        <v>113</v>
+        <v>-5.334523009906633</v>
       </c>
       <c r="BJ11" t="n">
-        <v>42475000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="n">
-        <v>233000</v>
+        <v>6</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.142857142857142</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>3.729328111679422</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>-0.2161152045359207</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.738095238095241</v>
+        <v>9</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.284154322961058</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>0.6122474747474698</v>
-      </c>
+        <v>-4</v>
+      </c>
+      <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="n">
-        <v>2.434427609427587</v>
+        <v>-3.424845559042797</v>
       </c>
       <c r="BT11" t="n">
-        <v>4854889.647842834</v>
+        <v>32250000</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.725657616307373</v>
+        <v>-1.573122718460752</v>
       </c>
       <c r="BV11" t="n">
-        <v>2.992340067340066</v>
+        <v>4578.795913969218</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -690,112 +690,112 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
     </row>
@@ -955,70 +955,70 @@
         <v>0.7166666666666667</v>
       </c>
       <c r="BA2" t="n">
+        <v>-1.941722783389423</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>763.3904662341956</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2.93603674123078</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.387373737373737</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>9722.558922558936</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1.152892707643371</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.289225589225591</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.7089929165849265</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>3.338816331350671</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>4.286812570145898</v>
+      </c>
+      <c r="BM2" t="n">
         <v>-4.604166666666671</v>
       </c>
-      <c r="BB2" t="n">
-        <v>1.387373737373737</v>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BN2" t="n">
         <v>18900659.37149271</v>
       </c>
-      <c r="BD2" t="n">
-        <v>1.289225589225591</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BO2" t="n">
+        <v>22437500</v>
+      </c>
+      <c r="BP2" t="n">
         <v>3.32362454205753</v>
       </c>
-      <c r="BF2" t="n">
-        <v>-1.941722783389423</v>
-      </c>
-      <c r="BG2" t="n">
+      <c r="BQ2" t="n">
         <v>9887342.949404109</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BR2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BS2" t="n">
         <v>-2500</v>
       </c>
-      <c r="BI2" t="n">
-        <v>3.338816331350671</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BK2" t="n">
+      <c r="BT2" t="n">
         <v>3.395679012345667</v>
       </c>
-      <c r="BL2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BM2" t="n">
+      <c r="BU2" t="n">
+        <v>7.895833333333371</v>
+      </c>
+      <c r="BV2" t="n">
         <v>18.625</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.286812570145898</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.7089929165849265</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7.895833333333371</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>9722.558922558936</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1.152892707643371</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>22437500</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>2.93603674123078</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>763.3904662341956</v>
       </c>
     </row>
     <row r="3">
@@ -1179,70 +1179,70 @@
         <v>0.05000000000000002</v>
       </c>
       <c r="BA3" t="n">
+        <v>1.595187991021305</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-4664.495765946158</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-3.216018783695205</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-0.6440235690235692</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-22794.41638608306</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.3713890961176141</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-0.43124298540965</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-0.3505211916031004</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-3.793188136816582</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>-6.307687991021339</v>
+      </c>
+      <c r="BM3" t="n">
         <v>-0.01458333333333428</v>
       </c>
-      <c r="BB3" t="n">
-        <v>-0.6440235690235692</v>
-      </c>
-      <c r="BC3" t="n">
+      <c r="BN3" t="n">
         <v>-15123539.21156004</v>
       </c>
-      <c r="BD3" t="n">
-        <v>-0.43124298540965</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="BO3" t="n">
+        <v>-13050000</v>
+      </c>
+      <c r="BP3" t="n">
         <v>-0.5405410588119537</v>
       </c>
-      <c r="BF3" t="n">
-        <v>1.595187991021305</v>
-      </c>
-      <c r="BG3" t="n">
+      <c r="BQ3" t="n">
         <v>-4414738.05619707</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BR3" t="n">
+        <v>227.375</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10875</v>
       </c>
-      <c r="BI3" t="n">
-        <v>-3.793188136816582</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>227.375</v>
-      </c>
-      <c r="BK3" t="n">
+      <c r="BT3" t="n">
         <v>-5.384862514029194</v>
       </c>
-      <c r="BL3" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="BM3" t="n">
+      <c r="BU3" t="n">
+        <v>3.564583333333303</v>
+      </c>
+      <c r="BV3" t="n">
         <v>218.25</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>-6.307687991021339</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-0.3505211916031004</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>3.564583333333303</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>-22794.41638608306</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>-0.3713890961176141</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>-13050000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>-3.216018783695205</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>-4664.495765946158</v>
       </c>
     </row>
     <row r="4">
@@ -1399,70 +1399,70 @@
         <v>0.3657894736842105</v>
       </c>
       <c r="BA4" t="n">
+        <v>-4.439826839826821</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-3.285714285714286</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-4522.525224811514</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.926641934805957</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.9239177489177492</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-6027.849927849937</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1.34412972130119</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.1168831168831161</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.7183114813431091</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3.032553303548738</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>2.377994227994222</v>
+      </c>
+      <c r="BM4" t="n">
         <v>1.97891156462585</v>
       </c>
-      <c r="BB4" t="n">
-        <v>0.9239177489177492</v>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BN4" t="n">
         <v>11862673.16017316</v>
       </c>
-      <c r="BD4" t="n">
-        <v>0.1168831168831161</v>
-      </c>
-      <c r="BE4" t="n">
+      <c r="BO4" t="n">
+        <v>-5842857.142857142</v>
+      </c>
+      <c r="BP4" t="n">
         <v>-6.14971809051616</v>
       </c>
-      <c r="BF4" t="n">
-        <v>-4.439826839826821</v>
-      </c>
-      <c r="BG4" t="n">
+      <c r="BQ4" t="n">
         <v>11494271.64248613</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BR4" t="n">
+        <v>-253</v>
+      </c>
+      <c r="BS4" t="n">
         <v>-83857.14285714286</v>
       </c>
-      <c r="BI4" t="n">
-        <v>3.032553303548738</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-253</v>
-      </c>
-      <c r="BK4" t="n">
+      <c r="BT4" t="n">
         <v>2.005122655122676</v>
       </c>
-      <c r="BL4" t="n">
-        <v>-3.285714285714286</v>
-      </c>
-      <c r="BM4" t="n">
+      <c r="BU4" t="n">
+        <v>-3.975510204081644</v>
+      </c>
+      <c r="BV4" t="n">
         <v>-235.5714285714286</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>2.377994227994222</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.7183114813431091</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-2.285714285714286</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-3.975510204081644</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>-6027.849927849937</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.34412972130119</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>-5842857.142857142</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1.926641934805957</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>-4522.525224811514</v>
       </c>
     </row>
     <row r="5">
@@ -1623,70 +1623,70 @@
         <v>0.3081232492997199</v>
       </c>
       <c r="BA5" t="n">
+        <v>-1.594097222222246</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-2.017857142857143</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>32831.93550228376</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-1.946428571428572</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.248300806506606</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.4715277777777778</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>27050</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.6212777580447764</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.05451388888888431</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.3987567793095539</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.392012837943895</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>3.13611111111112</v>
+      </c>
+      <c r="BM5" t="n">
         <v>0.1011904761904816</v>
       </c>
-      <c r="BB5" t="n">
-        <v>0.4715277777777778</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BN5" t="n">
         <v>7966388.888888888</v>
       </c>
-      <c r="BD5" t="n">
-        <v>-0.05451388888888431</v>
-      </c>
-      <c r="BE5" t="n">
+      <c r="BO5" t="n">
+        <v>9985357.142857142</v>
+      </c>
+      <c r="BP5" t="n">
         <v>-0.9882385373017541</v>
       </c>
-      <c r="BF5" t="n">
-        <v>-1.594097222222246</v>
-      </c>
-      <c r="BG5" t="n">
+      <c r="BQ5" t="n">
         <v>7508226.668306904</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BR5" t="n">
+        <v>-139.0357142857143</v>
+      </c>
+      <c r="BS5" t="n">
         <v>32125</v>
       </c>
-      <c r="BI5" t="n">
-        <v>4.392012837943895</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-139.0357142857143</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BT5" t="n">
         <v>3.429861111111109</v>
       </c>
-      <c r="BL5" t="n">
-        <v>-2.017857142857143</v>
-      </c>
-      <c r="BM5" t="n">
+      <c r="BU5" t="n">
+        <v>0.6443452380952408</v>
+      </c>
+      <c r="BV5" t="n">
         <v>-131.4464285714286</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>3.13611111111112</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.3987567793095539</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>-1.946428571428572</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.6443452380952408</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>27050</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>-0.6212777580447764</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>9985357.142857142</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.248300806506606</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>32831.93550228376</v>
       </c>
     </row>
     <row r="6">
@@ -1851,70 +1851,70 @@
         <v>0.4393939393939393</v>
       </c>
       <c r="BA6" t="n">
+        <v>-0.01042368125706616</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>27045.34410062633</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.12598410185177</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.7670454545454546</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>42714.74466891133</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.7431934166773999</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.4229938271604929</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.5991299890041311</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>3.792933672748703</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>6.74339225589226</v>
+      </c>
+      <c r="BM6" t="n">
         <v>-3.891666666666666</v>
       </c>
-      <c r="BB6" t="n">
-        <v>0.7670454545454546</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BN6" t="n">
         <v>16258498.17620651</v>
       </c>
-      <c r="BD6" t="n">
-        <v>0.4229938271604929</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BO6" t="n">
+        <v>39050000</v>
+      </c>
+      <c r="BP6" t="n">
         <v>1.873100277410003</v>
       </c>
-      <c r="BF6" t="n">
-        <v>-0.01042368125706616</v>
-      </c>
-      <c r="BG6" t="n">
+      <c r="BQ6" t="n">
         <v>9706274.149888515</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BR6" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="BS6" t="n">
         <v>92875</v>
       </c>
-      <c r="BI6" t="n">
-        <v>3.792933672748703</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="BK6" t="n">
+      <c r="BT6" t="n">
         <v>6.688482042648701</v>
       </c>
-      <c r="BL6" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BU6" t="n">
+        <v>9.631249999999994</v>
+      </c>
+      <c r="BV6" t="n">
         <v>52.875</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6.74339225589226</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.5991299890041311</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>9.631249999999994</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>42714.74466891133</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-0.7431934166773999</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>39050000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.12598410185177</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>27045.34410062633</v>
       </c>
     </row>
     <row r="7">
@@ -2075,70 +2075,70 @@
         <v>0.5215311004784688</v>
       </c>
       <c r="BA7" t="n">
+        <v>-1.023313492063465</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>48158.11625427853</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.288964613197066</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.9900793650793651</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>59973.71031746032</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.6555253429156878</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-1.561011904761905</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.4953282828282828</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.738999487354747</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>5.504464285714292</v>
+      </c>
+      <c r="BM7" t="n">
         <v>4.629166666666663</v>
       </c>
-      <c r="BB7" t="n">
-        <v>0.9900793650793651</v>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BN7" t="n">
         <v>21760515.87301587</v>
       </c>
-      <c r="BD7" t="n">
-        <v>-1.561011904761905</v>
-      </c>
-      <c r="BE7" t="n">
+      <c r="BO7" t="n">
+        <v>86625000</v>
+      </c>
+      <c r="BP7" t="n">
         <v>-0.7433702506070858</v>
       </c>
-      <c r="BF7" t="n">
-        <v>-1.023313492063465</v>
-      </c>
-      <c r="BG7" t="n">
+      <c r="BQ7" t="n">
         <v>11473003.2755581</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BR7" t="n">
+        <v>64.875</v>
+      </c>
+      <c r="BS7" t="n">
         <v>340000</v>
       </c>
-      <c r="BI7" t="n">
-        <v>6.738999487354747</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>64.875</v>
-      </c>
-      <c r="BK7" t="n">
+      <c r="BT7" t="n">
         <v>6.004960317460316</v>
       </c>
-      <c r="BL7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM7" t="n">
+      <c r="BU7" t="n">
+        <v>2.345833333333331</v>
+      </c>
+      <c r="BV7" t="n">
         <v>85.75</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.504464285714292</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.4953282828282828</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>7.875</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>2.345833333333331</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>59973.71031746032</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.6555253429156878</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>86625000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.288964613197066</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>48158.11625427853</v>
       </c>
     </row>
     <row r="8">
@@ -2297,70 +2297,70 @@
         <v>-0.2717086834733893</v>
       </c>
       <c r="BA8" t="n">
+        <v>-1.028968253968316</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.428571428571428</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-90515.85861345063</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-6.285714285714286</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-8.101394411621584</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-1.548340548340548</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-114863.5642135642</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.400119536123377</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.4187590187590189</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0.8848258022171065</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-6.802558449443552</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-9.465656565656573</v>
+      </c>
+      <c r="BM8" t="n">
         <v>0.06666666666666998</v>
       </c>
-      <c r="BB8" t="n">
-        <v>-1.548340548340548</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BN8" t="n">
         <v>-38347085.13708514</v>
       </c>
-      <c r="BD8" t="n">
-        <v>0.4187590187590189</v>
-      </c>
-      <c r="BE8" t="n">
+      <c r="BO8" t="n">
+        <v>-112025000</v>
+      </c>
+      <c r="BP8" t="n">
         <v>-1.255718273612842</v>
       </c>
-      <c r="BF8" t="n">
-        <v>-1.028968253968316</v>
-      </c>
-      <c r="BG8" t="n">
+      <c r="BQ8" t="n">
         <v>-24776728.25297444</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BR8" t="n">
+        <v>-140.8571428571428</v>
+      </c>
+      <c r="BS8" t="n">
         <v>-434285.7142857143</v>
       </c>
-      <c r="BI8" t="n">
-        <v>-6.802558449443552</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>-140.8571428571428</v>
-      </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>-9.039321789321775</v>
       </c>
-      <c r="BL8" t="n">
-        <v>-1.428571428571428</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BU8" t="n">
+        <v>2.473809523809535</v>
+      </c>
+      <c r="BV8" t="n">
         <v>-136.7142857142858</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>-9.465656565656573</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>-0.8848258022171065</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>-6.285714285714286</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>2.473809523809535</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>-114863.5642135642</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>2.400119536123373</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>-112025000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>-8.101394411621584</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>-90515.85861345063</v>
       </c>
     </row>
     <row r="9">
@@ -2521,70 +2521,70 @@
         <v>0.06140350877192985</v>
       </c>
       <c r="BA9" t="n">
+        <v>-1.186174242424244</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-1.125</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-8876.576005251636</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.4954443196963325</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.04886363636363633</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-15131.47095959596</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.197000838702785</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.900347222222226</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.02856511337632606</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.2844038111858396</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-2.140751262626253</v>
+      </c>
+      <c r="BM9" t="n">
         <v>0.96875</v>
       </c>
-      <c r="BB9" t="n">
-        <v>0.04886363636363633</v>
-      </c>
-      <c r="BC9" t="n">
+      <c r="BN9" t="n">
         <v>-2766874.210858585</v>
       </c>
-      <c r="BD9" t="n">
-        <v>1.900347222222226</v>
-      </c>
-      <c r="BE9" t="n">
+      <c r="BO9" t="n">
+        <v>-9025000</v>
+      </c>
+      <c r="BP9" t="n">
         <v>-0.5349000068708847</v>
       </c>
-      <c r="BF9" t="n">
-        <v>-1.186174242424244</v>
-      </c>
-      <c r="BG9" t="n">
+      <c r="BQ9" t="n">
         <v>-512178.6814933629</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BR9" t="n">
+        <v>-96</v>
+      </c>
+      <c r="BS9" t="n">
         <v>-54500</v>
       </c>
-      <c r="BI9" t="n">
-        <v>0.2844038111858396</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>-96</v>
-      </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>-3.28573232323231</v>
       </c>
-      <c r="BL9" t="n">
-        <v>-1.125</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BU9" t="n">
+        <v>-5.729166666666657</v>
+      </c>
+      <c r="BV9" t="n">
         <v>-90.125</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>-2.140751262626253</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.02856511337632606</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>-0.875</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>-5.729166666666657</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>-15131.47095959596</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>2.197000838702785</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>-9025000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>-0.4954443196963325</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>-8876.576005251636</v>
       </c>
     </row>
     <row r="10">
@@ -2749,70 +2749,70 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
+        <v>-1.679707792207779</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-12369.96120216495</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.7792009476898727</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-0.01136363636363624</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-9881.457431457431</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.6741084627380438</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.6568181818181849</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0.06618026364403184</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.7397192144314886</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>2.873701298701292</v>
+      </c>
+      <c r="BM10" t="n">
         <v>-1.525595238095242</v>
       </c>
-      <c r="BB10" t="n">
-        <v>-0.01136363636363624</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BN10" t="n">
         <v>2897864.357864358</v>
       </c>
-      <c r="BD10" t="n">
-        <v>0.6568181818181813</v>
-      </c>
-      <c r="BE10" t="n">
+      <c r="BO10" t="n">
+        <v>-6296875</v>
+      </c>
+      <c r="BP10" t="n">
         <v>-2.541641222438301</v>
       </c>
-      <c r="BF10" t="n">
-        <v>-1.679707792207779</v>
-      </c>
-      <c r="BG10" t="n">
+      <c r="BQ10" t="n">
         <v>249516.1717702746</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BR10" t="n">
+        <v>-65.875</v>
+      </c>
+      <c r="BS10" t="n">
         <v>-31875</v>
       </c>
-      <c r="BI10" t="n">
-        <v>0.7397192144314886</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>-65.875</v>
-      </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>2.936165223665213</v>
       </c>
-      <c r="BL10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BU10" t="n">
+        <v>-5.723511904761949</v>
+      </c>
+      <c r="BV10" t="n">
         <v>-86.125</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>2.873701298701292</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-0.06618026364403184</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-5.723511904761949</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>-9881.457431457431</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>0.6741084627380438</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>-6296875</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>0.7792009476898727</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>-12369.96120216495</v>
       </c>
     </row>
     <row r="11">
@@ -2970,57 +2970,57 @@
       <c r="AZ11" t="n">
         <v>0.15</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4578.795913969218</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-1.573122718460752</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="n">
+        <v>-3.424845559042797</v>
+      </c>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="n">
+        <v>-0.2161152045359207</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-5.334523009906633</v>
+      </c>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="n">
         <v>-1.375</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
-        <v>3.750050402265714</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="n">
-        <v>-2412054.686712421</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>235000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>-5.334523009906633</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>464</v>
-      </c>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="n">
-        <v>6</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>437</v>
       </c>
       <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="n">
-        <v>-0.2161152045359207</v>
+        <v>32250000</v>
       </c>
       <c r="BP11" t="n">
-        <v>9</v>
+        <v>3.750050402265714</v>
       </c>
       <c r="BQ11" t="n">
+        <v>-2412054.686712421</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>464</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>235000</v>
+      </c>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="n">
         <v>-4</v>
       </c>
-      <c r="BR11" t="inlineStr"/>
-      <c r="BS11" t="n">
-        <v>-3.424845559042797</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>32250000</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>-1.573122718460752</v>
-      </c>
       <c r="BV11" t="n">
-        <v>4578.795913969218</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
+++ b/data/italy/p6_deployment/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV11"/>
+  <dimension ref="A1:BV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,135 +690,135 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>z7KrCz8T</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45619.58333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
         <v>77</v>
@@ -840,207 +840,207 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1149999999999998</v>
+        <v>-0.4199999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.082</v>
+        <v>0.3469999999999995</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.75</v>
+        <v>-1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.616666666666667</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="T2" t="n">
-        <v>3.666666666666667</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>12.75</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>8.083333333333332</v>
+        <v>3.949999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.277777777777778</v>
+        <v>0.6500000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.8</v>
+        <v>0.7499999999999998</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.00274956126249</v>
+        <v>18.35171125171125</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.40871921131234</v>
+        <v>19.44909368336529</v>
       </c>
       <c r="AC2" t="n">
-        <v>716.567779888348</v>
+        <v>913.7334122784957</v>
       </c>
       <c r="AD2" t="n">
-        <v>869.4719324376954</v>
+        <v>832.1630846528394</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-0.6749999999999972</v>
+        <v>34.23529411764704</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>12.325</v>
+        <v>24.47058823529412</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.75</v>
+        <v>17.66666666666666</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.283333333333324</v>
+        <v>7.349999999999998</v>
       </c>
       <c r="AK2" t="n">
-        <v>33.5</v>
+        <v>-12.66666666666667</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.888888888888886</v>
+        <v>12.89999999999999</v>
       </c>
       <c r="AM2" t="n">
-        <v>314.75</v>
+        <v>-124.6666666666667</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.51666666666665</v>
+        <v>114.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.4046052631578949</v>
+        <v>-1.384210526315789</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>-2.5</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>-5.333333333333336</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.161111111111113</v>
+        <v>-1.200000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>-38.99460410678287</v>
+        <v>20.07917292004148</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.99105134364158</v>
+        <v>-5.87013755954715</v>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-0.04183045572618022</v>
+        <v>0.01387383437463409</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.5</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.2000000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>-1.941722783389423</v>
+        <v>-1.443440018854776</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.25</v>
+        <v>0.6627522351880941</v>
       </c>
       <c r="BC2" t="n">
-        <v>763.3904662341956</v>
+        <v>0.4796626984126995</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.25</v>
+        <v>1.330357142857139</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.93603674123078</v>
+        <v>11150972.75093781</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.387373737373737</v>
+        <v>1.779769091964653</v>
       </c>
       <c r="BG2" t="n">
-        <v>9722.558922558936</v>
+        <v>0.125</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.152892707643371</v>
+        <v>-3.142857142857142</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.289225589225591</v>
+        <v>4446.42857142858</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7089929165849265</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="BK2" t="n">
-        <v>3.338816331350671</v>
+        <v>1.822916666666671</v>
       </c>
       <c r="BL2" t="n">
-        <v>4.286812570145898</v>
+        <v>0.348549578440883</v>
       </c>
       <c r="BM2" t="n">
-        <v>-4.604166666666671</v>
+        <v>10.85714285714283</v>
       </c>
       <c r="BN2" t="n">
-        <v>18900659.37149271</v>
+        <v>37903.27380952382</v>
       </c>
       <c r="BO2" t="n">
-        <v>22437500</v>
+        <v>-3.89702380952383</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.32362454205753</v>
+        <v>31567.69321970573</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9887342.949404109</v>
+        <v>-14619642.85714285</v>
       </c>
       <c r="BR2" t="n">
-        <v>22</v>
+        <v>11746428.57142857</v>
       </c>
       <c r="BS2" t="n">
-        <v>-2500</v>
+        <v>1.13244047619051</v>
       </c>
       <c r="BT2" t="n">
-        <v>3.395679012345667</v>
+        <v>3.392857142857167</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.895833333333371</v>
+        <v>-1.850595238095234</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.625</v>
+        <v>-0.5262862391866747</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45606.58333333334</v>
+        <v>45619.45833333334</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
         <v>77</v>
@@ -1062,209 +1062,209 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="M3" t="n">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7030000000000001</v>
+        <v>-1.316666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4636842105263159</v>
+        <v>-1.216842105263158</v>
       </c>
       <c r="Q3" t="n">
         <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.6928571428571428</v>
+        <v>-1.255263157894737</v>
       </c>
       <c r="S3" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.794736842105264</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-3.678947368421053</v>
+      </c>
+      <c r="W3" t="n">
         <v>-2</v>
       </c>
-      <c r="T3" t="n">
-        <v>-0.04285714285714359</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-2.416666666666668</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.511904761904761</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.75</v>
-      </c>
       <c r="X3" t="n">
-        <v>-0.430952380952381</v>
+        <v>-1.626315789473684</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.4214285714285715</v>
+        <v>-2.052631578947369</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.00380719426772</v>
+        <v>20.77400793650794</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.06744734706117</v>
+        <v>21.66349433283797</v>
       </c>
       <c r="AC3" t="n">
-        <v>860.2254382590581</v>
+        <v>1013.403114811687</v>
       </c>
       <c r="AD3" t="n">
-        <v>863.4369109923971</v>
+        <v>975.3425938465875</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-3.3125</v>
+        <v>6.5</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>3.1875</v>
+        <v>-0.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0833333333333357</v>
+        <v>4.999999999999996</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.673809523809517</v>
+        <v>-4.234210526315792</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-26.66666666666667</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.961904761904762</v>
+        <v>-25.32631578947368</v>
       </c>
       <c r="AM3" t="n">
-        <v>-11.91666666666669</v>
+        <v>-285.6666666666667</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.01666666666659</v>
+        <v>-249.9368421052631</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.2500000000000002</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.638095238095238</v>
+        <v>0.8391812865497077</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AS3" t="n">
-        <v>-4.5</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>-3.866666666666665</v>
+        <v>1.75526315789474</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.343786731743993</v>
+        <v>-1.92302785497159</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.134244869950436</v>
+        <v>17.92830265120259</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>0.009899025146038236</v>
+        <v>0.0377714285648382</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.08333333333333334</v>
+        <v>-1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.05000000000000002</v>
+        <v>-0.3710526315789473</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.595187991021305</v>
+        <v>-2.427599268342259</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.125</v>
+        <v>-8.759513829515257</v>
       </c>
       <c r="BC3" t="n">
-        <v>-4664.495765946158</v>
+        <v>-3.81527777777778</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.875</v>
+        <v>-7.97026515151515</v>
       </c>
       <c r="BE3" t="n">
-        <v>-3.216018783695205</v>
+        <v>-22416211.15039375</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.6440235690235692</v>
+        <v>-5.835769804423251</v>
       </c>
       <c r="BG3" t="n">
-        <v>-22794.41638608306</v>
+        <v>1.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.3713890961176141</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.43124298540965</v>
+        <v>-131000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.3505211916031004</v>
+        <v>-2.302020202020202</v>
       </c>
       <c r="BK3" t="n">
-        <v>-3.793188136816582</v>
+        <v>-11.48964646464647</v>
       </c>
       <c r="BL3" t="n">
-        <v>-6.307687991021339</v>
+        <v>-1.412805333253703</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.01458333333333428</v>
+        <v>113.625</v>
       </c>
       <c r="BN3" t="n">
-        <v>-15123539.21156004</v>
+        <v>-101657.0075757576</v>
       </c>
       <c r="BO3" t="n">
-        <v>-13050000</v>
+        <v>2.697916666666657</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.5405410588119537</v>
+        <v>-78502.83781936027</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-4414738.05619707</v>
+        <v>-38842500</v>
       </c>
       <c r="BR3" t="n">
-        <v>227.375</v>
+        <v>-38521250</v>
       </c>
       <c r="BS3" t="n">
-        <v>10875</v>
+        <v>1.089046717171698</v>
       </c>
       <c r="BT3" t="n">
-        <v>-5.384862514029194</v>
+        <v>105.875</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.564583333333303</v>
+        <v>-0.1041666666666643</v>
       </c>
       <c r="BV3" t="n">
-        <v>218.25</v>
+        <v>-1.890012866614711</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
         <v>77</v>
@@ -1286,205 +1286,207 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1125</v>
+        <v>0.1149999999999998</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6646315789473687</v>
+        <v>1.082</v>
       </c>
       <c r="Q4" t="n">
         <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9394736842105263</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="S4" t="n">
-        <v>-2</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2315789473684209</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>12.75</v>
       </c>
       <c r="V4" t="n">
-        <v>4.592105263157896</v>
+        <v>8.083333333333332</v>
       </c>
       <c r="W4" t="n">
-        <v>0.25</v>
+        <v>-1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5842105263157893</v>
+        <v>1.277777777777778</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6631578947368424</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.39420995670996</v>
+        <v>14.00274956126249</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.57130313328832</v>
+        <v>17.40871921131234</v>
       </c>
       <c r="AC4" t="n">
-        <v>829.3144892915774</v>
+        <v>716.567779888348</v>
       </c>
       <c r="AD4" t="n">
-        <v>926.957930921918</v>
+        <v>869.4719324376954</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-1.670588235294119</v>
+        <v>-0.6749999999999972</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>7.686274509803923</v>
+        <v>12.325</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.5</v>
+        <v>8.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6.292105263157897</v>
+        <v>3.283333333333324</v>
       </c>
       <c r="AK4" t="n">
-        <v>5</v>
+        <v>33.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4.215789473684211</v>
+        <v>7.888888888888886</v>
       </c>
       <c r="AM4" t="n">
-        <v>56</v>
+        <v>314.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>-47.4131578947368</v>
+        <v>78.51666666666665</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.7526315789473683</v>
+        <v>-0.4046052631578949</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="AS4" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.144736842105264</v>
+        <v>1.161111111111113</v>
       </c>
       <c r="AU4" t="n">
-        <v>-8.782858980104226</v>
+        <v>-38.99460410678287</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.915384080070243</v>
+        <v>-1.99105134364158</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-0.01778969254522732</v>
+        <v>-0.04183045572618022</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.3657894736842105</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="BA4" t="n">
-        <v>-4.439826839826821</v>
+        <v>1.152892707643371</v>
       </c>
       <c r="BB4" t="n">
-        <v>-3.285714285714286</v>
+        <v>3.338816331350671</v>
       </c>
       <c r="BC4" t="n">
-        <v>-4522.525224811514</v>
+        <v>1.289225589225591</v>
       </c>
       <c r="BD4" t="n">
-        <v>-2.285714285714286</v>
+        <v>3.395679012345667</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.926641934805957</v>
+        <v>9887342.949404109</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.9239177489177492</v>
+        <v>2.93603674123078</v>
       </c>
       <c r="BG4" t="n">
-        <v>-6027.849927849937</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>1.34412972130119</v>
+        <v>-5</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1168831168831161</v>
+        <v>-145000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7183114813431091</v>
+        <v>1.387373737373737</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.032553303548738</v>
+        <v>4.286812570145898</v>
       </c>
       <c r="BL4" t="n">
-        <v>2.377994227994222</v>
+        <v>0.7089929165849265</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.97891156462585</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>11862673.16017316</v>
+        <v>9722.558922558936</v>
       </c>
       <c r="BO4" t="n">
-        <v>-5842857.142857142</v>
+        <v>6.666666666666657</v>
       </c>
       <c r="BP4" t="n">
-        <v>-6.14971809051616</v>
+        <v>763.3904662341956</v>
       </c>
       <c r="BQ4" t="n">
-        <v>11494271.64248613</v>
+        <v>-14000000</v>
       </c>
       <c r="BR4" t="n">
-        <v>-253</v>
+        <v>18900659.37149271</v>
       </c>
       <c r="BS4" t="n">
-        <v>-83857.14285714286</v>
+        <v>-1.941722783389423</v>
       </c>
       <c r="BT4" t="n">
-        <v>2.005122655122676</v>
+        <v>-12</v>
       </c>
       <c r="BU4" t="n">
-        <v>-3.975510204081644</v>
+        <v>-7</v>
       </c>
       <c r="BV4" t="n">
-        <v>-235.5714285714286</v>
+        <v>3.32362454205753</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
         <v>77</v>
@@ -1506,209 +1508,209 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.5625</v>
+        <v>-0.7030000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.170446428571428</v>
+        <v>-0.4636842105263159</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>-1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.352941176470588</v>
+        <v>-0.6928571428571428</v>
       </c>
       <c r="S5" t="n">
-        <v>6.166666666666667</v>
+        <v>-2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.145658263305322</v>
+        <v>-0.04285714285714359</v>
       </c>
       <c r="U5" t="n">
-        <v>10.75</v>
+        <v>-2.416666666666668</v>
       </c>
       <c r="V5" t="n">
-        <v>8.862745098039214</v>
+        <v>1.511904761904761</v>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>-0.75</v>
       </c>
       <c r="X5" t="n">
-        <v>1.694677871148459</v>
+        <v>-0.430952380952381</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>-0.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.80672268907563</v>
+        <v>-0.4214285714285715</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.13972431077694</v>
+        <v>21.00380719426772</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.61527740125752</v>
+        <v>20.06744734706117</v>
       </c>
       <c r="AC5" t="n">
-        <v>785.7485545983095</v>
+        <v>860.2254382590581</v>
       </c>
       <c r="AD5" t="n">
-        <v>698.5024096746274</v>
+        <v>863.4369109923971</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>51.92063492063491</v>
+        <v>-3.3125</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>28.77777777777778</v>
+        <v>3.1875</v>
       </c>
       <c r="AI5" t="n">
-        <v>16.58333333333333</v>
+        <v>0.0833333333333357</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19.52100840336134</v>
+        <v>1.673809523809517</v>
       </c>
       <c r="AK5" t="n">
-        <v>9.166666666666671</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>26.25210084033614</v>
+        <v>4.961904761904762</v>
       </c>
       <c r="AM5" t="n">
-        <v>107.4166666666667</v>
+        <v>-11.91666666666669</v>
       </c>
       <c r="AN5" t="n">
-        <v>218.3025210084033</v>
+        <v>44.01666666666659</v>
       </c>
       <c r="AO5" t="n">
-        <v>-3.166666666666667</v>
+        <v>-0.2500000000000002</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1.369747899159664</v>
+        <v>-0.638095238095238</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2.5</v>
+        <v>0.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>-2.25</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-13.08333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>-3.058823529411764</v>
+        <v>-3.866666666666665</v>
       </c>
       <c r="AU5" t="n">
-        <v>10.55747745310245</v>
+        <v>9.343786731743993</v>
       </c>
       <c r="AV5" t="n">
-        <v>-10.26355733736644</v>
+        <v>6.134244869950436</v>
       </c>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>0.0105024421106325</v>
+        <v>0.009899025146038236</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.25</v>
+        <v>0.08333333333333334</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3081232492997199</v>
+        <v>0.05000000000000002</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1.594097222222246</v>
+        <v>-0.3713890961176141</v>
       </c>
       <c r="BB5" t="n">
-        <v>-2.017857142857143</v>
+        <v>-3.793188136816582</v>
       </c>
       <c r="BC5" t="n">
-        <v>32831.93550228376</v>
+        <v>-0.43124298540965</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.946428571428572</v>
+        <v>-5.384862514029194</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.248300806506606</v>
+        <v>-4414738.05619707</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4715277777777778</v>
+        <v>-3.216018783695205</v>
       </c>
       <c r="BG5" t="n">
-        <v>27050</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.6212777580447764</v>
+        <v>5</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.05451388888888431</v>
+        <v>109000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.3987567793095539</v>
+        <v>-0.6440235690235692</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.392012837943895</v>
+        <v>-6.307687991021339</v>
       </c>
       <c r="BL5" t="n">
-        <v>3.13611111111112</v>
+        <v>-0.3505211916031004</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1011904761904816</v>
+        <v>377</v>
       </c>
       <c r="BN5" t="n">
-        <v>7966388.888888888</v>
+        <v>-22794.41638608306</v>
       </c>
       <c r="BO5" t="n">
-        <v>9985357.142857142</v>
+        <v>-6</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.9882385373017541</v>
+        <v>-4664.495765946158</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7508226.668306904</v>
+        <v>27800000</v>
       </c>
       <c r="BR5" t="n">
-        <v>-139.0357142857143</v>
+        <v>-15123539.21156004</v>
       </c>
       <c r="BS5" t="n">
-        <v>32125</v>
+        <v>1.595187991021305</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.429861111111109</v>
+        <v>373</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.6443452380952408</v>
+        <v>1.333333333333332</v>
       </c>
       <c r="BV5" t="n">
-        <v>-131.4464285714286</v>
+        <v>-0.5405410588119537</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45606.35416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="n">
+        <v>62</v>
+      </c>
+      <c r="D6" t="n">
+        <v>55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>140</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>22</v>
-      </c>
-      <c r="F6" t="n">
-        <v>175</v>
       </c>
       <c r="G6" t="n">
         <v>77</v>
@@ -1730,213 +1732,205 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="M6" t="n">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.0185</v>
+        <v>0.1125</v>
       </c>
       <c r="P6" t="n">
-        <v>1.568888888888889</v>
+        <v>0.6646315789473687</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.55</v>
+        <v>0.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0.9394736842105263</v>
       </c>
       <c r="S6" t="n">
-        <v>5.85</v>
+        <v>-2</v>
       </c>
       <c r="T6" t="n">
-        <v>5.313131313131314</v>
+        <v>0.2315789473684209</v>
       </c>
       <c r="U6" t="n">
-        <v>6.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>10.95454545454545</v>
+        <v>4.592105263157896</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2</v>
+        <v>0.25</v>
       </c>
       <c r="X6" t="n">
-        <v>2.146464646464646</v>
+        <v>0.5842105263157893</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>0.6631578947368424</v>
       </c>
       <c r="AA6" t="n">
-        <v>18.05365701549912</v>
+        <v>19.39420995670996</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.69606419501039</v>
+        <v>18.57130313328832</v>
       </c>
       <c r="AC6" t="n">
-        <v>775.8598167929163</v>
+        <v>829.3144892915774</v>
       </c>
       <c r="AD6" t="n">
-        <v>711.5179669833035</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-1</v>
-      </c>
+        <v>926.957930921918</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>59.92222222222223</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-9</v>
-      </c>
+        <v>-1.670588235294119</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>53.33333333333333</v>
+        <v>7.686274509803923</v>
       </c>
       <c r="AI6" t="n">
-        <v>14.8</v>
+        <v>2.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.52020202020202</v>
+        <v>6.292105263157897</v>
       </c>
       <c r="AK6" t="n">
-        <v>24.59999999999999</v>
+        <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>35.22222222222223</v>
+        <v>-4.215789473684211</v>
       </c>
       <c r="AM6" t="n">
-        <v>247.7</v>
+        <v>56</v>
       </c>
       <c r="AN6" t="n">
-        <v>298.9242424242425</v>
+        <v>-47.4131578947368</v>
       </c>
       <c r="AO6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.7526315789473683</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.144736842105264</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-8.782858980104226</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.915384080070243</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>-0.01778969254522732</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.3657894736842105</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.34412972130119</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.032553303548738</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.1168831168831161</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.005122655122676</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>11494271.64248613</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.926641934805957</v>
+      </c>
+      <c r="BG6" t="n">
         <v>-2</v>
       </c>
-      <c r="AP6" t="n">
-        <v>-1.916666666666667</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-6.199999999999999</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-0.4090909090909083</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.2936373400421459</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-17.13664205801063</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-0.02004345783415551</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.02545740079368261</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.4393939393939393</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-0.01042368125706616</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>27045.34410062633</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.12598410185177</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0.7670454545454546</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>42714.74466891133</v>
-      </c>
       <c r="BH6" t="n">
-        <v>-0.7431934166773999</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.4229938271604929</v>
+        <v>-7000</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5991299890041311</v>
+        <v>0.9239177489177492</v>
       </c>
       <c r="BK6" t="n">
-        <v>3.792933672748703</v>
+        <v>2.377994227994222</v>
       </c>
       <c r="BL6" t="n">
-        <v>6.74339225589226</v>
+        <v>0.7183114813431091</v>
       </c>
       <c r="BM6" t="n">
-        <v>-3.891666666666666</v>
+        <v>-143</v>
       </c>
       <c r="BN6" t="n">
-        <v>16258498.17620651</v>
+        <v>-6027.849927849937</v>
       </c>
       <c r="BO6" t="n">
-        <v>39050000</v>
+        <v>-2.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.873100277410003</v>
+        <v>-4522.525224811514</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9706274.149888515</v>
+        <v>25700000</v>
       </c>
       <c r="BR6" t="n">
-        <v>64.25</v>
+        <v>11862673.16017316</v>
       </c>
       <c r="BS6" t="n">
-        <v>92875</v>
+        <v>-4.439826839826821</v>
       </c>
       <c r="BT6" t="n">
-        <v>6.688482042648701</v>
+        <v>-132</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.631249999999994</v>
+        <v>2.25</v>
       </c>
       <c r="BV6" t="n">
-        <v>52.875</v>
+        <v>-6.14971809051616</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45605.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="G7" t="n">
         <v>77</v>
@@ -1958,209 +1952,209 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>243</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.065</v>
+        <v>2.5625</v>
       </c>
       <c r="P7" t="n">
-        <v>1.080861244019139</v>
+        <v>1.170446428571428</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.543062200956938</v>
+        <v>1.352941176470588</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="T7" t="n">
-        <v>3.861244019138756</v>
+        <v>3.145658263305322</v>
       </c>
       <c r="U7" t="n">
-        <v>14.75</v>
+        <v>10.75</v>
       </c>
       <c r="V7" t="n">
-        <v>9.45933014354067</v>
+        <v>8.862745098039214</v>
       </c>
       <c r="W7" t="n">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>1.413875598086124</v>
+        <v>1.694677871148459</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.995215311004785</v>
+        <v>2.80672268907563</v>
       </c>
       <c r="AA7" t="n">
-        <v>14.84787561576355</v>
+        <v>19.13972431077694</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.45190579944482</v>
+        <v>17.61527740125752</v>
       </c>
       <c r="AC7" t="n">
-        <v>760.5645416822183</v>
+        <v>785.7485545983095</v>
       </c>
       <c r="AD7" t="n">
-        <v>877.9109824474808</v>
+        <v>698.5024096746274</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>6.088888888888889</v>
+        <v>51.92063492063491</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>16.24444444444444</v>
+        <v>28.77777777777778</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.75</v>
+        <v>16.58333333333333</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.516746411483254</v>
+        <v>19.52100840336134</v>
       </c>
       <c r="AK7" t="n">
-        <v>39</v>
+        <v>9.166666666666671</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.555023923444978</v>
+        <v>26.25210084033614</v>
       </c>
       <c r="AM7" t="n">
-        <v>379.25</v>
+        <v>107.4166666666667</v>
       </c>
       <c r="AN7" t="n">
-        <v>26.49760765550235</v>
+        <v>218.3025210084033</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.75</v>
+        <v>-3.166666666666667</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.04040404040404066</v>
+        <v>-1.369747899159664</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.2</v>
+        <v>-2.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.5</v>
+        <v>-13.08333333333333</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.12200956937799</v>
+        <v>-3.058823529411764</v>
       </c>
       <c r="AU7" t="n">
-        <v>-30.27642179502794</v>
+        <v>10.55747745310245</v>
       </c>
       <c r="AV7" t="n">
-        <v>-7.323631888893029</v>
+        <v>-10.26355733736644</v>
       </c>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-0.02175734009148228</v>
+        <v>0.0105024421106325</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5215311004784688</v>
+        <v>0.3081232492997199</v>
       </c>
       <c r="BA7" t="n">
-        <v>-1.023313492063465</v>
+        <v>-0.6212777580447764</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.75</v>
+        <v>4.392012837943895</v>
       </c>
       <c r="BC7" t="n">
-        <v>48158.11625427853</v>
+        <v>-0.05451388888888431</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.875</v>
+        <v>3.429861111111109</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.288964613197066</v>
+        <v>7508226.668306904</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.9900793650793651</v>
+        <v>4.248300806506606</v>
       </c>
       <c r="BG7" t="n">
-        <v>59973.71031746032</v>
+        <v>-4</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.6555253429156878</v>
+        <v>-3</v>
       </c>
       <c r="BI7" t="n">
-        <v>-1.561011904761905</v>
+        <v>30000</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.4953282828282828</v>
+        <v>0.4715277777777778</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.738999487354747</v>
+        <v>3.13611111111112</v>
       </c>
       <c r="BL7" t="n">
-        <v>5.504464285714292</v>
+        <v>0.3987567793095539</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.629166666666663</v>
+        <v>-280</v>
       </c>
       <c r="BN7" t="n">
-        <v>21760515.87301587</v>
+        <v>27050</v>
       </c>
       <c r="BO7" t="n">
-        <v>86625000</v>
+        <v>-7.166666666666657</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.7433702506070858</v>
+        <v>32831.93550228376</v>
       </c>
       <c r="BQ7" t="n">
-        <v>11473003.2755581</v>
+        <v>18570000</v>
       </c>
       <c r="BR7" t="n">
-        <v>64.875</v>
+        <v>7966388.888888888</v>
       </c>
       <c r="BS7" t="n">
-        <v>340000</v>
+        <v>-1.594097222222246</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.004960317460316</v>
+        <v>-253</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.345833333333331</v>
+        <v>2.166666666666668</v>
       </c>
       <c r="BV7" t="n">
-        <v>85.75</v>
+        <v>-0.9882385373017541</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45605.58333333334</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="G8" t="n">
         <v>77</v>
@@ -2182,207 +2176,213 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.155</v>
+        <v>2.0185</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4602476780185751</v>
+        <v>1.568888888888889</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.313131313131314</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10.95454545454545</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.146464646464646</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>18.05365701549912</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>17.69606419501039</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>775.8598167929163</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>711.5179669833035</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>59.92222222222223</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>53.33333333333333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>14.52020202020202</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24.59999999999999</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>35.22222222222223</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>247.7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>298.9242424242425</v>
+      </c>
+      <c r="AO8" t="n">
         <v>-2</v>
       </c>
-      <c r="R8" t="n">
-        <v>-0.7731092436974787</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-5.066666666666666</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.403361344537815</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.666666666666664</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.7450980392156872</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-1.533333333333333</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.3781512605042019</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.3865546218487395</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>22.0072496947497</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>21.12045655313997</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>857.4779994033482</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>922.6351566888964</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="n">
-        <v>-26.00793650793651</v>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>-11.95238095238095</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-0.2016806722689068</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-8.933333333333323</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-29.72549019607844</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-82.26666666666671</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-256.7619047619048</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.5999999999999999</v>
-      </c>
       <c r="AP8" t="n">
-        <v>-0.6442577030812326</v>
+        <v>-1.916666666666667</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>0.2000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.133333333333333</v>
+        <v>-6.199999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.252100840336134</v>
+        <v>-0.4090909090909083</v>
       </c>
       <c r="AU8" t="n">
-        <v>-10.29283998066457</v>
+        <v>0.2936373400421459</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.32906625244443</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
+        <v>-17.13664205801063</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.02004345783415551</v>
+      </c>
       <c r="AX8" t="n">
-        <v>-0.02606482078087154</v>
+        <v>0.02545740079368261</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.7333333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.2717086834733893</v>
+        <v>0.4393939393939393</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.028968253968316</v>
+        <v>-0.7431934166773999</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.428571428571428</v>
+        <v>3.792933672748703</v>
       </c>
       <c r="BC8" t="n">
-        <v>-90515.85861345063</v>
+        <v>0.4229938271604929</v>
       </c>
       <c r="BD8" t="n">
-        <v>-6.285714285714286</v>
+        <v>6.688482042648701</v>
       </c>
       <c r="BE8" t="n">
-        <v>-8.101394411621584</v>
+        <v>9706274.149888515</v>
       </c>
       <c r="BF8" t="n">
-        <v>-1.548340548340548</v>
+        <v>5.12598410185177</v>
       </c>
       <c r="BG8" t="n">
-        <v>-114863.5642135642</v>
+        <v>-2</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.400119536123377</v>
+        <v>-4</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.4187590187590189</v>
+        <v>91000</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0.8848258022171065</v>
+        <v>0.7670454545454546</v>
       </c>
       <c r="BK8" t="n">
-        <v>-6.802558449443552</v>
+        <v>6.74339225589226</v>
       </c>
       <c r="BL8" t="n">
-        <v>-9.465656565656573</v>
+        <v>0.5991299890041311</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.06666666666666998</v>
+        <v>-141</v>
       </c>
       <c r="BN8" t="n">
-        <v>-38347085.13708514</v>
+        <v>42714.74466891133</v>
       </c>
       <c r="BO8" t="n">
-        <v>-112025000</v>
+        <v>8.266666666666652</v>
       </c>
       <c r="BP8" t="n">
-        <v>-1.255718273612842</v>
+        <v>27045.34410062633</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-24776728.25297444</v>
+        <v>31000000</v>
       </c>
       <c r="BR8" t="n">
-        <v>-140.8571428571428</v>
+        <v>16258498.17620651</v>
       </c>
       <c r="BS8" t="n">
-        <v>-434285.7142857143</v>
+        <v>-0.01042368125706616</v>
       </c>
       <c r="BT8" t="n">
-        <v>-9.039321789321775</v>
+        <v>-133</v>
       </c>
       <c r="BU8" t="n">
-        <v>2.473809523809535</v>
+        <v>-2.266666666666669</v>
       </c>
       <c r="BV8" t="n">
-        <v>-136.7142857142858</v>
+        <v>1.873100277410003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45605.45833333334</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
         <v>77</v>
@@ -2404,209 +2404,209 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="M9" t="n">
-        <v>235</v>
+        <v>23</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.309166666666667</v>
+        <v>1.065</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4315497076023391</v>
+        <v>1.080861244019139</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.157894736842105</v>
+        <v>1.543062200956938</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.25</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08479532163742665</v>
+        <v>3.861244019138756</v>
       </c>
       <c r="U9" t="n">
-        <v>2.916666666666666</v>
+        <v>14.75</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6432748538011701</v>
+        <v>9.45933014354067</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3333333333333335</v>
+        <v>0.75</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4590643274853803</v>
+        <v>1.413875598086124</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8596491228070178</v>
+        <v>1.995215311004785</v>
       </c>
       <c r="AA9" t="n">
-        <v>23.828619053948</v>
+        <v>14.84787561576355</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.33048135199737</v>
+        <v>16.45190579944482</v>
       </c>
       <c r="AC9" t="n">
-        <v>763.1555004877468</v>
+        <v>760.5645416822183</v>
       </c>
       <c r="AD9" t="n">
-        <v>816.7093682547279</v>
+        <v>877.9109824474808</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>9.73333333333332</v>
+        <v>6.088888888888889</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>1.133333333333333</v>
+        <v>16.24444444444444</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.583333333333329</v>
+        <v>5.75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-1.497076023391813</v>
+        <v>4.516746411483254</v>
       </c>
       <c r="AK9" t="n">
-        <v>14.16666666666667</v>
+        <v>39</v>
       </c>
       <c r="AL9" t="n">
-        <v>9.315789473684205</v>
+        <v>3.555023923444978</v>
       </c>
       <c r="AM9" t="n">
-        <v>142.6666666666666</v>
+        <v>379.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>83.9736842105263</v>
+        <v>26.49760765550235</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8333333333333335</v>
+        <v>1.75</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.131578947368421</v>
+        <v>-0.04040404040404066</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.35</v>
+        <v>0.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.666666666666668</v>
+        <v>4.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.6140350877193015</v>
+        <v>2.12200956937799</v>
       </c>
       <c r="AU9" t="n">
-        <v>-6.035355657414485</v>
+        <v>-30.27642179502794</v>
       </c>
       <c r="AV9" t="n">
-        <v>-4.247109940296767</v>
+        <v>-7.323631888893029</v>
       </c>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>-0.02159095192671039</v>
+        <v>-0.02175734009148228</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.06140350877192985</v>
+        <v>0.5215311004784688</v>
       </c>
       <c r="BA9" t="n">
-        <v>-1.186174242424244</v>
+        <v>0.6555253429156878</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1.125</v>
+        <v>6.738999487354747</v>
       </c>
       <c r="BC9" t="n">
-        <v>-8876.576005251636</v>
+        <v>-1.561011904761905</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.875</v>
+        <v>6.004960317460316</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.4954443196963325</v>
+        <v>11473003.2755581</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.04886363636363633</v>
+        <v>5.288964613197066</v>
       </c>
       <c r="BG9" t="n">
-        <v>-15131.47095959596</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.197000838702785</v>
+        <v>7</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.900347222222226</v>
+        <v>308000</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.02856511337632606</v>
+        <v>0.9900793650793651</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.2844038111858396</v>
+        <v>5.504464285714292</v>
       </c>
       <c r="BL9" t="n">
-        <v>-2.140751262626253</v>
+        <v>0.4953282828282828</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.96875</v>
+        <v>2</v>
       </c>
       <c r="BN9" t="n">
-        <v>-2766874.210858585</v>
+        <v>59973.71031746032</v>
       </c>
       <c r="BO9" t="n">
-        <v>-9025000</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.5349000068708847</v>
+        <v>48158.11625427853</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-512178.6814933629</v>
+        <v>84600000</v>
       </c>
       <c r="BR9" t="n">
-        <v>-96</v>
+        <v>21760515.87301587</v>
       </c>
       <c r="BS9" t="n">
-        <v>-54500</v>
+        <v>-1.023313492063465</v>
       </c>
       <c r="BT9" t="n">
-        <v>-3.28573232323231</v>
+        <v>26</v>
       </c>
       <c r="BU9" t="n">
-        <v>-5.729166666666657</v>
+        <v>3.25</v>
       </c>
       <c r="BV9" t="n">
-        <v>-90.125</v>
+        <v>-0.7433702506070858</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45604.69791666666</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
         <v>77</v>
@@ -2628,213 +2628,207 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="M10" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8899999999999998</v>
+        <v>-1.155</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6546078431372547</v>
+        <v>-0.4602476780185751</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>-2</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9473684210526319</v>
+        <v>-0.7731092436974787</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5</v>
+        <v>-5.066666666666666</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>-0.403361344537815</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>1.666666666666664</v>
       </c>
       <c r="V10" t="n">
-        <v>7.94736842105263</v>
+        <v>0.7450980392156872</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.25</v>
+        <v>-1.533333333333333</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.736842105263158</v>
+        <v>-0.3781512605042019</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1578947368421051</v>
+        <v>-0.3865546218487395</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.27866771708683</v>
+        <v>22.0072496947497</v>
       </c>
       <c r="AB10" t="n">
-        <v>17.65287590391672</v>
+        <v>21.12045655313997</v>
       </c>
       <c r="AC10" t="n">
-        <v>757.5685879164397</v>
+        <v>857.4779994033482</v>
       </c>
       <c r="AD10" t="n">
-        <v>786.8172503290782</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>64</v>
-      </c>
+        <v>922.6351566888964</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>57</v>
-      </c>
+        <v>-26.00793650793651</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>24.875</v>
+        <v>-11.95238095238095</v>
       </c>
       <c r="AI10" t="n">
-        <v>25.75</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11.10526315789475</v>
+        <v>-0.2016806722689068</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>-8.933333333333323</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.842105263157904</v>
+        <v>-29.72549019607844</v>
       </c>
       <c r="AM10" t="n">
-        <v>131.5</v>
+        <v>-82.26666666666671</v>
       </c>
       <c r="AN10" t="n">
-        <v>29.78947368421052</v>
+        <v>-256.7619047619048</v>
       </c>
       <c r="AO10" t="n">
-        <v>-2.25</v>
+        <v>0.5999999999999999</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1.789473684210526</v>
+        <v>-0.6442577030812326</v>
       </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>0.1333333333333332</v>
+        <v>0.2000000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>-5.75</v>
+        <v>3.133333333333333</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.4210526315789451</v>
+        <v>1.252100840336134</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1694931196983092</v>
+        <v>-10.29283998066457</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.6575616268584454</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.1210699023199023</v>
-      </c>
+        <v>12.32906625244443</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>0.04336511095442891</v>
+        <v>-0.02606482078087154</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.5</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0.2717086834733893</v>
       </c>
       <c r="BA10" t="n">
-        <v>-1.679707792207779</v>
+        <v>2.400119536123377</v>
       </c>
       <c r="BB10" t="n">
+        <v>-6.802558449443552</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.4187590187590189</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-9.039321789321775</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-24776728.25297444</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-8.101394411621584</v>
+      </c>
+      <c r="BG10" t="n">
         <v>-1</v>
       </c>
-      <c r="BC10" t="n">
-        <v>-12369.96120216495</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0.7792009476898727</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>-0.01136363636363624</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>-9881.457431457431</v>
-      </c>
       <c r="BH10" t="n">
-        <v>0.6741084627380438</v>
+        <v>-6</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.6568181818181849</v>
+        <v>-443000</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.06618026364403184</v>
+        <v>-1.548340548340548</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.7397192144314886</v>
+        <v>-9.465656565656573</v>
       </c>
       <c r="BL10" t="n">
-        <v>2.873701298701292</v>
+        <v>-0.8848258022171065</v>
       </c>
       <c r="BM10" t="n">
-        <v>-1.525595238095242</v>
+        <v>-103</v>
       </c>
       <c r="BN10" t="n">
-        <v>2897864.357864358</v>
+        <v>-114863.5642135642</v>
       </c>
       <c r="BO10" t="n">
-        <v>-6296875</v>
+        <v>6.833333333333343</v>
       </c>
       <c r="BP10" t="n">
-        <v>-2.541641222438301</v>
+        <v>-90515.85861345063</v>
       </c>
       <c r="BQ10" t="n">
-        <v>249516.1717702746</v>
+        <v>-82900000</v>
       </c>
       <c r="BR10" t="n">
-        <v>-65.875</v>
+        <v>-38347085.13708514</v>
       </c>
       <c r="BS10" t="n">
-        <v>-31875</v>
+        <v>-1.028968253968316</v>
       </c>
       <c r="BT10" t="n">
-        <v>2.936165223665213</v>
+        <v>-112</v>
       </c>
       <c r="BU10" t="n">
-        <v>-5.723511904761949</v>
+        <v>-4.166666666666668</v>
       </c>
       <c r="BV10" t="n">
-        <v>-86.125</v>
+        <v>-1.255718273612842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45603.69791666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>187</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
         <v>77</v>
@@ -2856,171 +2850,415 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="M11" t="n">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5549999999999997</v>
+        <v>1.309166666666667</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5047368421052629</v>
+        <v>0.4315497076023391</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.5785714285714284</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5999999999999996</v>
+        <v>-0.25</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261904761904762</v>
+        <v>-0.08479532163742665</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.549999999999999</v>
+        <v>2.916666666666666</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.726190476190476</v>
+        <v>0.6432748538011701</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.25</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1047619047619046</v>
+        <v>0.4590643274853803</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.3000000000000003</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1571428571428573</v>
+        <v>0.8596491228070178</v>
       </c>
       <c r="AA11" t="n">
-        <v>23.13213744588744</v>
+        <v>23.828619053948</v>
       </c>
       <c r="AB11" t="n">
-        <v>22.31460960683705</v>
+        <v>23.33048135199737</v>
       </c>
       <c r="AC11" t="n">
-        <v>1038.220342264347</v>
+        <v>763.1555004877468</v>
       </c>
       <c r="AD11" t="n">
-        <v>878.5164106126172</v>
+        <v>816.7093682547279</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>-11.89583333333333</v>
+        <v>9.73333333333332</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>-8.791666666666671</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.75</v>
+        <v>8.583333333333329</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-3.338095238095242</v>
+        <v>-1.497076023391813</v>
       </c>
       <c r="AK11" t="n">
-        <v>-39.2</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="AL11" t="n">
-        <v>-14.49523809523811</v>
+        <v>9.315789473684205</v>
       </c>
       <c r="AM11" t="n">
-        <v>-355.7</v>
+        <v>142.6666666666666</v>
       </c>
       <c r="AN11" t="n">
-        <v>-132.5500000000001</v>
+        <v>83.9736842105263</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.04999999999999982</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.9190476190476189</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
+        <v>-0.131578947368421</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.5</v>
+      </c>
       <c r="AR11" t="n">
-        <v>-2</v>
+        <v>-1.35</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.949999999999999</v>
+        <v>1.666666666666668</v>
       </c>
       <c r="AT11" t="n">
-        <v>-3.897619047619049</v>
+        <v>0.6140350877193015</v>
       </c>
       <c r="AU11" t="n">
-        <v>23.32209273209233</v>
+        <v>-6.035355657414485</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.70635463554281</v>
+        <v>-4.247109940296767</v>
       </c>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>-0.01960614388159125</v>
+        <v>-0.02159095192671039</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
+        <v>0.06140350877192985</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.197000838702785</v>
+      </c>
       <c r="BB11" t="n">
+        <v>0.2844038111858396</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.900347222222226</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-3.28573232323231</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-512178.6814933629</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.4954443196963325</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-148000</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.04886363636363633</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-2.140751262626253</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.02856511337632606</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-321</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-15131.47095959596</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-1.666666666666657</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-8876.576005251636</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-31300000</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-2766874.210858585</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-1.186174242424244</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-308</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0.6666666666666679</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.5349000068708847</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C12" t="n">
+        <v>117</v>
+      </c>
+      <c r="D12" t="n">
+        <v>84</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H12" t="n">
+        <v>771</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>227</v>
+      </c>
+      <c r="M12" t="n">
+        <v>148</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8899999999999998</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.6546078431372547</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.9473684210526319</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
         <v>6</v>
       </c>
-      <c r="BC11" t="n">
-        <v>4578.795913969218</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-1.573122718460752</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="n">
-        <v>-3.424845559042797</v>
-      </c>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="n">
-        <v>-0.2161152045359207</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>-5.334523009906633</v>
-      </c>
-      <c r="BL11" t="inlineStr"/>
-      <c r="BM11" t="n">
-        <v>-1.375</v>
-      </c>
-      <c r="BN11" t="inlineStr"/>
-      <c r="BO11" t="n">
-        <v>32250000</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>3.750050402265714</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>-2412054.686712421</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>464</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>235000</v>
-      </c>
-      <c r="BT11" t="inlineStr"/>
-      <c r="BU11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>437</v>
+      <c r="V12" t="n">
+        <v>7.94736842105263</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.736842105263158</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.1578947368421051</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>17.27866771708683</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>17.65287590391672</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>757.5685879164397</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>786.8172503290782</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>64</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>57</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>11.10526315789475</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4.842105263157904</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>29.78947368421052</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1.789473684210526</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>0.1333333333333332</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-0.4210526315789451</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.1694931196983092</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.6575616268584454</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.1210699023199023</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.04336511095442891</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.6741084627380438</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.7397192144314886</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.6568181818181849</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.936165223665213</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>249516.1717702746</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.7792009476898727</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-47000</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0.01136363636363624</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2.873701298701292</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0.06618026364403184</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-9881.457431457431</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-3.571428571428584</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-12369.96120216495</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-8575000</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2897864.357864358</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-1.679707792207779</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-26</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0.7142857142857153</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-2.541641222438301</v>
       </c>
     </row>
   </sheetData>
